--- a/ai/manualisation.xlsx
+++ b/ai/manualisation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DiskE\SKRIPSI-CODE\skripsi-code\ai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65D2401-0F3A-412A-A738-D2CBA9D8018B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2FAEBD-D003-4D94-908F-16632D3F0EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{145D0042-0CBE-48BE-846C-2BE8EAD29D31}"/>
   </bookViews>
@@ -565,9 +565,6 @@
     <t>O_MHA</t>
   </si>
   <si>
-    <t>O_FFN</t>
-  </si>
-  <si>
     <t>(termasuk residual)</t>
   </si>
   <si>
@@ -782,6 +779,9 @@
   </si>
   <si>
     <t>POSITIONAL ENCODING</t>
+  </si>
+  <si>
+    <t>O_Attn</t>
   </si>
 </sst>
 </file>
@@ -1333,6 +1333,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1351,13 +1358,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -7733,7 +7733,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I10">
         <f>AVERAGE(B4:B9)</f>
@@ -7758,7 +7758,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I11">
         <f>_xlfn.STDEV.P(B4:B9)</f>
@@ -7818,11 +7818,11 @@
       <c r="A15">
         <v>1</v>
       </c>
-      <c r="B15" s="77" t="s">
+      <c r="B15" s="84" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="77"/>
-      <c r="D15" s="77"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
       <c r="E15" t="s">
         <v>42</v>
       </c>
@@ -7840,11 +7840,11 @@
       <c r="A16">
         <v>2</v>
       </c>
-      <c r="B16" s="78" t="s">
-        <v>194</v>
-      </c>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
+      <c r="B16" s="85" t="s">
+        <v>193</v>
+      </c>
+      <c r="C16" s="85"/>
+      <c r="D16" s="85"/>
       <c r="E16" t="s">
         <v>42</v>
       </c>
@@ -7862,9 +7862,9 @@
       <c r="A17">
         <v>3</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
+      <c r="B17" s="85"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
       <c r="E17" t="s">
         <v>44</v>
       </c>
@@ -7882,9 +7882,9 @@
       <c r="A18">
         <v>4</v>
       </c>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
+      <c r="B18" s="85"/>
+      <c r="C18" s="85"/>
+      <c r="D18" s="85"/>
       <c r="E18" t="s">
         <v>42</v>
       </c>
@@ -7897,7 +7897,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B19" s="32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -7927,99 +7927,99 @@
       </c>
       <c r="C2">
         <f ca="1">RAND()</f>
-        <v>0.58721926002363067</v>
+        <v>0.10803336282564091</v>
       </c>
       <c r="D2">
         <f t="shared" ref="D2:Z2" ca="1" si="0">RAND()</f>
-        <v>0.1818174421619585</v>
+        <v>0.26484253059165164</v>
       </c>
       <c r="E2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.17058199906136795</v>
+        <v>0.74030511160553691</v>
       </c>
       <c r="F2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.19248748244615965</v>
+        <v>0.8669100084688891</v>
       </c>
       <c r="G2">
         <f t="shared" ca="1" si="0"/>
-        <v>7.0391028522679755E-2</v>
+        <v>0.78513870986033518</v>
       </c>
       <c r="H2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.47049780682744047</v>
+        <v>0.74116346421657064</v>
       </c>
       <c r="I2">
         <f t="shared" ca="1" si="0"/>
-        <v>7.0817042932585506E-2</v>
+        <v>0.54735576782478346</v>
       </c>
       <c r="J2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.89768083063562076</v>
+        <v>0.89592292185851252</v>
       </c>
       <c r="K2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.17332404762921894</v>
+        <v>7.3430529415092871E-2</v>
       </c>
       <c r="L2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.49394953406032815</v>
+        <v>2.5176309101693994E-2</v>
       </c>
       <c r="M2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.20424460577855941</v>
+        <v>0.37646540213625634</v>
       </c>
       <c r="N2">
         <f t="shared" ca="1" si="0"/>
-        <v>4.1247752842149321E-2</v>
+        <v>0.80117039857117711</v>
       </c>
       <c r="O2">
         <f t="shared" ca="1" si="0"/>
-        <v>9.3671187433734593E-2</v>
+        <v>0.59660859219810858</v>
       </c>
       <c r="P2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.90695531140462526</v>
+        <v>5.3513354511471656E-2</v>
       </c>
       <c r="Q2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.6614459420237</v>
+        <v>0.26335791473110592</v>
       </c>
       <c r="R2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.71040769137921966</v>
+        <v>0.64554997819644822</v>
       </c>
       <c r="S2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.10258253376816551</v>
+        <v>0.40987718217251645</v>
       </c>
       <c r="T2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.25102612101188448</v>
+        <v>0.62459377008707428</v>
       </c>
       <c r="U2">
         <f t="shared" ca="1" si="0"/>
-        <v>8.9449792871929557E-2</v>
+        <v>0.28390042493753398</v>
       </c>
       <c r="V2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.78455037873091404</v>
+        <v>2.1773990481188776E-2</v>
       </c>
       <c r="W2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.12230072447194029</v>
+        <v>0.84453416524938818</v>
       </c>
       <c r="X2">
         <f t="shared" ca="1" si="0"/>
-        <v>3.8543381792818243E-3</v>
+        <v>0.38282287569535178</v>
       </c>
       <c r="Y2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.73176679398602229</v>
+        <v>2.1420738429736463E-2</v>
       </c>
       <c r="Z2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.75230998353208367</v>
+        <v>0.66220624662448535</v>
       </c>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.25">
@@ -9716,16 +9716,16 @@
         <v>1</v>
       </c>
       <c r="U7" cm="1">
-        <f t="array" ref="U7:U18">M34*P7:P18</f>
-        <v>-2.1372514222528685E-2</v>
+        <f t="array" ref="U7:U18">M34*M7:M18</f>
+        <v>0.59436365037016081</v>
       </c>
       <c r="V7" cm="1">
-        <f t="array" ref="V7:V18">M35*Q7:Q18</f>
-        <v>-2.8685761798026895E-2</v>
+        <f t="array" ref="V7:V18">M35*M7:M18</f>
+        <v>0.1593108271611868</v>
       </c>
       <c r="W7" s="8" cm="1">
-        <f t="array" ref="W7:W18">M36*R7:R18</f>
-        <v>-0.15040705920766417</v>
+        <f t="array" ref="W7:W18">M36*M7:M18</f>
+        <v>0.72042711116499081</v>
       </c>
       <c r="Z7">
         <v>1</v>
@@ -9807,13 +9807,13 @@
         <v>2</v>
       </c>
       <c r="U8">
-        <v>-0.15072407418126571</v>
+        <v>0.14772448081975634</v>
       </c>
       <c r="V8">
-        <v>-1.7100305095694125E-3</v>
+        <v>3.9595471924798169E-2</v>
       </c>
       <c r="W8" s="8">
-        <v>0.19158534148431261</v>
+        <v>0.17905657739844189</v>
       </c>
       <c r="Z8">
         <v>2</v>
@@ -9895,13 +9895,13 @@
         <v>3</v>
       </c>
       <c r="U9">
-        <v>-9.8887752372893906E-2</v>
+        <v>0.17007740273290414</v>
       </c>
       <c r="V9">
-        <v>1.3338237974641417E-2</v>
+        <v>4.5586858641053808E-2</v>
       </c>
       <c r="W9" s="8">
-        <v>-2.3392357537438773E-2</v>
+        <v>0.20615051382937363</v>
       </c>
       <c r="Z9">
         <v>3</v>
@@ -9943,7 +9943,7 @@
     </row>
     <row r="10" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L10">
         <v>4</v>
@@ -9968,13 +9968,13 @@
         <v>4</v>
       </c>
       <c r="U10">
-        <v>-4.6413445065342139E-2</v>
+        <v>0.25685279446653447</v>
       </c>
       <c r="V10">
-        <v>-8.6356540733255327E-3</v>
+        <v>6.8845783418353235E-2</v>
       </c>
       <c r="W10" s="8">
-        <v>3.5958500016228197E-2</v>
+        <v>0.31133081001326057</v>
       </c>
       <c r="Z10">
         <v>4</v>
@@ -10042,13 +10042,13 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>-9.2029408256709327E-2</v>
+        <v>0.62705437071134051</v>
       </c>
       <c r="V11">
-        <v>-7.9088911067585321E-3</v>
+        <v>0.16807311552590246</v>
       </c>
       <c r="W11" s="8">
-        <v>3.3445271520470311E-2</v>
+        <v>0.76005147446956256</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -10119,13 +10119,13 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <v>9.1231926382734377E-2</v>
+        <v>0.14500457891110863</v>
       </c>
       <c r="V12">
-        <v>3.8133680363397898E-2</v>
+        <v>3.88664404259942E-2</v>
       </c>
       <c r="W12" s="8">
-        <v>0.14634722856067067</v>
+        <v>0.17575978918893601</v>
       </c>
       <c r="Z12">
         <v>6</v>
@@ -10205,13 +10205,13 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>-3.349423870694794E-2</v>
+        <v>0.29718182518508041</v>
       </c>
       <c r="V13">
-        <v>-3.689390824396007E-2</v>
+        <v>7.9655413580593401E-2</v>
       </c>
       <c r="W13" s="8">
-        <v>4.8717967763922072E-2</v>
+        <v>0.3602135555824954</v>
       </c>
       <c r="AI13">
         <v>0</v>
@@ -10277,13 +10277,13 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>8.7563509762449615E-2</v>
+        <v>7.3862240409878169E-2</v>
       </c>
       <c r="V14">
-        <v>7.9088911067585321E-3</v>
+        <v>1.9797735962399084E-2</v>
       </c>
       <c r="W14" s="8">
-        <v>-9.8209236603461966E-2</v>
+        <v>8.9528288699220943E-2</v>
       </c>
       <c r="Z14" s="4"/>
       <c r="AA14" s="40" t="s">
@@ -10363,13 +10363,13 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>0.15790141104704028</v>
+        <v>8.5038701366452071E-2</v>
       </c>
       <c r="V15">
-        <v>-4.0484972314055838E-2</v>
+        <v>2.2793429320526904E-2</v>
       </c>
       <c r="W15" s="8">
-        <v>-0.17495936835852968</v>
+        <v>0.10307525691468682</v>
       </c>
       <c r="Z15" s="7"/>
       <c r="AA15">
@@ -10433,13 +10433,13 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>7.4803799778850391E-2</v>
+        <v>0.12842639723326724</v>
       </c>
       <c r="V16">
-        <v>1.5604028399820887E-2</v>
+        <v>3.4422891709176617E-2</v>
       </c>
       <c r="W16" s="8">
-        <v>-4.0018330663221705E-2</v>
+        <v>0.15566540500663029</v>
       </c>
       <c r="Z16" s="7">
         <v>1</v>
@@ -10512,13 +10512,13 @@
         <v>11</v>
       </c>
       <c r="U17">
-        <v>3.8438626325592633E-2</v>
+        <v>0.31352718535567026</v>
       </c>
       <c r="V17">
-        <v>2.0776870691268361E-2</v>
+        <v>8.4036557762951228E-2</v>
       </c>
       <c r="W17" s="8">
-        <v>-1.1599516134267161E-3</v>
+        <v>0.38002573723478128</v>
       </c>
       <c r="Z17" s="7">
         <v>2</v>
@@ -10608,13 +10608,13 @@
         <v>12</v>
       </c>
       <c r="U18" s="14">
-        <v>-2.6635894590763362E-2</v>
+        <v>7.2502289455554314E-2</v>
       </c>
       <c r="V18" s="14">
-        <v>-1.8895837130742006E-2</v>
+        <v>1.94332202129971E-2</v>
       </c>
       <c r="W18" s="11">
-        <v>1.9332526890445268E-3</v>
+        <v>8.7879894594468003E-2</v>
       </c>
       <c r="Z18" s="9">
         <v>3</v>
@@ -13158,7 +13158,7 @@
         <v>1.426184227044502</v>
       </c>
       <c r="K4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="BL4" t="s">
         <v>90</v>
@@ -13215,13 +13215,13 @@
         <v>92</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O5">
         <v>2</v>
       </c>
       <c r="P5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W5" t="s">
         <v>46</v>
@@ -13314,13 +13314,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O6">
         <v>2</v>
       </c>
       <c r="P6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="W6">
         <v>1</v>
@@ -13352,52 +13352,52 @@
       <c r="AM6" t="s">
         <v>113</v>
       </c>
-      <c r="AN6" s="85" t="s">
+      <c r="AN6" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="AO6" s="85" t="s">
+      <c r="AO6" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="AP6" s="85" t="s">
+      <c r="AP6" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="AQ6" s="85" t="s">
+      <c r="AQ6" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="AR6" s="85" t="s">
+      <c r="AR6" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="AS6" s="85" t="s">
+      <c r="AS6" s="79" t="s">
         <v>123</v>
       </c>
       <c r="AT6" s="25"/>
       <c r="AU6" t="s">
         <v>124</v>
       </c>
-      <c r="AW6" s="83" t="s">
+      <c r="AW6" s="77" t="s">
         <v>125</v>
       </c>
-      <c r="AX6" s="87"/>
+      <c r="AX6" s="81"/>
       <c r="AY6" t="s">
         <v>126</v>
       </c>
-      <c r="AZ6" s="84" t="s">
+      <c r="AZ6" s="78" t="s">
         <v>131</v>
       </c>
-      <c r="BB6" s="83" t="s">
+      <c r="BB6" s="77" t="s">
         <v>129</v>
       </c>
-      <c r="BC6" s="87"/>
+      <c r="BC6" s="81"/>
       <c r="BD6" t="s">
         <v>127</v>
       </c>
-      <c r="BE6" s="84" t="s">
+      <c r="BE6" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="BG6" s="83" t="s">
+      <c r="BG6" s="77" t="s">
         <v>130</v>
       </c>
-      <c r="BH6" s="87"/>
+      <c r="BH6" s="81"/>
       <c r="BI6" t="s">
         <v>128</v>
       </c>
@@ -13505,16 +13505,16 @@
         <v>1</v>
       </c>
       <c r="AE7" cm="1">
-        <f t="array" ref="AE7:AE18">W34*Z7:Z18</f>
-        <v>-3.4869496943208621E-3</v>
+        <f t="array" ref="AE7:AE18">W34*W7:W18</f>
+        <v>1.0074891727250733E-2</v>
       </c>
       <c r="AF7" cm="1">
-        <f t="array" ref="AF7:AF18">W35*AA7:AA18</f>
-        <v>-3.6992188208372799E-3</v>
+        <f t="array" ref="AF7:AF18">W35*W7:W18</f>
+        <v>2.1344550132518262E-3</v>
       </c>
       <c r="AG7" s="8" cm="1">
-        <f t="array" ref="AG7:AG18">W36*AB7:AB18</f>
-        <v>-0.30794950892867018</v>
+        <f t="array" ref="AG7:AG18">W36*W7:W18</f>
+        <v>0.15324962585409685</v>
       </c>
       <c r="AK7" s="25">
         <v>1</v>
@@ -13523,22 +13523,22 @@
       <c r="AM7">
         <v>1</v>
       </c>
-      <c r="AN7" s="85">
-        <v>1</v>
-      </c>
-      <c r="AO7" s="85">
-        <v>1</v>
-      </c>
-      <c r="AP7" s="85">
-        <v>1</v>
-      </c>
-      <c r="AQ7" s="85">
-        <v>1</v>
-      </c>
-      <c r="AR7" s="85">
-        <v>1</v>
-      </c>
-      <c r="AS7" s="85">
+      <c r="AN7" s="79">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="79">
+        <v>1</v>
+      </c>
+      <c r="AP7" s="79">
+        <v>1</v>
+      </c>
+      <c r="AQ7" s="79">
+        <v>1</v>
+      </c>
+      <c r="AR7" s="79">
+        <v>1</v>
+      </c>
+      <c r="AS7" s="79">
         <v>1</v>
       </c>
       <c r="AT7" s="25"/>
@@ -13548,40 +13548,40 @@
       <c r="AV7">
         <v>2</v>
       </c>
-      <c r="AW7" s="83">
-        <v>1</v>
-      </c>
-      <c r="AX7" s="87">
+      <c r="AW7" s="77">
+        <v>1</v>
+      </c>
+      <c r="AX7" s="81">
         <v>2</v>
       </c>
       <c r="AY7">
         <v>1</v>
       </c>
-      <c r="AZ7" s="84">
+      <c r="AZ7" s="78">
         <v>1</v>
       </c>
       <c r="BA7">
         <v>2</v>
       </c>
-      <c r="BB7" s="83">
-        <v>1</v>
-      </c>
-      <c r="BC7" s="87">
+      <c r="BB7" s="77">
+        <v>1</v>
+      </c>
+      <c r="BC7" s="81">
         <v>2</v>
       </c>
       <c r="BD7">
         <v>1</v>
       </c>
-      <c r="BE7" s="84">
+      <c r="BE7" s="78">
         <v>1</v>
       </c>
       <c r="BF7">
         <v>2</v>
       </c>
-      <c r="BG7" s="83">
-        <v>1</v>
-      </c>
-      <c r="BH7" s="87">
+      <c r="BG7" s="77">
+        <v>1</v>
+      </c>
+      <c r="BH7" s="81">
         <v>2</v>
       </c>
       <c r="BI7">
@@ -13691,13 +13691,13 @@
         <v>2</v>
       </c>
       <c r="AE8">
-        <v>-2.459080194875533E-2</v>
+        <v>1.6921414596890116E-2</v>
       </c>
       <c r="AF8">
-        <v>-2.2051975086958449E-4</v>
+        <v>3.5849515007642407E-3</v>
       </c>
       <c r="AG8" s="8">
-        <v>0.39225959299268909</v>
+        <v>0.25739238952626486</v>
       </c>
       <c r="AJ8">
         <v>1</v>
@@ -13711,27 +13711,27 @@
         <f t="array" ref="AM8:AM9">_xlfn.ANCHORARRAY(AK8)*(1-$O$59:$O$60)</f>
         <v>-2.3113465138950131E-4</v>
       </c>
-      <c r="AN8" s="85" cm="1">
+      <c r="AN8" s="79" cm="1">
         <f t="array" ref="AN8:AN9">_xlfn.ANCHORARRAY(AM8)*(1-$R$59:$R$60*$R$59:$R$60)</f>
         <v>-3.9795312029872705E-5</v>
       </c>
-      <c r="AO8" s="85" cm="1">
+      <c r="AO8" s="79" cm="1">
         <f t="array" ref="AO8:AO9">_xlfn.ANCHORARRAY(AK8)*(_xlfn.ANCHORARRAY(T53)-$R$59:$R$60)</f>
         <v>6.2011649599711196E-4</v>
       </c>
-      <c r="AP8" s="85" cm="1">
+      <c r="AP8" s="79" cm="1">
         <f t="array" ref="AP8:AP9">_xlfn.ANCHORARRAY(AO8)*($O$59:$O$60*(1-$O$59:$O$60))</f>
         <v>8.4887679241149805E-5</v>
       </c>
-      <c r="AQ8" s="85" cm="1">
+      <c r="AQ8" s="79" cm="1">
         <f t="array" ref="AQ8:AQ9">MMULT(TRANSPOSE($P$23:$Q$24),_xlfn.ANCHORARRAY($AN$8))*_xlfn.ANCHORARRAY($T$53)</f>
         <v>-3.4070185739920485E-5</v>
       </c>
-      <c r="AR8" s="85" cm="1">
+      <c r="AR8" s="79" cm="1">
         <f t="array" ref="AR8:AR9">_xlfn.ANCHORARRAY($AQ$8)*($L$59:$L$60*(1-$L$59:$L$60))</f>
         <v>-2.3147026388781518E-6</v>
       </c>
-      <c r="AS8" s="85" cm="1">
+      <c r="AS8" s="79" cm="1">
         <f t="array" ref="AS8:AS9">_xlfn.ANCHORARRAY(AK8)*$O$59:$O$60+MMULT(TRANSPOSE($P$23:$Q$24),_xlfn.ANCHORARRAY(AN8))*$L$59:$L$60+MMULT(TRANSPOSE($P$18:$Q$19),_xlfn.ANCHORARRAY(AP8))+MMULT(TRANSPOSE($P$13:$Q$14),_xlfn.ANCHORARRAY(AR8))</f>
         <v>-2.8108228537107277E-3</v>
       </c>
@@ -13743,47 +13743,47 @@
       <c r="AV8">
         <v>-5.009807347650241E-5</v>
       </c>
-      <c r="AW8" s="83" cm="1">
+      <c r="AW8" s="77" cm="1">
         <f t="array" ref="AW8:AX9">MMULT(_xlfn.ANCHORARRAY(AN8),TRANSPOSE($L$59:$L$60*_xlfn.ANCHORARRAY($T$53)))</f>
         <v>-1.7358527243956582E-5</v>
       </c>
-      <c r="AX8" s="87">
+      <c r="AX8" s="81">
         <v>-3.5459522469303295E-5</v>
       </c>
       <c r="AY8" cm="1">
         <f t="array" ref="AY8:AY9">_xlfn.ANCHORARRAY(AN8)</f>
         <v>-3.9795312029872705E-5</v>
       </c>
-      <c r="AZ8" s="84" cm="1">
+      <c r="AZ8" s="78" cm="1">
         <f t="array" ref="AZ8:BA9">MMULT(_xlfn.ANCHORARRAY(AP8),TRANSPOSE(H14:H15))</f>
         <v>2.592529759819988E-4</v>
       </c>
       <c r="BA8">
         <v>1.0686457713110925E-4</v>
       </c>
-      <c r="BB8" s="83" cm="1">
+      <c r="BB8" s="77" cm="1">
         <f t="array" ref="BB8:BC9">MMULT(_xlfn.ANCHORARRAY(AP8),TRANSPOSE(_xlfn.ANCHORARRAY($T$53)))</f>
         <v>3.9957022828628233E-5</v>
       </c>
-      <c r="BC8" s="87">
+      <c r="BC8" s="81">
         <v>8.2798546130498249E-5</v>
       </c>
       <c r="BD8" cm="1">
         <f t="array" ref="BD8:BD9">_xlfn.ANCHORARRAY(AP8)</f>
         <v>8.4887679241149805E-5</v>
       </c>
-      <c r="BE8" s="84" cm="1">
+      <c r="BE8" s="78" cm="1">
         <f t="array" ref="BE8:BF9">MMULT(_xlfn.ANCHORARRAY(AR8),TRANSPOSE($H$14:$H$15))</f>
         <v>-7.0692655637079518E-6</v>
       </c>
       <c r="BF8">
         <v>-2.9139649110358442E-6</v>
       </c>
-      <c r="BG8" s="83" cm="1">
+      <c r="BG8" s="77" cm="1">
         <f t="array" ref="BG8:BH9">MMULT(_xlfn.ANCHORARRAY(AR8),TRANSPOSE(_xlfn.ANCHORARRAY($T$53)))</f>
         <v>-1.0895412268298402E-6</v>
       </c>
-      <c r="BH8" s="87">
+      <c r="BH8" s="81">
         <v>-2.2577365164983009E-6</v>
       </c>
       <c r="BI8" cm="1">
@@ -13887,13 +13887,13 @@
         <v>3</v>
       </c>
       <c r="AE9">
-        <v>-1.613364783939503E-2</v>
+        <v>2.3886423897261682E-2</v>
       </c>
       <c r="AF9">
-        <v>1.720054056782759E-3</v>
+        <v>5.0605503876795738E-3</v>
       </c>
       <c r="AG9" s="8">
-        <v>-4.7894460900217338E-2</v>
+        <v>0.36333745556257435</v>
       </c>
       <c r="AJ9">
         <v>2</v>
@@ -13905,22 +13905,22 @@
       <c r="AM9">
         <v>0.20480725277953932</v>
       </c>
-      <c r="AN9" s="85">
+      <c r="AN9" s="79">
         <v>9.0017344798799947E-5</v>
       </c>
-      <c r="AO9" s="85">
+      <c r="AO9" s="79">
         <v>-7.7569321423110495E-3</v>
       </c>
-      <c r="AP9" s="85">
+      <c r="AP9" s="79">
         <v>-1.7784017778548749E-3</v>
       </c>
-      <c r="AQ9" s="85">
+      <c r="AQ9" s="79">
         <v>4.9468951206888654E-5</v>
       </c>
-      <c r="AR9" s="85">
+      <c r="AR9" s="79">
         <v>3.9076889111879151E-6</v>
       </c>
-      <c r="AS9" s="85">
+      <c r="AS9" s="79">
         <v>0.1136012263119789</v>
       </c>
       <c r="AT9" s="25"/>
@@ -13930,40 +13930,40 @@
       <c r="AV9">
         <v>1.1332228154172252E-4</v>
       </c>
-      <c r="AW9" s="83">
+      <c r="AW9" s="77">
         <v>3.9265140852411112E-5</v>
       </c>
-      <c r="AX9" s="87">
+      <c r="AX9" s="81">
         <v>8.0209750789841434E-5</v>
       </c>
       <c r="AY9">
         <v>9.0017344798799947E-5</v>
       </c>
-      <c r="AZ9" s="84">
+      <c r="AZ9" s="78">
         <v>-5.431364804906272E-3</v>
       </c>
       <c r="BA9">
         <v>-2.2388190566475885E-3</v>
       </c>
-      <c r="BB9" s="83">
+      <c r="BB9" s="77">
         <v>-8.3710193365462728E-4</v>
       </c>
-      <c r="BC9" s="87">
+      <c r="BC9" s="81">
         <v>-1.7346343186502983E-3</v>
       </c>
       <c r="BD9">
         <v>-1.7784017778548749E-3</v>
       </c>
-      <c r="BE9" s="84">
+      <c r="BE9" s="78">
         <v>1.1934358301389714E-5</v>
       </c>
       <c r="BF9">
         <v>4.9193655285087629E-6</v>
       </c>
-      <c r="BG9" s="83">
+      <c r="BG9" s="77">
         <v>1.8393672253419706E-6</v>
       </c>
-      <c r="BH9" s="87">
+      <c r="BH9" s="81">
         <v>3.8115185085633231E-6</v>
       </c>
       <c r="BI9">
@@ -14035,16 +14035,16 @@
     </row>
     <row r="10" spans="2:82" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K10" t="s">
+        <v>232</v>
+      </c>
+      <c r="O10" t="s">
         <v>233</v>
       </c>
-      <c r="O10" t="s">
-        <v>234</v>
-      </c>
       <c r="S10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="V10">
         <v>4</v>
@@ -14069,31 +14069,31 @@
         <v>4</v>
       </c>
       <c r="AE10">
-        <v>-7.5724056794579907E-3</v>
+        <v>2.4574654920102076E-2</v>
       </c>
       <c r="AF10">
-        <v>-1.1136247418914017E-3</v>
+        <v>5.2063582233115684E-3</v>
       </c>
       <c r="AG10" s="8">
-        <v>7.3622890309424996E-2</v>
+        <v>0.37380616824026919</v>
       </c>
       <c r="AK10" s="25"/>
       <c r="AL10" s="25"/>
-      <c r="AN10" s="85"/>
-      <c r="AO10" s="85"/>
-      <c r="AP10" s="85"/>
-      <c r="AQ10" s="85"/>
-      <c r="AR10" s="85"/>
-      <c r="AS10" s="85"/>
+      <c r="AN10" s="79"/>
+      <c r="AO10" s="79"/>
+      <c r="AP10" s="79"/>
+      <c r="AQ10" s="79"/>
+      <c r="AR10" s="79"/>
+      <c r="AS10" s="79"/>
       <c r="AT10" s="25"/>
-      <c r="AW10" s="83"/>
-      <c r="AX10" s="87"/>
-      <c r="AZ10" s="84"/>
-      <c r="BB10" s="83"/>
-      <c r="BC10" s="87"/>
-      <c r="BE10" s="84"/>
-      <c r="BG10" s="83"/>
-      <c r="BH10" s="87"/>
+      <c r="AW10" s="77"/>
+      <c r="AX10" s="81"/>
+      <c r="AZ10" s="78"/>
+      <c r="BB10" s="77"/>
+      <c r="BC10" s="81"/>
+      <c r="BE10" s="78"/>
+      <c r="BG10" s="77"/>
+      <c r="BH10" s="81"/>
       <c r="BK10">
         <v>5</v>
       </c>
@@ -14196,36 +14196,36 @@
         <v>5</v>
       </c>
       <c r="AE11">
-        <v>-1.5014701295695054E-2</v>
+        <v>2.5381596405848698E-2</v>
       </c>
       <c r="AF11">
-        <v>-1.0199038477718282E-3</v>
+        <v>5.3773159215460839E-3</v>
       </c>
       <c r="AG11" s="8">
-        <v>6.8477204427583468E-2</v>
+        <v>0.38608059104546238</v>
       </c>
       <c r="AK11" s="43" t="s">
         <v>108</v>
       </c>
       <c r="AL11" s="25"/>
-      <c r="AN11" s="85"/>
-      <c r="AO11" s="85"/>
-      <c r="AP11" s="85"/>
-      <c r="AQ11" s="85"/>
-      <c r="AR11" s="85"/>
-      <c r="AS11" s="85"/>
+      <c r="AN11" s="79"/>
+      <c r="AO11" s="79"/>
+      <c r="AP11" s="79"/>
+      <c r="AQ11" s="79"/>
+      <c r="AR11" s="79"/>
+      <c r="AS11" s="79"/>
       <c r="AT11" s="25"/>
       <c r="AU11" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="AW11" s="83"/>
-      <c r="AX11" s="87"/>
-      <c r="AZ11" s="84"/>
-      <c r="BB11" s="83"/>
-      <c r="BC11" s="87"/>
-      <c r="BE11" s="84"/>
-      <c r="BG11" s="83"/>
-      <c r="BH11" s="87"/>
+      <c r="AW11" s="77"/>
+      <c r="AX11" s="81"/>
+      <c r="AZ11" s="78"/>
+      <c r="BB11" s="77"/>
+      <c r="BC11" s="81"/>
+      <c r="BE11" s="78"/>
+      <c r="BG11" s="77"/>
+      <c r="BH11" s="81"/>
       <c r="BK11">
         <v>6</v>
       </c>
@@ -14335,13 +14335,13 @@
         <v>6</v>
       </c>
       <c r="AE12">
-        <v>1.4884591232474126E-2</v>
+        <v>2.5790336578663964E-2</v>
       </c>
       <c r="AF12">
-        <v>4.9175904443917338E-3</v>
+        <v>5.4639111460508972E-3</v>
       </c>
       <c r="AG12" s="8">
-        <v>0.29963724711954154</v>
+        <v>0.39229795598111239</v>
       </c>
       <c r="AK12" s="25" t="s">
         <v>106</v>
@@ -14350,52 +14350,52 @@
       <c r="AM12" t="s">
         <v>113</v>
       </c>
-      <c r="AN12" s="85" t="s">
+      <c r="AN12" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="AO12" s="85" t="s">
+      <c r="AO12" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="AP12" s="85" t="s">
+      <c r="AP12" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="AQ12" s="85" t="s">
+      <c r="AQ12" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="AR12" s="85" t="s">
+      <c r="AR12" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="AS12" s="85" t="s">
+      <c r="AS12" s="79" t="s">
         <v>123</v>
       </c>
       <c r="AT12" s="25"/>
       <c r="AU12" t="s">
         <v>124</v>
       </c>
-      <c r="AW12" s="83" t="s">
+      <c r="AW12" s="77" t="s">
         <v>125</v>
       </c>
-      <c r="AX12" s="87"/>
+      <c r="AX12" s="81"/>
       <c r="AY12" t="s">
         <v>126</v>
       </c>
-      <c r="AZ12" s="84" t="s">
+      <c r="AZ12" s="78" t="s">
         <v>131</v>
       </c>
-      <c r="BB12" s="83" t="s">
+      <c r="BB12" s="77" t="s">
         <v>129</v>
       </c>
-      <c r="BC12" s="87"/>
+      <c r="BC12" s="81"/>
       <c r="BD12" t="s">
         <v>127</v>
       </c>
-      <c r="BE12" s="84" t="s">
+      <c r="BE12" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="BG12" s="83" t="s">
+      <c r="BG12" s="77" t="s">
         <v>130</v>
       </c>
-      <c r="BH12" s="87"/>
+      <c r="BH12" s="81"/>
       <c r="BI12" t="s">
         <v>128</v>
       </c>
@@ -14499,13 +14499,13 @@
         <v>7</v>
       </c>
       <c r="AE13">
-        <v>-5.4646226552789619E-3</v>
+        <v>7.8405086603671043E-3</v>
       </c>
       <c r="AF13">
-        <v>-4.7577136250112851E-3</v>
+        <v>1.6610811778055388E-3</v>
       </c>
       <c r="AG13" s="8">
-        <v>9.9747141709543546E-2</v>
+        <v>0.11926232571384159</v>
       </c>
       <c r="AK13" s="25">
         <v>1</v>
@@ -14514,22 +14514,22 @@
       <c r="AM13">
         <v>1</v>
       </c>
-      <c r="AN13" s="85">
-        <v>1</v>
-      </c>
-      <c r="AO13" s="85">
-        <v>1</v>
-      </c>
-      <c r="AP13" s="85">
-        <v>1</v>
-      </c>
-      <c r="AQ13" s="85">
-        <v>1</v>
-      </c>
-      <c r="AR13" s="85">
-        <v>1</v>
-      </c>
-      <c r="AS13" s="85">
+      <c r="AN13" s="79">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="79">
+        <v>1</v>
+      </c>
+      <c r="AP13" s="79">
+        <v>1</v>
+      </c>
+      <c r="AQ13" s="79">
+        <v>1</v>
+      </c>
+      <c r="AR13" s="79">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="79">
         <v>1</v>
       </c>
       <c r="AT13" s="25"/>
@@ -14539,40 +14539,40 @@
       <c r="AV13">
         <v>2</v>
       </c>
-      <c r="AW13" s="83">
-        <v>1</v>
-      </c>
-      <c r="AX13" s="87">
+      <c r="AW13" s="77">
+        <v>1</v>
+      </c>
+      <c r="AX13" s="81">
         <v>2</v>
       </c>
       <c r="AY13">
         <v>1</v>
       </c>
-      <c r="AZ13" s="84">
+      <c r="AZ13" s="78">
         <v>1</v>
       </c>
       <c r="BA13">
         <v>2</v>
       </c>
-      <c r="BB13" s="83">
-        <v>1</v>
-      </c>
-      <c r="BC13" s="87">
+      <c r="BB13" s="77">
+        <v>1</v>
+      </c>
+      <c r="BC13" s="81">
         <v>2</v>
       </c>
       <c r="BD13">
         <v>1</v>
       </c>
-      <c r="BE13" s="84">
+      <c r="BE13" s="78">
         <v>1</v>
       </c>
       <c r="BF13">
         <v>2</v>
       </c>
-      <c r="BG13" s="83">
-        <v>1</v>
-      </c>
-      <c r="BH13" s="87">
+      <c r="BG13" s="77">
+        <v>1</v>
+      </c>
+      <c r="BH13" s="81">
         <v>2</v>
       </c>
       <c r="BI13">
@@ -14685,13 +14685,13 @@
         <v>8</v>
       </c>
       <c r="AE14">
-        <v>1.428608494165786E-2</v>
+        <v>1.3881934818820555E-2</v>
       </c>
       <c r="AF14">
-        <v>1.0199038477718282E-3</v>
+        <v>2.9410107989073391E-3</v>
       </c>
       <c r="AG14" s="8">
-        <v>-0.20107757138273066</v>
+        <v>0.21115872752865225</v>
       </c>
       <c r="AJ14">
         <v>1</v>
@@ -14705,27 +14705,27 @@
         <f t="array" ref="AM14:AM15">_xlfn.ANCHORARRAY(AK14)*(1-$O$53:$O$54)</f>
         <v>1.1832771859769751E-4</v>
       </c>
-      <c r="AN14" s="85" cm="1">
+      <c r="AN14" s="79" cm="1">
         <f t="array" ref="AN14:AN15">_xlfn.ANCHORARRAY(AM14)*(1-$R$53:$R$54*$R$53:$R$54)</f>
         <v>1.1575685065873315E-4</v>
       </c>
-      <c r="AO14" s="85" cm="1">
+      <c r="AO14" s="79" cm="1">
         <f t="array" ref="AO14:AO15">_xlfn.ANCHORARRAY(AK14)*(_xlfn.ANCHORARRAY(T53)-$R$53:$R$54)</f>
         <v>1.5422328950255977E-4</v>
       </c>
-      <c r="AP14" s="85" cm="1">
+      <c r="AP14" s="79" cm="1">
         <f t="array" ref="AP14:AP15">_xlfn.ANCHORARRAY(AO14)*($O$53:$O$54*(1-$O$53:$O$54))</f>
         <v>2.8766338487590423E-5</v>
       </c>
-      <c r="AQ14" s="85" cm="1">
+      <c r="AQ14" s="79" cm="1">
         <f t="array" ref="AQ14:AQ15">MMULT(TRANSPOSE($P$23:$Q$24),_xlfn.ANCHORARRAY(AN14))*_xlfn.ANCHORARRAY(T47)</f>
         <v>3.8082090083221792E-5</v>
       </c>
-      <c r="AR14" s="85" cm="1">
+      <c r="AR14" s="79" cm="1">
         <f t="array" ref="AR14:AR15">_xlfn.ANCHORARRAY(AQ14)*($L$53:$L$54*(1-$L$53:$L$54))</f>
         <v>7.2353147058706737E-7</v>
       </c>
-      <c r="AS14" s="85" cm="1">
+      <c r="AS14" s="79" cm="1">
         <f t="array" ref="AS14:AS15">_xlfn.ANCHORARRAY(AK14)*$O$53:$O$54+MMULT(TRANSPOSE($P$23:$Q$24),_xlfn.ANCHORARRAY(AN14))*$L$53:$L$54+MMULT(TRANSPOSE($P$18:$Q$19),_xlfn.ANCHORARRAY(AP14))+MMULT(TRANSPOSE($P$13:$Q$14),_xlfn.ANCHORARRAY(AR14))</f>
         <v>-4.777639803162665E-4</v>
       </c>
@@ -14737,47 +14737,47 @@
       <c r="AV14">
         <v>6.2163738364749327E-5</v>
       </c>
-      <c r="AW14" s="83" cm="1">
+      <c r="AW14" s="77" cm="1">
         <f t="array" ref="AW14:AX15">MMULT(_xlfn.ANCHORARRAY(AN14),TRANSPOSE($L$53:$L$54*_xlfn.ANCHORARRAY(T47)))</f>
         <v>6.5538295566505768E-5</v>
       </c>
-      <c r="AX14" s="87">
+      <c r="AX14" s="81">
         <v>9.0777872571756767E-5</v>
       </c>
       <c r="AY14" cm="1">
         <f t="array" ref="AY14:AY15">_xlfn.ANCHORARRAY(AN14)</f>
         <v>1.1575685065873315E-4</v>
       </c>
-      <c r="AZ14" s="84" cm="1">
+      <c r="AZ14" s="78" cm="1">
         <f t="array" ref="AZ14:BA15">MMULT(_xlfn.ANCHORARRAY(AP14),TRANSPOSE($G$14:$G$15))</f>
         <v>1.3001998607878998E-4</v>
       </c>
       <c r="BA14">
         <v>1.5448097708932266E-5</v>
       </c>
-      <c r="BB14" s="83" cm="1">
+      <c r="BB14" s="77" cm="1">
         <f t="array" ref="BB14:BC15">MMULT(_xlfn.ANCHORARRAY(AP14),TRANSPOSE(_xlfn.ANCHORARRAY(T47)))</f>
         <v>1.6608480609180702E-5</v>
       </c>
-      <c r="BC14" s="87">
+      <c r="BC14" s="81">
         <v>2.7166339948933329E-5</v>
       </c>
       <c r="BD14" cm="1">
         <f t="array" ref="BD14:BD15">_xlfn.ANCHORARRAY(AP14)</f>
         <v>2.8766338487590423E-5</v>
       </c>
-      <c r="BE14" s="84" cm="1">
+      <c r="BE14" s="78" cm="1">
         <f t="array" ref="BE14:BF15">MMULT(_xlfn.ANCHORARRAY(AR14),TRANSPOSE($G$14:$G$15))</f>
         <v>3.2702650625445274E-6</v>
       </c>
       <c r="BF14">
         <v>3.8855083548218069E-7</v>
       </c>
-      <c r="BG14" s="83" cm="1">
+      <c r="BG14" s="77" cm="1">
         <f t="array" ref="BG14:BH15">MMULT(_xlfn.ANCHORARRAY(AR14),TRANSPOSE(_xlfn.ANCHORARRAY(T47)))</f>
         <v>4.1773680736466493E-7</v>
       </c>
-      <c r="BH14" s="87">
+      <c r="BH14" s="81">
         <v>6.8328827814493128E-7</v>
       </c>
       <c r="BI14" cm="1">
@@ -14878,13 +14878,13 @@
         <v>9</v>
       </c>
       <c r="AE15">
-        <v>2.576179251774368E-2</v>
+        <v>1.870062647260589E-2</v>
       </c>
       <c r="AF15">
-        <v>-5.2208051018374129E-3</v>
+        <v>3.9618932893778864E-3</v>
       </c>
       <c r="AG15" s="8">
-        <v>-0.35821890177435284</v>
+        <v>0.28445606044702554</v>
       </c>
       <c r="AJ15">
         <v>2</v>
@@ -14896,22 +14896,22 @@
       <c r="AM15">
         <v>9.4616790342762838E-2</v>
       </c>
-      <c r="AN15" s="85">
+      <c r="AN15" s="79">
         <v>2.3332133399675298E-5</v>
       </c>
-      <c r="AO15" s="85">
+      <c r="AO15" s="79">
         <v>-4.1464672377211839E-3</v>
       </c>
-      <c r="AP15" s="85">
+      <c r="AP15" s="79">
         <v>-1.0222971915964977E-3</v>
       </c>
-      <c r="AQ15" s="85">
+      <c r="AQ15" s="79">
         <v>1.0063757060511586E-4</v>
       </c>
-      <c r="AR15" s="85">
+      <c r="AR15" s="79">
         <v>1.4173451445842819E-5</v>
       </c>
-      <c r="AS15" s="85">
+      <c r="AS15" s="79">
         <v>7.4977033991124556E-2</v>
       </c>
       <c r="AT15" s="25"/>
@@ -14921,40 +14921,40 @@
       <c r="AV15">
         <v>1.252982115438556E-5</v>
       </c>
-      <c r="AW15" s="83">
+      <c r="AW15" s="77">
         <v>1.3210002226591294E-5</v>
       </c>
-      <c r="AX15" s="87">
+      <c r="AX15" s="81">
         <v>1.829733117763567E-5</v>
       </c>
       <c r="AY15">
         <v>2.3332133399675298E-5</v>
       </c>
-      <c r="AZ15" s="84">
+      <c r="AZ15" s="78">
         <v>-4.6206459913938295E-3</v>
       </c>
       <c r="BA15">
         <v>-5.4899398858713035E-4</v>
       </c>
-      <c r="BB15" s="83">
+      <c r="BB15" s="77">
         <v>-5.9023163795332686E-4</v>
       </c>
-      <c r="BC15" s="87">
+      <c r="BC15" s="81">
         <v>-9.6543649612309689E-4</v>
       </c>
       <c r="BD15">
         <v>-1.0222971915964977E-3</v>
       </c>
-      <c r="BE15" s="84">
+      <c r="BE15" s="78">
         <v>6.4062096761875785E-5</v>
       </c>
       <c r="BF15">
         <v>7.6114262127118383E-6</v>
       </c>
-      <c r="BG15" s="83">
+      <c r="BG15" s="77">
         <v>8.1831580200933189E-6</v>
       </c>
-      <c r="BH15" s="87">
+      <c r="BH15" s="81">
         <v>1.3385116788275653E-5</v>
       </c>
       <c r="BI15">
@@ -15055,31 +15055,31 @@
         <v>10</v>
       </c>
       <c r="AE16">
-        <v>1.2204323930123015E-2</v>
+        <v>1.9799338288249632E-2</v>
       </c>
       <c r="AF16">
-        <v>2.0122427266849583E-3</v>
+        <v>4.1946651152702285E-3</v>
       </c>
       <c r="AG16" s="8">
-        <v>-8.1935152118553622E-2</v>
+        <v>0.30116861470837308</v>
       </c>
       <c r="AK16" s="25"/>
       <c r="AL16" s="25"/>
-      <c r="AN16" s="85"/>
-      <c r="AO16" s="85"/>
-      <c r="AP16" s="85"/>
-      <c r="AQ16" s="85"/>
-      <c r="AR16" s="85"/>
-      <c r="AS16" s="85"/>
+      <c r="AN16" s="79"/>
+      <c r="AO16" s="79"/>
+      <c r="AP16" s="79"/>
+      <c r="AQ16" s="79"/>
+      <c r="AR16" s="79"/>
+      <c r="AS16" s="79"/>
       <c r="AT16" s="25"/>
-      <c r="AW16" s="83"/>
-      <c r="AX16" s="87"/>
-      <c r="AZ16" s="84"/>
-      <c r="BB16" s="83"/>
-      <c r="BC16" s="87"/>
-      <c r="BE16" s="84"/>
-      <c r="BG16" s="83"/>
-      <c r="BH16" s="87"/>
+      <c r="AW16" s="77"/>
+      <c r="AX16" s="81"/>
+      <c r="AZ16" s="78"/>
+      <c r="BB16" s="77"/>
+      <c r="BC16" s="81"/>
+      <c r="BE16" s="78"/>
+      <c r="BG16" s="77"/>
+      <c r="BH16" s="81"/>
       <c r="BK16">
         <v>2</v>
       </c>
@@ -15146,36 +15146,36 @@
         <v>11</v>
       </c>
       <c r="AE17">
-        <v>6.2713050472487141E-3</v>
+        <v>1.8815138993987835E-2</v>
       </c>
       <c r="AF17">
-        <v>2.6793149730654515E-3</v>
+        <v>3.9861537809008554E-3</v>
       </c>
       <c r="AG17" s="8">
-        <v>-2.3749319454653226E-3</v>
+        <v>0.28619791549941537</v>
       </c>
       <c r="AK17" s="43" t="s">
         <v>110</v>
       </c>
       <c r="AL17" s="25"/>
-      <c r="AN17" s="85"/>
-      <c r="AO17" s="85"/>
-      <c r="AP17" s="85"/>
-      <c r="AQ17" s="85"/>
-      <c r="AR17" s="85"/>
-      <c r="AS17" s="85"/>
+      <c r="AN17" s="79"/>
+      <c r="AO17" s="79"/>
+      <c r="AP17" s="79"/>
+      <c r="AQ17" s="79"/>
+      <c r="AR17" s="79"/>
+      <c r="AS17" s="79"/>
       <c r="AT17" s="25"/>
       <c r="AU17" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="AW17" s="83"/>
-      <c r="AX17" s="87"/>
-      <c r="AZ17" s="84"/>
-      <c r="BB17" s="83"/>
-      <c r="BC17" s="87"/>
-      <c r="BE17" s="84"/>
-      <c r="BG17" s="83"/>
-      <c r="BH17" s="87"/>
+      <c r="AW17" s="77"/>
+      <c r="AX17" s="81"/>
+      <c r="AZ17" s="78"/>
+      <c r="BB17" s="77"/>
+      <c r="BC17" s="81"/>
+      <c r="BE17" s="78"/>
+      <c r="BG17" s="77"/>
+      <c r="BH17" s="81"/>
       <c r="BK17">
         <v>3</v>
       </c>
@@ -15248,13 +15248,13 @@
         <v>12</v>
       </c>
       <c r="AE18" s="14">
-        <v>-4.3456761115789845E-3</v>
+        <v>1.9954739220686232E-2</v>
       </c>
       <c r="AF18" s="14">
-        <v>-2.4367432471089088E-3</v>
+        <v>4.2275881786919553E-3</v>
       </c>
       <c r="AG18" s="11">
-        <v>3.9582199091088713E-3</v>
+        <v>0.3035324251986507</v>
       </c>
       <c r="AK18" s="25" t="s">
         <v>106</v>
@@ -15263,52 +15263,52 @@
       <c r="AM18" t="s">
         <v>113</v>
       </c>
-      <c r="AN18" s="85" t="s">
+      <c r="AN18" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="AO18" s="85" t="s">
+      <c r="AO18" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="AP18" s="85" t="s">
+      <c r="AP18" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="AQ18" s="85" t="s">
+      <c r="AQ18" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="AR18" s="85" t="s">
+      <c r="AR18" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="AS18" s="85" t="s">
+      <c r="AS18" s="79" t="s">
         <v>123</v>
       </c>
       <c r="AT18" s="25"/>
       <c r="AU18" t="s">
         <v>124</v>
       </c>
-      <c r="AW18" s="83" t="s">
+      <c r="AW18" s="77" t="s">
         <v>125</v>
       </c>
-      <c r="AX18" s="87"/>
+      <c r="AX18" s="81"/>
       <c r="AY18" t="s">
         <v>126</v>
       </c>
-      <c r="AZ18" s="84" t="s">
+      <c r="AZ18" s="78" t="s">
         <v>131</v>
       </c>
-      <c r="BB18" s="83" t="s">
+      <c r="BB18" s="77" t="s">
         <v>129</v>
       </c>
-      <c r="BC18" s="87"/>
+      <c r="BC18" s="81"/>
       <c r="BD18" t="s">
         <v>127</v>
       </c>
-      <c r="BE18" s="84" t="s">
+      <c r="BE18" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="BG18" s="83" t="s">
+      <c r="BG18" s="77" t="s">
         <v>130</v>
       </c>
-      <c r="BH18" s="87"/>
+      <c r="BH18" s="81"/>
       <c r="BI18" t="s">
         <v>128</v>
       </c>
@@ -15368,22 +15368,22 @@
       <c r="AM19">
         <v>1</v>
       </c>
-      <c r="AN19" s="85">
-        <v>1</v>
-      </c>
-      <c r="AO19" s="85">
-        <v>1</v>
-      </c>
-      <c r="AP19" s="85">
-        <v>1</v>
-      </c>
-      <c r="AQ19" s="85">
-        <v>1</v>
-      </c>
-      <c r="AR19" s="85">
-        <v>1</v>
-      </c>
-      <c r="AS19" s="85">
+      <c r="AN19" s="79">
+        <v>1</v>
+      </c>
+      <c r="AO19" s="79">
+        <v>1</v>
+      </c>
+      <c r="AP19" s="79">
+        <v>1</v>
+      </c>
+      <c r="AQ19" s="79">
+        <v>1</v>
+      </c>
+      <c r="AR19" s="79">
+        <v>1</v>
+      </c>
+      <c r="AS19" s="79">
         <v>1</v>
       </c>
       <c r="AT19" s="25"/>
@@ -15393,40 +15393,40 @@
       <c r="AV19">
         <v>2</v>
       </c>
-      <c r="AW19" s="83">
-        <v>1</v>
-      </c>
-      <c r="AX19" s="87">
+      <c r="AW19" s="77">
+        <v>1</v>
+      </c>
+      <c r="AX19" s="81">
         <v>2</v>
       </c>
       <c r="AY19">
         <v>1</v>
       </c>
-      <c r="AZ19" s="84">
+      <c r="AZ19" s="78">
         <v>1</v>
       </c>
       <c r="BA19">
         <v>2</v>
       </c>
-      <c r="BB19" s="83">
-        <v>1</v>
-      </c>
-      <c r="BC19" s="87">
+      <c r="BB19" s="77">
+        <v>1</v>
+      </c>
+      <c r="BC19" s="81">
         <v>2</v>
       </c>
       <c r="BD19">
         <v>1</v>
       </c>
-      <c r="BE19" s="84">
+      <c r="BE19" s="78">
         <v>1</v>
       </c>
       <c r="BF19">
         <v>2</v>
       </c>
-      <c r="BG19" s="83">
-        <v>1</v>
-      </c>
-      <c r="BH19" s="87">
+      <c r="BG19" s="77">
+        <v>1</v>
+      </c>
+      <c r="BH19" s="81">
         <v>2</v>
       </c>
       <c r="BI19">
@@ -15480,27 +15480,27 @@
         <f t="array" ref="AM20:AM21">_xlfn.ANCHORARRAY(AK20)*(1-$O$47:$O$48)</f>
         <v>-5.3539719132453178E-3</v>
       </c>
-      <c r="AN20" s="85" cm="1">
+      <c r="AN20" s="79" cm="1">
         <f t="array" ref="AN20:AN21">_xlfn.ANCHORARRAY(AM20)*(1-$R$47:$R$48*$R$47:$R$48)</f>
         <v>-1.1005330914292486E-3</v>
       </c>
-      <c r="AO20" s="85" cm="1">
+      <c r="AO20" s="79" cm="1">
         <f t="array" ref="AO20:AO21">_xlfn.ANCHORARRAY(AK20)*(_xlfn.ANCHORARRAY(T41)-$R$47:$R$48)</f>
         <v>1.2771850576267228E-2</v>
       </c>
-      <c r="AP20" s="85" cm="1">
+      <c r="AP20" s="79" cm="1">
         <f t="array" ref="AP20:AP21">_xlfn.ANCHORARRAY(AO20)*($O$47:$O$48*(1-$O$47:$O$48))</f>
         <v>1.6809252207025467E-3</v>
       </c>
-      <c r="AQ20" s="85" cm="1">
+      <c r="AQ20" s="79" cm="1">
         <f t="array" ref="AQ20:AQ21">MMULT(TRANSPOSE($P$23:$Q$24),_xlfn.ANCHORARRAY(AN20))*_xlfn.ANCHORARRAY(T47)</f>
         <v>-5.9752722132898014E-4</v>
       </c>
-      <c r="AR20" s="85" cm="1">
+      <c r="AR20" s="79" cm="1">
         <f t="array" ref="AR20:AR21">_xlfn.ANCHORARRAY(AQ20)*($L$47:$L$48*(1-$L$47:$L$48))</f>
         <v>-9.8427923932025517E-5</v>
       </c>
-      <c r="AS20" s="85" cm="1">
+      <c r="AS20" s="79" cm="1">
         <f t="array" ref="AS20:AS21">_xlfn.ANCHORARRAY(AK20)*$O$47:$O$48+MMULT(TRANSPOSE($P$23:$Q$24),_xlfn.ANCHORARRAY(AN20))*$L$47:$L$48+MMULT(TRANSPOSE($P$18:$Q$19),_xlfn.ANCHORARRAY(AP20))+MMULT(TRANSPOSE($P$13:$Q$14),_xlfn.ANCHORARRAY(AR20))</f>
         <v>-3.1377210363402928E-2</v>
       </c>
@@ -15512,47 +15512,47 @@
       <c r="AV20">
         <v>-4.4573060240816841E-4</v>
       </c>
-      <c r="AW20" s="83" cm="1">
+      <c r="AW20" s="77" cm="1">
         <f t="array" ref="AW20:AX21">MMULT(_xlfn.ANCHORARRAY(AN20),TRANSPOSE($L$47:$L$48*_xlfn.ANCHORARRAY($T$41)))</f>
         <v>-4.5269728701219218E-4</v>
       </c>
-      <c r="AX20" s="87">
+      <c r="AX20" s="81">
         <v>-8.2618389231634622E-4</v>
       </c>
       <c r="AY20" cm="1">
         <f t="array" ref="AY20:AY21">_xlfn.ANCHORARRAY(AN20)</f>
         <v>-1.1005330914292486E-3</v>
       </c>
-      <c r="AZ20" s="84" cm="1">
+      <c r="AZ20" s="78" cm="1">
         <f t="array" ref="AZ20:BA21">MMULT(_xlfn.ANCHORARRAY(AP20),TRANSPOSE($F$14:$F$15))</f>
         <v>2.5372106973068709E-3</v>
       </c>
       <c r="BA20">
         <v>6.8079716735623208E-4</v>
       </c>
-      <c r="BB20" s="83" cm="1">
+      <c r="BB20" s="77" cm="1">
         <f t="array" ref="BB20:BC21">MMULT(_xlfn.ANCHORARRAY(AP20),TRANSPOSE(_xlfn.ANCHORARRAY(T47)))</f>
         <v>9.7049591297705424E-4</v>
       </c>
-      <c r="BC20" s="87">
+      <c r="BC20" s="81">
         <v>1.5874312955762694E-3</v>
       </c>
       <c r="BD20" cm="1">
         <f t="array" ref="BD20:BD21">_xlfn.ANCHORARRAY(AP20)</f>
         <v>1.6809252207025467E-3</v>
       </c>
-      <c r="BE20" s="84" cm="1">
+      <c r="BE20" s="78" cm="1">
         <f t="array" ref="BE20:BF21">MMULT(_xlfn.ANCHORARRAY(AR20),TRANSPOSE($F$14:$F$15))</f>
         <v>-1.4856840651701676E-4</v>
       </c>
       <c r="BF20">
         <v>-3.9864623944229294E-5</v>
       </c>
-      <c r="BG20" s="83" cm="1">
+      <c r="BG20" s="77" cm="1">
         <f t="array" ref="BG20:BH21">MMULT(_xlfn.ANCHORARRAY(AR20),TRANSPOSE(_xlfn.ANCHORARRAY(T41)))</f>
         <v>-5.1119664865092387E-5</v>
       </c>
-      <c r="BH20" s="87">
+      <c r="BH20" s="81">
         <v>-9.0350087309373694E-5</v>
       </c>
       <c r="BI20" cm="1">
@@ -15619,22 +15619,22 @@
       <c r="AM21">
         <v>3.7741199135426742E-2</v>
       </c>
-      <c r="AN21" s="85">
+      <c r="AN21" s="79">
         <v>5.825938900697608E-4</v>
       </c>
-      <c r="AO21" s="85">
+      <c r="AO21" s="79">
         <v>-7.8820048327675318E-3</v>
       </c>
-      <c r="AP21" s="85">
+      <c r="AP21" s="79">
         <v>-1.8067550417377471E-3</v>
       </c>
-      <c r="AQ21" s="85">
+      <c r="AQ21" s="79">
         <v>-2.7991772932824696E-4</v>
       </c>
-      <c r="AR21" s="85">
+      <c r="AR21" s="79">
         <v>-4.170317835035915E-5</v>
       </c>
-      <c r="AS21" s="85">
+      <c r="AS21" s="79">
         <v>7.0073502014047898E-2</v>
       </c>
       <c r="AT21" s="25"/>
@@ -15644,40 +15644,40 @@
       <c r="AV21">
         <v>2.3595830748066797E-4</v>
       </c>
-      <c r="AW21" s="83">
+      <c r="AW21" s="77">
         <v>2.3964629098244188E-4</v>
       </c>
-      <c r="AX21" s="87">
+      <c r="AX21" s="81">
         <v>4.3736048600997508E-4</v>
       </c>
       <c r="AY21">
         <v>5.825938900697608E-4</v>
       </c>
-      <c r="AZ21" s="84">
+      <c r="AZ21" s="78">
         <v>-2.7271398887061681E-3</v>
       </c>
       <c r="BA21">
         <v>-7.3175992564830075E-4</v>
       </c>
-      <c r="BB21" s="83">
+      <c r="BB21" s="77">
         <v>-1.0431447884542493E-3</v>
       </c>
-      <c r="BC21" s="87">
+      <c r="BC21" s="81">
         <v>-1.7062623972623717E-3</v>
       </c>
       <c r="BD21">
         <v>-1.8067550417377471E-3</v>
       </c>
-      <c r="BE21" s="84">
+      <c r="BE21" s="78">
         <v>-6.2947327411747744E-5</v>
       </c>
       <c r="BF21">
         <v>-1.689034428242441E-5</v>
       </c>
-      <c r="BG21" s="83">
+      <c r="BG21" s="77">
         <v>-2.1659021301229485E-5</v>
       </c>
-      <c r="BH21" s="87">
+      <c r="BH21" s="81">
         <v>-3.8280659131197769E-5</v>
       </c>
       <c r="BI21">
@@ -15725,21 +15725,21 @@
       </c>
       <c r="AK22" s="25"/>
       <c r="AL22" s="25"/>
-      <c r="AN22" s="85"/>
-      <c r="AO22" s="85"/>
-      <c r="AP22" s="85"/>
-      <c r="AQ22" s="85"/>
-      <c r="AR22" s="85"/>
-      <c r="AS22" s="85"/>
+      <c r="AN22" s="79"/>
+      <c r="AO22" s="79"/>
+      <c r="AP22" s="79"/>
+      <c r="AQ22" s="79"/>
+      <c r="AR22" s="79"/>
+      <c r="AS22" s="79"/>
       <c r="AT22" s="25"/>
-      <c r="AW22" s="83"/>
-      <c r="AX22" s="87"/>
-      <c r="AZ22" s="84"/>
-      <c r="BB22" s="83"/>
-      <c r="BC22" s="87"/>
-      <c r="BE22" s="84"/>
-      <c r="BG22" s="83"/>
-      <c r="BH22" s="87"/>
+      <c r="AW22" s="77"/>
+      <c r="AX22" s="81"/>
+      <c r="AZ22" s="78"/>
+      <c r="BB22" s="77"/>
+      <c r="BC22" s="81"/>
+      <c r="BE22" s="78"/>
+      <c r="BG22" s="77"/>
+      <c r="BH22" s="81"/>
       <c r="BK22" s="4"/>
       <c r="BL22" s="40" t="s">
         <v>50</v>
@@ -15799,24 +15799,24 @@
         <v>111</v>
       </c>
       <c r="AL23" s="25"/>
-      <c r="AN23" s="85"/>
-      <c r="AO23" s="85"/>
-      <c r="AP23" s="85"/>
-      <c r="AQ23" s="85"/>
-      <c r="AR23" s="85"/>
-      <c r="AS23" s="85"/>
+      <c r="AN23" s="79"/>
+      <c r="AO23" s="79"/>
+      <c r="AP23" s="79"/>
+      <c r="AQ23" s="79"/>
+      <c r="AR23" s="79"/>
+      <c r="AS23" s="79"/>
       <c r="AT23" s="25"/>
       <c r="AU23" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="AW23" s="83"/>
-      <c r="AX23" s="87"/>
-      <c r="AZ23" s="84"/>
-      <c r="BB23" s="83"/>
-      <c r="BC23" s="87"/>
-      <c r="BE23" s="84"/>
-      <c r="BG23" s="83"/>
-      <c r="BH23" s="87"/>
+      <c r="AW23" s="77"/>
+      <c r="AX23" s="81"/>
+      <c r="AZ23" s="78"/>
+      <c r="BB23" s="77"/>
+      <c r="BC23" s="81"/>
+      <c r="BE23" s="78"/>
+      <c r="BG23" s="77"/>
+      <c r="BH23" s="81"/>
       <c r="BK23" s="7"/>
       <c r="BL23">
         <v>1</v>
@@ -15883,52 +15883,52 @@
       <c r="AM24" t="s">
         <v>113</v>
       </c>
-      <c r="AN24" s="85" t="s">
+      <c r="AN24" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="AO24" s="85" t="s">
+      <c r="AO24" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="AP24" s="85" t="s">
+      <c r="AP24" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="AQ24" s="85" t="s">
+      <c r="AQ24" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="AR24" s="85" t="s">
+      <c r="AR24" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="AS24" s="85" t="s">
+      <c r="AS24" s="79" t="s">
         <v>123</v>
       </c>
       <c r="AT24" s="25"/>
       <c r="AU24" t="s">
         <v>124</v>
       </c>
-      <c r="AW24" s="83" t="s">
+      <c r="AW24" s="77" t="s">
         <v>125</v>
       </c>
-      <c r="AX24" s="87"/>
+      <c r="AX24" s="81"/>
       <c r="AY24" t="s">
         <v>126</v>
       </c>
-      <c r="AZ24" s="84" t="s">
+      <c r="AZ24" s="78" t="s">
         <v>131</v>
       </c>
-      <c r="BB24" s="83" t="s">
+      <c r="BB24" s="77" t="s">
         <v>129</v>
       </c>
-      <c r="BC24" s="87"/>
+      <c r="BC24" s="81"/>
       <c r="BD24" t="s">
         <v>127</v>
       </c>
-      <c r="BE24" s="84" t="s">
+      <c r="BE24" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="BG24" s="83" t="s">
+      <c r="BG24" s="77" t="s">
         <v>130</v>
       </c>
-      <c r="BH24" s="87"/>
+      <c r="BH24" s="81"/>
       <c r="BI24" t="s">
         <v>128</v>
       </c>
@@ -15963,22 +15963,22 @@
       <c r="AM25">
         <v>1</v>
       </c>
-      <c r="AN25" s="85">
-        <v>1</v>
-      </c>
-      <c r="AO25" s="85">
-        <v>1</v>
-      </c>
-      <c r="AP25" s="85">
-        <v>1</v>
-      </c>
-      <c r="AQ25" s="85">
-        <v>1</v>
-      </c>
-      <c r="AR25" s="85">
-        <v>1</v>
-      </c>
-      <c r="AS25" s="85">
+      <c r="AN25" s="79">
+        <v>1</v>
+      </c>
+      <c r="AO25" s="79">
+        <v>1</v>
+      </c>
+      <c r="AP25" s="79">
+        <v>1</v>
+      </c>
+      <c r="AQ25" s="79">
+        <v>1</v>
+      </c>
+      <c r="AR25" s="79">
+        <v>1</v>
+      </c>
+      <c r="AS25" s="79">
         <v>1</v>
       </c>
       <c r="AT25" s="25"/>
@@ -15988,40 +15988,40 @@
       <c r="AV25">
         <v>2</v>
       </c>
-      <c r="AW25" s="83">
-        <v>1</v>
-      </c>
-      <c r="AX25" s="87">
+      <c r="AW25" s="77">
+        <v>1</v>
+      </c>
+      <c r="AX25" s="81">
         <v>2</v>
       </c>
       <c r="AY25">
         <v>1</v>
       </c>
-      <c r="AZ25" s="84">
+      <c r="AZ25" s="78">
         <v>1</v>
       </c>
       <c r="BA25">
         <v>2</v>
       </c>
-      <c r="BB25" s="83">
-        <v>1</v>
-      </c>
-      <c r="BC25" s="87">
+      <c r="BB25" s="77">
+        <v>1</v>
+      </c>
+      <c r="BC25" s="81">
         <v>2</v>
       </c>
       <c r="BD25">
         <v>1</v>
       </c>
-      <c r="BE25" s="84">
+      <c r="BE25" s="78">
         <v>1</v>
       </c>
       <c r="BF25">
         <v>2</v>
       </c>
-      <c r="BG25" s="83">
-        <v>1</v>
-      </c>
-      <c r="BH25" s="87">
+      <c r="BG25" s="77">
+        <v>1</v>
+      </c>
+      <c r="BH25" s="81">
         <v>2</v>
       </c>
       <c r="BI25">
@@ -16067,27 +16067,27 @@
         <f t="array" ref="AM26:AM27">_xlfn.ANCHORARRAY(AK26)*(1-$O$41:$O$42)</f>
         <v>-4.0157752295966798E-2</v>
       </c>
-      <c r="AN26" s="85" cm="1">
+      <c r="AN26" s="79" cm="1">
         <f t="array" ref="AN26:AN27">_xlfn.ANCHORARRAY(AM26)*(1-$R$41:$R$42*$R$41:$R$42)</f>
         <v>-5.5235567156430828E-3</v>
       </c>
-      <c r="AO26" s="85" cm="1">
+      <c r="AO26" s="79" cm="1">
         <f t="array" ref="AO26:AO27">_xlfn.ANCHORARRAY(AK26)*(_xlfn.ANCHORARRAY(T35)-$R$41:$R$42)</f>
         <v>0.10251448797734228</v>
       </c>
-      <c r="AP26" s="85" cm="1">
+      <c r="AP26" s="79" cm="1">
         <f t="array" ref="AP26:AP27">_xlfn.ANCHORARRAY(AO26)*($O$41:$O$42*(1-$O$41:$O$42))</f>
         <v>1.6437466017227093E-2</v>
       </c>
-      <c r="AQ26" s="85" cm="1">
+      <c r="AQ26" s="79" cm="1">
         <f t="array" ref="AQ26:AQ27">MMULT(TRANSPOSE($P$23:$Q$24),_xlfn.ANCHORARRAY(AN26))*_xlfn.ANCHORARRAY(T41)</f>
         <v>-1.9216457549755034E-3</v>
       </c>
-      <c r="AR26" s="85" cm="1">
+      <c r="AR26" s="79" cm="1">
         <f t="array" ref="AR26:AR27">_xlfn.ANCHORARRAY(AQ26)*($L$41:$L$42*(1-$L$41:$L$42))</f>
         <v>-8.3828762785564568E-5</v>
       </c>
-      <c r="AS26" s="85" cm="1">
+      <c r="AS26" s="79" cm="1">
         <f t="array" ref="AS26:AS27">_xlfn.ANCHORARRAY(AK26)*$O$41:$O$42+MMULT(TRANSPOSE($P$23:$Q$24),_xlfn.ANCHORARRAY(AN26))*$L$41:$L$42+MMULT(TRANSPOSE($P$18:$Q$19),_xlfn.ANCHORARRAY(AP26))+MMULT(TRANSPOSE($P$13:$Q$14),_xlfn.ANCHORARRAY(AR26))</f>
         <v>-0.15486594492623409</v>
       </c>
@@ -16099,47 +16099,47 @@
       <c r="AV26">
         <v>-1.0159566207919621E-2</v>
       </c>
-      <c r="AW26" s="83" cm="1">
+      <c r="AW26" s="77" cm="1">
         <f t="array" ref="AW26:AX27">MMULT(_xlfn.ANCHORARRAY(AN26),TRANSPOSE($L$41:$L$42*_xlfn.ANCHORARRAY(T35)))</f>
         <v>-2.1962638925708791E-3</v>
       </c>
-      <c r="AX26" s="87">
+      <c r="AX26" s="81">
         <v>-3.3977790999380384E-3</v>
       </c>
       <c r="AY26" cm="1">
         <f t="array" ref="AY26:AY27">_xlfn.ANCHORARRAY(AN26)</f>
         <v>-5.5235567156430828E-3</v>
       </c>
-      <c r="AZ26" s="84" cm="1">
+      <c r="AZ26" s="78" cm="1">
         <f t="array" ref="AZ26:BA27">MMULT(_xlfn.ANCHORARRAY(AP26),TRANSPOSE($E$14:$E$15))</f>
         <v>5.5541008108119849E-2</v>
       </c>
       <c r="BA26">
         <v>3.0233694137601467E-2</v>
       </c>
-      <c r="BB26" s="83" cm="1">
+      <c r="BB26" s="77" cm="1">
         <f t="array" ref="BB26:BC27">MMULT(_xlfn.ANCHORARRAY(AP26),TRANSPOSE(_xlfn.ANCHORARRAY(T35)))</f>
         <v>6.8489124462661347E-3</v>
       </c>
-      <c r="BC26" s="87">
+      <c r="BC26" s="81">
         <v>1.0688841835681057E-2</v>
       </c>
       <c r="BD26" cm="1">
         <f t="array" ref="BD26:BD27">_xlfn.ANCHORARRAY(AP26)</f>
         <v>1.6437466017227093E-2</v>
       </c>
-      <c r="BE26" s="84" cm="1">
+      <c r="BE26" s="78" cm="1">
         <f t="array" ref="BE26:BF27">MMULT(_xlfn.ANCHORARRAY(AR26),TRANSPOSE($E$14:$E$15))</f>
         <v>-2.8325132284301609E-4</v>
       </c>
       <c r="BF26">
         <v>-1.5418758410427153E-4</v>
       </c>
-      <c r="BG26" s="83" cm="1">
+      <c r="BG26" s="77" cm="1">
         <f t="array" ref="BG26:BH27">MMULT(_xlfn.ANCHORARRAY(AR26),TRANSPOSE(_xlfn.ANCHORARRAY(T35)))</f>
         <v>-3.4928489354467912E-5</v>
       </c>
-      <c r="BH26" s="87">
+      <c r="BH26" s="81">
         <v>-5.4511588693576593E-5</v>
       </c>
       <c r="BI26" cm="1">
@@ -16202,22 +16202,22 @@
       <c r="AM27">
         <v>-0.12330856421514255</v>
       </c>
-      <c r="AN27" s="85">
+      <c r="AN27" s="79">
         <v>-2.3301061059144021E-5</v>
       </c>
-      <c r="AO27" s="85">
+      <c r="AO27" s="79">
         <v>5.6316521331561592E-2</v>
       </c>
-      <c r="AP27" s="85">
+      <c r="AP27" s="79">
         <v>1.0108103518260591E-2</v>
       </c>
-      <c r="AQ27" s="85">
+      <c r="AQ27" s="79">
         <v>-3.7761100167608662E-3</v>
       </c>
-      <c r="AR27" s="85">
+      <c r="AR27" s="79">
         <v>-1.9297654564656705E-4</v>
       </c>
-      <c r="AS27" s="85">
+      <c r="AS27" s="79">
         <v>-2.6648059022153361E-2</v>
       </c>
       <c r="AT27" s="25"/>
@@ -16227,40 +16227,40 @@
       <c r="AV27">
         <v>-4.2858014270899019E-5</v>
       </c>
-      <c r="AW27" s="83">
+      <c r="AW27" s="77">
         <v>-9.2649142024477743E-6</v>
       </c>
-      <c r="AX27" s="87">
+      <c r="AX27" s="81">
         <v>-1.433349241240153E-5</v>
       </c>
       <c r="AY27">
         <v>-2.3301061059144021E-5</v>
       </c>
-      <c r="AZ27" s="84">
+      <c r="AZ27" s="78">
         <v>3.4154550274175029E-2</v>
       </c>
       <c r="BA27">
         <v>1.8591996464784655E-2</v>
       </c>
-      <c r="BB27" s="83">
+      <c r="BB27" s="77">
         <v>4.2116902886251617E-3</v>
       </c>
-      <c r="BC27" s="87">
+      <c r="BC27" s="81">
         <v>6.5730277192448359E-3</v>
       </c>
       <c r="BD27">
         <v>1.0108103518260591E-2</v>
       </c>
-      <c r="BE27" s="84">
+      <c r="BE27" s="78">
         <v>-6.5205378220705974E-4</v>
       </c>
       <c r="BF27">
         <v>-3.5494484677227794E-4</v>
       </c>
-      <c r="BG27" s="83">
+      <c r="BG27" s="77">
         <v>-8.0406521536290773E-5</v>
       </c>
-      <c r="BH27" s="87">
+      <c r="BH27" s="81">
         <v>-1.2548745483339444E-4</v>
       </c>
       <c r="BI27">
@@ -16323,21 +16323,21 @@
       </c>
       <c r="AK28" s="25"/>
       <c r="AL28" s="25"/>
-      <c r="AN28" s="85"/>
-      <c r="AO28" s="85"/>
-      <c r="AP28" s="85"/>
-      <c r="AQ28" s="85"/>
-      <c r="AR28" s="85"/>
-      <c r="AS28" s="85"/>
+      <c r="AN28" s="79"/>
+      <c r="AO28" s="79"/>
+      <c r="AP28" s="79"/>
+      <c r="AQ28" s="79"/>
+      <c r="AR28" s="79"/>
+      <c r="AS28" s="79"/>
       <c r="AT28" s="25"/>
-      <c r="AW28" s="83"/>
-      <c r="AX28" s="87"/>
-      <c r="AZ28" s="84"/>
-      <c r="BB28" s="83"/>
-      <c r="BC28" s="87"/>
-      <c r="BE28" s="84"/>
-      <c r="BG28" s="83"/>
-      <c r="BH28" s="87"/>
+      <c r="AW28" s="77"/>
+      <c r="AX28" s="81"/>
+      <c r="AZ28" s="78"/>
+      <c r="BB28" s="77"/>
+      <c r="BC28" s="81"/>
+      <c r="BE28" s="78"/>
+      <c r="BG28" s="77"/>
+      <c r="BH28" s="81"/>
       <c r="BK28" s="9">
         <v>5</v>
       </c>
@@ -16407,24 +16407,24 @@
         <v>112</v>
       </c>
       <c r="AL29" s="25"/>
-      <c r="AN29" s="85"/>
-      <c r="AO29" s="85"/>
-      <c r="AP29" s="85"/>
-      <c r="AQ29" s="85"/>
-      <c r="AR29" s="85"/>
-      <c r="AS29" s="85"/>
+      <c r="AN29" s="79"/>
+      <c r="AO29" s="79"/>
+      <c r="AP29" s="79"/>
+      <c r="AQ29" s="79"/>
+      <c r="AR29" s="79"/>
+      <c r="AS29" s="79"/>
       <c r="AT29" s="25"/>
       <c r="AU29" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="AW29" s="83"/>
-      <c r="AX29" s="87"/>
-      <c r="AZ29" s="84"/>
-      <c r="BB29" s="83"/>
-      <c r="BC29" s="87"/>
-      <c r="BE29" s="84"/>
-      <c r="BG29" s="83"/>
-      <c r="BH29" s="87"/>
+      <c r="AW29" s="77"/>
+      <c r="AX29" s="81"/>
+      <c r="AZ29" s="78"/>
+      <c r="BB29" s="77"/>
+      <c r="BC29" s="81"/>
+      <c r="BE29" s="78"/>
+      <c r="BG29" s="77"/>
+      <c r="BH29" s="81"/>
     </row>
     <row r="30" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J30">
@@ -16478,52 +16478,52 @@
       <c r="AM30" t="s">
         <v>113</v>
       </c>
-      <c r="AN30" s="85" t="s">
+      <c r="AN30" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="AO30" s="85" t="s">
+      <c r="AO30" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="AP30" s="85" t="s">
+      <c r="AP30" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="AQ30" s="85" t="s">
+      <c r="AQ30" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="AR30" s="85" t="s">
+      <c r="AR30" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="AS30" s="85" t="s">
+      <c r="AS30" s="79" t="s">
         <v>123</v>
       </c>
       <c r="AT30" s="25"/>
       <c r="AU30" t="s">
         <v>124</v>
       </c>
-      <c r="AW30" s="83" t="s">
+      <c r="AW30" s="77" t="s">
         <v>125</v>
       </c>
-      <c r="AX30" s="87"/>
+      <c r="AX30" s="81"/>
       <c r="AY30" t="s">
         <v>126</v>
       </c>
-      <c r="AZ30" s="84" t="s">
+      <c r="AZ30" s="78" t="s">
         <v>131</v>
       </c>
-      <c r="BB30" s="83" t="s">
+      <c r="BB30" s="77" t="s">
         <v>129</v>
       </c>
-      <c r="BC30" s="87"/>
+      <c r="BC30" s="81"/>
       <c r="BD30" t="s">
         <v>127</v>
       </c>
-      <c r="BE30" s="84" t="s">
+      <c r="BE30" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="BG30" s="83" t="s">
+      <c r="BG30" s="77" t="s">
         <v>130</v>
       </c>
-      <c r="BH30" s="87"/>
+      <c r="BH30" s="81"/>
       <c r="BI30" t="s">
         <v>128</v>
       </c>
@@ -16543,22 +16543,22 @@
       <c r="AM31">
         <v>1</v>
       </c>
-      <c r="AN31" s="85">
-        <v>1</v>
-      </c>
-      <c r="AO31" s="85">
-        <v>1</v>
-      </c>
-      <c r="AP31" s="85">
-        <v>1</v>
-      </c>
-      <c r="AQ31" s="85">
-        <v>1</v>
-      </c>
-      <c r="AR31" s="85">
-        <v>1</v>
-      </c>
-      <c r="AS31" s="85">
+      <c r="AN31" s="79">
+        <v>1</v>
+      </c>
+      <c r="AO31" s="79">
+        <v>1</v>
+      </c>
+      <c r="AP31" s="79">
+        <v>1</v>
+      </c>
+      <c r="AQ31" s="79">
+        <v>1</v>
+      </c>
+      <c r="AR31" s="79">
+        <v>1</v>
+      </c>
+      <c r="AS31" s="79">
         <v>1</v>
       </c>
       <c r="AT31" s="25"/>
@@ -16568,40 +16568,40 @@
       <c r="AV31">
         <v>2</v>
       </c>
-      <c r="AW31" s="83">
-        <v>1</v>
-      </c>
-      <c r="AX31" s="87">
+      <c r="AW31" s="77">
+        <v>1</v>
+      </c>
+      <c r="AX31" s="81">
         <v>2</v>
       </c>
       <c r="AY31">
         <v>1</v>
       </c>
-      <c r="AZ31" s="84">
+      <c r="AZ31" s="78">
         <v>1</v>
       </c>
       <c r="BA31">
         <v>2</v>
       </c>
-      <c r="BB31" s="83">
-        <v>1</v>
-      </c>
-      <c r="BC31" s="87">
+      <c r="BB31" s="77">
+        <v>1</v>
+      </c>
+      <c r="BC31" s="81">
         <v>2</v>
       </c>
       <c r="BD31">
         <v>1</v>
       </c>
-      <c r="BE31" s="84">
+      <c r="BE31" s="78">
         <v>1</v>
       </c>
       <c r="BF31">
         <v>2</v>
       </c>
-      <c r="BG31" s="83">
-        <v>1</v>
-      </c>
-      <c r="BH31" s="87">
+      <c r="BG31" s="77">
+        <v>1</v>
+      </c>
+      <c r="BH31" s="81">
         <v>2</v>
       </c>
       <c r="BI31">
@@ -16639,27 +16639,27 @@
         <f t="array" ref="AM32:AM33">_xlfn.ANCHORARRAY(AK32)*(1-$O$35:$O$36)</f>
         <v>-7.9838559221756991E-2</v>
       </c>
-      <c r="AN32" s="85" cm="1">
+      <c r="AN32" s="79" cm="1">
         <f t="array" ref="AN32:AN33">_xlfn.ANCHORARRAY(AM32)*(1-$R$35:$R$36*$R$35:$R$36)</f>
         <v>-6.1543184725528985E-2</v>
       </c>
-      <c r="AO32" s="85" cm="1">
+      <c r="AO32" s="79" cm="1">
         <f t="array" ref="AO32:AO33">_xlfn.ANCHORARRAY(AK32)*(_xlfn.ANCHORARRAY(T29)-$R$35:$R$36)</f>
         <v>2.2677441107102819E-2</v>
       </c>
-      <c r="AP32" s="85" cm="1">
+      <c r="AP32" s="79" cm="1">
         <f t="array" ref="AP32:AP33">_xlfn.ANCHORARRAY(AO32)*($O$35:$O$36*(1-$O$35:$O$36))</f>
         <v>4.9528834022813228E-3</v>
       </c>
-      <c r="AQ32" s="85" cm="1">
+      <c r="AQ32" s="79" cm="1">
         <f t="array" ref="AQ32:AQ33">MMULT(TRANSPOSE($P$23:$Q$24),_xlfn.ANCHORARRAY(AN32))*_xlfn.ANCHORARRAY(T29)</f>
         <v>-1.6074689272760907E-2</v>
       </c>
-      <c r="AR32" s="85" cm="1">
+      <c r="AR32" s="79" cm="1">
         <f t="array" ref="AR32:AR33">_xlfn.ANCHORARRAY(AQ32)*($L$35:$L$36*(1-$L$35:$L$36))</f>
         <v>-5.0874302401144591E-4</v>
       </c>
-      <c r="AS32" s="85" cm="1">
+      <c r="AS32" s="79" cm="1">
         <f t="array" ref="AS32:AS33">_xlfn.ANCHORARRAY(AK32)*$O$35:$O$36+MMULT(TRANSPOSE($P$23:$Q$24),_xlfn.ANCHORARRAY(AN32))*$L$35:$L$36+MMULT(TRANSPOSE($P$18:$Q$19),_xlfn.ANCHORARRAY(AP32))+MMULT(TRANSPOSE($P$13:$Q$14),_xlfn.ANCHORARRAY(AR32))</f>
         <v>-0.24986384386875077</v>
       </c>
@@ -16671,47 +16671,47 @@
       <c r="AV32">
         <v>-5.1355427603056399E-2</v>
       </c>
-      <c r="AW32" s="83" cm="1">
+      <c r="AW32" s="77" cm="1">
         <f t="array" ref="AW32:AX33">MMULT(_xlfn.ANCHORARRAY(AN32),TRANSPOSE($L$35:$L$36*_xlfn.ANCHORARRAY(T29)))</f>
         <v>-2.3047934728207792E-2</v>
       </c>
-      <c r="AX32" s="87">
+      <c r="AX32" s="81">
         <v>-1.1315831465269259E-2</v>
       </c>
       <c r="AY32" cm="1">
         <f t="array" ref="AY32:AY33">_xlfn.ANCHORARRAY(AN32)</f>
         <v>-6.1543184725528985E-2</v>
       </c>
-      <c r="AZ32" s="84" cm="1">
+      <c r="AZ32" s="78" cm="1">
         <f t="array" ref="AZ32:BA33">MMULT(_xlfn.ANCHORARRAY(AP32),TRANSPOSE($D$14:$D$15))</f>
         <v>1.5729244508890169E-2</v>
       </c>
       <c r="BA32">
         <v>4.1329912666467367E-3</v>
       </c>
-      <c r="BB32" s="83" cm="1">
+      <c r="BB32" s="77" cm="1">
         <f t="array" ref="BB32:BC33">MMULT(_xlfn.ANCHORARRAY(AP32),TRANSPOSE(_xlfn.ANCHORARRAY(T29)))</f>
         <v>1.9175981772813168E-3</v>
       </c>
-      <c r="BC32" s="87">
+      <c r="BC32" s="81">
         <v>1.0670383871815192E-3</v>
       </c>
       <c r="BD32" cm="1">
         <f t="array" ref="BD32:BD33">_xlfn.ANCHORARRAY(AP32)</f>
         <v>4.9528834022813228E-3</v>
       </c>
-      <c r="BE32" s="84" cm="1">
+      <c r="BE32" s="78" cm="1">
         <f t="array" ref="BE32:BF33">MMULT(_xlfn.ANCHORARRAY(AR32),TRANSPOSE($D$14:$D$15))</f>
         <v>-1.615653502600604E-3</v>
       </c>
       <c r="BF32">
         <v>-4.2452654432330772E-4</v>
       </c>
-      <c r="BG32" s="83" cm="1">
+      <c r="BG32" s="77" cm="1">
         <f t="array" ref="BG32:BH33">MMULT(_xlfn.ANCHORARRAY(AR32),TRANSPOSE(_xlfn.ANCHORARRAY(T29)))</f>
         <v>-1.9696904132642895E-4</v>
       </c>
-      <c r="BH32" s="87">
+      <c r="BH32" s="81">
         <v>-1.0960248641851401E-4</v>
       </c>
       <c r="BI32" cm="1">
@@ -16777,22 +16777,22 @@
       <c r="AM33">
         <v>0.13760720939036664</v>
       </c>
-      <c r="AN33" s="85">
+      <c r="AN33" s="79">
         <v>3.1876997045577205E-4</v>
       </c>
-      <c r="AO33" s="85">
+      <c r="AO33" s="79">
         <v>-0.19421696340672884</v>
       </c>
-      <c r="AP33" s="85">
+      <c r="AP33" s="79">
         <v>-4.7965466595473946E-2</v>
       </c>
-      <c r="AQ33" s="85">
+      <c r="AQ33" s="79">
         <v>-9.7635289342273869E-3</v>
       </c>
-      <c r="AR33" s="85">
+      <c r="AR33" s="79">
         <v>-1.2210668864400408E-3</v>
       </c>
-      <c r="AS33" s="85">
+      <c r="AS33" s="79">
         <v>8.3374751570801237E-2</v>
       </c>
       <c r="AT33" s="25"/>
@@ -16802,40 +16802,40 @@
       <c r="AV33">
         <v>2.6600131619414045E-4</v>
       </c>
-      <c r="AW33" s="83">
+      <c r="AW33" s="77">
         <v>1.1937941634225708E-4</v>
       </c>
-      <c r="AX33" s="87">
+      <c r="AX33" s="81">
         <v>5.8611644456710767E-5</v>
       </c>
       <c r="AY33">
         <v>3.1876997045577205E-4</v>
       </c>
-      <c r="AZ33" s="84">
+      <c r="AZ33" s="78">
         <v>-0.15232754151161829</v>
       </c>
       <c r="BA33">
         <v>-4.0025342500172499E-2</v>
       </c>
-      <c r="BB33" s="83">
+      <c r="BB33" s="77">
         <v>-1.8570695864466136E-2</v>
       </c>
-      <c r="BC33" s="87">
+      <c r="BC33" s="81">
         <v>-1.0333575406372243E-2</v>
       </c>
       <c r="BD33">
         <v>-4.7965466595473946E-2</v>
       </c>
-      <c r="BE33" s="84">
+      <c r="BE33" s="78">
         <v>-3.8778339925543241E-3</v>
       </c>
       <c r="BF33">
         <v>-1.0189334914130414E-3</v>
       </c>
-      <c r="BG33" s="83">
+      <c r="BG33" s="77">
         <v>-4.7275807758718504E-4</v>
       </c>
-      <c r="BH33" s="87">
+      <c r="BH33" s="81">
         <v>-2.6306398421323761E-4</v>
       </c>
       <c r="BI33">
@@ -16896,21 +16896,21 @@
       </c>
       <c r="AK34" s="25"/>
       <c r="AL34" s="25"/>
-      <c r="AN34" s="85"/>
-      <c r="AO34" s="85"/>
-      <c r="AP34" s="85"/>
-      <c r="AQ34" s="85"/>
-      <c r="AR34" s="85"/>
-      <c r="AS34" s="85"/>
+      <c r="AN34" s="79"/>
+      <c r="AO34" s="79"/>
+      <c r="AP34" s="79"/>
+      <c r="AQ34" s="79"/>
+      <c r="AR34" s="79"/>
+      <c r="AS34" s="79"/>
       <c r="AT34" s="25"/>
-      <c r="AW34" s="83"/>
-      <c r="AX34" s="87"/>
-      <c r="AZ34" s="84"/>
-      <c r="BB34" s="83"/>
-      <c r="BC34" s="87"/>
-      <c r="BE34" s="84"/>
-      <c r="BG34" s="83"/>
-      <c r="BH34" s="87"/>
+      <c r="AW34" s="77"/>
+      <c r="AX34" s="81"/>
+      <c r="AZ34" s="78"/>
+      <c r="BB34" s="77"/>
+      <c r="BC34" s="81"/>
+      <c r="BE34" s="78"/>
+      <c r="BG34" s="77"/>
+      <c r="BH34" s="81"/>
       <c r="BL34">
         <v>1</v>
       </c>
@@ -16977,24 +16977,24 @@
         <v>105</v>
       </c>
       <c r="AL35" s="25"/>
-      <c r="AN35" s="85"/>
-      <c r="AO35" s="85"/>
-      <c r="AP35" s="85"/>
-      <c r="AQ35" s="85"/>
-      <c r="AR35" s="85"/>
-      <c r="AS35" s="85"/>
+      <c r="AN35" s="79"/>
+      <c r="AO35" s="79"/>
+      <c r="AP35" s="79"/>
+      <c r="AQ35" s="79"/>
+      <c r="AR35" s="79"/>
+      <c r="AS35" s="79"/>
       <c r="AT35" s="25"/>
       <c r="AU35" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="AW35" s="83"/>
-      <c r="AX35" s="87"/>
-      <c r="AZ35" s="84"/>
-      <c r="BB35" s="83"/>
-      <c r="BC35" s="87"/>
-      <c r="BE35" s="84"/>
-      <c r="BG35" s="83"/>
-      <c r="BH35" s="87"/>
+      <c r="AW35" s="77"/>
+      <c r="AX35" s="81"/>
+      <c r="AZ35" s="78"/>
+      <c r="BB35" s="77"/>
+      <c r="BC35" s="81"/>
+      <c r="BE35" s="78"/>
+      <c r="BG35" s="77"/>
+      <c r="BH35" s="81"/>
       <c r="BK35">
         <v>1</v>
       </c>
@@ -17064,52 +17064,52 @@
       <c r="AM36" t="s">
         <v>113</v>
       </c>
-      <c r="AN36" s="85" t="s">
+      <c r="AN36" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="AO36" s="85" t="s">
+      <c r="AO36" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="AP36" s="85" t="s">
+      <c r="AP36" s="79" t="s">
         <v>116</v>
       </c>
-      <c r="AQ36" s="85" t="s">
+      <c r="AQ36" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="AR36" s="85" t="s">
+      <c r="AR36" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="AS36" s="86" t="s">
+      <c r="AS36" s="80" t="s">
         <v>123</v>
       </c>
       <c r="AT36" s="25"/>
       <c r="AU36" t="s">
         <v>124</v>
       </c>
-      <c r="AW36" s="83" t="s">
+      <c r="AW36" s="77" t="s">
         <v>125</v>
       </c>
-      <c r="AX36" s="87"/>
+      <c r="AX36" s="81"/>
       <c r="AY36" t="s">
         <v>126</v>
       </c>
-      <c r="AZ36" s="84" t="s">
+      <c r="AZ36" s="78" t="s">
         <v>131</v>
       </c>
-      <c r="BB36" s="83" t="s">
+      <c r="BB36" s="77" t="s">
         <v>129</v>
       </c>
-      <c r="BC36" s="87"/>
+      <c r="BC36" s="81"/>
       <c r="BD36" t="s">
         <v>127</v>
       </c>
-      <c r="BE36" s="84" t="s">
+      <c r="BE36" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="BG36" s="83" t="s">
+      <c r="BG36" s="77" t="s">
         <v>130</v>
       </c>
-      <c r="BH36" s="87"/>
+      <c r="BH36" s="81"/>
       <c r="BI36" t="s">
         <v>128</v>
       </c>
@@ -17145,22 +17145,22 @@
       <c r="AM37">
         <v>1</v>
       </c>
-      <c r="AN37" s="85">
-        <v>1</v>
-      </c>
-      <c r="AO37" s="85">
-        <v>1</v>
-      </c>
-      <c r="AP37" s="85">
-        <v>1</v>
-      </c>
-      <c r="AQ37" s="85">
-        <v>1</v>
-      </c>
-      <c r="AR37" s="85">
-        <v>1</v>
-      </c>
-      <c r="AS37" s="86">
+      <c r="AN37" s="79">
+        <v>1</v>
+      </c>
+      <c r="AO37" s="79">
+        <v>1</v>
+      </c>
+      <c r="AP37" s="79">
+        <v>1</v>
+      </c>
+      <c r="AQ37" s="79">
+        <v>1</v>
+      </c>
+      <c r="AR37" s="79">
+        <v>1</v>
+      </c>
+      <c r="AS37" s="80">
         <v>1</v>
       </c>
       <c r="AT37" s="25"/>
@@ -17170,40 +17170,40 @@
       <c r="AV37">
         <v>2</v>
       </c>
-      <c r="AW37" s="83">
-        <v>1</v>
-      </c>
-      <c r="AX37" s="87">
+      <c r="AW37" s="77">
+        <v>1</v>
+      </c>
+      <c r="AX37" s="81">
         <v>2</v>
       </c>
       <c r="AY37">
         <v>1</v>
       </c>
-      <c r="AZ37" s="84">
+      <c r="AZ37" s="78">
         <v>1</v>
       </c>
       <c r="BA37">
         <v>2</v>
       </c>
-      <c r="BB37" s="83">
-        <v>1</v>
-      </c>
-      <c r="BC37" s="87">
+      <c r="BB37" s="77">
+        <v>1</v>
+      </c>
+      <c r="BC37" s="81">
         <v>2</v>
       </c>
       <c r="BD37">
         <v>1</v>
       </c>
-      <c r="BE37" s="84">
+      <c r="BE37" s="78">
         <v>1</v>
       </c>
       <c r="BF37">
         <v>2</v>
       </c>
-      <c r="BG37" s="83">
-        <v>1</v>
-      </c>
-      <c r="BH37" s="87">
+      <c r="BG37" s="77">
+        <v>1</v>
+      </c>
+      <c r="BH37" s="81">
         <v>2</v>
       </c>
       <c r="BI37">
@@ -17249,27 +17249,27 @@
         <f t="array" ref="AM38:AM39">_xlfn.ANCHORARRAY(AK38)*(1-$O$29:$O$30)</f>
         <v>-0.32200517746869323</v>
       </c>
-      <c r="AN38" s="85" cm="1">
+      <c r="AN38" s="79" cm="1">
         <f t="array" ref="AN38:AN39">_xlfn.ANCHORARRAY(AM38)*(1-$R$29:$R$30*$R$29:$R$30)</f>
         <v>-0.3165680204831281</v>
       </c>
-      <c r="AO38" s="85" cm="1">
+      <c r="AO38" s="79" cm="1">
         <f t="array" ref="AO38:AO39">_xlfn.ANCHORARRAY(AK38)*(L7:L8-$R$29:$R$30)</f>
         <v>-0.35118945644240018</v>
       </c>
-      <c r="AP38" s="85" cm="1">
+      <c r="AP38" s="79" cm="1">
         <f t="array" ref="AP38:AP39">_xlfn.ANCHORARRAY(AO38)*($O$29:$O$30*(1-$O$29:$O$30))</f>
         <v>-8.2827639773356512E-2</v>
       </c>
-      <c r="AQ38" s="85" cm="1">
+      <c r="AQ38" s="79" cm="1">
         <f t="array" ref="AQ38:AQ39">MMULT(TRANSPOSE($P$23:$Q$24),_xlfn.ANCHORARRAY(AN38))*$L$7:$L$8</f>
         <v>-0.1713453958113591</v>
       </c>
-      <c r="AR38" s="85" cm="1">
+      <c r="AR38" s="79" cm="1">
         <f t="array" ref="AR38:AR39">_xlfn.ANCHORARRAY(AQ38)*($L$29:$L$30*(1-$L$29:$L$30))</f>
         <v>-1.1525797189335389E-3</v>
       </c>
-      <c r="AS38" s="86" cm="1">
+      <c r="AS38" s="80" cm="1">
         <f t="array" ref="AS38:AS39">_xlfn.ANCHORARRAY(AK38)*$O$29:$O$30+MMULT(TRANSPOSE($P$23:$Q$24),_xlfn.ANCHORARRAY(AN38))*$L$29:$L$30+MMULT(TRANSPOSE($P$18:$Q$19),_xlfn.ANCHORARRAY(AP38))+MMULT(TRANSPOSE($P$13:$Q$14),_xlfn.ANCHORARRAY(AR38))</f>
         <v>-0.46671760958528241</v>
       </c>
@@ -17281,47 +17281,47 @@
       <c r="AV38">
         <v>-0.45148431759973812</v>
       </c>
-      <c r="AW38" s="83" cm="1">
+      <c r="AW38" s="77" cm="1">
         <f t="array" ref="AW38:AX39">MMULT(_xlfn.ANCHORARRAY(AN38),TRANSPOSE($L$29:$L$30*L7:L8))</f>
         <v>-0.25311136802835993</v>
       </c>
-      <c r="AX38" s="87">
+      <c r="AX38" s="81">
         <v>0.27098505005070261</v>
       </c>
       <c r="AY38" cm="1">
         <f t="array" ref="AY38:AY39">_xlfn.ANCHORARRAY(AN38)</f>
         <v>-0.3165680204831281</v>
       </c>
-      <c r="AZ38" s="84" cm="1">
+      <c r="AZ38" s="78" cm="1">
         <f t="array" ref="AZ38:BA39">MMULT(_xlfn.ANCHORARRAY(AP38),TRANSPOSE($C$14:$C$15))</f>
         <v>-0.33376786288625365</v>
       </c>
       <c r="BA38">
         <v>-0.11812747340808491</v>
       </c>
-      <c r="BB38" s="83" cm="1">
+      <c r="BB38" s="77" cm="1">
         <f t="array" ref="BB38:BC39">MMULT(_xlfn.ANCHORARRAY(AP38),TRANSPOSE(L7:L8))</f>
         <v>-6.6676250017551994E-2</v>
       </c>
-      <c r="BC38" s="87">
+      <c r="BC38" s="81">
         <v>8.0922604058569311E-2</v>
       </c>
       <c r="BD38" cm="1">
         <f t="array" ref="BD38:BD39">_xlfn.ANCHORARRAY(AP38)</f>
         <v>-8.2827639773356512E-2</v>
       </c>
-      <c r="BE38" s="84" cm="1">
+      <c r="BE38" s="78" cm="1">
         <f t="array" ref="BE38:BF39">MMULT(_xlfn.ANCHORARRAY(AR38),TRANSPOSE($C$14:$C$15))</f>
         <v>-4.644513240352313E-3</v>
       </c>
       <c r="BF38">
         <v>-1.6437910155543986E-3</v>
       </c>
-      <c r="BG38" s="83" cm="1">
+      <c r="BG38" s="77" cm="1">
         <f t="array" ref="BG38:BH39">MMULT(_xlfn.ANCHORARRAY(AR38),TRANSPOSE(L7:L8))</f>
         <v>-9.2782667374149887E-4</v>
       </c>
-      <c r="BH38" s="87">
+      <c r="BH38" s="81">
         <v>1.1260703853980675E-3</v>
       </c>
       <c r="BI38" cm="1">
@@ -17385,22 +17385,22 @@
       <c r="AM39">
         <v>7.7345353630166355E-2</v>
       </c>
-      <c r="AN39" s="85">
+      <c r="AN39" s="79">
         <v>2.3217673271367311E-4</v>
       </c>
-      <c r="AO39" s="85">
+      <c r="AO39" s="79">
         <v>-0.25313468721999938</v>
       </c>
-      <c r="AP39" s="85">
+      <c r="AP39" s="79">
         <v>-6.0566063886024535E-2</v>
       </c>
-      <c r="AQ39" s="85">
+      <c r="AQ39" s="79">
         <v>0.22897952293383958</v>
       </c>
-      <c r="AR39" s="85">
+      <c r="AR39" s="79">
         <v>2.4845008821427306E-2</v>
       </c>
-      <c r="AS39" s="86">
+      <c r="AS39" s="80">
         <v>-0.22154785483655021</v>
       </c>
       <c r="AT39" s="25"/>
@@ -17410,40 +17410,40 @@
       <c r="AV39">
         <v>3.3112679408296784E-4</v>
       </c>
-      <c r="AW39" s="83">
+      <c r="AW39" s="77">
         <v>1.8563647190839578E-4</v>
       </c>
-      <c r="AX39" s="87">
+      <c r="AX39" s="81">
         <v>-1.9874535475505024E-4</v>
       </c>
       <c r="AY39">
         <v>2.3217673271367311E-4</v>
       </c>
-      <c r="AZ39" s="84">
+      <c r="AZ39" s="78">
         <v>-0.24406111005922149</v>
       </c>
       <c r="BA39">
         <v>-8.6378365008417821E-2</v>
       </c>
-      <c r="BB39" s="83">
+      <c r="BB39" s="77">
         <v>-4.875568142824975E-2</v>
       </c>
-      <c r="BC39" s="87">
+      <c r="BC39" s="81">
         <v>5.9173044416645969E-2</v>
       </c>
       <c r="BD39">
         <v>-6.0566063886024535E-2</v>
       </c>
-      <c r="BE39" s="84">
+      <c r="BE39" s="78">
         <v>0.10011712902128814</v>
       </c>
       <c r="BF39">
         <v>3.5433559701901138E-2</v>
       </c>
-      <c r="BG39" s="83">
+      <c r="BG39" s="77">
         <v>2.0000232101248981E-2</v>
       </c>
-      <c r="BH39" s="87">
+      <c r="BH39" s="81">
         <v>-2.4273573618534477E-2</v>
       </c>
       <c r="BI39">
@@ -17723,63 +17723,63 @@
         <v>1</v>
       </c>
       <c r="AU44">
-        <f>SUM(AU8,AU14,AU20,AU26,AU32,AU38)</f>
+        <f t="shared" ref="AU44:BI44" si="10">SUM(AU8,AU14,AU20,AU26,AU32,AU38)</f>
         <v>-1.4910344327143772</v>
       </c>
       <c r="AV44" s="8">
-        <f>SUM(AV8,AV14,AV20,AV26,AV32,AV38)</f>
+        <f t="shared" si="10"/>
         <v>-0.51343297634823404</v>
       </c>
       <c r="AW44" s="7">
-        <f>SUM(AW8,AW14,AW20,AW26,AW32,AW38)</f>
+        <f t="shared" si="10"/>
         <v>-0.27876008416782827</v>
       </c>
       <c r="AX44" s="8">
-        <f>SUM(AX8,AX14,AX20,AX26,AX32,AX38)</f>
+        <f t="shared" si="10"/>
         <v>0.25550057394328141</v>
       </c>
       <c r="AY44" s="19">
-        <f>SUM(AY8,AY14,AY20,AY26,AY32,AY38)</f>
+        <f t="shared" si="10"/>
         <v>-0.38465933347710057</v>
       </c>
       <c r="AZ44" s="7">
-        <f>SUM(AZ8,AZ14,AZ20,AZ26,AZ32,AZ38)</f>
+        <f t="shared" si="10"/>
         <v>-0.25957112660987597</v>
       </c>
       <c r="BA44" s="8">
-        <f>SUM(BA8,BA14,BA20,BA26,BA32,BA38)</f>
+        <f t="shared" si="10"/>
         <v>-8.295767816164043E-2</v>
       </c>
       <c r="BB44" s="7">
-        <f>SUM(BB8,BB14,BB20,BB26,BB32,BB38)</f>
+        <f t="shared" si="10"/>
         <v>-5.6882677977589682E-2</v>
       </c>
       <c r="BC44" s="8">
-        <f>SUM(BC8,BC14,BC20,BC26,BC32,BC38)</f>
+        <f t="shared" si="10"/>
         <v>9.4375880463087591E-2</v>
       </c>
       <c r="BD44" s="19">
-        <f>SUM(BD8,BD14,BD20,BD26,BD32,BD38)</f>
+        <f t="shared" si="10"/>
         <v>-5.9642711115416809E-2</v>
       </c>
       <c r="BE44" s="7">
-        <f>SUM(BE8,BE14,BE20,BE26,BE32,BE38)</f>
+        <f t="shared" si="10"/>
         <v>-6.6957854728141135E-3</v>
       </c>
       <c r="BF44" s="8">
-        <f>SUM(BF8,BF14,BF20,BF26,BF32,BF38)</f>
+        <f t="shared" si="10"/>
         <v>-2.2648951820017607E-3</v>
       </c>
       <c r="BG44" s="7">
-        <f>SUM(BG8,BG14,BG20,BG26,BG32,BG38)</f>
+        <f t="shared" si="10"/>
         <v>-1.2115156737069533E-3</v>
       </c>
       <c r="BH44" s="8">
-        <f>SUM(BH8,BH14,BH20,BH26,BH32,BH38)</f>
+        <f t="shared" si="10"/>
         <v>8.7003177473824974E-4</v>
       </c>
       <c r="BI44" s="19">
-        <f>SUM(BI8,BI14,BI20,BI26,BI32,BI38)</f>
+        <f t="shared" si="10"/>
         <v>-1.8451706008308661E-3</v>
       </c>
       <c r="BK44" s="7">
@@ -17842,63 +17842,63 @@
         <v>2</v>
       </c>
       <c r="AU45" s="14">
-        <f>SUM(AU9,AU15,AU21,AU27,AU33,AU39)</f>
+        <f t="shared" ref="AU45:BI45" si="11">SUM(AU9,AU15,AU21,AU27,AU33,AU39)</f>
         <v>3.1289566057609718E-3</v>
       </c>
       <c r="AV45" s="11">
-        <f>SUM(AV9,AV15,AV21,AV27,AV33,AV39)</f>
+        <f t="shared" si="11"/>
         <v>9.1608050618298528E-4</v>
       </c>
       <c r="AW45" s="9">
-        <f>SUM(AW9,AW15,AW21,AW27,AW33,AW39)</f>
+        <f t="shared" si="11"/>
         <v>5.878724081096494E-4</v>
       </c>
       <c r="AX45" s="11">
-        <f>SUM(AX9,AX15,AX21,AX27,AX33,AX39)</f>
+        <f t="shared" si="11"/>
         <v>3.8140036526671114E-4</v>
       </c>
       <c r="AY45" s="20">
-        <f>SUM(AY9,AY15,AY21,AY27,AY33,AY39)</f>
+        <f t="shared" si="11"/>
         <v>1.2235890103785372E-3</v>
       </c>
       <c r="AZ45" s="9">
-        <f>SUM(AZ9,AZ15,AZ21,AZ27,AZ33,AZ39)</f>
+        <f t="shared" si="11"/>
         <v>-0.37501325198167101</v>
       </c>
       <c r="BA45" s="11">
-        <f>SUM(BA9,BA15,BA21,BA27,BA33,BA39)</f>
+        <f t="shared" si="11"/>
         <v>-0.11133128401468868</v>
       </c>
       <c r="BB45" s="9">
-        <f>SUM(BB9,BB15,BB21,BB27,BB33,BB39)</f>
+        <f t="shared" si="11"/>
         <v>-6.5585165364152931E-2</v>
       </c>
       <c r="BC45" s="11">
-        <f>SUM(BC9,BC15,BC21,BC27,BC33,BC39)</f>
+        <f t="shared" si="11"/>
         <v>5.10061635174828E-2</v>
       </c>
       <c r="BD45" s="20">
-        <f>SUM(BD9,BD15,BD21,BD27,BD33,BD39)</f>
+        <f t="shared" si="11"/>
         <v>-0.103030880974427</v>
       </c>
       <c r="BE45" s="9">
-        <f>SUM(BE9,BE15,BE21,BE27,BE33,BE39)</f>
+        <f t="shared" si="11"/>
         <v>9.5600290374178276E-2</v>
       </c>
       <c r="BF45" s="11">
-        <f>SUM(BF9,BF15,BF21,BF27,BF33,BF39)</f>
+        <f t="shared" si="11"/>
         <v>3.4055321811174613E-2</v>
       </c>
       <c r="BG45" s="9">
-        <f>SUM(BG9,BG15,BG21,BG27,BG33,BG39)</f>
+        <f t="shared" si="11"/>
         <v>1.943543100606971E-2</v>
       </c>
       <c r="BH45" s="11">
-        <f>SUM(BH9,BH15,BH21,BH27,BH33,BH39)</f>
+        <f t="shared" si="11"/>
         <v>-2.4683209081415469E-2</v>
       </c>
       <c r="BI45" s="20">
-        <f>SUM(BI9,BI15,BI21,BI27,BI33,BI39)</f>
+        <f t="shared" si="11"/>
         <v>2.3407343351347372E-2</v>
       </c>
       <c r="BK45" s="7">
@@ -18216,11 +18216,11 @@
         <v>1</v>
       </c>
       <c r="AE52">
-        <f t="shared" ref="AE52:AF57" si="10">$AE34*1/$AG$51</f>
+        <f t="shared" ref="AE52:AF57" si="12">$AE34*1/$AG$51</f>
         <v>4.4762402714626649E-2</v>
       </c>
       <c r="AF52">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>4.4762402714626649E-2</v>
       </c>
     </row>
@@ -18260,11 +18260,11 @@
         <v>2</v>
       </c>
       <c r="AE53">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-9.2885791296650491E-2</v>
       </c>
       <c r="AF53">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-9.2885791296650491E-2</v>
       </c>
       <c r="AT53" s="4"/>
@@ -18305,11 +18305,11 @@
         <v>3</v>
       </c>
       <c r="AE54">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-0.16883895717922329</v>
       </c>
       <c r="AF54">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-0.16883895717922329</v>
       </c>
       <c r="AT54" s="7"/>
@@ -18323,11 +18323,11 @@
         <v>4</v>
       </c>
       <c r="AE55">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-3.3859292730872827E-2</v>
       </c>
       <c r="AF55">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-3.3859292730872827E-2</v>
       </c>
       <c r="AT55" s="7"/>
@@ -18346,11 +18346,11 @@
         <v>5</v>
       </c>
       <c r="AE56">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>3.2878440374244219E-3</v>
       </c>
       <c r="AF56">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>3.2878440374244219E-3</v>
       </c>
       <c r="AT56" s="7">
@@ -18391,11 +18391,11 @@
         <v>6</v>
       </c>
       <c r="AE57">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-1.412099724789511E-3</v>
       </c>
       <c r="AF57">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-1.412099724789511E-3</v>
       </c>
       <c r="AT57" s="7">
@@ -18569,17 +18569,17 @@
         <v>2</v>
       </c>
       <c r="AE62" s="51">
-        <f t="shared" ref="AE62:AF66" si="11">AG44+AE53</f>
+        <f t="shared" ref="AE62:AF66" si="13">AG44+AE53</f>
         <v>-9.2885791296650491E-2</v>
       </c>
       <c r="AF62" s="53">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.2745624799964137</v>
       </c>
     </row>
     <row r="63" spans="10:52" x14ac:dyDescent="0.25">
       <c r="J63" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N63" t="s">
         <v>54</v>
@@ -18591,11 +18591,11 @@
         <v>3</v>
       </c>
       <c r="AE63" s="51">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-0.16883895717922329</v>
       </c>
       <c r="AF63" s="53">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-0.23114701186205289</v>
       </c>
     </row>
@@ -18616,11 +18616,11 @@
         <v>4</v>
       </c>
       <c r="AE64" s="51">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-3.3859292730872827E-2</v>
       </c>
       <c r="AF64" s="53">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>3.1077567157202772E-2</v>
       </c>
     </row>
@@ -18636,22 +18636,22 @@
         <v>0.21543781682606056</v>
       </c>
       <c r="N65">
-        <f t="shared" ref="N65:N70" si="12">MAX(_xlfn.ANCHORARRAY(K65))</f>
+        <f t="shared" ref="N65:N70" si="14">MAX(_xlfn.ANCHORARRAY(K65))</f>
         <v>0.38716804364868784</v>
       </c>
       <c r="P65">
-        <f t="shared" ref="P65:P70" si="13">AVERAGE(_xlfn.ANCHORARRAY(K65))</f>
+        <f t="shared" ref="P65:P70" si="15">AVERAGE(_xlfn.ANCHORARRAY(K65))</f>
         <v>0.3013029302373742</v>
       </c>
       <c r="AD65" s="7">
         <v>5</v>
       </c>
       <c r="AE65" s="51">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>3.2878440374244219E-3</v>
       </c>
       <c r="AF65" s="53">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>5.5730443321541007E-2</v>
       </c>
     </row>
@@ -18667,22 +18667,22 @@
         <v>0.65027309102745778</v>
       </c>
       <c r="N66">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.65027309102745778</v>
       </c>
       <c r="P66">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.53346891374762251</v>
       </c>
       <c r="AD66" s="9">
         <v>6</v>
       </c>
       <c r="AE66" s="52">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-1.412099724789511E-3</v>
       </c>
       <c r="AF66" s="54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.3180273290716179</v>
       </c>
     </row>
@@ -18698,11 +18698,11 @@
         <v>0.91793145379932639</v>
       </c>
       <c r="N67">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.91793145379932639</v>
       </c>
       <c r="P67">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.71864642940231738</v>
       </c>
     </row>
@@ -18718,11 +18718,11 @@
         <v>0.94437948578866504</v>
       </c>
       <c r="N68">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.94437948578866504</v>
       </c>
       <c r="P68">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.76086882897867159</v>
       </c>
       <c r="AD68" s="59"/>
@@ -18743,11 +18743,11 @@
         <v>0.97538944250417403</v>
       </c>
       <c r="N69">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.97538944250417403</v>
       </c>
       <c r="P69">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.72304703142137494</v>
       </c>
       <c r="AD69" s="62"/>
@@ -18770,11 +18770,11 @@
         <v>0.99109691980057746</v>
       </c>
       <c r="N70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.99109691980057746</v>
       </c>
       <c r="P70">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.76684073186571911</v>
       </c>
       <c r="AD70" s="64" t="s">
@@ -18886,7 +18886,7 @@
       </c>
       <c r="AD77" s="59"/>
       <c r="AE77" s="74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AF77" s="74"/>
       <c r="AG77" s="74"/>
@@ -19546,16 +19546,16 @@
         <v>1</v>
       </c>
       <c r="AO7" cm="1">
-        <f t="array" ref="AO7:AO18">AG34*AJ7:AJ18</f>
-        <v>-1.5259872677937807E-2</v>
+        <f t="array" ref="AO7:AO18">AG34*AG7:AG18</f>
+        <v>0.4820380122578849</v>
       </c>
       <c r="AP7" cm="1">
-        <f t="array" ref="AP7:AP18">AG35*AK7:AK18</f>
-        <v>-4.0768771388087065E-2</v>
+        <f t="array" ref="AP7:AP18">AG35*AG7:AG18</f>
+        <v>0.25718182792886268</v>
       </c>
       <c r="AQ7" s="8" cm="1">
-        <f t="array" ref="AQ7:AQ18">AG36*AL7:AL18</f>
-        <v>-0.26030777680371747</v>
+        <f t="array" ref="AQ7:AQ18">AG36*AG7:AG18</f>
+        <v>1.416259125688706</v>
       </c>
       <c r="AT7" s="7">
         <v>1</v>
@@ -19730,13 +19730,13 @@
         <v>2</v>
       </c>
       <c r="AO8">
-        <v>-0.10761626627351661</v>
+        <v>0.43642718905018696</v>
       </c>
       <c r="AP8">
-        <v>-2.4303291438501975E-3</v>
+        <v>0.23284707716729747</v>
       </c>
       <c r="AQ8" s="8">
-        <v>0.33157455888494092</v>
+        <v>1.2822515516895048</v>
       </c>
       <c r="AT8" s="9">
         <v>2</v>
@@ -19901,13 +19901,13 @@
         <v>3</v>
       </c>
       <c r="AO9">
-        <v>-7.0605381047174925E-2</v>
+        <v>0.44343369369523844</v>
       </c>
       <c r="AP9">
-        <v>1.8956567322031541E-2</v>
+        <v>0.23658525885874962</v>
       </c>
       <c r="AQ9" s="8">
-        <v>-4.0484885595436781E-2</v>
+        <v>1.3028371194049111</v>
       </c>
       <c r="CB9">
         <v>4</v>
@@ -19975,7 +19975,7 @@
     </row>
     <row r="10" spans="2:99" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I10">
         <v>4</v>
@@ -20057,13 +20057,13 @@
         <v>4</v>
       </c>
       <c r="AO10">
-        <v>-3.31389772334321E-2</v>
+        <v>0.29745503652683547</v>
       </c>
       <c r="AP10">
-        <v>-1.2273162176443498E-2</v>
+        <v>0.15870123947754458</v>
       </c>
       <c r="AQ10" s="8">
-        <v>6.2232964634307782E-2</v>
+        <v>0.87394230174906129</v>
       </c>
       <c r="AU10" t="s">
         <v>163</v>
@@ -20213,13 +20213,13 @@
         <v>5</v>
       </c>
       <c r="AO11">
-        <v>-6.5708556232612791E-2</v>
+        <v>0.40870806421910594</v>
       </c>
       <c r="AP11">
-        <v>-1.1240272290307163E-2</v>
+        <v>0.21805808747900732</v>
       </c>
       <c r="AQ11" s="8">
-        <v>5.7883348826533572E-2</v>
+        <v>1.2008109546829755</v>
       </c>
       <c r="AU11">
         <v>1</v>
@@ -20293,7 +20293,7 @@
     </row>
     <row r="12" spans="2:99" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="6"/>
@@ -20377,13 +20377,13 @@
         <v>6</v>
       </c>
       <c r="AO12">
-        <v>6.5139157998361383E-2</v>
+        <v>0.39924214773252159</v>
       </c>
       <c r="AP12">
-        <v>5.4196339907859409E-2</v>
+        <v>0.21300773534258843</v>
       </c>
       <c r="AQ12" s="8">
-        <v>0.25328147434500531</v>
+        <v>1.1729994745377952</v>
       </c>
       <c r="AT12">
         <v>1</v>
@@ -20460,13 +20460,13 @@
         <v>7</v>
       </c>
       <c r="AO13">
-        <v>-2.3914725838559248E-2</v>
+        <v>0.46801512837860038</v>
       </c>
       <c r="AP13">
-        <v>-5.2434351278568013E-2</v>
+        <v>0.24970019615460509</v>
       </c>
       <c r="AQ13" s="8">
-        <v>8.4315629504546019E-2</v>
+        <v>1.3750589780707112</v>
       </c>
       <c r="AT13">
         <v>2</v>
@@ -20558,13 +20558,13 @@
         <v>8</v>
       </c>
       <c r="AO14">
-        <v>6.2519926120804897E-2</v>
+        <v>0.42051832676377726</v>
       </c>
       <c r="AP14">
-        <v>1.1240272290307163E-2</v>
+        <v>0.22435921899212413</v>
       </c>
       <c r="AQ14" s="8">
-        <v>-0.16996960233456104</v>
+        <v>1.2355102764798669</v>
       </c>
       <c r="AT14">
         <v>3</v>
@@ -20677,13 +20677,13 @@
         <v>9</v>
       </c>
       <c r="AO15">
-        <v>0.11274085038177932</v>
+        <v>0.33770611537674677</v>
       </c>
       <c r="AP15">
-        <v>-5.7538042480653424E-2</v>
+        <v>0.18017640486178579</v>
       </c>
       <c r="AQ15" s="8">
-        <v>-0.30280017738735776</v>
+        <v>0.99220259718299275</v>
       </c>
       <c r="AT15">
         <v>4</v>
@@ -20834,13 +20834,13 @@
         <v>10</v>
       </c>
       <c r="AO16">
-        <v>5.3409554372782317E-2</v>
+        <v>0.14603486290615539</v>
       </c>
       <c r="AP16">
-        <v>2.2176753437633052E-2</v>
+        <v>7.7914006838641303E-2</v>
       </c>
       <c r="AQ16" s="8">
-        <v>-6.9259267093019938E-2</v>
+        <v>0.42905995377993883</v>
       </c>
       <c r="AT16">
         <v>5</v>
@@ -20972,13 +20972,13 @@
         <v>11</v>
       </c>
       <c r="AO17">
-        <v>2.7444994890917992E-2</v>
+        <v>0.38555634723269616</v>
       </c>
       <c r="AP17">
-        <v>2.9528499097779898E-2</v>
+        <v>0.20570594772478576</v>
       </c>
       <c r="AQ17" s="8">
-        <v>-2.0075149882034767E-3</v>
+        <v>1.1327896998782332</v>
       </c>
       <c r="AT17">
         <v>6</v>
@@ -21105,13 +21105,13 @@
         <v>12</v>
       </c>
       <c r="AO18" s="14">
-        <v>-1.9017901023997117E-2</v>
+        <v>0.29305386057034838</v>
       </c>
       <c r="AP18" s="14">
-        <v>-2.6855137039544685E-2</v>
+        <v>0.15635307927286687</v>
       </c>
       <c r="AQ18" s="11">
-        <v>3.3458583136724614E-3</v>
+        <v>0.86101135967887066</v>
       </c>
       <c r="CB18">
         <v>4</v>
@@ -22063,7 +22063,7 @@
     </row>
     <row r="33" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M33" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AF33" s="7"/>
       <c r="AG33">
@@ -22665,7 +22665,7 @@
         <v>162</v>
       </c>
       <c r="M45" s="38" t="s">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="N45" s="6"/>
       <c r="P45" t="s">
@@ -23047,7 +23047,7 @@
         <v>2</v>
       </c>
       <c r="AU51" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="9:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -23103,7 +23103,7 @@
     </row>
     <row r="53" spans="9:77" x14ac:dyDescent="0.25">
       <c r="M53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T53" s="7">
         <v>7</v>
@@ -23190,7 +23190,7 @@
         <v>-7.8283033501264032E-2</v>
       </c>
       <c r="BT55" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="9:77" x14ac:dyDescent="0.25">
@@ -23301,11 +23301,11 @@
       <c r="BK61" t="s">
         <v>137</v>
       </c>
-      <c r="BL61" s="83"/>
-      <c r="BM61" s="89"/>
-      <c r="BN61" s="88"/>
-      <c r="BS61" s="84"/>
-      <c r="BU61" s="84"/>
+      <c r="BL61" s="77"/>
+      <c r="BM61" s="83"/>
+      <c r="BN61" s="82"/>
+      <c r="BS61" s="78"/>
+      <c r="BU61" s="78"/>
       <c r="BX61" s="32" t="s">
         <v>137</v>
       </c>
@@ -23323,13 +23323,13 @@
         <v>0.17342326150584964</v>
       </c>
       <c r="AU62" t="s">
+        <v>168</v>
+      </c>
+      <c r="AW62" t="s">
         <v>169</v>
       </c>
-      <c r="AW62" t="s">
+      <c r="BD62" t="s">
         <v>170</v>
-      </c>
-      <c r="BD62" t="s">
-        <v>171</v>
       </c>
       <c r="BF62">
         <f>ROW(AW64)</f>
@@ -23348,28 +23348,28 @@
         <v>0</v>
       </c>
       <c r="BK62" t="s">
+        <v>171</v>
+      </c>
+      <c r="BL62" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="BL62" s="83" t="s">
+      <c r="BM62" s="83" t="s">
         <v>173</v>
       </c>
-      <c r="BM62" s="89" t="s">
+      <c r="BN62" s="82" t="s">
         <v>174</v>
       </c>
-      <c r="BN62" s="88" t="s">
+      <c r="BO62" t="s">
         <v>175</v>
       </c>
-      <c r="BO62" t="s">
-        <v>176</v>
-      </c>
       <c r="BQ62" t="s">
+        <v>177</v>
+      </c>
+      <c r="BS62" s="78" t="s">
         <v>178</v>
       </c>
-      <c r="BS62" s="84" t="s">
+      <c r="BU62" s="78" t="s">
         <v>179</v>
-      </c>
-      <c r="BU62" s="84" t="s">
-        <v>180</v>
       </c>
       <c r="BX62" t="s">
         <v>18</v>
@@ -23429,13 +23429,13 @@
       <c r="BK63">
         <v>1</v>
       </c>
-      <c r="BL63" s="83">
-        <v>1</v>
-      </c>
-      <c r="BM63" s="89">
-        <v>1</v>
-      </c>
-      <c r="BN63" s="88">
+      <c r="BL63" s="77">
+        <v>1</v>
+      </c>
+      <c r="BM63" s="83">
+        <v>1</v>
+      </c>
+      <c r="BN63" s="82">
         <v>1</v>
       </c>
       <c r="BO63">
@@ -23447,13 +23447,13 @@
       <c r="BR63">
         <v>2</v>
       </c>
-      <c r="BS63" s="84">
+      <c r="BS63" s="78">
         <v>1</v>
       </c>
       <c r="BT63">
         <v>2</v>
       </c>
-      <c r="BU63" s="84">
+      <c r="BU63" s="78">
         <v>1</v>
       </c>
       <c r="BV63">
@@ -23532,15 +23532,15 @@
         <f t="array" ref="BK64:BK69">(1/SQRT($G$2))*MMULT(TRANSPOSE($BD$64:$BI$69),_xlfn.ANCHORARRAY($J$7))</f>
         <v>0.17159399970181854</v>
       </c>
-      <c r="BL64" s="83" cm="1">
+      <c r="BL64" s="77" cm="1">
         <f t="array" ref="BL64:BL69">(1/SQRT($G$2))*MMULT($BD$64:$BI$69,_xlfn.ANCHORARRAY(L7))</f>
         <v>-6.7954731938485544E-2</v>
       </c>
-      <c r="BM64" s="89" cm="1">
+      <c r="BM64" s="83" cm="1">
         <f t="array" ref="BM64:BM65">MMULT(TRANSPOSE(_xlfn.ANCHORARRAY($C$4)),_xlfn.ANCHORARRAY($BL$64))</f>
         <v>-5.2833171166982662E-2</v>
       </c>
-      <c r="BN64" s="88" cm="1">
+      <c r="BN64" s="82" cm="1">
         <f t="array" ref="BN64:BN65">MMULT(TRANSPOSE(_xlfn.ANCHORARRAY($C$4)),_xlfn.ANCHORARRAY($BK$64))</f>
         <v>0.21507490122091952</v>
       </c>
@@ -23555,14 +23555,14 @@
       <c r="BR64">
         <v>-5.9800164105867276E-2</v>
       </c>
-      <c r="BS64" s="84" cm="1">
+      <c r="BS64" s="78" cm="1">
         <f t="array" ref="BS64:BT69">MMULT(_xlfn.ANCHORARRAY(BK64),TRANSPOSE(E25:E26))</f>
         <v>7.0181945878043786E-2</v>
       </c>
       <c r="BT64">
         <v>-0.12492043178292389</v>
       </c>
-      <c r="BU64" s="84" cm="1">
+      <c r="BU64" s="78" cm="1">
         <f t="array" ref="BU64:BV69">MMULT(_xlfn.ANCHORARRAY(AU64),TRANSPOSE(G25:G26))</f>
         <v>-7.1145799712848425E-4</v>
       </c>
@@ -23640,13 +23640,13 @@
       <c r="BK65">
         <v>-5.2429971972223818E-4</v>
       </c>
-      <c r="BL65" s="83">
+      <c r="BL65" s="77">
         <v>-6.8824741998961079E-3</v>
       </c>
-      <c r="BM65" s="89">
+      <c r="BM65" s="83">
         <v>2.1091226610279214E-3</v>
       </c>
-      <c r="BN65" s="88">
+      <c r="BN65" s="82">
         <v>0.14187246761890959</v>
       </c>
       <c r="BO65">
@@ -23658,13 +23658,13 @@
       <c r="BR65">
         <v>-6.056577295908575E-3</v>
       </c>
-      <c r="BS65" s="84">
+      <c r="BS65" s="78">
         <v>-2.1443858536639539E-4</v>
       </c>
       <c r="BT65">
         <v>3.816901959577894E-4</v>
       </c>
-      <c r="BU65" s="84">
+      <c r="BU65" s="78">
         <v>-6.4509608854836813E-4</v>
       </c>
       <c r="BV65">
@@ -23740,24 +23740,24 @@
       <c r="BK66">
         <v>2.057549066409408E-2</v>
       </c>
-      <c r="BL66" s="83">
+      <c r="BL66" s="77">
         <v>5.7740380493337129E-2</v>
       </c>
-      <c r="BM66" s="89"/>
-      <c r="BN66" s="88"/>
+      <c r="BM66" s="83"/>
+      <c r="BN66" s="82"/>
       <c r="BQ66">
         <v>-4.9772207985256604E-2</v>
       </c>
       <c r="BR66">
         <v>5.0811534834136675E-2</v>
       </c>
-      <c r="BS66" s="84">
+      <c r="BS66" s="78">
         <v>8.4153756816144776E-3</v>
       </c>
       <c r="BT66">
         <v>-1.4978957203460489E-2</v>
       </c>
-      <c r="BU66" s="84">
+      <c r="BU66" s="78">
         <v>-1.7934028550657896E-3</v>
       </c>
       <c r="BV66">
@@ -23822,24 +23822,24 @@
       <c r="BK67">
         <v>-7.5075754733779684E-2</v>
       </c>
-      <c r="BL67" s="83">
+      <c r="BL67" s="77">
         <v>-2.8923881868992878E-3</v>
       </c>
-      <c r="BM67" s="89"/>
-      <c r="BN67" s="88"/>
+      <c r="BM67" s="83"/>
+      <c r="BN67" s="82"/>
       <c r="BQ67">
         <v>2.4932386171071861E-3</v>
       </c>
       <c r="BR67">
         <v>-2.5453016044713734E-3</v>
       </c>
-      <c r="BS67" s="84">
+      <c r="BS67" s="78">
         <v>-3.0705983686115889E-2</v>
       </c>
       <c r="BT67">
         <v>5.4655149446191612E-2</v>
       </c>
-      <c r="BU67" s="84">
+      <c r="BU67" s="78">
         <v>-2.0138557137223427E-3</v>
       </c>
       <c r="BV67">
@@ -23904,24 +23904,24 @@
       <c r="BK68">
         <v>-5.1111032192391145E-2</v>
       </c>
-      <c r="BL68" s="83">
+      <c r="BL68" s="77">
         <v>1.6400863935678384E-2</v>
       </c>
-      <c r="BM68" s="89"/>
-      <c r="BN68" s="88"/>
+      <c r="BM68" s="83"/>
+      <c r="BN68" s="82"/>
       <c r="BQ68">
         <v>-1.4137544712554767E-2</v>
       </c>
       <c r="BR68">
         <v>1.4432760263396977E-2</v>
       </c>
-      <c r="BS68" s="84">
+      <c r="BS68" s="78">
         <v>-2.0904412166687977E-2</v>
       </c>
       <c r="BT68">
         <v>3.7208831436060755E-2</v>
       </c>
-      <c r="BU68" s="84">
+      <c r="BU68" s="78">
         <v>-6.4386392351112071E-4</v>
       </c>
       <c r="BV68">
@@ -23986,24 +23986,24 @@
       <c r="BK69">
         <v>-6.5458403720019501E-2</v>
       </c>
-      <c r="BL69" s="83">
+      <c r="BL69" s="77">
         <v>-7.2052860863325886E-3</v>
       </c>
-      <c r="BM69" s="89"/>
-      <c r="BN69" s="88"/>
+      <c r="BM69" s="83"/>
+      <c r="BN69" s="82"/>
       <c r="BQ69">
         <v>6.2109566064186914E-3</v>
       </c>
       <c r="BR69">
         <v>-6.3406517559726778E-3</v>
       </c>
-      <c r="BS69" s="84">
+      <c r="BS69" s="78">
         <v>-2.6772487121487974E-2</v>
       </c>
       <c r="BT69">
         <v>4.7653717908174194E-2</v>
       </c>
-      <c r="BU69" s="84">
+      <c r="BU69" s="78">
         <v>-1.5455509431101639E-3</v>
       </c>
       <c r="BV69">
@@ -24017,18 +24017,18 @@
       </c>
     </row>
     <row r="70" spans="40:77" x14ac:dyDescent="0.25">
-      <c r="BL70" s="83"/>
-      <c r="BM70" s="89"/>
-      <c r="BN70" s="88"/>
-      <c r="BS70" s="84"/>
-      <c r="BU70" s="84"/>
+      <c r="BL70" s="77"/>
+      <c r="BM70" s="83"/>
+      <c r="BN70" s="82"/>
+      <c r="BS70" s="78"/>
+      <c r="BU70" s="78"/>
     </row>
     <row r="71" spans="40:77" x14ac:dyDescent="0.25">
-      <c r="BL71" s="83"/>
-      <c r="BM71" s="89"/>
-      <c r="BN71" s="88"/>
-      <c r="BS71" s="84"/>
-      <c r="BU71" s="84"/>
+      <c r="BL71" s="77"/>
+      <c r="BM71" s="83"/>
+      <c r="BN71" s="82"/>
+      <c r="BS71" s="78"/>
+      <c r="BU71" s="78"/>
     </row>
     <row r="72" spans="40:77" x14ac:dyDescent="0.25">
       <c r="AU72" s="55" t="s">
@@ -24037,24 +24037,24 @@
       <c r="BK72" t="s">
         <v>138</v>
       </c>
-      <c r="BL72" s="83"/>
-      <c r="BM72" s="89"/>
-      <c r="BN72" s="88"/>
-      <c r="BS72" s="84"/>
-      <c r="BU72" s="84"/>
+      <c r="BL72" s="77"/>
+      <c r="BM72" s="83"/>
+      <c r="BN72" s="82"/>
+      <c r="BS72" s="78"/>
+      <c r="BU72" s="78"/>
       <c r="BX72" s="32" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="73" spans="40:77" x14ac:dyDescent="0.25">
       <c r="AU73" t="s">
+        <v>168</v>
+      </c>
+      <c r="AW73" t="s">
         <v>169</v>
       </c>
-      <c r="AW73" t="s">
+      <c r="BD73" t="s">
         <v>170</v>
-      </c>
-      <c r="BD73" t="s">
-        <v>171</v>
       </c>
       <c r="BF73">
         <f>ROW(AW75)</f>
@@ -24073,28 +24073,28 @@
         <v>0</v>
       </c>
       <c r="BK73" t="s">
+        <v>171</v>
+      </c>
+      <c r="BL73" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="BL73" s="83" t="s">
+      <c r="BM73" s="83" t="s">
         <v>173</v>
       </c>
-      <c r="BM73" s="89" t="s">
+      <c r="BN73" s="82" t="s">
         <v>174</v>
       </c>
-      <c r="BN73" s="88" t="s">
+      <c r="BO73" t="s">
         <v>175</v>
       </c>
-      <c r="BO73" t="s">
-        <v>176</v>
-      </c>
       <c r="BQ73" t="s">
+        <v>177</v>
+      </c>
+      <c r="BS73" s="78" t="s">
         <v>178</v>
       </c>
-      <c r="BS73" s="84" t="s">
+      <c r="BU73" s="78" t="s">
         <v>179</v>
-      </c>
-      <c r="BU73" s="84" t="s">
-        <v>180</v>
       </c>
       <c r="BX73" t="s">
         <v>18</v>
@@ -24143,13 +24143,13 @@
       <c r="BK74">
         <v>1</v>
       </c>
-      <c r="BL74" s="83">
-        <v>1</v>
-      </c>
-      <c r="BM74" s="89">
-        <v>1</v>
-      </c>
-      <c r="BN74" s="88">
+      <c r="BL74" s="77">
+        <v>1</v>
+      </c>
+      <c r="BM74" s="83">
+        <v>1</v>
+      </c>
+      <c r="BN74" s="82">
         <v>1</v>
       </c>
       <c r="BO74">
@@ -24161,13 +24161,13 @@
       <c r="BR74">
         <v>2</v>
       </c>
-      <c r="BS74" s="84">
+      <c r="BS74" s="78">
         <v>1</v>
       </c>
       <c r="BT74">
         <v>2</v>
       </c>
-      <c r="BU74" s="84">
+      <c r="BU74" s="78">
         <v>1</v>
       </c>
       <c r="BV74">
@@ -24235,15 +24235,15 @@
         <f t="array" ref="BK75:BK80">(1/SQRT($G$2))*MMULT(TRANSPOSE($BD$75:$BI$80),_xlfn.ANCHORARRAY(J17))</f>
         <v>0.71639551875113883</v>
       </c>
-      <c r="BL75" s="83" cm="1">
+      <c r="BL75" s="77" cm="1">
         <f t="array" ref="BL75:BL80">(1/SQRT($G$2))*MMULT($BD$75:$BI$80,_xlfn.ANCHORARRAY(L17))</f>
         <v>-0.2003226743414861</v>
       </c>
-      <c r="BM75" s="89" cm="1">
+      <c r="BM75" s="83" cm="1">
         <f t="array" ref="BM75:BM76">MMULT(TRANSPOSE(_xlfn.ANCHORARRAY($C$4)),_xlfn.ANCHORARRAY(BL75))</f>
         <v>-0.55793549784225449</v>
       </c>
-      <c r="BN75" s="88" cm="1">
+      <c r="BN75" s="82" cm="1">
         <f t="array" ref="BN75:BN76">MMULT(TRANSPOSE(_xlfn.ANCHORARRAY($C$4)),_xlfn.ANCHORARRAY(BK75))</f>
         <v>0.55494654156176892</v>
       </c>
@@ -24258,14 +24258,14 @@
       <c r="BR75">
         <v>-4.7676796493273686E-2</v>
       </c>
-      <c r="BS75" s="84" cm="1">
+      <c r="BS75" s="78" cm="1">
         <f t="array" ref="BS75:BT80">MMULT(_xlfn.ANCHORARRAY(BK75),TRANSPOSE(E31:E32))</f>
         <v>0.17981527520653584</v>
       </c>
       <c r="BT75">
         <v>-5.8744432537593386E-2</v>
       </c>
-      <c r="BU75" s="84" cm="1">
+      <c r="BU75" s="78" cm="1">
         <f t="array" ref="BU75:BV80">MMULT(_xlfn.ANCHORARRAY(AU75),TRANSPOSE(G31:G32))</f>
         <v>2.9596068071359755E-2</v>
       </c>
@@ -24332,13 +24332,13 @@
       <c r="BK76">
         <v>-0.53614411724748123</v>
       </c>
-      <c r="BL76" s="83">
+      <c r="BL76" s="77">
         <v>0.1569886148599153</v>
       </c>
-      <c r="BM76" s="89">
+      <c r="BM76" s="83">
         <v>-0.28666944460472288</v>
       </c>
-      <c r="BN76" s="88">
+      <c r="BN76" s="82">
         <v>0.46172112508298047</v>
       </c>
       <c r="BO76">
@@ -24350,13 +24350,13 @@
       <c r="BR76">
         <v>3.7363290336659839E-2</v>
       </c>
-      <c r="BS76" s="84">
+      <c r="BS76" s="78">
         <v>-0.13457217342911779</v>
       </c>
       <c r="BT76">
         <v>4.3963817614293466E-2</v>
       </c>
-      <c r="BU76" s="84">
+      <c r="BU76" s="78">
         <v>3.2840787282016129E-2</v>
       </c>
       <c r="BV76">
@@ -24421,24 +24421,24 @@
       <c r="BK77">
         <v>0.3891837823987459</v>
       </c>
-      <c r="BL77" s="83">
+      <c r="BL77" s="77">
         <v>-2.9399427893421797E-2</v>
       </c>
-      <c r="BM77" s="89"/>
-      <c r="BN77" s="88"/>
+      <c r="BM77" s="83"/>
+      <c r="BN77" s="82"/>
       <c r="BQ77">
         <v>1.4317521384096414E-2</v>
       </c>
       <c r="BR77">
         <v>-6.9970638386343872E-3</v>
       </c>
-      <c r="BS77" s="84">
+      <c r="BS77" s="78">
         <v>9.768512938208522E-2</v>
       </c>
       <c r="BT77">
         <v>-3.1913070156697164E-2</v>
       </c>
-      <c r="BU77" s="84">
+      <c r="BU77" s="78">
         <v>3.8327310249563082E-2</v>
       </c>
       <c r="BV77">
@@ -24503,24 +24503,24 @@
       <c r="BK78">
         <v>0.13167543081267849</v>
       </c>
-      <c r="BL78" s="83">
+      <c r="BL78" s="77">
         <v>-3.9615850454265591E-2</v>
       </c>
-      <c r="BM78" s="89"/>
-      <c r="BN78" s="88"/>
+      <c r="BM78" s="83"/>
+      <c r="BN78" s="82"/>
       <c r="BQ78">
         <v>1.9292919171227343E-2</v>
       </c>
       <c r="BR78">
         <v>-9.4285724081152097E-3</v>
       </c>
-      <c r="BS78" s="84">
+      <c r="BS78" s="78">
         <v>3.3050533133982304E-2</v>
       </c>
       <c r="BT78">
         <v>-1.0797385326639637E-2</v>
       </c>
-      <c r="BU78" s="84">
+      <c r="BU78" s="78">
         <v>5.5265975655781417E-2</v>
       </c>
       <c r="BV78">
@@ -24585,24 +24585,24 @@
       <c r="BK79">
         <v>-1.1946925984738926E-3</v>
       </c>
-      <c r="BL79" s="83">
+      <c r="BL79" s="77">
         <v>1.8628675664855009E-2</v>
       </c>
-      <c r="BM79" s="89"/>
-      <c r="BN79" s="88"/>
+      <c r="BM79" s="83"/>
+      <c r="BN79" s="82"/>
       <c r="BQ79">
         <v>-9.0721650487843898E-3</v>
       </c>
       <c r="BR79">
         <v>4.4336248082354921E-3</v>
       </c>
-      <c r="BS79" s="84">
+      <c r="BS79" s="78">
         <v>-2.9986784221694706E-4</v>
       </c>
       <c r="BT79">
         <v>9.7964793074859202E-5</v>
       </c>
-      <c r="BU79" s="84">
+      <c r="BU79" s="78">
         <v>3.5373407052995763E-2</v>
       </c>
       <c r="BV79">
@@ -24667,24 +24667,24 @@
       <c r="BK80">
         <v>-0.69991592211660802</v>
       </c>
-      <c r="BL80" s="83">
+      <c r="BL80" s="77">
         <v>-5.7079927097065442E-2</v>
       </c>
-      <c r="BM80" s="89"/>
-      <c r="BN80" s="88"/>
+      <c r="BM80" s="83"/>
+      <c r="BN80" s="82"/>
       <c r="BQ80">
         <v>2.779792449627087E-2</v>
       </c>
       <c r="BR80">
         <v>-1.3585022649101575E-2</v>
       </c>
-      <c r="BS80" s="84">
+      <c r="BS80" s="78">
         <v>-0.17567889645126861</v>
       </c>
       <c r="BT80">
         <v>5.7393105613561861E-2</v>
       </c>
-      <c r="BU80" s="84">
+      <c r="BU80" s="78">
         <v>4.2096046729808073E-2</v>
       </c>
       <c r="BV80">
@@ -24700,7 +24700,7 @@
     <row r="81" spans="75:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="82" spans="75:80" x14ac:dyDescent="0.25">
       <c r="BX82" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="CA82" s="38" t="s">
         <v>80</v>
@@ -24836,7 +24836,7 @@
     </row>
     <row r="91" spans="75:80" x14ac:dyDescent="0.25">
       <c r="CA91" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -24875,18 +24875,18 @@
         <v>77</v>
       </c>
       <c r="Q2" s="32" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R2" s="13"/>
-      <c r="T2" s="82" t="s">
-        <v>223</v>
-      </c>
-      <c r="U2" s="82"/>
-      <c r="V2" s="82"/>
-      <c r="W2" s="82"/>
-      <c r="X2" s="82"/>
-      <c r="Y2" s="82"/>
-      <c r="Z2" s="82"/>
+      <c r="T2" s="89" t="s">
+        <v>222</v>
+      </c>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
+      <c r="W2" s="89"/>
+      <c r="X2" s="89"/>
+      <c r="Y2" s="89"/>
+      <c r="Z2" s="89"/>
     </row>
     <row r="3" spans="2:31" x14ac:dyDescent="0.25">
       <c r="E3" t="s">
@@ -24899,7 +24899,7 @@
         <v>44</v>
       </c>
       <c r="I3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L3" t="s">
         <v>76</v>
@@ -24913,18 +24913,18 @@
       <c r="Q3" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="T3" s="82"/>
-      <c r="U3" s="82"/>
-      <c r="V3" s="82"/>
-      <c r="W3" s="82"/>
-      <c r="X3" s="82"/>
-      <c r="Y3" s="82"/>
-      <c r="Z3" s="82"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="W3" s="89"/>
+      <c r="X3" s="89"/>
+      <c r="Y3" s="89"/>
+      <c r="Z3" s="89"/>
     </row>
     <row r="4" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
       <c r="C4" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14">
@@ -24953,18 +24953,18 @@
         <v>44</v>
       </c>
       <c r="Q4" t="s">
+        <v>200</v>
+      </c>
+      <c r="R4" t="s">
         <v>201</v>
       </c>
-      <c r="R4" t="s">
-        <v>202</v>
-      </c>
       <c r="T4" s="33" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="2:31" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -25057,7 +25057,7 @@
     <row r="7" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="14"/>
       <c r="C7" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D7" s="14">
         <v>1</v>
@@ -25100,11 +25100,11 @@
       </c>
     </row>
     <row r="8" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="79" t="s">
-        <v>194</v>
+      <c r="B8" s="86" t="s">
+        <v>193</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -25146,9 +25146,9 @@
       </c>
     </row>
     <row r="9" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B9" s="80"/>
+      <c r="B9" s="87"/>
       <c r="C9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -25189,9 +25189,9 @@
       </c>
     </row>
     <row r="10" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="80"/>
+      <c r="B10" s="87"/>
       <c r="C10" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D10" s="14">
         <v>4</v>
@@ -25224,51 +25224,51 @@
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" t="s">
+        <v>209</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="S10" t="s">
+        <v>201</v>
+      </c>
+      <c r="T10" t="s">
+        <v>205</v>
+      </c>
+      <c r="U10" t="s">
+        <v>207</v>
+      </c>
+      <c r="V10" t="s">
         <v>210</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="S10" t="s">
-        <v>202</v>
-      </c>
-      <c r="T10" t="s">
+      <c r="W10" t="s">
+        <v>208</v>
+      </c>
+      <c r="X10" t="s">
         <v>206</v>
       </c>
-      <c r="U10" t="s">
-        <v>208</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="Y10" t="s">
         <v>211</v>
       </c>
-      <c r="W10" t="s">
+      <c r="Z10" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB10" t="s">
         <v>209</v>
       </c>
-      <c r="X10" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y10" t="s">
+      <c r="AC10" t="s">
+        <v>211</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>210</v>
+      </c>
+      <c r="AE10" t="s">
         <v>212</v>
       </c>
-      <c r="Z10" t="s">
-        <v>213</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>212</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>211</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>213</v>
-      </c>
     </row>
     <row r="11" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="79" t="s">
-        <v>194</v>
+      <c r="B11" s="86" t="s">
+        <v>193</v>
       </c>
       <c r="C11" t="s">
         <v>91</v>
@@ -25362,7 +25362,7 @@
       </c>
     </row>
     <row r="12" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B12" s="80"/>
+      <c r="B12" s="87"/>
       <c r="C12" t="s">
         <v>91</v>
       </c>
@@ -25436,7 +25436,7 @@
       </c>
     </row>
     <row r="13" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="80"/>
+      <c r="B13" s="87"/>
       <c r="C13" s="14" t="s">
         <v>91</v>
       </c>
@@ -25508,11 +25508,11 @@
       </c>
     </row>
     <row r="14" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="79" t="s">
-        <v>194</v>
+      <c r="B14" s="86" t="s">
+        <v>193</v>
       </c>
       <c r="C14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -25583,9 +25583,9 @@
       </c>
     </row>
     <row r="15" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B15" s="80"/>
+      <c r="B15" s="87"/>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D15">
         <v>3</v>
@@ -25671,9 +25671,9 @@
       </c>
     </row>
     <row r="16" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="81"/>
+      <c r="B16" s="88"/>
       <c r="C16" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
@@ -25756,13 +25756,13 @@
         <v>0</v>
       </c>
       <c r="AC17" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD17" t="s">
         <v>214</v>
       </c>
-      <c r="AD17" t="s">
+      <c r="AE17" t="s">
         <v>215</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="18" spans="5:31" x14ac:dyDescent="0.25">
@@ -25791,7 +25791,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AC18">
         <f>ABS(AC12-AC11)</f>
@@ -25864,7 +25864,7 @@
         <v>73</v>
       </c>
       <c r="M20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="R20" s="3">
         <f>IF($Q$6&gt;$Q19,1,0)</f>
@@ -25910,10 +25910,10 @@
       <c r="G21" t="s">
         <v>75</v>
       </c>
-      <c r="M21" s="77" t="s">
-        <v>201</v>
-      </c>
-      <c r="N21" s="77"/>
+      <c r="M21" s="84" t="s">
+        <v>200</v>
+      </c>
+      <c r="N21" s="84"/>
       <c r="R21" s="3">
         <f>IF($Q$7&gt;$Q19,1,0)</f>
         <v>1</v>
@@ -25958,14 +25958,14 @@
       <c r="F22">
         <v>3</v>
       </c>
-      <c r="K22" s="80" t="s">
-        <v>202</v>
+      <c r="K22" s="87" t="s">
+        <v>201</v>
       </c>
       <c r="M22" t="s">
+        <v>203</v>
+      </c>
+      <c r="N22" t="s">
         <v>204</v>
-      </c>
-      <c r="N22" t="s">
-        <v>205</v>
       </c>
       <c r="R22" s="3">
         <f>IF($Q$8&gt;$Q19,1,0)</f>
@@ -25992,7 +25992,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AE22" s="34">
         <f>SUM(AE18:AE21)</f>
@@ -26006,15 +26006,15 @@
       <c r="F23">
         <v>16</v>
       </c>
-      <c r="K23" s="80"/>
+      <c r="K23" s="87"/>
       <c r="L23" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M23" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q23" s="3">
         <v>0.15</v>
@@ -26063,15 +26063,15 @@
       <c r="F24">
         <v>7</v>
       </c>
-      <c r="K24" s="80"/>
+      <c r="K24" s="87"/>
       <c r="L24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R24" s="3">
         <f>IF($Q$6&gt;$Q23,1,0)</f>
@@ -26098,20 +26098,20 @@
         <v>0</v>
       </c>
       <c r="AC24" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD24" t="s">
         <v>214</v>
       </c>
-      <c r="AD24" t="s">
+      <c r="AE24" t="s">
         <v>215</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="25" spans="5:31" x14ac:dyDescent="0.25">
       <c r="F25" t="s">
-        <v>200</v>
-      </c>
-      <c r="K25" s="80"/>
+        <v>199</v>
+      </c>
+      <c r="K25" s="87"/>
       <c r="R25" s="3">
         <f>IF($Q$7&gt;$Q23,1,0)</f>
         <v>1</v>
@@ -26137,7 +26137,7 @@
         <v>0</v>
       </c>
       <c r="AB25" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AC25">
         <f>ABS(AD12-AD11)</f>
@@ -26307,7 +26307,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AE29" s="34">
         <f>SUM(AE25:AE28)</f>
@@ -26340,7 +26340,7 @@
         <v>0</v>
       </c>
       <c r="AB30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31" spans="5:31" x14ac:dyDescent="0.25">
@@ -26358,10 +26358,10 @@
     </row>
     <row r="34" spans="17:31" x14ac:dyDescent="0.25">
       <c r="Q34" t="s">
+        <v>200</v>
+      </c>
+      <c r="R34" t="s">
         <v>201</v>
-      </c>
-      <c r="R34" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="35" spans="17:31" x14ac:dyDescent="0.25">
@@ -26409,46 +26409,46 @@
     </row>
     <row r="40" spans="17:31" x14ac:dyDescent="0.25">
       <c r="Q40" t="s">
+        <v>209</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="S40" t="s">
+        <v>201</v>
+      </c>
+      <c r="T40" t="s">
+        <v>205</v>
+      </c>
+      <c r="U40" t="s">
+        <v>207</v>
+      </c>
+      <c r="V40" t="s">
         <v>210</v>
       </c>
-      <c r="R40" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="S40" t="s">
-        <v>202</v>
-      </c>
-      <c r="T40" t="s">
+      <c r="W40" t="s">
+        <v>208</v>
+      </c>
+      <c r="X40" t="s">
         <v>206</v>
       </c>
-      <c r="U40" t="s">
-        <v>208</v>
-      </c>
-      <c r="V40" t="s">
+      <c r="Y40" t="s">
         <v>211</v>
       </c>
-      <c r="W40" t="s">
+      <c r="Z40" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB40" t="s">
         <v>209</v>
       </c>
-      <c r="X40" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y40" t="s">
+      <c r="AC40" t="s">
+        <v>211</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>210</v>
+      </c>
+      <c r="AE40" t="s">
         <v>212</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>213</v>
-      </c>
-      <c r="AB40" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC40" t="s">
-        <v>212</v>
-      </c>
-      <c r="AD40" t="s">
-        <v>211</v>
-      </c>
-      <c r="AE40" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="41" spans="17:31" x14ac:dyDescent="0.25">
@@ -26727,13 +26727,13 @@
         <v>0</v>
       </c>
       <c r="AC47" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD47" t="s">
         <v>214</v>
       </c>
-      <c r="AD47" t="s">
+      <c r="AE47" t="s">
         <v>215</v>
-      </c>
-      <c r="AE47" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="48" spans="17:31" x14ac:dyDescent="0.25">
@@ -26762,7 +26762,7 @@
         <v>0</v>
       </c>
       <c r="AB48" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AC48">
         <f>ABS(AC42-AC41)</f>
@@ -26932,7 +26932,7 @@
         <v>0</v>
       </c>
       <c r="AD52" s="37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AE52" s="34">
         <f>SUM(AE48:AE51)</f>
@@ -27006,13 +27006,13 @@
         <v>0</v>
       </c>
       <c r="AC54" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD54" t="s">
         <v>214</v>
       </c>
-      <c r="AD54" t="s">
+      <c r="AE54" t="s">
         <v>215</v>
-      </c>
-      <c r="AE54" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="55" spans="17:31" x14ac:dyDescent="0.25">
@@ -27041,7 +27041,7 @@
         <v>0</v>
       </c>
       <c r="AB55" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AC55">
         <f>ABS(AD42-AD41)</f>
@@ -27211,7 +27211,7 @@
         <v>0</v>
       </c>
       <c r="AD59" s="37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AE59" s="34">
         <f>SUM(AE55:AE58)</f>
@@ -27244,7 +27244,7 @@
         <v>0</v>
       </c>
       <c r="AB60" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="63" spans="17:31" x14ac:dyDescent="0.25">
@@ -27255,10 +27255,10 @@
     </row>
     <row r="64" spans="17:31" x14ac:dyDescent="0.25">
       <c r="Q64" t="s">
+        <v>200</v>
+      </c>
+      <c r="R64" t="s">
         <v>201</v>
-      </c>
-      <c r="R64" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="65" spans="17:31" x14ac:dyDescent="0.25">
@@ -27306,46 +27306,46 @@
     </row>
     <row r="70" spans="17:31" x14ac:dyDescent="0.25">
       <c r="Q70" t="s">
+        <v>209</v>
+      </c>
+      <c r="R70" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="S70" t="s">
+        <v>201</v>
+      </c>
+      <c r="T70" t="s">
+        <v>205</v>
+      </c>
+      <c r="U70" t="s">
+        <v>207</v>
+      </c>
+      <c r="V70" t="s">
         <v>210</v>
       </c>
-      <c r="R70" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="S70" t="s">
-        <v>202</v>
-      </c>
-      <c r="T70" t="s">
+      <c r="W70" t="s">
+        <v>208</v>
+      </c>
+      <c r="X70" t="s">
         <v>206</v>
       </c>
-      <c r="U70" t="s">
-        <v>208</v>
-      </c>
-      <c r="V70" t="s">
+      <c r="Y70" t="s">
         <v>211</v>
       </c>
-      <c r="W70" t="s">
+      <c r="Z70" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB70" t="s">
         <v>209</v>
       </c>
-      <c r="X70" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y70" t="s">
+      <c r="AC70" t="s">
+        <v>211</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>210</v>
+      </c>
+      <c r="AE70" t="s">
         <v>212</v>
-      </c>
-      <c r="Z70" t="s">
-        <v>213</v>
-      </c>
-      <c r="AB70" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC70" t="s">
-        <v>212</v>
-      </c>
-      <c r="AD70" t="s">
-        <v>211</v>
-      </c>
-      <c r="AE70" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="71" spans="17:31" x14ac:dyDescent="0.25">
@@ -27624,13 +27624,13 @@
         <v>0</v>
       </c>
       <c r="AC77" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD77" t="s">
         <v>214</v>
       </c>
-      <c r="AD77" t="s">
+      <c r="AE77" t="s">
         <v>215</v>
-      </c>
-      <c r="AE77" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="78" spans="17:31" x14ac:dyDescent="0.25">
@@ -27659,7 +27659,7 @@
         <v>1</v>
       </c>
       <c r="AB78" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AC78">
         <f>ABS(AC72-AC71)</f>
@@ -27829,7 +27829,7 @@
         <v>0</v>
       </c>
       <c r="AD82" s="37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AE82" s="34">
         <f>SUM(AE78:AE81)</f>
@@ -27903,13 +27903,13 @@
         <v>0</v>
       </c>
       <c r="AC84" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD84" t="s">
         <v>214</v>
       </c>
-      <c r="AD84" t="s">
+      <c r="AE84" t="s">
         <v>215</v>
-      </c>
-      <c r="AE84" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="85" spans="17:31" x14ac:dyDescent="0.25">
@@ -27938,7 +27938,7 @@
         <v>0</v>
       </c>
       <c r="AB85" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AC85">
         <f>ABS(AD72-AD71)</f>
@@ -28108,7 +28108,7 @@
         <v>0</v>
       </c>
       <c r="AD89" s="37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AE89" s="34">
         <f>SUM(AE85:AE88)</f>
@@ -28141,19 +28141,19 @@
         <v>0</v>
       </c>
       <c r="AB90" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="92" spans="17:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="93" spans="17:31" x14ac:dyDescent="0.25">
       <c r="AB93" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AC93" s="6"/>
     </row>
     <row r="94" spans="17:31" x14ac:dyDescent="0.25">
       <c r="AB94" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AC94" s="8">
         <f>AVERAGE(AE29,AE59,AE89)</f>
@@ -28162,7 +28162,7 @@
     </row>
     <row r="95" spans="17:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AB95" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AC95" s="11">
         <f>AVERAGE(AE22,AE52,AE82)</f>
@@ -28190,7 +28190,7 @@
   <sheetData>
     <row r="2" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="B2" s="30" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
@@ -28204,47 +28204,47 @@
     </row>
     <row r="4" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="C4" s="30" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D4" s="30"/>
       <c r="E4" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="C5" s="30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D5" s="30"/>
       <c r="E5" s="31" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="C6" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D6" s="30"/>
       <c r="E6" s="31" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="C7" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D7" s="30"/>
       <c r="E7" s="31" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="C8" s="30" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D8" s="30"/>
       <c r="E8" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="21" x14ac:dyDescent="0.35">
@@ -28259,14 +28259,14 @@
     </row>
     <row r="11" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="B11" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
     </row>
     <row r="12" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="C12" s="30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D12" s="30"/>
       <c r="E12" s="30"/>
@@ -28280,7 +28280,7 @@
     </row>
     <row r="14" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="C14" s="30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D14" s="30"/>
       <c r="E14" s="30"/>
@@ -28358,30 +28358,30 @@
       <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77" t="s">
-        <v>2</v>
-      </c>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77" t="s">
+      <c r="O2" s="84" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="84"/>
+      <c r="S2" s="84" t="s">
+        <v>2</v>
+      </c>
+      <c r="T2" s="84"/>
+      <c r="U2" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="V2" s="77"/>
-      <c r="W2" s="77" t="s">
+      <c r="V2" s="84"/>
+      <c r="W2" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="X2" s="77"/>
-      <c r="Y2" s="77" t="s">
+      <c r="X2" s="84"/>
+      <c r="Y2" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="Z2" s="77"/>
+      <c r="Z2" s="84"/>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -28554,14 +28554,14 @@
       <c r="D6" s="1">
         <v>0.62184138330161254</v>
       </c>
-      <c r="O6" s="77" t="s">
+      <c r="O6" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="P6" s="77"/>
-      <c r="S6" s="77" t="s">
+      <c r="P6" s="84"/>
+      <c r="S6" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="T6" s="77"/>
+      <c r="T6" s="84"/>
     </row>
     <row r="7" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B7" t="s">

--- a/ai/manualisation.xlsx
+++ b/ai/manualisation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DiskE\SKRIPSI-CODE\skripsi-code\ai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2FAEBD-D003-4D94-908F-16632D3F0EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972670CB-96EA-4A81-9D27-14A329773C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{145D0042-0CBE-48BE-846C-2BE8EAD29D31}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -595,9 +595,6 @@
     <t>L wrt WV</t>
   </si>
   <si>
-    <t>(2.90)</t>
-  </si>
-  <si>
     <t>term1</t>
   </si>
   <si>
@@ -782,6 +779,9 @@
   </si>
   <si>
     <t>O_Attn</t>
+  </si>
+  <si>
+    <t>(2.91)</t>
   </si>
 </sst>
 </file>
@@ -7733,7 +7733,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I10">
         <f>AVERAGE(B4:B9)</f>
@@ -7758,7 +7758,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I11">
         <f>_xlfn.STDEV.P(B4:B9)</f>
@@ -7841,7 +7841,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C16" s="85"/>
       <c r="D16" s="85"/>
@@ -7897,7 +7897,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B19" s="32" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -7927,99 +7927,99 @@
       </c>
       <c r="C2">
         <f ca="1">RAND()</f>
-        <v>0.10803336282564091</v>
+        <v>0.46293499115903169</v>
       </c>
       <c r="D2">
         <f t="shared" ref="D2:Z2" ca="1" si="0">RAND()</f>
-        <v>0.26484253059165164</v>
+        <v>0.4470864134000867</v>
       </c>
       <c r="E2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.74030511160553691</v>
+        <v>0.3880882657530822</v>
       </c>
       <c r="F2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.8669100084688891</v>
+        <v>0.69921771351351503</v>
       </c>
       <c r="G2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.78513870986033518</v>
+        <v>0.9645844580929539</v>
       </c>
       <c r="H2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.74116346421657064</v>
+        <v>0.61201903967237892</v>
       </c>
       <c r="I2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.54735576782478346</v>
+        <v>0.47537000075456604</v>
       </c>
       <c r="J2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.89592292185851252</v>
+        <v>0.13403415517922579</v>
       </c>
       <c r="K2">
         <f t="shared" ca="1" si="0"/>
-        <v>7.3430529415092871E-2</v>
+        <v>0.47229311495923199</v>
       </c>
       <c r="L2">
         <f t="shared" ca="1" si="0"/>
-        <v>2.5176309101693994E-2</v>
+        <v>0.52374578227005419</v>
       </c>
       <c r="M2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.37646540213625634</v>
+        <v>0.5960008569573213</v>
       </c>
       <c r="N2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.80117039857117711</v>
+        <v>0.10926169926226725</v>
       </c>
       <c r="O2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.59660859219810858</v>
+        <v>0.65774177067028672</v>
       </c>
       <c r="P2">
         <f t="shared" ca="1" si="0"/>
-        <v>5.3513354511471656E-2</v>
+        <v>0.74192695206864712</v>
       </c>
       <c r="Q2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.26335791473110592</v>
+        <v>0.32083277710577573</v>
       </c>
       <c r="R2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.64554997819644822</v>
+        <v>0.95850666957382391</v>
       </c>
       <c r="S2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.40987718217251645</v>
+        <v>0.54396753806056219</v>
       </c>
       <c r="T2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.62459377008707428</v>
+        <v>0.95247107296513078</v>
       </c>
       <c r="U2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.28390042493753398</v>
+        <v>0.95923758007524806</v>
       </c>
       <c r="V2">
         <f t="shared" ca="1" si="0"/>
-        <v>2.1773990481188776E-2</v>
+        <v>8.7819419387165087E-2</v>
       </c>
       <c r="W2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.84453416524938818</v>
+        <v>0.67115969164518785</v>
       </c>
       <c r="X2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.38282287569535178</v>
+        <v>0.62967991394682621</v>
       </c>
       <c r="Y2">
         <f t="shared" ca="1" si="0"/>
-        <v>2.1420738429736463E-2</v>
+        <v>0.27667229792767489</v>
       </c>
       <c r="Z2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.66220624662448535</v>
+        <v>0.90226336463001666</v>
       </c>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.25">
@@ -9943,7 +9943,7 @@
     </row>
     <row r="10" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L10">
         <v>4</v>
@@ -13158,7 +13158,7 @@
         <v>1.426184227044502</v>
       </c>
       <c r="K4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BL4" t="s">
         <v>90</v>
@@ -13215,13 +13215,13 @@
         <v>92</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O5">
         <v>2</v>
       </c>
       <c r="P5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="W5" t="s">
         <v>46</v>
@@ -13314,13 +13314,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O6">
         <v>2</v>
       </c>
       <c r="P6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W6">
         <v>1</v>
@@ -14035,16 +14035,16 @@
     </row>
     <row r="10" spans="2:82" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K10" t="s">
+        <v>231</v>
+      </c>
+      <c r="O10" t="s">
         <v>232</v>
       </c>
-      <c r="O10" t="s">
-        <v>233</v>
-      </c>
       <c r="S10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="V10">
         <v>4</v>
@@ -18579,7 +18579,7 @@
     </row>
     <row r="63" spans="10:52" x14ac:dyDescent="0.25">
       <c r="J63" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N63" t="s">
         <v>54</v>
@@ -18886,7 +18886,7 @@
       </c>
       <c r="AD77" s="59"/>
       <c r="AE77" s="74" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AF77" s="74"/>
       <c r="AG77" s="74"/>
@@ -19975,7 +19975,7 @@
     </row>
     <row r="10" spans="2:99" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I10">
         <v>4</v>
@@ -20293,7 +20293,7 @@
     </row>
     <row r="12" spans="2:99" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="6"/>
@@ -22665,7 +22665,7 @@
         <v>162</v>
       </c>
       <c r="M45" s="38" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N45" s="6"/>
       <c r="P45" t="s">
@@ -23190,7 +23190,7 @@
         <v>-7.8283033501264032E-2</v>
       </c>
       <c r="BT55" t="s">
-        <v>176</v>
+        <v>238</v>
       </c>
     </row>
     <row r="56" spans="9:77" x14ac:dyDescent="0.25">
@@ -23363,13 +23363,13 @@
         <v>175</v>
       </c>
       <c r="BQ62" t="s">
+        <v>176</v>
+      </c>
+      <c r="BS62" s="78" t="s">
         <v>177</v>
       </c>
-      <c r="BS62" s="78" t="s">
+      <c r="BU62" s="78" t="s">
         <v>178</v>
-      </c>
-      <c r="BU62" s="78" t="s">
-        <v>179</v>
       </c>
       <c r="BX62" t="s">
         <v>18</v>
@@ -24088,13 +24088,13 @@
         <v>175</v>
       </c>
       <c r="BQ73" t="s">
+        <v>176</v>
+      </c>
+      <c r="BS73" s="78" t="s">
         <v>177</v>
       </c>
-      <c r="BS73" s="78" t="s">
+      <c r="BU73" s="78" t="s">
         <v>178</v>
-      </c>
-      <c r="BU73" s="78" t="s">
-        <v>179</v>
       </c>
       <c r="BX73" t="s">
         <v>18</v>
@@ -24700,7 +24700,7 @@
     <row r="81" spans="75:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="82" spans="75:80" x14ac:dyDescent="0.25">
       <c r="BX82" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="CA82" s="38" t="s">
         <v>80</v>
@@ -24836,7 +24836,7 @@
     </row>
     <row r="91" spans="75:80" x14ac:dyDescent="0.25">
       <c r="CA91" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -24875,11 +24875,11 @@
         <v>77</v>
       </c>
       <c r="Q2" s="32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R2" s="13"/>
       <c r="T2" s="89" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U2" s="89"/>
       <c r="V2" s="89"/>
@@ -24899,7 +24899,7 @@
         <v>44</v>
       </c>
       <c r="I3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L3" t="s">
         <v>76</v>
@@ -24924,7 +24924,7 @@
     <row r="4" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
       <c r="C4" s="14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14">
@@ -24953,18 +24953,18 @@
         <v>44</v>
       </c>
       <c r="Q4" t="s">
+        <v>199</v>
+      </c>
+      <c r="R4" t="s">
         <v>200</v>
       </c>
-      <c r="R4" t="s">
-        <v>201</v>
-      </c>
       <c r="T4" s="33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="2:31" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -25057,7 +25057,7 @@
     <row r="7" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="14"/>
       <c r="C7" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D7" s="14">
         <v>1</v>
@@ -25101,10 +25101,10 @@
     </row>
     <row r="8" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="86" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -25148,7 +25148,7 @@
     <row r="9" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B9" s="87"/>
       <c r="C9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -25191,7 +25191,7 @@
     <row r="10" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="87"/>
       <c r="C10" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D10" s="14">
         <v>4</v>
@@ -25224,51 +25224,51 @@
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" t="s">
+        <v>208</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="S10" t="s">
+        <v>200</v>
+      </c>
+      <c r="T10" t="s">
+        <v>204</v>
+      </c>
+      <c r="U10" t="s">
+        <v>206</v>
+      </c>
+      <c r="V10" t="s">
         <v>209</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="S10" t="s">
-        <v>201</v>
-      </c>
-      <c r="T10" t="s">
+      <c r="W10" t="s">
+        <v>207</v>
+      </c>
+      <c r="X10" t="s">
         <v>205</v>
       </c>
-      <c r="U10" t="s">
-        <v>207</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="Y10" t="s">
         <v>210</v>
       </c>
-      <c r="W10" t="s">
+      <c r="Z10" t="s">
+        <v>211</v>
+      </c>
+      <c r="AB10" t="s">
         <v>208</v>
       </c>
-      <c r="X10" t="s">
-        <v>206</v>
-      </c>
-      <c r="Y10" t="s">
+      <c r="AC10" t="s">
+        <v>210</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>209</v>
+      </c>
+      <c r="AE10" t="s">
         <v>211</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>212</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>211</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>210</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="11" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="86" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C11" t="s">
         <v>91</v>
@@ -25509,10 +25509,10 @@
     </row>
     <row r="14" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="86" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -25585,7 +25585,7 @@
     <row r="15" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B15" s="87"/>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D15">
         <v>3</v>
@@ -25673,7 +25673,7 @@
     <row r="16" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="88"/>
       <c r="C16" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
@@ -25756,13 +25756,13 @@
         <v>0</v>
       </c>
       <c r="AC17" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD17" t="s">
         <v>213</v>
       </c>
-      <c r="AD17" t="s">
+      <c r="AE17" t="s">
         <v>214</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="18" spans="5:31" x14ac:dyDescent="0.25">
@@ -25791,7 +25791,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AC18">
         <f>ABS(AC12-AC11)</f>
@@ -25864,7 +25864,7 @@
         <v>73</v>
       </c>
       <c r="M20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R20" s="3">
         <f>IF($Q$6&gt;$Q19,1,0)</f>
@@ -25911,7 +25911,7 @@
         <v>75</v>
       </c>
       <c r="M21" s="84" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N21" s="84"/>
       <c r="R21" s="3">
@@ -25959,13 +25959,13 @@
         <v>3</v>
       </c>
       <c r="K22" s="87" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M22" t="s">
+        <v>202</v>
+      </c>
+      <c r="N22" t="s">
         <v>203</v>
-      </c>
-      <c r="N22" t="s">
-        <v>204</v>
       </c>
       <c r="R22" s="3">
         <f>IF($Q$8&gt;$Q19,1,0)</f>
@@ -25992,7 +25992,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AE22" s="34">
         <f>SUM(AE18:AE21)</f>
@@ -26008,13 +26008,13 @@
       </c>
       <c r="K23" s="87"/>
       <c r="L23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q23" s="3">
         <v>0.15</v>
@@ -26065,13 +26065,13 @@
       </c>
       <c r="K24" s="87"/>
       <c r="L24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R24" s="3">
         <f>IF($Q$6&gt;$Q23,1,0)</f>
@@ -26098,18 +26098,18 @@
         <v>0</v>
       </c>
       <c r="AC24" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD24" t="s">
         <v>213</v>
       </c>
-      <c r="AD24" t="s">
+      <c r="AE24" t="s">
         <v>214</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="25" spans="5:31" x14ac:dyDescent="0.25">
       <c r="F25" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K25" s="87"/>
       <c r="R25" s="3">
@@ -26137,7 +26137,7 @@
         <v>0</v>
       </c>
       <c r="AB25" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AC25">
         <f>ABS(AD12-AD11)</f>
@@ -26307,7 +26307,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AE29" s="34">
         <f>SUM(AE25:AE28)</f>
@@ -26340,7 +26340,7 @@
         <v>0</v>
       </c>
       <c r="AB30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31" spans="5:31" x14ac:dyDescent="0.25">
@@ -26358,10 +26358,10 @@
     </row>
     <row r="34" spans="17:31" x14ac:dyDescent="0.25">
       <c r="Q34" t="s">
+        <v>199</v>
+      </c>
+      <c r="R34" t="s">
         <v>200</v>
-      </c>
-      <c r="R34" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="35" spans="17:31" x14ac:dyDescent="0.25">
@@ -26409,46 +26409,46 @@
     </row>
     <row r="40" spans="17:31" x14ac:dyDescent="0.25">
       <c r="Q40" t="s">
+        <v>208</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="S40" t="s">
+        <v>200</v>
+      </c>
+      <c r="T40" t="s">
+        <v>204</v>
+      </c>
+      <c r="U40" t="s">
+        <v>206</v>
+      </c>
+      <c r="V40" t="s">
         <v>209</v>
       </c>
-      <c r="R40" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="S40" t="s">
-        <v>201</v>
-      </c>
-      <c r="T40" t="s">
+      <c r="W40" t="s">
+        <v>207</v>
+      </c>
+      <c r="X40" t="s">
         <v>205</v>
       </c>
-      <c r="U40" t="s">
-        <v>207</v>
-      </c>
-      <c r="V40" t="s">
+      <c r="Y40" t="s">
         <v>210</v>
       </c>
-      <c r="W40" t="s">
+      <c r="Z40" t="s">
+        <v>211</v>
+      </c>
+      <c r="AB40" t="s">
         <v>208</v>
       </c>
-      <c r="X40" t="s">
-        <v>206</v>
-      </c>
-      <c r="Y40" t="s">
+      <c r="AC40" t="s">
+        <v>210</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>209</v>
+      </c>
+      <c r="AE40" t="s">
         <v>211</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>212</v>
-      </c>
-      <c r="AB40" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC40" t="s">
-        <v>211</v>
-      </c>
-      <c r="AD40" t="s">
-        <v>210</v>
-      </c>
-      <c r="AE40" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="41" spans="17:31" x14ac:dyDescent="0.25">
@@ -26727,13 +26727,13 @@
         <v>0</v>
       </c>
       <c r="AC47" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD47" t="s">
         <v>213</v>
       </c>
-      <c r="AD47" t="s">
+      <c r="AE47" t="s">
         <v>214</v>
-      </c>
-      <c r="AE47" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="48" spans="17:31" x14ac:dyDescent="0.25">
@@ -26762,7 +26762,7 @@
         <v>0</v>
       </c>
       <c r="AB48" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AC48">
         <f>ABS(AC42-AC41)</f>
@@ -26932,7 +26932,7 @@
         <v>0</v>
       </c>
       <c r="AD52" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AE52" s="34">
         <f>SUM(AE48:AE51)</f>
@@ -27006,13 +27006,13 @@
         <v>0</v>
       </c>
       <c r="AC54" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD54" t="s">
         <v>213</v>
       </c>
-      <c r="AD54" t="s">
+      <c r="AE54" t="s">
         <v>214</v>
-      </c>
-      <c r="AE54" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="55" spans="17:31" x14ac:dyDescent="0.25">
@@ -27041,7 +27041,7 @@
         <v>0</v>
       </c>
       <c r="AB55" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AC55">
         <f>ABS(AD42-AD41)</f>
@@ -27211,7 +27211,7 @@
         <v>0</v>
       </c>
       <c r="AD59" s="37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AE59" s="34">
         <f>SUM(AE55:AE58)</f>
@@ -27244,7 +27244,7 @@
         <v>0</v>
       </c>
       <c r="AB60" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="63" spans="17:31" x14ac:dyDescent="0.25">
@@ -27255,10 +27255,10 @@
     </row>
     <row r="64" spans="17:31" x14ac:dyDescent="0.25">
       <c r="Q64" t="s">
+        <v>199</v>
+      </c>
+      <c r="R64" t="s">
         <v>200</v>
-      </c>
-      <c r="R64" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="65" spans="17:31" x14ac:dyDescent="0.25">
@@ -27306,46 +27306,46 @@
     </row>
     <row r="70" spans="17:31" x14ac:dyDescent="0.25">
       <c r="Q70" t="s">
+        <v>208</v>
+      </c>
+      <c r="R70" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="S70" t="s">
+        <v>200</v>
+      </c>
+      <c r="T70" t="s">
+        <v>204</v>
+      </c>
+      <c r="U70" t="s">
+        <v>206</v>
+      </c>
+      <c r="V70" t="s">
         <v>209</v>
       </c>
-      <c r="R70" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="S70" t="s">
-        <v>201</v>
-      </c>
-      <c r="T70" t="s">
+      <c r="W70" t="s">
+        <v>207</v>
+      </c>
+      <c r="X70" t="s">
         <v>205</v>
       </c>
-      <c r="U70" t="s">
-        <v>207</v>
-      </c>
-      <c r="V70" t="s">
+      <c r="Y70" t="s">
         <v>210</v>
       </c>
-      <c r="W70" t="s">
+      <c r="Z70" t="s">
+        <v>211</v>
+      </c>
+      <c r="AB70" t="s">
         <v>208</v>
       </c>
-      <c r="X70" t="s">
-        <v>206</v>
-      </c>
-      <c r="Y70" t="s">
+      <c r="AC70" t="s">
+        <v>210</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>209</v>
+      </c>
+      <c r="AE70" t="s">
         <v>211</v>
-      </c>
-      <c r="Z70" t="s">
-        <v>212</v>
-      </c>
-      <c r="AB70" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC70" t="s">
-        <v>211</v>
-      </c>
-      <c r="AD70" t="s">
-        <v>210</v>
-      </c>
-      <c r="AE70" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="71" spans="17:31" x14ac:dyDescent="0.25">
@@ -27624,13 +27624,13 @@
         <v>0</v>
       </c>
       <c r="AC77" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD77" t="s">
         <v>213</v>
       </c>
-      <c r="AD77" t="s">
+      <c r="AE77" t="s">
         <v>214</v>
-      </c>
-      <c r="AE77" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="78" spans="17:31" x14ac:dyDescent="0.25">
@@ -27659,7 +27659,7 @@
         <v>1</v>
       </c>
       <c r="AB78" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AC78">
         <f>ABS(AC72-AC71)</f>
@@ -27829,7 +27829,7 @@
         <v>0</v>
       </c>
       <c r="AD82" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AE82" s="34">
         <f>SUM(AE78:AE81)</f>
@@ -27903,13 +27903,13 @@
         <v>0</v>
       </c>
       <c r="AC84" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD84" t="s">
         <v>213</v>
       </c>
-      <c r="AD84" t="s">
+      <c r="AE84" t="s">
         <v>214</v>
-      </c>
-      <c r="AE84" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="85" spans="17:31" x14ac:dyDescent="0.25">
@@ -27938,7 +27938,7 @@
         <v>0</v>
       </c>
       <c r="AB85" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AC85">
         <f>ABS(AD72-AD71)</f>
@@ -28108,7 +28108,7 @@
         <v>0</v>
       </c>
       <c r="AD89" s="37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AE89" s="34">
         <f>SUM(AE85:AE88)</f>
@@ -28141,19 +28141,19 @@
         <v>0</v>
       </c>
       <c r="AB90" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="17:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="93" spans="17:31" x14ac:dyDescent="0.25">
       <c r="AB93" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AC93" s="6"/>
     </row>
     <row r="94" spans="17:31" x14ac:dyDescent="0.25">
       <c r="AB94" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AC94" s="8">
         <f>AVERAGE(AE29,AE59,AE89)</f>
@@ -28162,7 +28162,7 @@
     </row>
     <row r="95" spans="17:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AB95" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AC95" s="11">
         <f>AVERAGE(AE22,AE52,AE82)</f>
@@ -28190,7 +28190,7 @@
   <sheetData>
     <row r="2" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="B2" s="30" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
@@ -28204,47 +28204,47 @@
     </row>
     <row r="4" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="C4" s="30" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D4" s="30"/>
       <c r="E4" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="C5" s="30" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D5" s="30"/>
       <c r="E5" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="C6" s="30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D6" s="30"/>
       <c r="E6" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="C7" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D7" s="30"/>
       <c r="E7" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="C8" s="30" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D8" s="30"/>
       <c r="E8" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="21" x14ac:dyDescent="0.35">
@@ -28259,14 +28259,14 @@
     </row>
     <row r="11" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="B11" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
     </row>
     <row r="12" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="C12" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D12" s="30"/>
       <c r="E12" s="30"/>
@@ -28280,7 +28280,7 @@
     </row>
     <row r="14" spans="2:5" ht="21" x14ac:dyDescent="0.35">
       <c r="C14" s="30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D14" s="30"/>
       <c r="E14" s="30"/>

--- a/ai/manualisation.xlsx
+++ b/ai/manualisation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DiskE\SKRIPSI-CODE\skripsi-code\ai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\100-KULIAH\SKRIPSI\skripsi-code\ai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972670CB-96EA-4A81-9D27-14A329773C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5158FE7-00A2-4216-9D11-DB6231D242E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{145D0042-0CBE-48BE-846C-2BE8EAD29D31}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{145D0042-0CBE-48BE-846C-2BE8EAD29D31}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="3" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="320">
   <si>
     <t>W_IR</t>
   </si>
@@ -781,7 +781,250 @@
     <t>O_Attn</t>
   </si>
   <si>
-    <t>(2.91)</t>
+    <t>Ini dijelaskan di Bab 2.2.4.1</t>
+  </si>
+  <si>
+    <t>Normalisasi per fitur/pita mel</t>
+  </si>
+  <si>
+    <t>Pers 2.20</t>
+  </si>
+  <si>
+    <t>Pers 2.9</t>
+  </si>
+  <si>
+    <t>Pers 2.8</t>
+  </si>
+  <si>
+    <t>Pers 2.15</t>
+  </si>
+  <si>
+    <t>Pers 2.16</t>
+  </si>
+  <si>
+    <t>Pers 2.23</t>
+  </si>
+  <si>
+    <t>Pers 2.24</t>
+  </si>
+  <si>
+    <t>Pers 2.92</t>
+  </si>
+  <si>
+    <t>Pers 2.94</t>
+  </si>
+  <si>
+    <t>Pers 2.95</t>
+  </si>
+  <si>
+    <t>Pers 2.122</t>
+  </si>
+  <si>
+    <t>Pers 2.100</t>
+  </si>
+  <si>
+    <t>Pers 2.101</t>
+  </si>
+  <si>
+    <t>Pers 2.102</t>
+  </si>
+  <si>
+    <t>Pers 2.104</t>
+  </si>
+  <si>
+    <t>Pers 2.25</t>
+  </si>
+  <si>
+    <t>Pers 2.26</t>
+  </si>
+  <si>
+    <t>Pers 2.27</t>
+  </si>
+  <si>
+    <t>Pers 2.31</t>
+  </si>
+  <si>
+    <t>Pers 2.10</t>
+  </si>
+  <si>
+    <t>Pers 2.11</t>
+  </si>
+  <si>
+    <t>Pers 2.13</t>
+  </si>
+  <si>
+    <t>Pers 2.14</t>
+  </si>
+  <si>
+    <t>Pers 2.17</t>
+  </si>
+  <si>
+    <t>Pers 2.18</t>
+  </si>
+  <si>
+    <t>Pers 2.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H  </t>
+  </si>
+  <si>
+    <t>Pers 2.32</t>
+  </si>
+  <si>
+    <t>Pers 2.34</t>
+  </si>
+  <si>
+    <t>Pers 2.35</t>
+  </si>
+  <si>
+    <t>Pers 2.37</t>
+  </si>
+  <si>
+    <t>Pers 2.38</t>
+  </si>
+  <si>
+    <t>Pers 2.93</t>
+  </si>
+  <si>
+    <t>Pers 2.39</t>
+  </si>
+  <si>
+    <t>Pers 2.43</t>
+  </si>
+  <si>
+    <t>Pers 2.44</t>
+  </si>
+  <si>
+    <t>Pers 2.45</t>
+  </si>
+  <si>
+    <t>Pers 2.46</t>
+  </si>
+  <si>
+    <t>Pers 2.47</t>
+  </si>
+  <si>
+    <t>Pers 2.48</t>
+  </si>
+  <si>
+    <t>Pers 2.49</t>
+  </si>
+  <si>
+    <t>Pers 2.50</t>
+  </si>
+  <si>
+    <t>Pers 2.51</t>
+  </si>
+  <si>
+    <t>Pers 2.52</t>
+  </si>
+  <si>
+    <t>Pers 2.53</t>
+  </si>
+  <si>
+    <t>Pers 2.54</t>
+  </si>
+  <si>
+    <t>Pers 2.55</t>
+  </si>
+  <si>
+    <t>Pers 2.56</t>
+  </si>
+  <si>
+    <t>Pers 2.57</t>
+  </si>
+  <si>
+    <t>Pers 2.58</t>
+  </si>
+  <si>
+    <t>Pers 2.59</t>
+  </si>
+  <si>
+    <t>Pers 2.91</t>
+  </si>
+  <si>
+    <t>Pers 2.63</t>
+  </si>
+  <si>
+    <t>Pers 2.62</t>
+  </si>
+  <si>
+    <t>Pers 2.60</t>
+  </si>
+  <si>
+    <t>Pers 2.64</t>
+  </si>
+  <si>
+    <t>Pers 2.65</t>
+  </si>
+  <si>
+    <t>Pers 2.66</t>
+  </si>
+  <si>
+    <t>Pers 2.67</t>
+  </si>
+  <si>
+    <t>Pers 2.68</t>
+  </si>
+  <si>
+    <t>Pers 2.71</t>
+  </si>
+  <si>
+    <t>Pers 2.72</t>
+  </si>
+  <si>
+    <t>Pers 2.73</t>
+  </si>
+  <si>
+    <t>Pers 2.74</t>
+  </si>
+  <si>
+    <t>Pers 2.75</t>
+  </si>
+  <si>
+    <t>Pers 2.78</t>
+  </si>
+  <si>
+    <t>Pers 2.76</t>
+  </si>
+  <si>
+    <t>Pers 2.82</t>
+  </si>
+  <si>
+    <t>Pers 2.83</t>
+  </si>
+  <si>
+    <t>Pers 2.84</t>
+  </si>
+  <si>
+    <t>Pers 2.86</t>
+  </si>
+  <si>
+    <t>Pers 2.87</t>
+  </si>
+  <si>
+    <t>Pers 2.88</t>
+  </si>
+  <si>
+    <t>Pers 2.89</t>
+  </si>
+  <si>
+    <t>Pers 2.90</t>
+  </si>
+  <si>
+    <t>Pers 2.123</t>
+  </si>
+  <si>
+    <t>Pers 2.124</t>
+  </si>
+  <si>
+    <t>Pers 2.125</t>
+  </si>
+  <si>
+    <t>Pers 2.126</t>
+  </si>
+  <si>
+    <t>Pers 2.127</t>
   </si>
 </sst>
 </file>
@@ -1237,7 +1480,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1358,6 +1601,18 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -7410,10 +7665,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03EC0F54-235A-426D-B2F4-B5B3CFC2F042}">
-  <dimension ref="A2:M19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>238</v>
+      </c>
+      <c r="K1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>45</v>
       </c>
@@ -7438,7 +7701,7 @@
       <c r="J2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>45</v>
       </c>
@@ -7473,7 +7736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -7516,7 +7779,7 @@
         <v>-0.54807215149909738</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -7559,7 +7822,7 @@
         <v>-1.6514230540804744</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -7602,7 +7865,7 @@
         <v>-0.51000095484744268</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -7645,7 +7908,7 @@
         <v>0.61213976054071273</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -7688,7 +7951,7 @@
         <v>1.3115002107703582</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -7731,7 +7994,7 @@
         <v>0.78585618911594302</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="H10" t="s">
         <v>225</v>
       </c>
@@ -7756,7 +8019,7 @@
         <v>-19.660174304379684</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="H11" t="s">
         <v>226</v>
       </c>
@@ -7781,7 +8044,7 @@
         <v>21.6415881341069</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>47</v>
       </c>
@@ -7789,7 +8052,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>42</v>
       </c>
@@ -7800,7 +8063,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>1</v>
       </c>
@@ -7814,7 +8077,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
@@ -7836,7 +8099,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -7858,7 +8121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>3</v>
       </c>
@@ -7878,7 +8141,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>4</v>
       </c>
@@ -7895,7 +8158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B19" s="32" t="s">
         <v>189</v>
       </c>
@@ -7915,114 +8178,114 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75D6B299-2029-405E-BE40-B239C331F6AC}">
   <dimension ref="B2:Z3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="3" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>40</v>
       </c>
       <c r="C2">
         <f ca="1">RAND()</f>
-        <v>0.46293499115903169</v>
+        <v>0.43057286975935449</v>
       </c>
       <c r="D2">
         <f t="shared" ref="D2:Z2" ca="1" si="0">RAND()</f>
-        <v>0.4470864134000867</v>
+        <v>0.31294853361309871</v>
       </c>
       <c r="E2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.3880882657530822</v>
+        <v>0.85297780739100126</v>
       </c>
       <c r="F2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.69921771351351503</v>
+        <v>0.58569296255756664</v>
       </c>
       <c r="G2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9645844580929539</v>
+        <v>0.19389175809730197</v>
       </c>
       <c r="H2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.61201903967237892</v>
+        <v>5.6549442343509337E-2</v>
       </c>
       <c r="I2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.47537000075456604</v>
+        <v>0.87197816177079868</v>
       </c>
       <c r="J2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.13403415517922579</v>
+        <v>0.28208267439078993</v>
       </c>
       <c r="K2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.47229311495923199</v>
+        <v>8.5751688364835044E-2</v>
       </c>
       <c r="L2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.52374578227005419</v>
+        <v>0.44424798035031066</v>
       </c>
       <c r="M2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.5960008569573213</v>
+        <v>0.22712171799441228</v>
       </c>
       <c r="N2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.10926169926226725</v>
+        <v>0.39875382855930841</v>
       </c>
       <c r="O2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.65774177067028672</v>
+        <v>0.63822439144489274</v>
       </c>
       <c r="P2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.74192695206864712</v>
+        <v>0.99804943511162092</v>
       </c>
       <c r="Q2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.32083277710577573</v>
+        <v>0.80684620760580572</v>
       </c>
       <c r="R2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.95850666957382391</v>
+        <v>0.86939368161052</v>
       </c>
       <c r="S2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.54396753806056219</v>
+        <v>0.4031934812499598</v>
       </c>
       <c r="T2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.95247107296513078</v>
+        <v>0.92020275315827238</v>
       </c>
       <c r="U2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.95923758007524806</v>
+        <v>0.2963478197933892</v>
       </c>
       <c r="V2">
         <f t="shared" ca="1" si="0"/>
-        <v>8.7819419387165087E-2</v>
+        <v>0.42771142867270973</v>
       </c>
       <c r="W2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.67115969164518785</v>
+        <v>0.25753363783364291</v>
       </c>
       <c r="X2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.62967991394682621</v>
+        <v>0.50400828660982977</v>
       </c>
       <c r="Y2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.27667229792767489</v>
+        <v>0.14199483609720931</v>
       </c>
       <c r="Z2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.90226336463001666</v>
-      </c>
-    </row>
-    <row r="3" spans="2:26" x14ac:dyDescent="0.25">
+        <v>0.18076993817588571</v>
+      </c>
+    </row>
+    <row r="3" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>41</v>
       </c>
@@ -8107,15 +8370,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40FC86D-D191-4819-9BFB-FCF3C2D84B35}">
   <dimension ref="A2:W54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="13" max="17" width="12.5703125" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" customWidth="1"/>
-    <col min="21" max="24" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.109375" customWidth="1"/>
+    <col min="14" max="17" width="12.5546875" customWidth="1"/>
+    <col min="20" max="20" width="11.44140625" customWidth="1"/>
+    <col min="21" max="24" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:23" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A2" cm="1">
         <f t="array" ref="A2:F9">DATA!H2:M9</f>
         <v>0</v>
@@ -8142,7 +8406,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:23" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A3">
         <v>0</v>
       </c>
@@ -8168,7 +8432,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -8188,7 +8452,7 @@
         <v>-0.54807215149909738</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -8222,7 +8486,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -8260,7 +8524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4</v>
       </c>
@@ -8304,7 +8568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -8342,7 +8606,7 @@
         <v>0.51600000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>6</v>
       </c>
@@ -8380,7 +8644,7 @@
         <v>-0.97699999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="L10" s="7">
         <v>4</v>
       </c>
@@ -8394,7 +8658,7 @@
         <v>-0.91400000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>59</v>
       </c>
@@ -8413,8 +8677,11 @@
       <c r="T11" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U11" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12">
         <v>1</v>
       </c>
@@ -8440,7 +8707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -8477,7 +8744,7 @@
         <v>1.426184227044502</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -8514,7 +8781,7 @@
         <v>0.83446165212430812</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>3</v>
       </c>
@@ -8554,7 +8821,7 @@
         <v>1.8393159934697598</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>4</v>
       </c>
@@ -8587,7 +8854,7 @@
         <v>0.40501335750777256</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>5</v>
       </c>
@@ -8614,6 +8881,9 @@
       </c>
       <c r="M17" t="s">
         <v>51</v>
+      </c>
+      <c r="N17" t="s">
+        <v>242</v>
       </c>
       <c r="S17">
         <v>5</v>
@@ -8623,7 +8893,7 @@
         <v>0.53701995183003415</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>6</v>
       </c>
@@ -8671,7 +8941,7 @@
         <v>1.2588938475691771</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>7</v>
       </c>
@@ -8720,7 +8990,7 @@
         <v>0.2231704534676876</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>8</v>
       </c>
@@ -8772,8 +9042,11 @@
       <c r="T20" s="6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U20" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>9</v>
       </c>
@@ -8826,7 +9099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>10</v>
       </c>
@@ -8882,7 +9155,7 @@
         <v>1.426184227044502</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L23">
         <v>5</v>
       </c>
@@ -8914,7 +9187,7 @@
         <v>0.83446165212430812</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>60</v>
       </c>
@@ -8949,7 +9222,7 @@
         <v>1.8393159934697598</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>1</v>
       </c>
@@ -8961,7 +9234,7 @@
         <v>0.40501335750777256</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1</v>
       </c>
@@ -8972,6 +9245,9 @@
       <c r="M26" t="s">
         <v>53</v>
       </c>
+      <c r="N26" t="s">
+        <v>241</v>
+      </c>
       <c r="S26" s="7">
         <v>5</v>
       </c>
@@ -8980,7 +9256,7 @@
         <v>0.53701995183003415</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2</v>
       </c>
@@ -9011,7 +9287,7 @@
         <v>1.2588938475691771</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -9043,7 +9319,7 @@
         <v>0.2231704534676876</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>4</v>
       </c>
@@ -9076,7 +9352,7 @@
       </c>
       <c r="T29" s="32"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>5</v>
       </c>
@@ -9108,7 +9384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>6</v>
       </c>
@@ -9140,7 +9416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L32">
         <v>5</v>
       </c>
@@ -9165,7 +9441,7 @@
         <v>3.6991230119856033</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>61</v>
       </c>
@@ -9193,12 +9469,12 @@
         <v>3.0540707238032767</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1</v>
       </c>
@@ -9206,7 +9482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2</v>
       </c>
@@ -9218,9 +9494,11 @@
       <c r="M36" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="N36" s="6"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N36" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -9233,7 +9511,7 @@
       </c>
       <c r="N37" s="8"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>4</v>
       </c>
@@ -9246,7 +9524,7 @@
       </c>
       <c r="N38" s="8"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>5</v>
       </c>
@@ -9262,7 +9540,7 @@
       </c>
       <c r="N39" s="8"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>6</v>
       </c>
@@ -9278,7 +9556,7 @@
       </c>
       <c r="N40" s="8"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>7</v>
       </c>
@@ -9294,7 +9572,7 @@
       </c>
       <c r="N41" s="8"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>8</v>
       </c>
@@ -9310,7 +9588,7 @@
       </c>
       <c r="N42" s="8"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="L43" s="7">
         <v>5</v>
       </c>
@@ -9320,7 +9598,7 @@
       </c>
       <c r="N43" s="8"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L44" s="9">
         <v>6</v>
       </c>
@@ -9330,15 +9608,17 @@
       </c>
       <c r="N44" s="11"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="L47" s="4"/>
       <c r="M47" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="N47" s="6"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="N47" s="90" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="L48" s="7"/>
       <c r="M48">
         <v>1</v>
@@ -9347,7 +9627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="12:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L49" s="7">
         <v>1</v>
       </c>
@@ -9360,7 +9640,7 @@
         <v>1.426184227044502</v>
       </c>
     </row>
-    <row r="50" spans="12:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L50" s="7">
         <v>2</v>
       </c>
@@ -9373,7 +9653,7 @@
         <v>0.83446165212430812</v>
       </c>
     </row>
-    <row r="51" spans="12:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L51" s="7">
         <v>3</v>
       </c>
@@ -9386,7 +9666,7 @@
         <v>1.8393159934697598</v>
       </c>
     </row>
-    <row r="52" spans="12:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L52" s="7">
         <v>4</v>
       </c>
@@ -9399,7 +9679,7 @@
         <v>0.40501335750777256</v>
       </c>
     </row>
-    <row r="53" spans="12:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L53" s="7">
         <v>5</v>
       </c>
@@ -9412,7 +9692,7 @@
         <v>0.53701995183003415</v>
       </c>
     </row>
-    <row r="54" spans="12:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="12:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L54" s="9">
         <v>6</v>
       </c>
@@ -9434,16 +9714,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2772A31-BCA1-42FB-B9A3-5280F010A639}">
   <dimension ref="B1:AS76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="6" width="12.5703125" customWidth="1"/>
-    <col min="9" max="10" width="12.140625" customWidth="1"/>
+    <col min="3" max="6" width="12.5546875" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" customWidth="1"/>
+    <col min="20" max="20" width="9.77734375" customWidth="1"/>
+    <col min="22" max="22" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:42" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:42" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B2" s="4"/>
       <c r="C2" s="5" t="s">
         <v>62</v>
@@ -9462,7 +9744,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="2:42" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:42" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B3" s="7"/>
       <c r="C3">
         <v>1</v>
@@ -9507,7 +9789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="7">
         <v>1</v>
       </c>
@@ -9543,7 +9825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -9571,11 +9853,16 @@
       <c r="U5" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="V5" s="5"/>
+      <c r="V5" s="5" t="s">
+        <v>251</v>
+      </c>
       <c r="W5" s="6"/>
       <c r="AA5" t="s">
         <v>89</v>
       </c>
+      <c r="AB5" t="s">
+        <v>255</v>
+      </c>
       <c r="AI5">
         <v>0</v>
       </c>
@@ -9601,7 +9888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -9674,7 +9961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -9765,7 +10052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -9853,7 +10140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="9">
         <v>6</v>
       </c>
@@ -9941,7 +10228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>224</v>
       </c>
@@ -10014,7 +10301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H11" s="4"/>
       <c r="I11" s="39" t="s">
         <v>52</v>
@@ -10088,7 +10375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:42" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>63</v>
       </c>
@@ -10163,7 +10450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C13">
         <v>1</v>
       </c>
@@ -10238,7 +10525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>1</v>
       </c>
@@ -10289,11 +10576,16 @@
       <c r="AA14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="AB14" s="6"/>
+      <c r="AB14" s="6" t="s">
+        <v>256</v>
+      </c>
       <c r="AD14" s="4"/>
       <c r="AE14" s="39" t="s">
         <v>52</v>
       </c>
+      <c r="AF14" s="91" t="s">
+        <v>257</v>
+      </c>
       <c r="AI14">
         <v>0</v>
       </c>
@@ -10319,7 +10611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>2</v>
       </c>
@@ -10340,6 +10632,9 @@
       <c r="I15" t="s">
         <v>51</v>
       </c>
+      <c r="J15" t="s">
+        <v>245</v>
+      </c>
       <c r="L15">
         <v>9</v>
       </c>
@@ -10386,7 +10681,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>3</v>
       </c>
@@ -10460,7 +10755,7 @@
         <v>0.35202308581165037</v>
       </c>
     </row>
-    <row r="17" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>4</v>
       </c>
@@ -10556,7 +10851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>5</v>
       </c>
@@ -10652,7 +10947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>6</v>
       </c>
@@ -10706,7 +11001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>7</v>
       </c>
@@ -10738,6 +11033,9 @@
       <c r="M20" t="s">
         <v>68</v>
       </c>
+      <c r="N20" t="s">
+        <v>248</v>
+      </c>
       <c r="O20" s="4"/>
       <c r="P20" s="39" t="s">
         <v>52</v>
@@ -10746,11 +11044,17 @@
       <c r="U20" s="39" t="s">
         <v>52</v>
       </c>
+      <c r="V20" t="s">
+        <v>252</v>
+      </c>
       <c r="Z20" s="4"/>
       <c r="AA20" s="40" t="s">
         <v>80</v>
       </c>
       <c r="AB20" s="6"/>
+      <c r="AC20" t="s">
+        <v>258</v>
+      </c>
       <c r="AI20">
         <v>0</v>
       </c>
@@ -10778,7 +11082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:42" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>8</v>
       </c>
@@ -10850,7 +11154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:42" x14ac:dyDescent="0.3">
       <c r="H22">
         <v>6</v>
       </c>
@@ -10920,7 +11224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:42" x14ac:dyDescent="0.3">
       <c r="L23">
         <v>2</v>
       </c>
@@ -10978,9 +11282,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I24" t="s">
         <v>53</v>
+      </c>
+      <c r="J24" t="s">
+        <v>246</v>
       </c>
       <c r="L24">
         <v>3</v>
@@ -11039,7 +11346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I25">
         <v>1</v>
       </c>
@@ -11084,7 +11391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:42" x14ac:dyDescent="0.3">
       <c r="H26">
         <v>1</v>
       </c>
@@ -11101,6 +11408,9 @@
         <v>69</v>
       </c>
       <c r="N26" s="6"/>
+      <c r="O26" t="s">
+        <v>249</v>
+      </c>
       <c r="U26" t="s">
         <v>81</v>
       </c>
@@ -11140,7 +11450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H27">
         <v>2</v>
       </c>
@@ -11160,6 +11470,9 @@
       <c r="U27">
         <v>1</v>
       </c>
+      <c r="V27" t="s">
+        <v>253</v>
+      </c>
       <c r="Z27" s="9">
         <v>6</v>
       </c>
@@ -11196,7 +11509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:42" x14ac:dyDescent="0.3">
       <c r="H28">
         <v>3</v>
       </c>
@@ -11250,7 +11563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:42" x14ac:dyDescent="0.3">
       <c r="H29">
         <v>4</v>
       </c>
@@ -11283,7 +11596,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H30">
         <v>5</v>
       </c>
@@ -11313,7 +11626,7 @@
         <v>-0.10894187193569127</v>
       </c>
     </row>
-    <row r="31" spans="2:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H31">
         <v>6</v>
       </c>
@@ -11333,12 +11646,15 @@
         <v>-1.9090599122439475E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:42" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:42" ht="25.8" x14ac:dyDescent="0.5">
       <c r="L32" s="4"/>
       <c r="M32" s="40" t="s">
         <v>72</v>
       </c>
       <c r="N32" s="6"/>
+      <c r="O32" t="s">
+        <v>250</v>
+      </c>
       <c r="T32">
         <v>5</v>
       </c>
@@ -11350,7 +11666,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="8:45" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="33" spans="8:45" ht="25.8" x14ac:dyDescent="0.5">
       <c r="I33" t="s">
         <v>54</v>
       </c>
@@ -11372,9 +11688,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="8:45" x14ac:dyDescent="0.25">
+    <row r="34" spans="8:45" x14ac:dyDescent="0.3">
       <c r="I34" t="s">
         <v>65</v>
+      </c>
+      <c r="J34" t="s">
+        <v>247</v>
       </c>
       <c r="L34" s="22" t="s">
         <v>76</v>
@@ -11399,6 +11718,9 @@
       <c r="AC34" t="s">
         <v>51</v>
       </c>
+      <c r="AD34" t="s">
+        <v>259</v>
+      </c>
       <c r="AI34">
         <v>0</v>
       </c>
@@ -11433,7 +11755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="8:45" x14ac:dyDescent="0.25">
+    <row r="35" spans="8:45" x14ac:dyDescent="0.3">
       <c r="I35">
         <v>1</v>
       </c>
@@ -11509,7 +11831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="8:45" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="8:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H36">
         <v>1</v>
       </c>
@@ -11599,7 +11921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="8:45" x14ac:dyDescent="0.25">
+    <row r="37" spans="8:45" x14ac:dyDescent="0.3">
       <c r="H37">
         <v>2</v>
       </c>
@@ -11680,7 +12002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="8:45" x14ac:dyDescent="0.25">
+    <row r="38" spans="8:45" x14ac:dyDescent="0.3">
       <c r="H38">
         <v>3</v>
       </c>
@@ -11760,7 +12082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="8:45" x14ac:dyDescent="0.25">
+    <row r="39" spans="8:45" x14ac:dyDescent="0.3">
       <c r="H39">
         <v>4</v>
       </c>
@@ -11841,7 +12163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="8:45" x14ac:dyDescent="0.25">
+    <row r="40" spans="8:45" x14ac:dyDescent="0.3">
       <c r="H40">
         <v>5</v>
       </c>
@@ -11914,7 +12236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="8:45" x14ac:dyDescent="0.25">
+    <row r="41" spans="8:45" x14ac:dyDescent="0.3">
       <c r="H41">
         <v>6</v>
       </c>
@@ -11922,6 +12244,9 @@
         <f t="shared" si="20"/>
         <v>0.90914028044519068</v>
       </c>
+      <c r="T41" t="s">
+        <v>254</v>
+      </c>
       <c r="U41" s="45" t="s">
         <v>54</v>
       </c>
@@ -11993,7 +12318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="8:45" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="8:45" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="U42">
         <v>1</v>
       </c>
@@ -12040,7 +12365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="8:45" x14ac:dyDescent="0.25">
+    <row r="43" spans="8:45" x14ac:dyDescent="0.3">
       <c r="I43" t="s">
         <v>57</v>
       </c>
@@ -12066,6 +12391,9 @@
       <c r="AA43" t="s">
         <v>89</v>
       </c>
+      <c r="AB43" t="s">
+        <v>260</v>
+      </c>
       <c r="AI43">
         <v>0</v>
       </c>
@@ -12100,9 +12428,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="8:45" x14ac:dyDescent="0.25">
+    <row r="44" spans="8:45" x14ac:dyDescent="0.3">
       <c r="I44" t="s">
         <v>65</v>
+      </c>
+      <c r="J44" t="s">
+        <v>247</v>
       </c>
       <c r="T44">
         <v>2</v>
@@ -12172,7 +12503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="8:45" x14ac:dyDescent="0.25">
+    <row r="45" spans="8:45" x14ac:dyDescent="0.3">
       <c r="I45">
         <v>1</v>
       </c>
@@ -12252,7 +12583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="8:45" x14ac:dyDescent="0.25">
+    <row r="46" spans="8:45" x14ac:dyDescent="0.3">
       <c r="H46">
         <v>1</v>
       </c>
@@ -12303,7 +12634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="8:45" x14ac:dyDescent="0.25">
+    <row r="47" spans="8:45" x14ac:dyDescent="0.3">
       <c r="H47">
         <v>2</v>
       </c>
@@ -12354,7 +12685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="8:45" x14ac:dyDescent="0.25">
+    <row r="48" spans="8:45" x14ac:dyDescent="0.3">
       <c r="H48">
         <v>3</v>
       </c>
@@ -12405,7 +12736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="8:37" x14ac:dyDescent="0.25">
+    <row r="49" spans="8:37" x14ac:dyDescent="0.3">
       <c r="H49">
         <v>4</v>
       </c>
@@ -12437,7 +12768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="8:37" x14ac:dyDescent="0.25">
+    <row r="50" spans="8:37" x14ac:dyDescent="0.3">
       <c r="H50">
         <v>5</v>
       </c>
@@ -12445,6 +12776,9 @@
         <f t="shared" si="30"/>
         <v>1.9657323607427737</v>
       </c>
+      <c r="T50" t="s">
+        <v>254</v>
+      </c>
       <c r="U50" s="44" t="s">
         <v>57</v>
       </c>
@@ -12475,7 +12809,7 @@
         <v>1.2484029880609355E-2</v>
       </c>
     </row>
-    <row r="51" spans="8:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="8:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H51">
         <v>6</v>
       </c>
@@ -12493,7 +12827,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="8:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="8:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="T52">
         <v>1</v>
       </c>
@@ -12509,19 +12843,26 @@
       <c r="AA52" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="AB52" s="5"/>
+      <c r="AB52" s="5" t="s">
+        <v>261</v>
+      </c>
       <c r="AC52" s="6"/>
       <c r="AE52" s="4"/>
       <c r="AF52" s="39" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="53" spans="8:37" x14ac:dyDescent="0.25">
+      <c r="AG52" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="53" spans="8:37" x14ac:dyDescent="0.3">
       <c r="H53" s="4"/>
       <c r="I53" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="J53" s="6"/>
+      <c r="J53" s="6" t="s">
+        <v>247</v>
+      </c>
       <c r="T53">
         <v>2</v>
       </c>
@@ -12548,7 +12889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="8:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="8:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H54" s="7"/>
       <c r="I54">
         <v>1</v>
@@ -12588,7 +12929,7 @@
         <v>0.26619459746597274</v>
       </c>
     </row>
-    <row r="55" spans="8:37" x14ac:dyDescent="0.25">
+    <row r="55" spans="8:37" x14ac:dyDescent="0.3">
       <c r="H55" s="7">
         <v>1</v>
       </c>
@@ -12624,7 +12965,7 @@
         <v>7.0294782268955955E-2</v>
       </c>
     </row>
-    <row r="56" spans="8:37" x14ac:dyDescent="0.25">
+    <row r="56" spans="8:37" x14ac:dyDescent="0.3">
       <c r="H56" s="7">
         <v>2</v>
       </c>
@@ -12660,7 +13001,7 @@
         <v>-0.23257473286654426</v>
       </c>
     </row>
-    <row r="57" spans="8:37" x14ac:dyDescent="0.25">
+    <row r="57" spans="8:37" x14ac:dyDescent="0.3">
       <c r="H57" s="7">
         <v>3</v>
       </c>
@@ -12696,7 +13037,7 @@
         <v>-0.1869752813273616</v>
       </c>
     </row>
-    <row r="58" spans="8:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="8:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H58" s="7">
         <v>4</v>
       </c>
@@ -12721,7 +13062,7 @@
         <v>-0.11765864222297037</v>
       </c>
     </row>
-    <row r="59" spans="8:37" x14ac:dyDescent="0.25">
+    <row r="59" spans="8:37" x14ac:dyDescent="0.3">
       <c r="H59" s="7">
         <v>5</v>
       </c>
@@ -12735,8 +13076,11 @@
         <v>79</v>
       </c>
       <c r="V59" s="6"/>
-    </row>
-    <row r="60" spans="8:37" x14ac:dyDescent="0.25">
+      <c r="W59" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="60" spans="8:37" x14ac:dyDescent="0.3">
       <c r="H60" s="7">
         <v>6</v>
       </c>
@@ -12753,7 +13097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="8:37" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="61" spans="8:37" ht="25.8" x14ac:dyDescent="0.5">
       <c r="H61" s="7">
         <v>7</v>
       </c>
@@ -12777,7 +13121,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="8:37" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="8:37" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="H62" s="7">
         <v>8</v>
       </c>
@@ -12810,7 +13154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="8:37" x14ac:dyDescent="0.25">
+    <row r="63" spans="8:37" x14ac:dyDescent="0.3">
       <c r="H63" s="7">
         <v>9</v>
       </c>
@@ -12833,6 +13177,9 @@
       <c r="AA63" t="s">
         <v>89</v>
       </c>
+      <c r="AB63" t="s">
+        <v>263</v>
+      </c>
       <c r="AI63">
         <v>0</v>
       </c>
@@ -12844,7 +13191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="8:37" x14ac:dyDescent="0.25">
+    <row r="64" spans="8:37" x14ac:dyDescent="0.3">
       <c r="H64" s="7">
         <v>10</v>
       </c>
@@ -12877,7 +13224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="8:37" x14ac:dyDescent="0.25">
+    <row r="65" spans="8:37" x14ac:dyDescent="0.3">
       <c r="H65" s="7">
         <v>11</v>
       </c>
@@ -12914,7 +13261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="8:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="8:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H66" s="9">
         <v>12</v>
       </c>
@@ -12951,7 +13298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="8:37" x14ac:dyDescent="0.25">
+    <row r="67" spans="8:37" x14ac:dyDescent="0.3">
       <c r="Z67">
         <v>3</v>
       </c>
@@ -12969,7 +13316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="8:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="8:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="Z68">
         <v>4</v>
       </c>
@@ -12987,7 +13334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="8:37" x14ac:dyDescent="0.25">
+    <row r="69" spans="8:37" x14ac:dyDescent="0.3">
       <c r="Z69">
         <v>5</v>
       </c>
@@ -13005,7 +13352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="8:37" x14ac:dyDescent="0.25">
+    <row r="70" spans="8:37" x14ac:dyDescent="0.3">
       <c r="Z70">
         <v>6</v>
       </c>
@@ -13014,18 +13361,24 @@
         <v>4.9893460414720578E-2</v>
       </c>
     </row>
-    <row r="71" spans="8:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="72" spans="8:37" x14ac:dyDescent="0.25">
+    <row r="71" spans="8:37" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="72" spans="8:37" x14ac:dyDescent="0.3">
       <c r="Z72" s="4"/>
       <c r="AA72" s="39" t="s">
         <v>50</v>
       </c>
+      <c r="AB72" t="s">
+        <v>264</v>
+      </c>
       <c r="AC72" s="4"/>
       <c r="AD72" s="39" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="73" spans="8:37" x14ac:dyDescent="0.25">
+      <c r="AE72" s="91" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="73" spans="8:37" x14ac:dyDescent="0.3">
       <c r="Z73" s="7"/>
       <c r="AA73" s="8">
         <v>1</v>
@@ -13035,7 +13388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="8:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="8:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="Z74" s="7">
         <v>1</v>
       </c>
@@ -13051,7 +13404,7 @@
         <v>0.73067696616934319</v>
       </c>
     </row>
-    <row r="75" spans="8:37" x14ac:dyDescent="0.25">
+    <row r="75" spans="8:37" x14ac:dyDescent="0.3">
       <c r="Z75" s="7">
         <v>2</v>
       </c>
@@ -13060,7 +13413,7 @@
         <v>1.2335232777721005E-2</v>
       </c>
     </row>
-    <row r="76" spans="8:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="8:37" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="Z76" s="9">
         <v>3</v>
       </c>
@@ -13080,27 +13433,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AEBF56A-20D9-424D-8A84-6D1B0450F81A}">
   <dimension ref="B1:CD85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="37" max="37" width="9.140625" customWidth="1"/>
-    <col min="38" max="38" width="1.85546875" customWidth="1"/>
-    <col min="39" max="39" width="9.5703125" customWidth="1"/>
-    <col min="40" max="40" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.109375" customWidth="1"/>
+    <col min="38" max="38" width="1.88671875" customWidth="1"/>
+    <col min="39" max="39" width="9.5546875" customWidth="1"/>
+    <col min="40" max="40" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="12" customWidth="1"/>
-    <col min="43" max="44" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" customWidth="1"/>
-    <col min="46" max="46" width="1.85546875" customWidth="1"/>
-    <col min="47" max="47" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="43" max="44" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.88671875" customWidth="1"/>
+    <col min="46" max="46" width="1.88671875" customWidth="1"/>
+    <col min="47" max="47" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:82" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:82" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:82" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:82" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B2" s="4"/>
       <c r="C2" s="40" t="s">
         <v>62</v>
@@ -13122,7 +13475,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="2:82" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:82" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B3" s="7"/>
       <c r="C3">
         <v>1</v>
@@ -13146,7 +13499,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:82" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:82" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="7">
         <v>1</v>
       </c>
@@ -13166,6 +13519,9 @@
       <c r="BN4" t="s">
         <v>51</v>
       </c>
+      <c r="BO4" t="s">
+        <v>259</v>
+      </c>
       <c r="BT4">
         <v>0</v>
       </c>
@@ -13200,7 +13556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:82" ht="21" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:82" ht="21" x14ac:dyDescent="0.4">
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -13236,14 +13592,46 @@
       <c r="AE5" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="AF5" s="5"/>
+      <c r="AF5" s="5" t="s">
+        <v>251</v>
+      </c>
       <c r="AG5" s="6"/>
       <c r="AK5" s="42" t="s">
         <v>107</v>
       </c>
+      <c r="AM5" t="s">
+        <v>274</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>275</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>276</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>277</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>278</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>279</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>280</v>
+      </c>
       <c r="AU5" s="42" t="s">
         <v>107</v>
       </c>
+      <c r="AY5" t="s">
+        <v>283</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>286</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>289</v>
+      </c>
       <c r="BL5">
         <v>1</v>
       </c>
@@ -13299,7 +13687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:82" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:82" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -13344,6 +13732,9 @@
       </c>
       <c r="AG6" s="8">
         <v>3</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>273</v>
       </c>
       <c r="AK6" s="25" t="s">
         <v>106</v>
@@ -13374,30 +13765,45 @@
       <c r="AU6" t="s">
         <v>124</v>
       </c>
+      <c r="AV6" t="s">
+        <v>281</v>
+      </c>
       <c r="AW6" s="77" t="s">
         <v>125</v>
       </c>
-      <c r="AX6" s="81"/>
+      <c r="AX6" s="81" t="s">
+        <v>282</v>
+      </c>
       <c r="AY6" t="s">
         <v>126</v>
       </c>
       <c r="AZ6" s="78" t="s">
         <v>131</v>
       </c>
+      <c r="BA6" t="s">
+        <v>284</v>
+      </c>
       <c r="BB6" s="77" t="s">
         <v>129</v>
       </c>
-      <c r="BC6" s="81"/>
+      <c r="BC6" s="81" t="s">
+        <v>285</v>
+      </c>
       <c r="BD6" t="s">
         <v>127</v>
       </c>
       <c r="BE6" s="78" t="s">
         <v>132</v>
       </c>
+      <c r="BF6" s="91" t="s">
+        <v>287</v>
+      </c>
       <c r="BG6" s="77" t="s">
         <v>130</v>
       </c>
-      <c r="BH6" s="81"/>
+      <c r="BH6" s="81" t="s">
+        <v>288</v>
+      </c>
       <c r="BI6" t="s">
         <v>128</v>
       </c>
@@ -13466,7 +13872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:82" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:82" x14ac:dyDescent="0.3">
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -13652,7 +14058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:82" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:82" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -13854,7 +14260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:82" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:82" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="9">
         <v>6</v>
       </c>
@@ -14033,7 +14439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:82" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:82" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>224</v>
       </c>
@@ -14158,7 +14564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:82" ht="21" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:82" ht="21" x14ac:dyDescent="0.4">
       <c r="K11" s="4"/>
       <c r="L11" s="5" t="s">
         <v>93</v>
@@ -14290,7 +14696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:82" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:82" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
         <v>58</v>
       </c>
@@ -14343,6 +14749,9 @@
       <c r="AG12" s="8">
         <v>0.39229795598111239</v>
       </c>
+      <c r="AJ12" t="s">
+        <v>273</v>
+      </c>
       <c r="AK12" s="25" t="s">
         <v>106</v>
       </c>
@@ -14433,7 +14842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:82" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:82" x14ac:dyDescent="0.3">
       <c r="C13" s="13" t="s">
         <v>105</v>
       </c>
@@ -14581,6 +14990,9 @@
       <c r="BL13" t="s">
         <v>89</v>
       </c>
+      <c r="BM13" t="s">
+        <v>260</v>
+      </c>
       <c r="BT13">
         <v>0</v>
       </c>
@@ -14615,7 +15027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:82" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:82" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>1</v>
       </c>
@@ -14833,7 +15245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:82" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:82" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>2</v>
       </c>
@@ -15017,7 +15429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:82" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:82" x14ac:dyDescent="0.3">
       <c r="K16" s="4"/>
       <c r="L16" s="5" t="s">
         <v>95</v>
@@ -15104,7 +15516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="10:74" ht="21" x14ac:dyDescent="0.35">
+    <row r="17" spans="8:74" ht="21" x14ac:dyDescent="0.4">
       <c r="K17" s="7"/>
       <c r="L17">
         <v>1</v>
@@ -15200,7 +15612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="8:74" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K18" s="7">
         <v>1</v>
       </c>
@@ -15256,6 +15668,9 @@
       <c r="AG18" s="11">
         <v>0.3035324251986507</v>
       </c>
+      <c r="AJ18" t="s">
+        <v>273</v>
+      </c>
       <c r="AK18" s="25" t="s">
         <v>106</v>
       </c>
@@ -15336,7 +15751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="8:74" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K19" s="9">
         <v>2</v>
       </c>
@@ -15456,9 +15871,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="8:74" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="W20" t="s">
         <v>68</v>
+      </c>
+      <c r="X20" t="s">
+        <v>248</v>
       </c>
       <c r="Y20" s="4"/>
       <c r="Z20" s="39" t="s">
@@ -15467,6 +15885,9 @@
       <c r="AD20" s="4"/>
       <c r="AE20" s="39" t="s">
         <v>52</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>252</v>
       </c>
       <c r="AJ20">
         <v>1</v>
@@ -15583,7 +16004,7 @@
         <v>5.1198187927677975E-4</v>
       </c>
     </row>
-    <row r="21" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="8:74" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K21" s="4"/>
       <c r="L21" s="5" t="s">
         <v>96</v>
@@ -15684,7 +16105,7 @@
         <v>-4.170317835035915E-5</v>
       </c>
     </row>
-    <row r="22" spans="10:74" x14ac:dyDescent="0.25">
+    <row r="22" spans="8:74" x14ac:dyDescent="0.3">
       <c r="K22" s="7"/>
       <c r="L22">
         <v>1</v>
@@ -15744,14 +16165,19 @@
       <c r="BL22" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="BM22" s="5"/>
+      <c r="BM22" s="5" t="s">
+        <v>261</v>
+      </c>
       <c r="BN22" s="6"/>
       <c r="BP22" s="4"/>
       <c r="BQ22" s="39" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="23" spans="10:74" ht="21" x14ac:dyDescent="0.35">
+      <c r="BR22" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="23" spans="8:74" ht="21" x14ac:dyDescent="0.4">
       <c r="K23" s="7">
         <v>1</v>
       </c>
@@ -15832,7 +16258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="8:74" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K24" s="9">
         <v>2</v>
       </c>
@@ -15876,6 +16302,9 @@
         <f>W36</f>
         <v>0.3958219909108871</v>
       </c>
+      <c r="AJ24" t="s">
+        <v>273</v>
+      </c>
       <c r="AK24" s="25" t="s">
         <v>106</v>
       </c>
@@ -15955,7 +16384,7 @@
         <v>0.22899438403528871</v>
       </c>
     </row>
-    <row r="25" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="8:74" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AK25" s="25">
         <v>1</v>
       </c>
@@ -16043,7 +16472,7 @@
         <v>4.5947036528498041E-2</v>
       </c>
     </row>
-    <row r="26" spans="10:74" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="8:74" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="K26" s="42" t="s">
         <v>105</v>
       </c>
@@ -16052,6 +16481,9 @@
         <v>69</v>
       </c>
       <c r="X26" s="6"/>
+      <c r="Y26" t="s">
+        <v>249</v>
+      </c>
       <c r="AE26" t="s">
         <v>81</v>
       </c>
@@ -16162,7 +16594,13 @@
         <v>-0.16718198407848409</v>
       </c>
     </row>
-    <row r="27" spans="10:74" x14ac:dyDescent="0.25">
+    <row r="27" spans="8:74" x14ac:dyDescent="0.3">
+      <c r="H27" t="s">
+        <v>99</v>
+      </c>
+      <c r="I27" t="s">
+        <v>267</v>
+      </c>
       <c r="K27" t="s">
         <v>99</v>
       </c>
@@ -16191,6 +16629,9 @@
       <c r="X27" s="8"/>
       <c r="AE27">
         <v>1</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>253</v>
       </c>
       <c r="AJ27">
         <v>2</v>
@@ -16282,7 +16723,13 @@
         <v>-0.2992518864090718</v>
       </c>
     </row>
-    <row r="28" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="8:74" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H28" t="s">
+        <v>101</v>
+      </c>
+      <c r="I28" t="s">
+        <v>268</v>
+      </c>
       <c r="K28">
         <v>1</v>
       </c>
@@ -16354,7 +16801,13 @@
         <v>-0.12634966406108461</v>
       </c>
     </row>
-    <row r="29" spans="10:74" ht="21" x14ac:dyDescent="0.35">
+    <row r="29" spans="8:74" ht="21" x14ac:dyDescent="0.4">
+      <c r="H29" t="s">
+        <v>122</v>
+      </c>
+      <c r="I29" t="s">
+        <v>269</v>
+      </c>
       <c r="J29">
         <v>1</v>
       </c>
@@ -16426,7 +16879,13 @@
       <c r="BG29" s="77"/>
       <c r="BH29" s="81"/>
     </row>
-    <row r="30" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="8:74" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H30" t="s">
+        <v>266</v>
+      </c>
+      <c r="I30" t="s">
+        <v>270</v>
+      </c>
       <c r="J30">
         <v>2</v>
       </c>
@@ -16471,6 +16930,9 @@
         <f t="array" ref="AE30">SUM(MMULT(TRANSPOSE($W$34:$W$36),TRANSPOSE(Z9:AB9)))</f>
         <v>-6.2308054682829607E-2</v>
       </c>
+      <c r="AJ30" t="s">
+        <v>273</v>
+      </c>
       <c r="AK30" s="25" t="s">
         <v>106</v>
       </c>
@@ -16528,7 +16990,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="10:74" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="8:74" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AD31">
         <v>4</v>
       </c>
@@ -16611,7 +17073,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="10:74" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="8:74" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="K32" s="42" t="s">
         <v>112</v>
       </c>
@@ -16620,6 +17082,9 @@
         <v>72</v>
       </c>
       <c r="X32" s="6"/>
+      <c r="Y32" t="s">
+        <v>250</v>
+      </c>
       <c r="AD32">
         <v>5</v>
       </c>
@@ -16731,7 +17196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="10:74" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:74" x14ac:dyDescent="0.3">
       <c r="K33" t="s">
         <v>99</v>
       </c>
@@ -16844,6 +17309,9 @@
       <c r="BL33" t="s">
         <v>89</v>
       </c>
+      <c r="BM33" t="s">
+        <v>263</v>
+      </c>
       <c r="BT33">
         <v>0</v>
       </c>
@@ -16855,7 +17323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="10:74" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:74" x14ac:dyDescent="0.3">
       <c r="K34">
         <v>1</v>
       </c>
@@ -16924,7 +17392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="10:74" ht="21" x14ac:dyDescent="0.35">
+    <row r="35" spans="10:74" ht="21" x14ac:dyDescent="0.4">
       <c r="J35">
         <v>1</v>
       </c>
@@ -17012,7 +17480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="10:74" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J36">
         <v>2</v>
       </c>
@@ -17057,6 +17525,9 @@
         <f t="array" ref="AE36">SUM(MMULT(TRANSPOSE($W$34:$W$36),TRANSPOSE(Z15:AB15)))</f>
         <v>-0.33767791435844657</v>
       </c>
+      <c r="AJ36" t="s">
+        <v>273</v>
+      </c>
       <c r="AK36" s="25" t="s">
         <v>106</v>
       </c>
@@ -17130,7 +17601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="10:74" x14ac:dyDescent="0.25">
+    <row r="37" spans="10:74" x14ac:dyDescent="0.3">
       <c r="AD37">
         <v>10</v>
       </c>
@@ -17226,7 +17697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="10:74" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="10:74" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="K38" s="42" t="s">
         <v>111</v>
       </c>
@@ -17345,7 +17816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="10:74" x14ac:dyDescent="0.25">
+    <row r="39" spans="10:74" x14ac:dyDescent="0.3">
       <c r="K39" t="s">
         <v>99</v>
       </c>
@@ -17466,7 +17937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="10:74" x14ac:dyDescent="0.25">
+    <row r="40" spans="10:74" x14ac:dyDescent="0.3">
       <c r="K40">
         <v>1</v>
       </c>
@@ -17496,7 +17967,7 @@
         <v>1.5988692705242835E-3</v>
       </c>
     </row>
-    <row r="41" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="10:74" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J41">
         <v>1</v>
       </c>
@@ -17528,6 +17999,9 @@
         <f t="array" ref="T41:T42">O41:O42*_xlfn.ANCHORARRAY(T35)+(1-O41:O42)*R41:R42</f>
         <v>0.51936140500530836</v>
       </c>
+      <c r="AD41" t="s">
+        <v>254</v>
+      </c>
       <c r="AE41" s="51" t="s">
         <v>54</v>
       </c>
@@ -17537,8 +18011,17 @@
       <c r="AU41" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="42" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AY41" t="s">
+        <v>283</v>
+      </c>
+      <c r="BD41" t="s">
+        <v>286</v>
+      </c>
+      <c r="BI41" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="42" spans="10:74" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J42">
         <v>2</v>
       </c>
@@ -17582,33 +18065,45 @@
       <c r="AU42" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="AV42" s="6"/>
+      <c r="AV42" s="6" t="s">
+        <v>281</v>
+      </c>
       <c r="AW42" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AX42" s="6"/>
+      <c r="AX42" s="6" t="s">
+        <v>282</v>
+      </c>
       <c r="AY42" s="18" t="s">
         <v>126</v>
       </c>
       <c r="AZ42" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="BA42" s="6"/>
+      <c r="BA42" s="6" t="s">
+        <v>284</v>
+      </c>
       <c r="BB42" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="BC42" s="6"/>
+      <c r="BC42" s="6" t="s">
+        <v>285</v>
+      </c>
       <c r="BD42" s="18" t="s">
         <v>127</v>
       </c>
       <c r="BE42" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="BF42" s="6"/>
+      <c r="BF42" s="92" t="s">
+        <v>287</v>
+      </c>
       <c r="BG42" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="BH42" s="6"/>
+      <c r="BH42" s="6" t="s">
+        <v>288</v>
+      </c>
       <c r="BI42" s="18" t="s">
         <v>128</v>
       </c>
@@ -17616,12 +18111,18 @@
       <c r="BL42" s="39" t="s">
         <v>50</v>
       </c>
+      <c r="BM42" t="s">
+        <v>264</v>
+      </c>
       <c r="BN42" s="4"/>
       <c r="BO42" s="39" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="43" spans="10:74" x14ac:dyDescent="0.25">
+      <c r="BP42" s="91" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="43" spans="10:74" x14ac:dyDescent="0.3">
       <c r="AD43">
         <v>1</v>
       </c>
@@ -17642,7 +18143,7 @@
         <v>0</v>
       </c>
       <c r="AT43" s="7"/>
-      <c r="AU43">
+      <c r="AU43" s="93">
         <v>1</v>
       </c>
       <c r="AV43" s="8">
@@ -17696,7 +18197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="10:74" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="10:74" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="K44" s="42" t="s">
         <v>110</v>
       </c>
@@ -17722,7 +18223,7 @@
       <c r="AT44" s="7">
         <v>1</v>
       </c>
-      <c r="AU44">
+      <c r="AU44" s="93">
         <f t="shared" ref="AU44:BI44" si="10">SUM(AU8,AU14,AU20,AU26,AU32,AU38)</f>
         <v>-1.4910344327143772</v>
       </c>
@@ -17797,7 +18298,7 @@
         <v>-0.28782411015095449</v>
       </c>
     </row>
-    <row r="45" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="10:74" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K45" t="s">
         <v>99</v>
       </c>
@@ -17909,7 +18410,7 @@
         <v>-3.0864173978404025E-4</v>
       </c>
     </row>
-    <row r="46" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="10:74" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K46">
         <v>1</v>
       </c>
@@ -17958,7 +18459,7 @@
         <v>7.1572330335793397E-4</v>
       </c>
     </row>
-    <row r="47" spans="10:74" x14ac:dyDescent="0.25">
+    <row r="47" spans="10:74" x14ac:dyDescent="0.3">
       <c r="J47">
         <v>1</v>
       </c>
@@ -18012,8 +18513,11 @@
       <c r="AU47" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="48" spans="10:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AV47" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="48" spans="10:74" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J48">
         <v>2</v>
       </c>
@@ -18079,7 +18583,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="10:52" x14ac:dyDescent="0.25">
+    <row r="49" spans="10:52" x14ac:dyDescent="0.3">
       <c r="AU49">
         <v>1</v>
       </c>
@@ -18099,9 +18603,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="10:52" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="10:52" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="K50" s="42" t="s">
         <v>108</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>254</v>
       </c>
       <c r="AE50" s="55" t="s">
         <v>57</v>
@@ -18137,7 +18644,7 @@
         <v>5.1198187927677975E-4</v>
       </c>
     </row>
-    <row r="51" spans="10:52" x14ac:dyDescent="0.25">
+    <row r="51" spans="10:52" x14ac:dyDescent="0.3">
       <c r="K51" t="s">
         <v>99</v>
       </c>
@@ -18190,7 +18697,7 @@
         <v>1.5988692705242835E-3</v>
       </c>
     </row>
-    <row r="52" spans="10:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="10:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K52">
         <v>1</v>
       </c>
@@ -18224,7 +18731,7 @@
         <v>4.4762402714626649E-2</v>
       </c>
     </row>
-    <row r="53" spans="10:52" x14ac:dyDescent="0.25">
+    <row r="53" spans="10:52" x14ac:dyDescent="0.3">
       <c r="J53">
         <v>1</v>
       </c>
@@ -18273,7 +18780,7 @@
       </c>
       <c r="AV53" s="6"/>
     </row>
-    <row r="54" spans="10:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="10:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J54">
         <v>2</v>
       </c>
@@ -18317,8 +18824,11 @@
         <v>58</v>
       </c>
       <c r="AV54" s="8"/>
-    </row>
-    <row r="55" spans="10:52" x14ac:dyDescent="0.25">
+      <c r="AW54" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="55" spans="10:52" x14ac:dyDescent="0.3">
       <c r="AD55">
         <v>4</v>
       </c>
@@ -18338,7 +18848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="10:52" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="10:52" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="K56" s="42" t="s">
         <v>107</v>
       </c>
@@ -18365,7 +18875,7 @@
         <v>-0.2716883329052453</v>
       </c>
     </row>
-    <row r="57" spans="10:52" x14ac:dyDescent="0.25">
+    <row r="57" spans="10:52" x14ac:dyDescent="0.3">
       <c r="K57" t="s">
         <v>99</v>
       </c>
@@ -18410,7 +18920,7 @@
         <v>-1.0651493819151606E-2</v>
       </c>
     </row>
-    <row r="58" spans="10:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="10:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K58">
         <v>1</v>
       </c>
@@ -18444,7 +18954,7 @@
         <v>-9.5365508647938628E-3</v>
       </c>
     </row>
-    <row r="59" spans="10:52" x14ac:dyDescent="0.25">
+    <row r="59" spans="10:52" x14ac:dyDescent="0.3">
       <c r="J59">
         <v>1</v>
       </c>
@@ -18481,6 +18991,9 @@
         <v>79</v>
       </c>
       <c r="AF59" s="6"/>
+      <c r="AG59" t="s">
+        <v>254</v>
+      </c>
       <c r="AT59" s="7">
         <v>4</v>
       </c>
@@ -18493,7 +19006,7 @@
         <v>1.4465151245891214E-3</v>
       </c>
     </row>
-    <row r="60" spans="10:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="10:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J60">
         <v>2</v>
       </c>
@@ -18540,7 +19053,7 @@
         <v>1.0068830431229235E-3</v>
       </c>
     </row>
-    <row r="61" spans="10:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="10:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AD61" s="22" t="s">
         <v>105</v>
       </c>
@@ -18564,7 +19077,16 @@
         <v>1.5988692705242835E-3</v>
       </c>
     </row>
-    <row r="62" spans="10:52" x14ac:dyDescent="0.25">
+    <row r="62" spans="10:52" x14ac:dyDescent="0.3">
+      <c r="J62" t="s">
+        <v>271</v>
+      </c>
+      <c r="N62" t="s">
+        <v>272</v>
+      </c>
+      <c r="P62" t="s">
+        <v>272</v>
+      </c>
       <c r="AD62" s="7">
         <v>2</v>
       </c>
@@ -18577,7 +19099,7 @@
         <v>0.2745624799964137</v>
       </c>
     </row>
-    <row r="63" spans="10:52" x14ac:dyDescent="0.25">
+    <row r="63" spans="10:52" x14ac:dyDescent="0.3">
       <c r="J63" t="s">
         <v>234</v>
       </c>
@@ -18599,7 +19121,7 @@
         <v>-0.23114701186205289</v>
       </c>
     </row>
-    <row r="64" spans="10:52" x14ac:dyDescent="0.25">
+    <row r="64" spans="10:52" x14ac:dyDescent="0.3">
       <c r="K64">
         <v>1</v>
       </c>
@@ -18624,7 +19146,7 @@
         <v>3.1077567157202772E-2</v>
       </c>
     </row>
-    <row r="65" spans="10:36" x14ac:dyDescent="0.25">
+    <row r="65" spans="10:36" x14ac:dyDescent="0.3">
       <c r="J65" s="13" t="s">
         <v>105</v>
       </c>
@@ -18635,11 +19157,11 @@
       <c r="L65" s="55">
         <v>0.21543781682606056</v>
       </c>
-      <c r="N65">
+      <c r="N65" s="51">
         <f t="shared" ref="N65:N70" si="14">MAX(_xlfn.ANCHORARRAY(K65))</f>
         <v>0.38716804364868784</v>
       </c>
-      <c r="P65">
+      <c r="P65" s="55">
         <f t="shared" ref="P65:P70" si="15">AVERAGE(_xlfn.ANCHORARRAY(K65))</f>
         <v>0.3013029302373742</v>
       </c>
@@ -18655,7 +19177,7 @@
         <v>5.5730443321541007E-2</v>
       </c>
     </row>
-    <row r="66" spans="10:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="10:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J66">
         <v>2</v>
       </c>
@@ -18666,11 +19188,11 @@
       <c r="L66" s="55">
         <v>0.65027309102745778</v>
       </c>
-      <c r="N66">
+      <c r="N66" s="51">
         <f t="shared" si="14"/>
         <v>0.65027309102745778</v>
       </c>
-      <c r="P66">
+      <c r="P66" s="55">
         <f t="shared" si="15"/>
         <v>0.53346891374762251</v>
       </c>
@@ -18686,7 +19208,7 @@
         <v>0.3180273290716179</v>
       </c>
     </row>
-    <row r="67" spans="10:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="10:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J67">
         <v>3</v>
       </c>
@@ -18697,16 +19219,16 @@
       <c r="L67" s="55">
         <v>0.91793145379932639</v>
       </c>
-      <c r="N67">
+      <c r="N67" s="51">
         <f t="shared" si="14"/>
         <v>0.91793145379932639</v>
       </c>
-      <c r="P67">
+      <c r="P67" s="55">
         <f t="shared" si="15"/>
         <v>0.71864642940231738</v>
       </c>
     </row>
-    <row r="68" spans="10:36" x14ac:dyDescent="0.25">
+    <row r="68" spans="10:36" x14ac:dyDescent="0.3">
       <c r="J68">
         <v>4</v>
       </c>
@@ -18717,11 +19239,11 @@
       <c r="L68" s="55">
         <v>0.94437948578866504</v>
       </c>
-      <c r="N68">
+      <c r="N68" s="51">
         <f t="shared" si="14"/>
         <v>0.94437948578866504</v>
       </c>
-      <c r="P68">
+      <c r="P68" s="55">
         <f t="shared" si="15"/>
         <v>0.76086882897867159</v>
       </c>
@@ -18731,7 +19253,7 @@
       </c>
       <c r="AF68" s="61"/>
     </row>
-    <row r="69" spans="10:36" x14ac:dyDescent="0.25">
+    <row r="69" spans="10:36" x14ac:dyDescent="0.3">
       <c r="J69">
         <v>5</v>
       </c>
@@ -18742,11 +19264,11 @@
       <c r="L69" s="55">
         <v>0.97538944250417403</v>
       </c>
-      <c r="N69">
+      <c r="N69" s="51">
         <f t="shared" si="14"/>
         <v>0.97538944250417403</v>
       </c>
-      <c r="P69">
+      <c r="P69" s="55">
         <f t="shared" si="15"/>
         <v>0.72304703142137494</v>
       </c>
@@ -18758,7 +19280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="10:36" x14ac:dyDescent="0.25">
+    <row r="70" spans="10:36" x14ac:dyDescent="0.3">
       <c r="J70">
         <v>6</v>
       </c>
@@ -18769,11 +19291,11 @@
       <c r="L70" s="55">
         <v>0.99109691980057746</v>
       </c>
-      <c r="N70">
+      <c r="N70" s="51">
         <f t="shared" si="14"/>
         <v>0.99109691980057746</v>
       </c>
-      <c r="P70">
+      <c r="P70" s="55">
         <f t="shared" si="15"/>
         <v>0.76684073186571911</v>
       </c>
@@ -18788,7 +19310,7 @@
         <v>0.3180273290716179</v>
       </c>
     </row>
-    <row r="71" spans="10:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="10:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AD71" s="62">
         <v>5</v>
       </c>
@@ -18800,11 +19322,14 @@
         <v>5.5730443321541007E-2</v>
       </c>
     </row>
-    <row r="72" spans="10:36" x14ac:dyDescent="0.25">
+    <row r="72" spans="10:36" x14ac:dyDescent="0.3">
       <c r="J72" s="4"/>
       <c r="K72" s="39" t="s">
         <v>64</v>
       </c>
+      <c r="L72" t="s">
+        <v>272</v>
+      </c>
       <c r="AD72" s="62">
         <v>4</v>
       </c>
@@ -18816,7 +19341,7 @@
         <v>3.1077567157202772E-2</v>
       </c>
     </row>
-    <row r="73" spans="10:36" x14ac:dyDescent="0.25">
+    <row r="73" spans="10:36" x14ac:dyDescent="0.3">
       <c r="J73" s="7"/>
       <c r="K73" s="8">
         <v>1</v>
@@ -18832,7 +19357,7 @@
         <v>-0.23114701186205289</v>
       </c>
     </row>
-    <row r="74" spans="10:36" x14ac:dyDescent="0.25">
+    <row r="74" spans="10:36" x14ac:dyDescent="0.3">
       <c r="J74" s="7">
         <v>1</v>
       </c>
@@ -18851,7 +19376,7 @@
         <v>0.2745624799964137</v>
       </c>
     </row>
-    <row r="75" spans="10:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="10:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J75" s="7">
         <v>2</v>
       </c>
@@ -18869,7 +19394,7 @@
         <v>4.4762402714626649E-2</v>
       </c>
     </row>
-    <row r="76" spans="10:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="10:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J76" s="7">
         <v>3</v>
       </c>
@@ -18877,7 +19402,7 @@
         <v>0.91793145379932639</v>
       </c>
     </row>
-    <row r="77" spans="10:36" x14ac:dyDescent="0.25">
+    <row r="77" spans="10:36" x14ac:dyDescent="0.3">
       <c r="J77" s="7">
         <v>4</v>
       </c>
@@ -18894,7 +19419,7 @@
       <c r="AI77" s="74"/>
       <c r="AJ77" s="61"/>
     </row>
-    <row r="78" spans="10:36" x14ac:dyDescent="0.25">
+    <row r="78" spans="10:36" x14ac:dyDescent="0.3">
       <c r="J78" s="7">
         <v>5</v>
       </c>
@@ -18921,7 +19446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="10:36" x14ac:dyDescent="0.25">
+    <row r="79" spans="10:36" x14ac:dyDescent="0.3">
       <c r="J79" s="7">
         <v>6</v>
       </c>
@@ -18951,7 +19476,7 @@
         <v>-0.27037327472920164</v>
       </c>
     </row>
-    <row r="80" spans="10:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="10:36" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J80" s="7">
         <v>7</v>
       </c>
@@ -18981,7 +19506,7 @@
         <v>4.4762402714626649E-2</v>
       </c>
     </row>
-    <row r="81" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J81" s="7">
         <v>8</v>
       </c>
@@ -18989,7 +19514,7 @@
         <v>0.53346891374762251</v>
       </c>
     </row>
-    <row r="82" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J82" s="7">
         <v>9</v>
       </c>
@@ -18997,7 +19522,7 @@
         <v>0.71864642940231738</v>
       </c>
     </row>
-    <row r="83" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J83" s="7">
         <v>10</v>
       </c>
@@ -19005,7 +19530,7 @@
         <v>0.76086882897867159</v>
       </c>
     </row>
-    <row r="84" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J84" s="7">
         <v>11</v>
       </c>
@@ -19013,7 +19538,7 @@
         <v>0.72304703142137494</v>
       </c>
     </row>
-    <row r="85" spans="10:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="10:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J85" s="9">
         <v>12</v>
       </c>
@@ -19022,6 +19547,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="AE28:AE39" formulaRange="1"/>
@@ -19032,22 +19558,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB3B3A1E-87F9-4538-9C64-36B1DAE0AAD0}">
   <dimension ref="B1:CU91"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="15" max="15" width="3.42578125" customWidth="1"/>
-    <col min="22" max="22" width="1.7109375" customWidth="1"/>
-    <col min="29" max="29" width="1.7109375" customWidth="1"/>
-    <col min="30" max="30" width="12.140625" customWidth="1"/>
+    <col min="15" max="15" width="3.44140625" customWidth="1"/>
+    <col min="22" max="22" width="1.6640625" customWidth="1"/>
+    <col min="29" max="29" width="1.6640625" customWidth="1"/>
+    <col min="30" max="30" width="12.109375" customWidth="1"/>
     <col min="55" max="55" width="2" customWidth="1"/>
-    <col min="56" max="56" width="9.140625" customWidth="1"/>
+    <col min="56" max="56" width="9.109375" customWidth="1"/>
     <col min="62" max="62" width="2" customWidth="1"/>
     <col min="68" max="68" width="2" customWidth="1"/>
     <col min="75" max="75" width="2" customWidth="1"/>
     <col min="78" max="78" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:99" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:99" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:99" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:99" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B2" s="4"/>
       <c r="C2" s="40" t="s">
         <v>62</v>
@@ -19076,7 +19602,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="2:99" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:99" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B3" s="7"/>
       <c r="C3">
         <v>1</v>
@@ -19107,7 +19633,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:99" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:99" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="7">
         <v>1</v>
       </c>
@@ -19124,9 +19650,18 @@
       <c r="G4" s="8">
         <v>2</v>
       </c>
+      <c r="H4" t="s">
+        <v>293</v>
+      </c>
       <c r="J4" s="51" t="s">
         <v>137</v>
       </c>
+      <c r="L4" t="s">
+        <v>292</v>
+      </c>
+      <c r="N4" t="s">
+        <v>292</v>
+      </c>
       <c r="P4" t="s">
         <v>137</v>
       </c>
@@ -19139,6 +19674,9 @@
       <c r="CE4" t="s">
         <v>51</v>
       </c>
+      <c r="CF4" t="s">
+        <v>259</v>
+      </c>
       <c r="CK4">
         <v>0</v>
       </c>
@@ -19173,7 +19711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:99" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -19189,6 +19727,9 @@
       <c r="G5" s="8">
         <v>2</v>
       </c>
+      <c r="I5" t="s">
+        <v>292</v>
+      </c>
       <c r="J5" t="s">
         <v>147</v>
       </c>
@@ -19206,6 +19747,9 @@
       </c>
       <c r="AD5" t="s">
         <v>152</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>294</v>
       </c>
       <c r="AG5" t="s">
         <v>46</v>
@@ -19220,17 +19764,23 @@
       <c r="AO5" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="AP5" s="5"/>
+      <c r="AP5" s="5" t="s">
+        <v>251</v>
+      </c>
       <c r="AQ5" s="6"/>
       <c r="AT5" s="4"/>
       <c r="AU5" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="AV5" s="6"/>
+      <c r="AV5" s="6" t="s">
+        <v>298</v>
+      </c>
       <c r="AX5" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="AY5" s="6"/>
+      <c r="AY5" s="6" t="s">
+        <v>299</v>
+      </c>
       <c r="CC5">
         <v>1</v>
       </c>
@@ -19286,7 +19836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:99" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:99" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -19451,7 +20001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:99" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:99" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -19640,7 +20190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:99" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:99" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -19811,7 +20361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:99" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:99" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="9">
         <v>6</v>
       </c>
@@ -19973,7 +20523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:99" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>224</v>
       </c>
@@ -20068,6 +20618,9 @@
       <c r="AU10" t="s">
         <v>163</v>
       </c>
+      <c r="AW10" t="s">
+        <v>300</v>
+      </c>
       <c r="CB10">
         <v>5</v>
       </c>
@@ -20132,7 +20685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:99" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:99" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I11">
         <v>5</v>
       </c>
@@ -20291,12 +20844,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:99" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:99" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="4" t="s">
         <v>236</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="6"/>
+      <c r="E12" t="s">
+        <v>295</v>
+      </c>
       <c r="I12">
         <v>6</v>
       </c>
@@ -20429,7 +20985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:99" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B13" s="7"/>
       <c r="C13">
         <v>1</v>
@@ -20480,6 +21036,9 @@
       <c r="CC13" t="s">
         <v>89</v>
       </c>
+      <c r="CD13" t="s">
+        <v>260</v>
+      </c>
       <c r="CK13">
         <v>0</v>
       </c>
@@ -20514,7 +21073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:99" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B14" s="7">
         <v>1</v>
       </c>
@@ -20529,6 +21088,12 @@
       <c r="J14" s="55" t="s">
         <v>138</v>
       </c>
+      <c r="L14" t="s">
+        <v>292</v>
+      </c>
+      <c r="N14" t="s">
+        <v>292</v>
+      </c>
       <c r="P14" t="s">
         <v>138</v>
       </c>
@@ -20624,7 +21189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:99" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B15" s="7">
         <v>2</v>
       </c>
@@ -20636,6 +21201,9 @@
         <f t="shared" ref="D15:D19" si="4">D5+COS($B15/POWER(10000,(2*($D$13-1)/$G$4)))</f>
         <v>1.8344616321243081</v>
       </c>
+      <c r="I15" t="s">
+        <v>292</v>
+      </c>
       <c r="J15" t="s">
         <v>147</v>
       </c>
@@ -20653,6 +21221,9 @@
       </c>
       <c r="AD15" t="s">
         <v>152</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>294</v>
       </c>
       <c r="AF15">
         <v>9</v>
@@ -20751,7 +21322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:99" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:99" x14ac:dyDescent="0.3">
       <c r="B16" s="7">
         <v>3</v>
       </c>
@@ -20875,7 +21446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:91" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:91" x14ac:dyDescent="0.3">
       <c r="B17" s="7">
         <v>4</v>
       </c>
@@ -21013,7 +21584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="7">
         <v>5</v>
       </c>
@@ -21137,7 +21708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="9">
         <v>6</v>
       </c>
@@ -21209,6 +21780,9 @@
       <c r="AU19" t="s">
         <v>53</v>
       </c>
+      <c r="AV19" t="s">
+        <v>301</v>
+      </c>
       <c r="CB19">
         <v>5</v>
       </c>
@@ -21233,7 +21807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:91" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:91" x14ac:dyDescent="0.3">
       <c r="I20">
         <v>4</v>
       </c>
@@ -21294,6 +21868,9 @@
       <c r="AG20" t="s">
         <v>68</v>
       </c>
+      <c r="AH20" t="s">
+        <v>248</v>
+      </c>
       <c r="AI20" s="4"/>
       <c r="AJ20" s="39" t="s">
         <v>52</v>
@@ -21302,6 +21879,9 @@
       <c r="AO20" s="39" t="s">
         <v>52</v>
       </c>
+      <c r="AP20" t="s">
+        <v>252</v>
+      </c>
       <c r="AU20">
         <v>1</v>
       </c>
@@ -21332,7 +21912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I21">
         <v>5</v>
       </c>
@@ -21413,7 +21993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I22">
         <v>6</v>
       </c>
@@ -21506,14 +22086,19 @@
       <c r="CC22" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="CD22" s="5"/>
+      <c r="CD22" s="5" t="s">
+        <v>261</v>
+      </c>
       <c r="CE22" s="6"/>
       <c r="CG22" s="4"/>
       <c r="CH22" s="39" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="23" spans="2:91" x14ac:dyDescent="0.25">
+      <c r="CI22" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="23" spans="2:91" x14ac:dyDescent="0.3">
       <c r="B23" s="4"/>
       <c r="C23" s="6" t="s">
         <v>139</v>
@@ -21569,7 +22154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="7"/>
       <c r="C24" s="8">
         <v>1</v>
@@ -21579,6 +22164,12 @@
       </c>
       <c r="G24" s="19">
         <v>1</v>
+      </c>
+      <c r="J24" t="s">
+        <v>292</v>
+      </c>
+      <c r="M24" t="s">
+        <v>296</v>
       </c>
       <c r="AF24">
         <v>3</v>
@@ -21633,7 +22224,7 @@
         <v>-7.1393634409119694E-2</v>
       </c>
     </row>
-    <row r="25" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="7">
         <v>1</v>
       </c>
@@ -21680,7 +22271,7 @@
         <v>-5.8255679584180285E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="9">
         <v>2</v>
       </c>
@@ -21710,6 +22301,9 @@
         <v>69</v>
       </c>
       <c r="AH26" s="6"/>
+      <c r="AI26" t="s">
+        <v>249</v>
+      </c>
       <c r="AO26" t="s">
         <v>81</v>
       </c>
@@ -21740,7 +22334,7 @@
         <v>-0.1521168507036246</v>
       </c>
     </row>
-    <row r="27" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I27">
         <v>1</v>
       </c>
@@ -21767,6 +22361,9 @@
       <c r="AO27">
         <v>1</v>
       </c>
+      <c r="AP27" t="s">
+        <v>253</v>
+      </c>
       <c r="CB27" s="7">
         <v>4</v>
       </c>
@@ -21783,7 +22380,7 @@
         <v>-0.40909550397849603</v>
       </c>
     </row>
-    <row r="28" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I28">
         <v>2</v>
       </c>
@@ -21820,11 +22417,15 @@
       <c r="AU28" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="AV28" s="6"/>
+      <c r="AV28" s="6" t="s">
+        <v>302</v>
+      </c>
       <c r="AX28" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="AY28" s="6"/>
+      <c r="AY28" s="6" t="s">
+        <v>303</v>
+      </c>
       <c r="CB28" s="9">
         <v>5</v>
       </c>
@@ -21841,7 +22442,7 @@
         <v>-9.6204952443682795E-2</v>
       </c>
     </row>
-    <row r="29" spans="2:91" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:91" x14ac:dyDescent="0.3">
       <c r="B29" s="4"/>
       <c r="C29" s="6" t="s">
         <v>142</v>
@@ -21898,7 +22499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="7"/>
       <c r="C30" s="8">
         <v>1</v>
@@ -21960,7 +22561,7 @@
         <v>0.14123210233425343</v>
       </c>
     </row>
-    <row r="31" spans="2:91" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:91" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="7">
         <v>1</v>
       </c>
@@ -22008,7 +22609,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="2:91" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:91" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="9">
         <v>2</v>
       </c>
@@ -22041,6 +22642,9 @@
         <v>72</v>
       </c>
       <c r="AH32" s="6"/>
+      <c r="AI32" t="s">
+        <v>250</v>
+      </c>
       <c r="AN32">
         <v>5</v>
       </c>
@@ -22061,7 +22665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M33" t="s">
         <v>166</v>
       </c>
@@ -22084,8 +22688,14 @@
         <v>164</v>
       </c>
       <c r="AV33" s="6"/>
+      <c r="AW33" t="s">
+        <v>304</v>
+      </c>
       <c r="CC33" t="s">
         <v>89</v>
+      </c>
+      <c r="CD33" t="s">
+        <v>263</v>
       </c>
       <c r="CK33">
         <v>0</v>
@@ -22098,7 +22708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:91" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:91" x14ac:dyDescent="0.3">
       <c r="B34" s="4"/>
       <c r="C34" s="5" t="s">
         <v>145</v>
@@ -22141,7 +22751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:91" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:91" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B35" s="7"/>
       <c r="C35">
         <v>1</v>
@@ -22196,7 +22806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="7">
         <v>1</v>
       </c>
@@ -22209,8 +22819,14 @@
       <c r="J36" t="s">
         <v>161</v>
       </c>
+      <c r="K36" t="s">
+        <v>297</v>
+      </c>
       <c r="M36" t="s">
         <v>53</v>
+      </c>
+      <c r="N36" t="s">
+        <v>297</v>
       </c>
       <c r="AF36" s="9">
         <v>3</v>
@@ -22255,7 +22871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="9">
         <v>2</v>
       </c>
@@ -22310,7 +22926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I38">
         <v>1</v>
       </c>
@@ -22362,7 +22978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I39">
         <v>2</v>
       </c>
@@ -22415,7 +23031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="4"/>
       <c r="C40" s="5" t="s">
         <v>157</v>
@@ -22460,7 +23076,7 @@
         <v>0.44421983963635014</v>
       </c>
     </row>
-    <row r="41" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="7"/>
       <c r="C41">
         <v>1</v>
@@ -22492,6 +23108,9 @@
         <f t="shared" si="15"/>
         <v>2.9982709342803977</v>
       </c>
+      <c r="AN41" t="s">
+        <v>254</v>
+      </c>
       <c r="AO41" s="51" t="s">
         <v>54</v>
       </c>
@@ -22499,7 +23118,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="7">
         <v>1</v>
       </c>
@@ -22549,12 +23168,18 @@
       <c r="CC42" s="39" t="s">
         <v>50</v>
       </c>
+      <c r="CD42" t="s">
+        <v>264</v>
+      </c>
       <c r="CE42" s="4"/>
       <c r="CF42" s="39" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="43" spans="2:91" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="CG42" s="91" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="43" spans="2:91" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="9">
         <v>2</v>
       </c>
@@ -22613,7 +23238,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="2:91" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:91" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="P44" t="s">
+        <v>272</v>
+      </c>
+      <c r="R44" t="s">
+        <v>272</v>
+      </c>
+      <c r="U44" t="s">
+        <v>272</v>
+      </c>
       <c r="AN44">
         <v>2</v>
       </c>
@@ -22651,7 +23285,7 @@
         <v>0.54173300130199498</v>
       </c>
     </row>
-    <row r="45" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="4"/>
       <c r="C45" s="5" t="s">
         <v>159</v>
@@ -22664,10 +23298,15 @@
       <c r="J45" t="s">
         <v>162</v>
       </c>
+      <c r="K45" t="s">
+        <v>297</v>
+      </c>
       <c r="M45" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="N45" s="6"/>
+      <c r="N45" s="6" t="s">
+        <v>297</v>
+      </c>
       <c r="P45" t="s">
         <v>54</v>
       </c>
@@ -22705,7 +23344,7 @@
         <v>0.11326058393356191</v>
       </c>
     </row>
-    <row r="46" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B46" s="7"/>
       <c r="C46">
         <v>1</v>
@@ -22764,7 +23403,9 @@
       <c r="AU46" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="AV46" s="6"/>
+      <c r="AV46" s="6" t="s">
+        <v>306</v>
+      </c>
       <c r="CB46" s="9">
         <v>3</v>
       </c>
@@ -22773,7 +23414,7 @@
         <v>2.030259403762626E-2</v>
       </c>
     </row>
-    <row r="47" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="7">
         <v>1</v>
       </c>
@@ -22849,7 +23490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="2:91" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:91" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="9">
         <v>2</v>
       </c>
@@ -22921,7 +23562,7 @@
         <v>-0.85556170060909542</v>
       </c>
     </row>
-    <row r="49" spans="9:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="9:77" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I49">
         <v>3</v>
       </c>
@@ -22964,7 +23605,7 @@
         <v>2.0283921236423654</v>
       </c>
     </row>
-    <row r="50" spans="9:77" x14ac:dyDescent="0.25">
+    <row r="50" spans="9:77" x14ac:dyDescent="0.3">
       <c r="I50">
         <v>4</v>
       </c>
@@ -22997,6 +23638,9 @@
       <c r="U50" s="58">
         <v>2.6120122844945275</v>
       </c>
+      <c r="AN50" t="s">
+        <v>254</v>
+      </c>
       <c r="AO50" s="55" t="s">
         <v>57</v>
       </c>
@@ -23004,7 +23648,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="51" spans="9:77" x14ac:dyDescent="0.25">
+    <row r="51" spans="9:77" x14ac:dyDescent="0.3">
       <c r="I51">
         <v>5</v>
       </c>
@@ -23049,8 +23693,11 @@
       <c r="AU51" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="52" spans="9:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AV51" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="52" spans="9:77" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I52">
         <v>6</v>
       </c>
@@ -23101,7 +23748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="9:77" x14ac:dyDescent="0.25">
+    <row r="53" spans="9:77" x14ac:dyDescent="0.3">
       <c r="M53" t="s">
         <v>166</v>
       </c>
@@ -23134,7 +23781,7 @@
         <v>-0.11308515933659957</v>
       </c>
     </row>
-    <row r="54" spans="9:77" x14ac:dyDescent="0.25">
+    <row r="54" spans="9:77" x14ac:dyDescent="0.3">
       <c r="T54" s="7">
         <v>8</v>
       </c>
@@ -23162,7 +23809,7 @@
         <v>0.12389379288279803</v>
       </c>
     </row>
-    <row r="55" spans="9:77" x14ac:dyDescent="0.25">
+    <row r="55" spans="9:77" x14ac:dyDescent="0.3">
       <c r="T55" s="7">
         <v>9</v>
       </c>
@@ -23190,10 +23837,10 @@
         <v>-7.8283033501264032E-2</v>
       </c>
       <c r="BT55" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="56" spans="9:77" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="56" spans="9:77" x14ac:dyDescent="0.3">
       <c r="T56" s="7">
         <v>10</v>
       </c>
@@ -23221,7 +23868,7 @@
         <v>1.7436984191050938E-2</v>
       </c>
     </row>
-    <row r="57" spans="9:77" x14ac:dyDescent="0.25">
+    <row r="57" spans="9:77" x14ac:dyDescent="0.3">
       <c r="T57" s="7">
         <v>11</v>
       </c>
@@ -23249,7 +23896,7 @@
         <v>2.1308914118574336E-2</v>
       </c>
     </row>
-    <row r="58" spans="9:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="9:77" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="T58" s="9">
         <v>12</v>
       </c>
@@ -23266,15 +23913,18 @@
         <v>0.27581802020789981</v>
       </c>
     </row>
-    <row r="59" spans="9:77" x14ac:dyDescent="0.25">
+    <row r="59" spans="9:77" x14ac:dyDescent="0.3">
       <c r="AN59" s="4"/>
       <c r="AO59" s="40" t="s">
         <v>79</v>
       </c>
       <c r="AP59" s="6"/>
+      <c r="AQ59" t="s">
+        <v>254</v>
+      </c>
       <c r="BK59" s="3"/>
     </row>
-    <row r="60" spans="9:77" x14ac:dyDescent="0.25">
+    <row r="60" spans="9:77" x14ac:dyDescent="0.3">
       <c r="AN60" s="7"/>
       <c r="AO60">
         <v>1</v>
@@ -23282,8 +23932,14 @@
       <c r="AP60" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" spans="9:77" x14ac:dyDescent="0.25">
+      <c r="BK60" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="BX60" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="61" spans="9:77" x14ac:dyDescent="0.3">
       <c r="AN61" s="22" t="s">
         <v>105</v>
       </c>
@@ -23298,19 +23954,31 @@
       <c r="AU61" s="51" t="s">
         <v>137</v>
       </c>
+      <c r="BD61" t="s">
+        <v>309</v>
+      </c>
       <c r="BK61" t="s">
-        <v>137</v>
-      </c>
-      <c r="BL61" s="77"/>
-      <c r="BM61" s="83"/>
-      <c r="BN61" s="82"/>
+        <v>310</v>
+      </c>
+      <c r="BL61" s="77" t="s">
+        <v>311</v>
+      </c>
+      <c r="BM61" s="83" t="s">
+        <v>312</v>
+      </c>
+      <c r="BN61" s="82" t="s">
+        <v>313</v>
+      </c>
+      <c r="BO61" s="91" t="s">
+        <v>314</v>
+      </c>
       <c r="BS61" s="78"/>
       <c r="BU61" s="78"/>
       <c r="BX61" s="32" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="62" spans="9:77" x14ac:dyDescent="0.25">
+    <row r="62" spans="9:77" x14ac:dyDescent="0.3">
       <c r="AN62" s="7">
         <v>2</v>
       </c>
@@ -23322,11 +23990,17 @@
         <f t="shared" si="31"/>
         <v>0.17342326150584964</v>
       </c>
+      <c r="AT62" t="s">
+        <v>307</v>
+      </c>
       <c r="AU62" t="s">
         <v>168</v>
       </c>
       <c r="AW62" t="s">
         <v>169</v>
+      </c>
+      <c r="AY62" t="s">
+        <v>308</v>
       </c>
       <c r="BD62" t="s">
         <v>170</v>
@@ -23375,7 +24049,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="9:77" x14ac:dyDescent="0.25">
+    <row r="63" spans="9:77" x14ac:dyDescent="0.3">
       <c r="AN63" s="7">
         <v>3</v>
       </c>
@@ -23466,7 +24140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="9:77" x14ac:dyDescent="0.25">
+    <row r="64" spans="9:77" x14ac:dyDescent="0.3">
       <c r="AN64" s="7">
         <v>4</v>
       </c>
@@ -23577,7 +24251,7 @@
         <v>-0.19358645708377689</v>
       </c>
     </row>
-    <row r="65" spans="40:77" x14ac:dyDescent="0.25">
+    <row r="65" spans="40:77" x14ac:dyDescent="0.3">
       <c r="AN65" s="7">
         <v>5</v>
       </c>
@@ -23677,7 +24351,7 @@
         <v>-1.3713776818784298E-2</v>
       </c>
     </row>
-    <row r="66" spans="40:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="40:77" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="AN66" s="9">
         <v>6</v>
       </c>
@@ -23770,7 +24444,7 @@
         <v>1.3484018975240958E-2</v>
       </c>
     </row>
-    <row r="67" spans="40:77" x14ac:dyDescent="0.25">
+    <row r="67" spans="40:77" x14ac:dyDescent="0.3">
       <c r="AT67">
         <v>4</v>
       </c>
@@ -23852,7 +24526,7 @@
         <v>2.7014107409180272E-2</v>
       </c>
     </row>
-    <row r="68" spans="40:77" x14ac:dyDescent="0.25">
+    <row r="68" spans="40:77" x14ac:dyDescent="0.3">
       <c r="AT68">
         <v>5</v>
       </c>
@@ -23934,7 +24608,7 @@
         <v>4.3618056652626837E-2</v>
       </c>
     </row>
-    <row r="69" spans="40:77" x14ac:dyDescent="0.25">
+    <row r="69" spans="40:77" x14ac:dyDescent="0.3">
       <c r="AT69">
         <v>6</v>
       </c>
@@ -24016,42 +24690,66 @@
         <v>2.2053123630367166E-2</v>
       </c>
     </row>
-    <row r="70" spans="40:77" x14ac:dyDescent="0.25">
+    <row r="70" spans="40:77" x14ac:dyDescent="0.3">
       <c r="BL70" s="77"/>
       <c r="BM70" s="83"/>
       <c r="BN70" s="82"/>
       <c r="BS70" s="78"/>
       <c r="BU70" s="78"/>
     </row>
-    <row r="71" spans="40:77" x14ac:dyDescent="0.25">
+    <row r="71" spans="40:77" x14ac:dyDescent="0.3">
+      <c r="BK71" s="55" t="s">
+        <v>138</v>
+      </c>
       <c r="BL71" s="77"/>
       <c r="BM71" s="83"/>
       <c r="BN71" s="82"/>
       <c r="BS71" s="78"/>
       <c r="BU71" s="78"/>
-    </row>
-    <row r="72" spans="40:77" x14ac:dyDescent="0.25">
+      <c r="BX71" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="72" spans="40:77" x14ac:dyDescent="0.3">
       <c r="AU72" s="55" t="s">
         <v>138</v>
       </c>
+      <c r="BD72" t="s">
+        <v>309</v>
+      </c>
       <c r="BK72" t="s">
-        <v>138</v>
-      </c>
-      <c r="BL72" s="77"/>
-      <c r="BM72" s="83"/>
-      <c r="BN72" s="82"/>
+        <v>310</v>
+      </c>
+      <c r="BL72" s="77" t="s">
+        <v>311</v>
+      </c>
+      <c r="BM72" s="83" t="s">
+        <v>312</v>
+      </c>
+      <c r="BN72" s="82" t="s">
+        <v>313</v>
+      </c>
+      <c r="BO72" s="91" t="s">
+        <v>314</v>
+      </c>
       <c r="BS72" s="78"/>
       <c r="BU72" s="78"/>
       <c r="BX72" s="32" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="73" spans="40:77" x14ac:dyDescent="0.25">
+    <row r="73" spans="40:77" x14ac:dyDescent="0.3">
+      <c r="AT73" t="s">
+        <v>307</v>
+      </c>
       <c r="AU73" t="s">
         <v>168</v>
       </c>
       <c r="AW73" t="s">
         <v>169</v>
+      </c>
+      <c r="AY73" t="s">
+        <v>308</v>
       </c>
       <c r="BD73" t="s">
         <v>170</v>
@@ -24100,7 +24798,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="40:77" x14ac:dyDescent="0.25">
+    <row r="74" spans="40:77" x14ac:dyDescent="0.3">
       <c r="AU74">
         <v>1</v>
       </c>
@@ -24180,7 +24878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="40:77" x14ac:dyDescent="0.25">
+    <row r="75" spans="40:77" x14ac:dyDescent="0.3">
       <c r="AT75">
         <v>1</v>
       </c>
@@ -24280,7 +24978,7 @@
         <v>-9.279764214087606E-2</v>
       </c>
     </row>
-    <row r="76" spans="40:77" x14ac:dyDescent="0.25">
+    <row r="76" spans="40:77" x14ac:dyDescent="0.3">
       <c r="AT76">
         <v>2</v>
       </c>
@@ -24369,7 +25067,7 @@
         <v>9.6444295747436917E-2</v>
       </c>
     </row>
-    <row r="77" spans="40:77" x14ac:dyDescent="0.25">
+    <row r="77" spans="40:77" x14ac:dyDescent="0.3">
       <c r="AT77">
         <v>3</v>
       </c>
@@ -24451,7 +25149,7 @@
         <v>-2.1267403880453308E-2</v>
       </c>
     </row>
-    <row r="78" spans="40:77" x14ac:dyDescent="0.25">
+    <row r="78" spans="40:77" x14ac:dyDescent="0.3">
       <c r="AT78">
         <v>4</v>
       </c>
@@ -24533,7 +25231,7 @@
         <v>5.2139358210810463E-3</v>
       </c>
     </row>
-    <row r="79" spans="40:77" x14ac:dyDescent="0.25">
+    <row r="79" spans="40:77" x14ac:dyDescent="0.3">
       <c r="AT79">
         <v>5</v>
       </c>
@@ -24615,7 +25313,7 @@
         <v>2.0814586498721102E-2</v>
       </c>
     </row>
-    <row r="80" spans="40:77" x14ac:dyDescent="0.25">
+    <row r="80" spans="40:77" x14ac:dyDescent="0.3">
       <c r="AT80">
         <v>6</v>
       </c>
@@ -24697,8 +25395,11 @@
         <v>6.318562828453067E-2</v>
       </c>
     </row>
-    <row r="81" spans="75:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="82" spans="75:80" x14ac:dyDescent="0.25">
+    <row r="81" spans="74:81" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="82" spans="74:81" x14ac:dyDescent="0.3">
+      <c r="BV82" t="s">
+        <v>291</v>
+      </c>
       <c r="BX82" t="s">
         <v>180</v>
       </c>
@@ -24706,8 +25407,11 @@
         <v>80</v>
       </c>
       <c r="CB82" s="6"/>
-    </row>
-    <row r="83" spans="75:80" x14ac:dyDescent="0.25">
+      <c r="CC82" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="83" spans="74:81" x14ac:dyDescent="0.3">
       <c r="BX83" t="s">
         <v>18</v>
       </c>
@@ -24716,7 +25420,7 @@
       </c>
       <c r="CB83" s="8"/>
     </row>
-    <row r="84" spans="75:80" x14ac:dyDescent="0.25">
+    <row r="84" spans="74:81" x14ac:dyDescent="0.3">
       <c r="BX84">
         <v>1</v>
       </c>
@@ -24730,7 +25434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="75:80" x14ac:dyDescent="0.25">
+    <row r="85" spans="74:81" x14ac:dyDescent="0.3">
       <c r="BW85">
         <v>1</v>
       </c>
@@ -24749,7 +25453,7 @@
         <v>-0.34703783046926057</v>
       </c>
     </row>
-    <row r="86" spans="75:80" x14ac:dyDescent="0.25">
+    <row r="86" spans="74:81" x14ac:dyDescent="0.3">
       <c r="BW86">
         <v>2</v>
       </c>
@@ -24766,7 +25470,7 @@
         <v>0.26571896627424363</v>
       </c>
     </row>
-    <row r="87" spans="75:80" x14ac:dyDescent="0.25">
+    <row r="87" spans="74:81" x14ac:dyDescent="0.3">
       <c r="BW87">
         <v>3</v>
       </c>
@@ -24783,7 +25487,7 @@
         <v>5.3769484092061781E-2</v>
       </c>
     </row>
-    <row r="88" spans="75:80" x14ac:dyDescent="0.25">
+    <row r="88" spans="74:81" x14ac:dyDescent="0.3">
       <c r="BW88">
         <v>4</v>
       </c>
@@ -24800,7 +25504,7 @@
         <v>5.2212388813391221E-2</v>
       </c>
     </row>
-    <row r="89" spans="75:80" x14ac:dyDescent="0.25">
+    <row r="89" spans="74:81" x14ac:dyDescent="0.3">
       <c r="BW89">
         <v>5</v>
       </c>
@@ -24817,7 +25521,7 @@
         <v>7.2850152955208775E-2</v>
       </c>
     </row>
-    <row r="90" spans="75:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="74:81" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="BW90">
         <v>6</v>
       </c>
@@ -24834,7 +25538,7 @@
         <v>0.44421983963635014</v>
       </c>
     </row>
-    <row r="91" spans="75:80" x14ac:dyDescent="0.25">
+    <row r="91" spans="74:81" x14ac:dyDescent="0.3">
       <c r="CA91" t="s">
         <v>179</v>
       </c>
@@ -24851,20 +25555,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6F9AD1-DA29-4072-9F68-4519EE583285}">
   <dimension ref="B2:AE95"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" customWidth="1"/>
+    <col min="2" max="2" width="4.33203125" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="8" max="8" width="2.28515625" customWidth="1"/>
+    <col min="8" max="8" width="2.33203125" customWidth="1"/>
     <col min="11" max="11" width="5" customWidth="1"/>
-    <col min="12" max="14" width="8.28515625" customWidth="1"/>
+    <col min="12" max="14" width="8.33203125" customWidth="1"/>
     <col min="15" max="15" width="5" customWidth="1"/>
-    <col min="27" max="27" width="3.42578125" customWidth="1"/>
+    <col min="27" max="27" width="3.44140625" customWidth="1"/>
+    <col min="28" max="28" width="13.21875" customWidth="1"/>
+    <col min="29" max="29" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:31" x14ac:dyDescent="0.3">
       <c r="E2" t="s">
         <v>47</v>
       </c>
@@ -24888,7 +25594,7 @@
       <c r="Y2" s="89"/>
       <c r="Z2" s="89"/>
     </row>
-    <row r="3" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:31" x14ac:dyDescent="0.3">
       <c r="E3" t="s">
         <v>42</v>
       </c>
@@ -24921,7 +25627,7 @@
       <c r="Y3" s="89"/>
       <c r="Z3" s="89"/>
     </row>
-    <row r="4" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="14"/>
       <c r="C4" s="14" t="s">
         <v>223</v>
@@ -24962,7 +25668,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="5" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:31" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>190</v>
       </c>
@@ -25008,7 +25714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:31" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>91</v>
       </c>
@@ -25054,7 +25760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="14"/>
       <c r="C7" s="14" t="s">
         <v>197</v>
@@ -25099,7 +25805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="86" t="s">
         <v>192</v>
       </c>
@@ -25145,7 +25851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B9" s="87"/>
       <c r="C9" t="s">
         <v>190</v>
@@ -25184,11 +25890,20 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
+      <c r="V9" t="s">
+        <v>316</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>315</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>317</v>
+      </c>
       <c r="AB9" s="32" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="87"/>
       <c r="C10" s="14" t="s">
         <v>190</v>
@@ -25266,7 +25981,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="11" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="86" t="s">
         <v>192</v>
       </c>
@@ -25361,7 +26076,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B12" s="87"/>
       <c r="C12" t="s">
         <v>91</v>
@@ -25435,7 +26150,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="87"/>
       <c r="C13" s="14" t="s">
         <v>91</v>
@@ -25507,7 +26222,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="86" t="s">
         <v>192</v>
       </c>
@@ -25582,7 +26297,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="15" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B15" s="87"/>
       <c r="C15" t="s">
         <v>197</v>
@@ -25670,7 +26385,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="16" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="88"/>
       <c r="C16" s="14" t="s">
         <v>197</v>
@@ -25730,7 +26445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="5:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:31" x14ac:dyDescent="0.3">
       <c r="R17" s="3">
         <f>IF($Q$7&gt;$Q15,1,0)</f>
         <v>1</v>
@@ -25755,6 +26470,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
+      <c r="AB17" t="s">
+        <v>318</v>
+      </c>
       <c r="AC17" t="s">
         <v>212</v>
       </c>
@@ -25765,7 +26483,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="18" spans="5:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:31" x14ac:dyDescent="0.3">
       <c r="R18" s="3">
         <f>IF($Q$8&gt;$Q15,1,0)</f>
         <v>1</v>
@@ -25806,7 +26524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="5:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="5:31" x14ac:dyDescent="0.3">
       <c r="Q19" s="3">
         <v>0.35</v>
       </c>
@@ -25859,7 +26577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="5:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:31" x14ac:dyDescent="0.3">
       <c r="F20" t="s">
         <v>73</v>
       </c>
@@ -25903,7 +26621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="5:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F21" t="s">
         <v>74</v>
       </c>
@@ -25951,7 +26669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="5:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E22" t="s">
         <v>42</v>
       </c>
@@ -25999,7 +26717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="5:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="5:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E23" t="s">
         <v>43</v>
       </c>
@@ -26056,7 +26774,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="5:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="5:31" x14ac:dyDescent="0.3">
       <c r="E24" t="s">
         <v>44</v>
       </c>
@@ -26097,6 +26815,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
+      <c r="AB24" t="s">
+        <v>318</v>
+      </c>
       <c r="AC24" t="s">
         <v>212</v>
       </c>
@@ -26107,7 +26828,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="25" spans="5:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="5:31" x14ac:dyDescent="0.3">
       <c r="F25" t="s">
         <v>198</v>
       </c>
@@ -26152,7 +26873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="5:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:31" x14ac:dyDescent="0.3">
       <c r="R26" s="3">
         <f>IF($Q$8&gt;$Q23,1,0)</f>
         <v>1</v>
@@ -26190,7 +26911,7 @@
         <v>0.19444444444444442</v>
       </c>
     </row>
-    <row r="27" spans="5:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="5:31" x14ac:dyDescent="0.3">
       <c r="Q27" s="3">
         <v>0</v>
       </c>
@@ -26243,7 +26964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="5:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="R28" s="3">
         <f>IF($Q$6&gt;$Q27,1,0)</f>
         <v>1</v>
@@ -26281,7 +27002,7 @@
         <v>0.2361111111111111</v>
       </c>
     </row>
-    <row r="29" spans="5:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="5:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="R29" s="3">
         <f>IF($Q$7&gt;$Q27,1,0)</f>
         <v>1</v>
@@ -26314,7 +27035,7 @@
         <v>0.43055555555555552</v>
       </c>
     </row>
-    <row r="30" spans="5:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="5:31" x14ac:dyDescent="0.3">
       <c r="R30" s="3">
         <f>IF($Q$8&gt;$Q27,1,0)</f>
         <v>1</v>
@@ -26343,20 +27064,20 @@
         <v>215</v>
       </c>
     </row>
-    <row r="31" spans="5:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="5:31" x14ac:dyDescent="0.3">
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
     </row>
-    <row r="32" spans="5:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="5:31" x14ac:dyDescent="0.3">
       <c r="R32" s="3"/>
     </row>
-    <row r="33" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q33" s="32" t="s">
         <v>43</v>
       </c>
       <c r="T33" s="13"/>
     </row>
-    <row r="34" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="34" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q34" t="s">
         <v>199</v>
       </c>
@@ -26364,7 +27085,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q35">
         <f>$F$5</f>
         <v>8.1256020712886692E-2</v>
@@ -26374,7 +27095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q36" cm="1">
         <f t="array" ref="Q36:Q38">F8:$F$10</f>
         <v>0.21139614185137856</v>
@@ -26384,7 +27105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="37" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q37">
         <v>0.64566804354494844</v>
       </c>
@@ -26392,7 +27113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="38" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q38" s="3">
         <v>0.83554519071599687</v>
       </c>
@@ -26400,14 +27121,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="39" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
+      <c r="V39" t="s">
+        <v>316</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>315</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>317</v>
+      </c>
       <c r="AB39" s="32" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="40" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q40" t="s">
         <v>208</v>
       </c>
@@ -26451,7 +27181,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="41" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="41" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q41" s="3">
         <v>0.7</v>
       </c>
@@ -26508,7 +27238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R42" s="3">
         <f>IF($Q$36&gt;$Q41,1,0)</f>
         <v>0</v>
@@ -26546,7 +27276,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="43" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="43" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R43" s="3">
         <f>IF($Q$37&gt;$Q41,1,0)</f>
         <v>0</v>
@@ -26584,7 +27314,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="44" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R44" s="3">
         <f>IF($Q$38&gt;$Q41,1,0)</f>
         <v>1</v>
@@ -26622,7 +27352,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="45" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="45" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q45" s="3">
         <v>0.6</v>
       </c>
@@ -26675,7 +27405,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="46" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R46" s="3">
         <f>IF($Q$36&gt;$Q45,1,0)</f>
         <v>0</v>
@@ -26701,7 +27431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="47" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R47" s="3">
         <f>IF($Q$37&gt;$Q45,1,0)</f>
         <v>1</v>
@@ -26726,6 +27456,9 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
+      <c r="AB47" t="s">
+        <v>318</v>
+      </c>
       <c r="AC47" t="s">
         <v>212</v>
       </c>
@@ -26736,7 +27469,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="48" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="48" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R48" s="3">
         <f>IF($Q$38&gt;$Q45,1,0)</f>
         <v>1</v>
@@ -26777,7 +27510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="49" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q49" s="3">
         <v>0.4</v>
       </c>
@@ -26830,7 +27563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="50" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R50" s="3">
         <f>IF($Q$36&gt;$Q49,1,0)</f>
         <v>0</v>
@@ -26868,7 +27601,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="51" spans="17:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="17:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="R51" s="3">
         <f>IF($Q$37&gt;$Q49,1,0)</f>
         <v>1</v>
@@ -26906,7 +27639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="17:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="17:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="R52" s="3">
         <f>IF($Q$38&gt;$Q49,1,0)</f>
         <v>1</v>
@@ -26939,7 +27672,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="53" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="53" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q53" s="3">
         <v>0.2</v>
       </c>
@@ -26980,7 +27713,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="54" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="54" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R54" s="3">
         <f>IF($Q$36&gt;$Q53,1,0)</f>
         <v>1</v>
@@ -27005,6 +27738,9 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
+      <c r="AB54" t="s">
+        <v>318</v>
+      </c>
       <c r="AC54" t="s">
         <v>212</v>
       </c>
@@ -27015,7 +27751,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="55" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="55" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R55" s="3">
         <f>IF($Q$37&gt;$Q53,1,0)</f>
         <v>1</v>
@@ -27056,7 +27792,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="56" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="56" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R56" s="3">
         <f>IF($Q$38&gt;$Q53,1,0)</f>
         <v>1</v>
@@ -27094,7 +27830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="57" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q57" s="3">
         <v>0</v>
       </c>
@@ -27147,7 +27883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="17:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="17:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="R58" s="3">
         <f>IF($Q$36&gt;$Q57,1,0)</f>
         <v>1</v>
@@ -27185,7 +27921,7 @@
         <v>0.20833333333333331</v>
       </c>
     </row>
-    <row r="59" spans="17:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="17:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="R59" s="3">
         <f>IF($Q$37&gt;$Q57,1,0)</f>
         <v>1</v>
@@ -27218,7 +27954,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="60" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="60" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R60" s="3">
         <f>IF($Q$38&gt;$Q57,1,0)</f>
         <v>1</v>
@@ -27247,13 +27983,13 @@
         <v>215</v>
       </c>
     </row>
-    <row r="63" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="63" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q63" s="32" t="s">
         <v>44</v>
       </c>
       <c r="T63" s="13"/>
     </row>
-    <row r="64" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="64" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q64" t="s">
         <v>199</v>
       </c>
@@ -27261,7 +27997,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="65" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="65" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q65">
         <f>$G$5</f>
         <v>0.53378606178880916</v>
@@ -27271,7 +28007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="66" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q66" cm="1">
         <f t="array" ref="Q66:Q68">G$8:$G10</f>
         <v>0.74796252013739595</v>
@@ -27281,7 +28017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="67" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q67">
         <v>0.979370096177136</v>
       </c>
@@ -27289,7 +28025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="68" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q68" s="3">
         <v>0.74381321270919576</v>
       </c>
@@ -27297,14 +28033,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="69" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q69" s="3"/>
       <c r="R69" s="3"/>
+      <c r="V69" t="s">
+        <v>316</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>315</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>317</v>
+      </c>
       <c r="AB69" s="32" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="70" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="70" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q70" t="s">
         <v>208</v>
       </c>
@@ -27348,7 +28093,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="71" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="71" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q71" s="3">
         <v>0.9</v>
       </c>
@@ -27405,7 +28150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="72" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R72" s="3">
         <f>IF($Q$66&gt;$Q71,1,0)</f>
         <v>0</v>
@@ -27443,7 +28188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="73" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R73" s="3">
         <f>IF($Q$67&gt;$Q71,1,0)</f>
         <v>1</v>
@@ -27481,7 +28226,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="74" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="74" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R74" s="3">
         <f>IF($Q$68&gt;$Q71,1,0)</f>
         <v>0</v>
@@ -27519,7 +28264,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="75" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="75" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q75" s="3">
         <v>0.75</v>
       </c>
@@ -27572,7 +28317,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="76" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="76" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R76" s="3">
         <f>IF($Q$66&gt;$Q75,1,0)</f>
         <v>0</v>
@@ -27598,7 +28343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="77" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R77" s="3">
         <f>IF($Q$67&gt;$Q75,1,0)</f>
         <v>1</v>
@@ -27623,6 +28368,9 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="AB77" t="s">
+        <v>318</v>
+      </c>
       <c r="AC77" t="s">
         <v>212</v>
       </c>
@@ -27633,7 +28381,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="78" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="78" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R78" s="3">
         <f>IF($Q$68&gt;$Q75,1,0)</f>
         <v>0</v>
@@ -27674,7 +28422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="79" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q79" s="3">
         <v>0.5</v>
       </c>
@@ -27727,7 +28475,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="80" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="80" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R80" s="3">
         <f>IF($Q$66&gt;$Q79,1,0)</f>
         <v>1</v>
@@ -27765,7 +28513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="17:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="17:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="R81" s="3">
         <f>IF($Q$67&gt;$Q79,1,0)</f>
         <v>1</v>
@@ -27803,7 +28551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="17:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="17:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="R82" s="3">
         <f>IF($Q$68&gt;$Q79,1,0)</f>
         <v>1</v>
@@ -27836,7 +28584,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="83" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="83" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q83" s="3">
         <v>0.25</v>
       </c>
@@ -27877,7 +28625,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="84" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="84" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R84" s="3">
         <f>IF($Q$66&gt;$Q83,1,0)</f>
         <v>1</v>
@@ -27902,6 +28650,9 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="AB84" t="s">
+        <v>318</v>
+      </c>
       <c r="AC84" t="s">
         <v>212</v>
       </c>
@@ -27912,7 +28663,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="85" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="85" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R85" s="3">
         <f>IF($Q$67&gt;$Q83,1,0)</f>
         <v>1</v>
@@ -27953,7 +28704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="86" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R86" s="3">
         <f>IF($Q$68&gt;$Q83,1,0)</f>
         <v>1</v>
@@ -27991,7 +28742,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="87" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="87" spans="17:31" x14ac:dyDescent="0.3">
       <c r="Q87" s="3">
         <v>0</v>
       </c>
@@ -28044,7 +28795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="17:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="17:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="R88" s="3">
         <f>IF($Q$66&gt;$Q87,1,0)</f>
         <v>1</v>
@@ -28082,7 +28833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="17:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="17:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="R89" s="3">
         <f>IF($Q$67&gt;$Q87,1,0)</f>
         <v>1</v>
@@ -28115,7 +28866,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="90" spans="17:31" x14ac:dyDescent="0.25">
+    <row r="90" spans="17:31" x14ac:dyDescent="0.3">
       <c r="R90" s="3">
         <f>IF($Q$68&gt;$Q87,1,0)</f>
         <v>1</v>
@@ -28144,27 +28895,31 @@
         <v>215</v>
       </c>
     </row>
-    <row r="92" spans="17:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="93" spans="17:31" x14ac:dyDescent="0.25">
-      <c r="AB93" s="4" t="s">
+    <row r="92" spans="17:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AB92" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="93" spans="17:31" ht="21" x14ac:dyDescent="0.4">
+      <c r="AB93" s="99" t="s">
         <v>220</v>
       </c>
-      <c r="AC93" s="6"/>
-    </row>
-    <row r="94" spans="17:31" x14ac:dyDescent="0.25">
-      <c r="AB94" s="7" t="s">
+      <c r="AC93" s="94"/>
+    </row>
+    <row r="94" spans="17:31" ht="21" x14ac:dyDescent="0.4">
+      <c r="AB94" s="95" t="s">
         <v>219</v>
       </c>
-      <c r="AC94" s="8">
+      <c r="AC94" s="96">
         <f>AVERAGE(AE29,AE59,AE89)</f>
         <v>0.37962962962962959</v>
       </c>
     </row>
-    <row r="95" spans="17:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="AB95" s="9" t="s">
+    <row r="95" spans="17:31" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="AB95" s="97" t="s">
         <v>216</v>
       </c>
-      <c r="AC95" s="11">
+      <c r="AC95" s="98">
         <f>AVERAGE(AE22,AE52,AE82)</f>
         <v>0.33333333333333331</v>
       </c>
@@ -28179,30 +28934,31 @@
     <mergeCell ref="B8:B10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817AFDBE-D2B7-413E-A3D5-D851765F9C1A}">
   <dimension ref="B2:E14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="30" t="s">
         <v>181</v>
       </c>
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
     </row>
-    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="C3" s="30" t="s">
         <v>40</v>
       </c>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
     </row>
-    <row r="4" spans="2:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="C4" s="30" t="s">
         <v>182</v>
       </c>
@@ -28211,7 +28967,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="C5" s="30" t="s">
         <v>183</v>
       </c>
@@ -28220,7 +28976,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="C6" s="30" t="s">
         <v>184</v>
       </c>
@@ -28229,7 +28985,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="C7" s="30" t="s">
         <v>185</v>
       </c>
@@ -28238,7 +28994,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="C8" s="30" t="s">
         <v>193</v>
       </c>
@@ -28247,38 +29003,38 @@
         <v>194</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
     </row>
-    <row r="10" spans="2:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
     </row>
-    <row r="11" spans="2:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="B11" s="30" t="s">
         <v>186</v>
       </c>
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
     </row>
-    <row r="12" spans="2:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="C12" s="30" t="s">
         <v>187</v>
       </c>
       <c r="D12" s="30"/>
       <c r="E12" s="30"/>
     </row>
-    <row r="13" spans="2:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="C13" s="30" t="s">
         <v>91</v>
       </c>
       <c r="D13" s="30"/>
       <c r="E13" s="30"/>
     </row>
-    <row r="14" spans="2:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" ht="21" x14ac:dyDescent="0.4">
       <c r="C14" s="30" t="s">
         <v>188</v>
       </c>
@@ -28293,42 +29049,42 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43F2746B-7BB6-4A66-B9F2-FBCB99C23FF4}">
   <dimension ref="C2:D9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="4" width="3.5703125" customWidth="1"/>
-    <col min="5" max="5" width="3.42578125" customWidth="1"/>
-    <col min="6" max="14" width="3.5703125" customWidth="1"/>
+    <col min="2" max="4" width="3.5546875" customWidth="1"/>
+    <col min="5" max="5" width="3.44140625" customWidth="1"/>
+    <col min="6" max="14" width="3.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
     </row>
-    <row r="3" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
     </row>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
     </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C5" s="17"/>
       <c r="D5" s="17"/>
     </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
     </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
     </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
     </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
     </row>
@@ -28340,18 +29096,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD033527-37AD-4DB1-BD2E-4C935B310A9F}">
   <dimension ref="B2:Z54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" customWidth="1"/>
-    <col min="2" max="2" width="4.5703125" customWidth="1"/>
+    <col min="1" max="1" width="1.44140625" customWidth="1"/>
+    <col min="2" max="2" width="4.5546875" customWidth="1"/>
     <col min="3" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="1.42578125" customWidth="1"/>
+    <col min="7" max="7" width="1.44140625" customWidth="1"/>
     <col min="8" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="1.42578125" customWidth="1"/>
-    <col min="15" max="26" width="5.7109375" customWidth="1"/>
+    <col min="14" max="14" width="1.44140625" customWidth="1"/>
+    <col min="15" max="26" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>15</v>
       </c>
@@ -28383,7 +29139,7 @@
       </c>
       <c r="Z2" s="84"/>
     </row>
-    <row r="3" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>7</v>
       </c>
@@ -28449,7 +29205,7 @@
         <v>0.51061699565780228</v>
       </c>
     </row>
-    <row r="4" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>8</v>
       </c>
@@ -28514,7 +29270,7 @@
         <v>0.30089049095355536</v>
       </c>
     </row>
-    <row r="5" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -28544,7 +29300,7 @@
         <v>X_6</v>
       </c>
     </row>
-    <row r="6" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>10</v>
       </c>
@@ -28563,7 +29319,7 @@
       </c>
       <c r="T6" s="84"/>
     </row>
-    <row r="7" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -28590,7 +29346,7 @@
         <v>0.60288218050147402</v>
       </c>
     </row>
-    <row r="8" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>12</v>
       </c>
@@ -28616,7 +29372,7 @@
         <v>3.353831251399042E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:26" x14ac:dyDescent="0.3">
       <c r="O9" t="s">
         <v>31</v>
       </c>
@@ -28624,7 +29380,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>38</v>
       </c>
@@ -28632,7 +29388,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>13</v>
       </c>
@@ -28640,7 +29396,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>16</v>
       </c>
@@ -28651,7 +29407,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C13" cm="1">
         <f t="array" ref="C13:C14">MMULT(O$3:P$4,H$3:H$4)</f>
         <v>0.62411361546242827</v>
@@ -28665,7 +29421,7 @@
         <v>1.317076111847346</v>
       </c>
     </row>
-    <row r="14" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C14">
         <v>0.7897161729094363</v>
       </c>
@@ -28677,12 +29433,12 @@
         <v>1.9559033815844153</v>
       </c>
     </row>
-    <row r="16" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>20</v>
       </c>
@@ -28693,7 +29449,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C18" cm="1">
         <f t="array" ref="C18:C19">MMULT($Q$3:$R$4,$H$3:$H$4)</f>
         <v>0.78366234361470832</v>
@@ -28707,7 +29463,7 @@
         <v>2.1823932041316936</v>
       </c>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C19">
         <v>0.48251104303892989</v>
       </c>
@@ -28719,12 +29475,12 @@
         <v>1.3131825630918288</v>
       </c>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>23</v>
       </c>
@@ -28738,7 +29494,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C23" cm="1">
         <f t="array" ref="C23:C24">MMULT($S$3:$T$4,$H$3:$H$4)</f>
         <v>0.65583462699784345</v>
@@ -28756,7 +29512,7 @@
         <v>2.3238963753317696</v>
       </c>
     </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C24">
         <v>0.38443325559022234</v>
       </c>
@@ -28772,17 +29528,17 @@
         <v>1.5309995108431966</v>
       </c>
     </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>26</v>
       </c>
@@ -28796,7 +29552,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C29" cm="1">
         <f t="array" ref="C29:C30">1-$E18:$E19</f>
         <v>-1.1823932041316936</v>
@@ -28814,7 +29570,7 @@
         <v>-0.85863640259673746</v>
       </c>
     </row>
-    <row r="30" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C30">
         <v>-0.31318256309182879</v>
       </c>
@@ -28831,7 +29587,7 @@
         <v>0.31221201613510774</v>
       </c>
     </row>
-    <row r="31" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
         <v>24</v>
       </c>
@@ -28842,7 +29598,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>13</v>
       </c>
@@ -28850,7 +29606,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C35" t="s">
         <v>16</v>
       </c>
@@ -28861,7 +29617,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C36" cm="1">
         <f t="array" ref="C36:C37">MMULT(O$3:P$4,H$3:H$4)</f>
         <v>0.62411361546242827</v>
@@ -28875,7 +29631,7 @@
         <v>0.7012357139183325</v>
       </c>
     </row>
-    <row r="37" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C37">
         <v>0.7897161729094363</v>
       </c>
@@ -28887,12 +29643,12 @@
         <v>1.0861390144718301</v>
       </c>
     </row>
-    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C40" t="s">
         <v>20</v>
       </c>
@@ -28903,7 +29659,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C41" cm="1">
         <f t="array" ref="C41:C42">MMULT($Q$3:$R$4,$H$3:$H$4)</f>
         <v>0.78366234361470832</v>
@@ -28917,7 +29673,7 @@
         <v>1.1313607868290743</v>
       </c>
     </row>
-    <row r="42" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C42">
         <v>0.48251104303892989</v>
       </c>
@@ -28929,12 +29685,12 @@
         <v>0.66201100267487245</v>
       </c>
     </row>
-    <row r="44" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
         <v>23</v>
       </c>
@@ -28948,7 +29704,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C46" cm="1">
         <f t="array" ref="C46:C47">MMULT($S$3:$T$4,$H$3:$H$4)</f>
         <v>0.65583462699784345</v>
@@ -28966,7 +29722,7 @@
         <v>0.89069962108654921</v>
       </c>
     </row>
-    <row r="47" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C47">
         <v>0.38443325559022234</v>
       </c>
@@ -28982,17 +29738,17 @@
         <v>0.55602969078262698</v>
       </c>
     </row>
-    <row r="48" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C51" t="s">
         <v>26</v>
       </c>
@@ -29006,7 +29762,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C52" cm="1">
         <f t="array" ref="C52:C53">1-$E41:$E42</f>
         <v>-0.13136078682907426</v>
@@ -29024,7 +29780,7 @@
         <v>0.25618070514883418</v>
       </c>
     </row>
-    <row r="53" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C53">
         <v>0.33798899732512755</v>
       </c>
@@ -29041,7 +29797,7 @@
         <v>0.21013464956603084</v>
       </c>
     </row>
-    <row r="54" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
         <v>24</v>
       </c>

--- a/ai/manualisation.xlsx
+++ b/ai/manualisation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\100-KULIAH\SKRIPSI\skripsi-code\ai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5158FE7-00A2-4216-9D11-DB6231D242E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DF2178-06BF-462D-8A95-8C659B7B09D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{145D0042-0CBE-48BE-846C-2BE8EAD29D31}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="5" xr2:uid="{145D0042-0CBE-48BE-846C-2BE8EAD29D31}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="3" r:id="rId1"/>
@@ -1480,7 +1480,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1583,12 +1583,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -1598,21 +1601,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -8081,11 +8078,11 @@
       <c r="A15">
         <v>1</v>
       </c>
-      <c r="B15" s="84" t="s">
+      <c r="B15" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="84"/>
-      <c r="D15" s="84"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
       <c r="E15" t="s">
         <v>42</v>
       </c>
@@ -8103,11 +8100,11 @@
       <c r="A16">
         <v>2</v>
       </c>
-      <c r="B16" s="85" t="s">
+      <c r="B16" s="96" t="s">
         <v>192</v>
       </c>
-      <c r="C16" s="85"/>
-      <c r="D16" s="85"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="96"/>
       <c r="E16" t="s">
         <v>42</v>
       </c>
@@ -8125,9 +8122,9 @@
       <c r="A17">
         <v>3</v>
       </c>
-      <c r="B17" s="85"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
+      <c r="B17" s="96"/>
+      <c r="C17" s="96"/>
+      <c r="D17" s="96"/>
       <c r="E17" t="s">
         <v>44</v>
       </c>
@@ -8145,9 +8142,9 @@
       <c r="A18">
         <v>4</v>
       </c>
-      <c r="B18" s="85"/>
-      <c r="C18" s="85"/>
-      <c r="D18" s="85"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="96"/>
       <c r="E18" t="s">
         <v>42</v>
       </c>
@@ -8190,99 +8187,99 @@
       </c>
       <c r="C2">
         <f ca="1">RAND()</f>
-        <v>0.43057286975935449</v>
+        <v>0.4791384538825213</v>
       </c>
       <c r="D2">
         <f t="shared" ref="D2:Z2" ca="1" si="0">RAND()</f>
-        <v>0.31294853361309871</v>
+        <v>0.19118964753366618</v>
       </c>
       <c r="E2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.85297780739100126</v>
+        <v>0.49791249125337567</v>
       </c>
       <c r="F2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.58569296255756664</v>
+        <v>0.76304610679394824</v>
       </c>
       <c r="G2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.19389175809730197</v>
+        <v>0.87375225444666982</v>
       </c>
       <c r="H2">
         <f t="shared" ca="1" si="0"/>
-        <v>5.6549442343509337E-2</v>
+        <v>5.0190931263846883E-2</v>
       </c>
       <c r="I2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.87197816177079868</v>
+        <v>0.17350610584198978</v>
       </c>
       <c r="J2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.28208267439078993</v>
+        <v>0.37840420650824114</v>
       </c>
       <c r="K2">
         <f t="shared" ca="1" si="0"/>
-        <v>8.5751688364835044E-2</v>
+        <v>5.8442778123235173E-2</v>
       </c>
       <c r="L2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.44424798035031066</v>
+        <v>0.53169126865397631</v>
       </c>
       <c r="M2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.22712171799441228</v>
+        <v>0.92669501386857589</v>
       </c>
       <c r="N2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.39875382855930841</v>
+        <v>4.1072367517818065E-2</v>
       </c>
       <c r="O2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.63822439144489274</v>
+        <v>0.39097151512844119</v>
       </c>
       <c r="P2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.99804943511162092</v>
+        <v>0.10103634661543637</v>
       </c>
       <c r="Q2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.80684620760580572</v>
+        <v>0.58652208754049207</v>
       </c>
       <c r="R2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.86939368161052</v>
+        <v>0.89944238924526099</v>
       </c>
       <c r="S2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.4031934812499598</v>
+        <v>0.55010313893927643</v>
       </c>
       <c r="T2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.92020275315827238</v>
+        <v>0.77905428209222782</v>
       </c>
       <c r="U2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.2963478197933892</v>
+        <v>2.1514924822608084E-2</v>
       </c>
       <c r="V2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.42771142867270973</v>
+        <v>0.49501734594943569</v>
       </c>
       <c r="W2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.25753363783364291</v>
+        <v>0.17774192807931799</v>
       </c>
       <c r="X2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.50400828660982977</v>
+        <v>0.14663009143723127</v>
       </c>
       <c r="Y2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.14199483609720931</v>
+        <v>0.29849531448034305</v>
       </c>
       <c r="Z2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.18076993817588571</v>
+        <v>0.53667491685710678</v>
       </c>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.3">
@@ -9614,7 +9611,7 @@
       <c r="M47" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="N47" s="90" t="s">
+      <c r="N47" s="84" t="s">
         <v>240</v>
       </c>
     </row>
@@ -10583,7 +10580,7 @@
       <c r="AE14" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="AF14" s="91" t="s">
+      <c r="AF14" t="s">
         <v>257</v>
       </c>
       <c r="AI14">
@@ -13374,7 +13371,7 @@
       <c r="AD72" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="AE72" s="91" t="s">
+      <c r="AE72" t="s">
         <v>265</v>
       </c>
     </row>
@@ -13795,7 +13792,7 @@
       <c r="BE6" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="BF6" s="91" t="s">
+      <c r="BF6" t="s">
         <v>287</v>
       </c>
       <c r="BG6" s="77" t="s">
@@ -18095,7 +18092,7 @@
       <c r="BE42" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="BF42" s="92" t="s">
+      <c r="BF42" s="6" t="s">
         <v>287</v>
       </c>
       <c r="BG42" s="4" t="s">
@@ -18118,7 +18115,7 @@
       <c r="BO42" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="BP42" s="91" t="s">
+      <c r="BP42" t="s">
         <v>265</v>
       </c>
     </row>
@@ -18143,7 +18140,7 @@
         <v>0</v>
       </c>
       <c r="AT43" s="7"/>
-      <c r="AU43" s="93">
+      <c r="AU43">
         <v>1</v>
       </c>
       <c r="AV43" s="8">
@@ -18223,7 +18220,7 @@
       <c r="AT44" s="7">
         <v>1</v>
       </c>
-      <c r="AU44" s="93">
+      <c r="AU44">
         <f t="shared" ref="AU44:BI44" si="10">SUM(AU8,AU14,AU20,AU26,AU32,AU38)</f>
         <v>-1.4910344327143772</v>
       </c>
@@ -23175,7 +23172,7 @@
       <c r="CF42" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="CG42" s="91" t="s">
+      <c r="CG42" t="s">
         <v>265</v>
       </c>
     </row>
@@ -23969,7 +23966,7 @@
       <c r="BN61" s="82" t="s">
         <v>313</v>
       </c>
-      <c r="BO61" s="91" t="s">
+      <c r="BO61" t="s">
         <v>314</v>
       </c>
       <c r="BS61" s="78"/>
@@ -24729,7 +24726,7 @@
       <c r="BN72" s="82" t="s">
         <v>313</v>
       </c>
-      <c r="BO72" s="91" t="s">
+      <c r="BO72" t="s">
         <v>314</v>
       </c>
       <c r="BS72" s="78"/>
@@ -25584,15 +25581,15 @@
         <v>190</v>
       </c>
       <c r="R2" s="13"/>
-      <c r="T2" s="89" t="s">
+      <c r="T2" s="95" t="s">
         <v>221</v>
       </c>
-      <c r="U2" s="89"/>
-      <c r="V2" s="89"/>
-      <c r="W2" s="89"/>
-      <c r="X2" s="89"/>
-      <c r="Y2" s="89"/>
-      <c r="Z2" s="89"/>
+      <c r="U2" s="95"/>
+      <c r="V2" s="95"/>
+      <c r="W2" s="95"/>
+      <c r="X2" s="95"/>
+      <c r="Y2" s="95"/>
+      <c r="Z2" s="95"/>
     </row>
     <row r="3" spans="2:31" x14ac:dyDescent="0.3">
       <c r="E3" t="s">
@@ -25619,13 +25616,13 @@
       <c r="Q3" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="T3" s="89"/>
-      <c r="U3" s="89"/>
-      <c r="V3" s="89"/>
-      <c r="W3" s="89"/>
-      <c r="X3" s="89"/>
-      <c r="Y3" s="89"/>
-      <c r="Z3" s="89"/>
+      <c r="T3" s="95"/>
+      <c r="U3" s="95"/>
+      <c r="V3" s="95"/>
+      <c r="W3" s="95"/>
+      <c r="X3" s="95"/>
+      <c r="Y3" s="95"/>
+      <c r="Z3" s="95"/>
     </row>
     <row r="4" spans="2:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="14"/>
@@ -25806,7 +25803,7 @@
       </c>
     </row>
     <row r="8" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="91" t="s">
         <v>192</v>
       </c>
       <c r="C8" t="s">
@@ -25852,7 +25849,7 @@
       </c>
     </row>
     <row r="9" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="B9" s="87"/>
+      <c r="B9" s="92"/>
       <c r="C9" t="s">
         <v>190</v>
       </c>
@@ -25904,7 +25901,7 @@
       </c>
     </row>
     <row r="10" spans="2:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="87"/>
+      <c r="B10" s="92"/>
       <c r="C10" s="14" t="s">
         <v>190</v>
       </c>
@@ -25982,7 +25979,7 @@
       </c>
     </row>
     <row r="11" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="91" t="s">
         <v>192</v>
       </c>
       <c r="C11" t="s">
@@ -26077,7 +26074,7 @@
       </c>
     </row>
     <row r="12" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="B12" s="87"/>
+      <c r="B12" s="92"/>
       <c r="C12" t="s">
         <v>91</v>
       </c>
@@ -26151,7 +26148,7 @@
       </c>
     </row>
     <row r="13" spans="2:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="87"/>
+      <c r="B13" s="92"/>
       <c r="C13" s="14" t="s">
         <v>91</v>
       </c>
@@ -26223,7 +26220,7 @@
       </c>
     </row>
     <row r="14" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="86" t="s">
+      <c r="B14" s="91" t="s">
         <v>192</v>
       </c>
       <c r="C14" t="s">
@@ -26298,7 +26295,7 @@
       </c>
     </row>
     <row r="15" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="B15" s="87"/>
+      <c r="B15" s="92"/>
       <c r="C15" t="s">
         <v>197</v>
       </c>
@@ -26386,7 +26383,7 @@
       </c>
     </row>
     <row r="16" spans="2:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="88"/>
+      <c r="B16" s="93"/>
       <c r="C16" s="14" t="s">
         <v>197</v>
       </c>
@@ -26628,10 +26625,10 @@
       <c r="G21" t="s">
         <v>75</v>
       </c>
-      <c r="M21" s="84" t="s">
+      <c r="M21" s="94" t="s">
         <v>199</v>
       </c>
-      <c r="N21" s="84"/>
+      <c r="N21" s="94"/>
       <c r="R21" s="3">
         <f>IF($Q$7&gt;$Q19,1,0)</f>
         <v>1</v>
@@ -26676,7 +26673,7 @@
       <c r="F22">
         <v>3</v>
       </c>
-      <c r="K22" s="87" t="s">
+      <c r="K22" s="92" t="s">
         <v>200</v>
       </c>
       <c r="M22" t="s">
@@ -26724,7 +26721,7 @@
       <c r="F23">
         <v>16</v>
       </c>
-      <c r="K23" s="87"/>
+      <c r="K23" s="92"/>
       <c r="L23" t="s">
         <v>202</v>
       </c>
@@ -26781,7 +26778,7 @@
       <c r="F24">
         <v>7</v>
       </c>
-      <c r="K24" s="87"/>
+      <c r="K24" s="92"/>
       <c r="L24" t="s">
         <v>203</v>
       </c>
@@ -26832,7 +26829,7 @@
       <c r="F25" t="s">
         <v>198</v>
       </c>
-      <c r="K25" s="87"/>
+      <c r="K25" s="92"/>
       <c r="R25" s="3">
         <f>IF($Q$7&gt;$Q23,1,0)</f>
         <v>1</v>
@@ -28901,25 +28898,25 @@
       </c>
     </row>
     <row r="93" spans="17:31" ht="21" x14ac:dyDescent="0.4">
-      <c r="AB93" s="99" t="s">
+      <c r="AB93" s="90" t="s">
         <v>220</v>
       </c>
-      <c r="AC93" s="94"/>
+      <c r="AC93" s="85"/>
     </row>
     <row r="94" spans="17:31" ht="21" x14ac:dyDescent="0.4">
-      <c r="AB94" s="95" t="s">
+      <c r="AB94" s="86" t="s">
         <v>219</v>
       </c>
-      <c r="AC94" s="96">
+      <c r="AC94" s="87">
         <f>AVERAGE(AE29,AE59,AE89)</f>
         <v>0.37962962962962959</v>
       </c>
     </row>
     <row r="95" spans="17:31" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="AB95" s="97" t="s">
+      <c r="AB95" s="88" t="s">
         <v>216</v>
       </c>
-      <c r="AC95" s="98">
+      <c r="AC95" s="89">
         <f>AVERAGE(AE22,AE52,AE82)</f>
         <v>0.33333333333333331</v>
       </c>
@@ -29114,30 +29111,30 @@
       <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="R2" s="84"/>
-      <c r="S2" s="84" t="s">
-        <v>2</v>
-      </c>
-      <c r="T2" s="84"/>
-      <c r="U2" s="84" t="s">
+      <c r="O2" s="94" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" s="94"/>
+      <c r="Q2" s="94" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="94"/>
+      <c r="S2" s="94" t="s">
+        <v>2</v>
+      </c>
+      <c r="T2" s="94"/>
+      <c r="U2" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="V2" s="84"/>
-      <c r="W2" s="84" t="s">
+      <c r="V2" s="94"/>
+      <c r="W2" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="X2" s="84"/>
-      <c r="Y2" s="84" t="s">
+      <c r="X2" s="94"/>
+      <c r="Y2" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="Z2" s="84"/>
+      <c r="Z2" s="94"/>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
@@ -29310,14 +29307,14 @@
       <c r="D6" s="1">
         <v>0.62184138330161254</v>
       </c>
-      <c r="O6" s="84" t="s">
+      <c r="O6" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="P6" s="84"/>
-      <c r="S6" s="84" t="s">
+      <c r="P6" s="94"/>
+      <c r="S6" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="T6" s="84"/>
+      <c r="T6" s="94"/>
     </row>
     <row r="7" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B7" t="s">

--- a/ai/manualisation.xlsx
+++ b/ai/manualisation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DiskE\SKRIPSI-CODE\skripsi-code\ai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF83F7DA-3170-450C-8D83-FECCCB20FC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF4B415-A896-4CA4-9350-3F9803BFC6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
+  <futureMetadata name="XLDAPR" count="2">
     <bk>
       <extLst>
         <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
@@ -56,10 +56,20 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <cellMetadata count="1">
+  <cellMetadata count="2">
     <bk>
       <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
     </bk>
   </cellMetadata>
 </metadata>
@@ -1086,7 +1096,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1148,6 +1158,14 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1514,7 +1532,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1637,6 +1655,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -1693,7 +1715,6 @@
               <a:rPr lang="en-ID"/>
               <a:t>ROC gembira</a:t>
             </a:r>
-            <a:endParaRPr/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -2073,7 +2094,6 @@
               <a:rPr lang="en-ID"/>
               <a:t>PR gembira</a:t>
             </a:r>
-            <a:endParaRPr/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -2453,7 +2473,6 @@
               <a:rPr lang="en-US"/>
               <a:t>ROC sedih</a:t>
             </a:r>
-            <a:endParaRPr/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -2833,7 +2852,6 @@
               <a:rPr lang="en-US"/>
               <a:t>PR sedih</a:t>
             </a:r>
-            <a:endParaRPr/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -3213,7 +3231,6 @@
               <a:rPr lang="en-US"/>
               <a:t>ROC tegang</a:t>
             </a:r>
-            <a:endParaRPr/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -3593,7 +3610,6 @@
               <a:rPr lang="en-US"/>
               <a:t>PR tegang</a:t>
             </a:r>
-            <a:endParaRPr/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -8793,99 +8809,99 @@
       </c>
       <c r="C2">
         <f ca="1">RAND()</f>
-        <v>0.76668469159746433</v>
+        <v>0.17128314214242568</v>
       </c>
       <c r="D2">
         <f t="shared" ref="D2:Z2" ca="1" si="0">RAND()</f>
-        <v>0.78217151846426736</v>
+        <v>0.21857157635191149</v>
       </c>
       <c r="E2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.61348325228630407</v>
+        <v>0.94804629569650312</v>
       </c>
       <c r="F2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.10988027125637501</v>
+        <v>0.46953326988813826</v>
       </c>
       <c r="G2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.98164100294553791</v>
+        <v>0.53598119810060396</v>
       </c>
       <c r="H2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.33699161420702672</v>
+        <v>0.16186833944361434</v>
       </c>
       <c r="I2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.47235621157106111</v>
+        <v>0.69730088454812611</v>
       </c>
       <c r="J2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.33204020547071567</v>
+        <v>0.31979896616546932</v>
       </c>
       <c r="K2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.43752457952342605</v>
+        <v>0.92860735895408975</v>
       </c>
       <c r="L2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.29175499098797253</v>
+        <v>0.67861996913231026</v>
       </c>
       <c r="M2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.35510578768996404</v>
+        <v>9.0023888281635767E-2</v>
       </c>
       <c r="N2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.63594790082513764</v>
+        <v>0.14448043785463116</v>
       </c>
       <c r="O2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.15031696977692444</v>
+        <v>0.17894560254217173</v>
       </c>
       <c r="P2">
         <f t="shared" ca="1" si="0"/>
-        <v>6.157200615529812E-2</v>
+        <v>0.16748130476973633</v>
       </c>
       <c r="Q2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.1710707031071762</v>
+        <v>0.1688396922692047</v>
       </c>
       <c r="R2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.61155472417605605</v>
+        <v>0.21986082977647692</v>
       </c>
       <c r="S2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.69446685405760966</v>
+        <v>0.84007424592234947</v>
       </c>
       <c r="T2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.87816184350667192</v>
+        <v>0.29159157184656448</v>
       </c>
       <c r="U2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.90796612726041026</v>
+        <v>0.77752464972350388</v>
       </c>
       <c r="V2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.51963373227785281</v>
+        <v>0.31248843975561735</v>
       </c>
       <c r="W2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.67364648301172347</v>
+        <v>0.95141203624893067</v>
       </c>
       <c r="X2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.27962097676779762</v>
+        <v>0.50094854836884484</v>
       </c>
       <c r="Y2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.94901713038535851</v>
+        <v>0.35070962059551514</v>
       </c>
       <c r="Z2">
         <f t="shared" ca="1" si="0"/>
-        <v>0.21664550513038694</v>
+        <v>0.58239213682425839</v>
       </c>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.25">
@@ -27635,6 +27651,7 @@
     <col min="13" max="13" width="15" customWidth="1"/>
     <col min="20" max="20" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="13.5703125" customWidth="1"/>
+    <col min="27" max="28" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="26.25" x14ac:dyDescent="0.4">
@@ -27761,11 +27778,11 @@
       </c>
       <c r="Q5" s="6"/>
       <c r="R5" s="7"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="6" t="s">
+      <c r="T5" s="90"/>
+      <c r="U5" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="V5" s="7" t="s">
+      <c r="V5" s="90" t="s">
         <v>42</v>
       </c>
       <c r="AA5" t="s">
@@ -27829,11 +27846,11 @@
       <c r="R6" s="10">
         <v>3</v>
       </c>
-      <c r="T6" s="9"/>
-      <c r="U6">
-        <v>1</v>
-      </c>
-      <c r="V6" s="10"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90">
+        <v>1</v>
+      </c>
+      <c r="V6" s="90"/>
       <c r="AA6">
         <v>1</v>
       </c>
@@ -27905,24 +27922,24 @@
       <c r="R7" s="10">
         <v>-0.77800000000000002</v>
       </c>
-      <c r="T7" s="9">
-        <v>1</v>
-      </c>
-      <c r="U7" s="1">
+      <c r="T7" s="90">
+        <v>1</v>
+      </c>
+      <c r="U7" s="91">
         <f>-1/3*((2/(1+DATA!$I$16))*N27/M21-((2*DATA!$I$16)/(1+DATA!$I$16))*(1-N27)*(1-M21))</f>
         <v>6.2694277333497389E-2</v>
       </c>
-      <c r="V7" s="10"/>
+      <c r="V7" s="90"/>
       <c r="Z7">
         <v>1</v>
       </c>
       <c r="AA7" s="17">
-        <f t="shared" ref="AA7:AA12" si="2">U60*IF(U60&gt;0,1,0)</f>
-        <v>0</v>
+        <f>U60*IF(I26&gt;0,1,0)</f>
+        <v>-9.7569668150918314E-3</v>
       </c>
       <c r="AB7" s="20">
-        <f t="shared" ref="AB7:AB12" si="3">V60*IF(V60&gt;0,1,0)</f>
-        <v>0</v>
+        <f>V60*IF(J26&gt;0,1,0)</f>
+        <v>-2.9387497635154727E-3</v>
       </c>
       <c r="AI7">
         <v>0</v>
@@ -27989,24 +28006,24 @@
       <c r="R8" s="10">
         <v>0.99099999999999999</v>
       </c>
-      <c r="T8" s="9">
-        <v>2</v>
-      </c>
-      <c r="U8" s="1">
+      <c r="T8" s="90">
+        <v>2</v>
+      </c>
+      <c r="U8" s="91">
         <f>-1/3*((2/(1+DATA!$I$17))*N28/M22-((2*DATA!$I$17)/(1+DATA!$I$17))*(1-N28)*(1-M22))</f>
         <v>-3.206419079779443</v>
       </c>
-      <c r="V8" s="10"/>
+      <c r="V8" s="90"/>
       <c r="Z8">
         <v>2</v>
       </c>
       <c r="AA8" s="17">
+        <f t="shared" ref="AA8:AB12" si="2">U61*IF(I27&gt;0,1,0)</f>
+        <v>-9.7569668150918314E-3</v>
+      </c>
+      <c r="AB8" s="20">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AB8" s="20">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-2.9387497635154727E-3</v>
       </c>
       <c r="AI8">
         <v>0</v>
@@ -28073,24 +28090,24 @@
       <c r="R9" s="10">
         <v>-0.121</v>
       </c>
-      <c r="T9" s="11">
+      <c r="T9" s="90">
         <v>3</v>
       </c>
-      <c r="U9" s="21">
+      <c r="U9" s="91">
         <f>-1/3*((2/(1+DATA!$I$18))*N29/M23-((2*DATA!$I$18)/(1+DATA!$I$18))*(1-N29)*(1-M23))</f>
         <v>-5.5450840530004015</v>
       </c>
-      <c r="V9" s="12"/>
+      <c r="V9" s="90"/>
       <c r="Z9">
         <v>3</v>
       </c>
       <c r="AA9" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9.7569668150918314E-3</v>
       </c>
       <c r="AB9" s="20">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>-0.4657008926345691</v>
       </c>
       <c r="AI9">
         <v>0</v>
@@ -28147,10 +28164,10 @@
       </c>
       <c r="AA10" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9.7569668150918314E-3</v>
       </c>
       <c r="AB10" s="20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AI10">
@@ -28193,8 +28210,8 @@
         <v>0.6006186867982517</v>
       </c>
       <c r="AB11" s="20">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>-2.9387497635154727E-3</v>
       </c>
       <c r="AI11">
         <v>0</v>
@@ -28231,23 +28248,23 @@
       <c r="I12" s="10">
         <v>1</v>
       </c>
-      <c r="T12" s="5" t="s">
+      <c r="T12" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="U12" s="6" t="s">
+      <c r="U12" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="V12" s="7"/>
+      <c r="V12" s="90"/>
       <c r="Z12">
         <v>6</v>
       </c>
       <c r="AA12" s="17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9.7569668150918314E-3</v>
       </c>
       <c r="AB12" s="20">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>-2.9387497635154727E-3</v>
       </c>
       <c r="AI12">
         <v>0</v>
@@ -28300,11 +28317,11 @@
       <c r="P13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="T13" s="9"/>
-      <c r="U13">
-        <v>1</v>
-      </c>
-      <c r="V13" s="10"/>
+      <c r="T13" s="90"/>
+      <c r="U13" s="90">
+        <v>1</v>
+      </c>
+      <c r="V13" s="90"/>
       <c r="AI13">
         <v>0</v>
       </c>
@@ -28350,14 +28367,14 @@
       <c r="P14" s="10">
         <v>1</v>
       </c>
-      <c r="T14" s="9">
-        <v>1</v>
-      </c>
-      <c r="U14">
+      <c r="T14" s="90">
+        <v>1</v>
+      </c>
+      <c r="U14" s="90">
         <f>-1/3*((2/(1+DATA!$I$16))*N27*(1-M21)-((2*DATA!$I$16)/(1+DATA!$I$16))*(1-N27)*M21)</f>
         <v>6.2712399078819221E-3</v>
       </c>
-      <c r="V14" s="10"/>
+      <c r="V14" s="90"/>
       <c r="Z14" s="5"/>
       <c r="AA14" s="16" t="s">
         <v>22</v>
@@ -28402,11 +28419,11 @@
         <v>2</v>
       </c>
       <c r="C15" s="17">
-        <f t="shared" ref="C15:D20" si="4">C4</f>
+        <f t="shared" ref="C15:D20" si="3">C4</f>
         <v>3.0296676785617889</v>
       </c>
       <c r="D15" s="20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.42618422704450198</v>
       </c>
       <c r="E15">
@@ -28431,14 +28448,14 @@
       <c r="P15" s="10">
         <v>0</v>
       </c>
-      <c r="T15" s="9">
-        <v>2</v>
-      </c>
-      <c r="U15">
+      <c r="T15" s="90">
+        <v>2</v>
+      </c>
+      <c r="U15" s="90">
         <f>-1/3*((2/(1+DATA!$I$17))*N28*(1-M22)-((2*DATA!$I$17)/(1+DATA!$I$17))*(1-N28)*M22)</f>
         <v>-0.35957997259247831</v>
       </c>
-      <c r="V15" s="10"/>
+      <c r="V15" s="90"/>
       <c r="Z15" s="9"/>
       <c r="AA15">
         <v>1</v>
@@ -28459,11 +28476,11 @@
         <v>3</v>
       </c>
       <c r="C16" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1757752467270279</v>
       </c>
       <c r="D16" s="20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E16">
@@ -28487,20 +28504,20 @@
       <c r="P16" s="10">
         <v>0</v>
       </c>
-      <c r="T16" s="11">
+      <c r="T16" s="90">
         <v>3</v>
       </c>
-      <c r="U16" s="13">
+      <c r="U16" s="90">
         <f>-1/3*((2/(1+DATA!$I$18))*N29*(1-M23)-((2*DATA!$I$18)/(1+DATA!$I$18))*(1-N29)*M23)</f>
         <v>-0.47549850662139692</v>
       </c>
-      <c r="V16" s="12"/>
+      <c r="V16" s="90"/>
       <c r="Z16" s="9">
         <v>1</v>
       </c>
       <c r="AA16" cm="1">
         <f t="array" ref="AA16">I7-M32*SUM($AA$7:$AB$12*AL5:AM10)</f>
-        <v>-0.23459630804204074</v>
+        <v>-0.22363669671570052</v>
       </c>
       <c r="AB16" s="10" cm="1">
         <f t="array" ref="AB16">J7-N32*SUM($AA$7:$AB$12*AM5:AN10)</f>
@@ -28511,7 +28528,7 @@
       </c>
       <c r="AE16" s="12">
         <f>I13-M32*SUM(AA7:AB12)</f>
-        <v>-6.0061868679825173E-2</v>
+        <v>-7.4377961034161558E-3</v>
       </c>
     </row>
     <row r="17" spans="2:47" x14ac:dyDescent="0.25">
@@ -28519,11 +28536,11 @@
         <v>4</v>
       </c>
       <c r="C17" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.3789276309323317</v>
       </c>
       <c r="D17" s="20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.83931599346975971</v>
       </c>
       <c r="E17">
@@ -28599,11 +28616,11 @@
         <v>5</v>
       </c>
       <c r="C18" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.50941318867619689</v>
       </c>
       <c r="D18" s="20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E18">
@@ -28662,16 +28679,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>6</v>
       </c>
       <c r="C19" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3.5198656803290969</v>
       </c>
       <c r="D19" s="20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E19">
@@ -28734,11 +28751,11 @@
         <v>7</v>
       </c>
       <c r="C20" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.0540707238032767</v>
       </c>
       <c r="D20" s="20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.2588938475691771</v>
       </c>
       <c r="E20">
@@ -28789,10 +28806,10 @@
       </c>
       <c r="AL20" s="5" cm="1">
         <f t="array" ref="AL20:AM25">AA7:AB12</f>
-        <v>0</v>
+        <v>-9.7569668150918314E-3</v>
       </c>
       <c r="AM20" s="7">
-        <v>0</v>
+        <v>-2.9387497635154727E-3</v>
       </c>
       <c r="AN20">
         <v>0</v>
@@ -28841,7 +28858,7 @@
         <v>1</v>
       </c>
       <c r="M21">
-        <f t="shared" ref="M21:M23" si="5">1/(1+EXP(-M15))</f>
+        <f t="shared" ref="M21:M23" si="4">1/(1+EXP(-M15))</f>
         <v>9.0932978664287886E-2</v>
       </c>
       <c r="N21" s="10" t="s">
@@ -28863,7 +28880,7 @@
         <v>-0.60906284121752341</v>
       </c>
       <c r="Z21" s="9"/>
-      <c r="AA21">
+      <c r="AA21" s="90">
         <v>1</v>
       </c>
       <c r="AB21" s="10">
@@ -28879,10 +28896,10 @@
         <v>0</v>
       </c>
       <c r="AL21" s="9">
-        <v>0</v>
+        <v>-9.7569668150918314E-3</v>
       </c>
       <c r="AM21" s="10">
-        <v>0</v>
+        <v>-2.9387497635154727E-3</v>
       </c>
       <c r="AN21">
         <v>0</v>
@@ -28919,7 +28936,7 @@
         <v>2</v>
       </c>
       <c r="M22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.12871006641053315</v>
       </c>
       <c r="N22" s="10" t="s">
@@ -28940,13 +28957,13 @@
       <c r="Z22" s="9">
         <v>1</v>
       </c>
-      <c r="AA22" s="17" cm="1">
-        <f t="array" ref="AA22">SUM(MMULT($AS$20:$AU$22,MMULT(AL19:AM21,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
-        <v>0</v>
-      </c>
-      <c r="AB22" s="14" cm="1">
-        <f t="array" ref="AB22">SUM(MMULT($AS$20:$AU$22,MMULT(AM19:AN21,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
-        <v>0</v>
+      <c r="AA22" s="92" cm="2">
+        <f t="array" ref="AA22">SUM(MMULT($AS$20:$AU$22,MMULT(AK19:AL21,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
+        <v>-5.6723424576570775E-3</v>
+      </c>
+      <c r="AB22" s="14" cm="2">
+        <f t="array" ref="AB22">SUM(MMULT($AS$20:$AU$22,MMULT(AL19:AM21,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
+        <v>1.5044230751469365E-2</v>
       </c>
       <c r="AI22">
         <v>0</v>
@@ -28958,10 +28975,10 @@
         <v>0</v>
       </c>
       <c r="AL22" s="9">
-        <v>0</v>
+        <v>-9.7569668150918314E-3</v>
       </c>
       <c r="AM22" s="10">
-        <v>0</v>
+        <v>-0.4657008926345691</v>
       </c>
       <c r="AN22">
         <v>0</v>
@@ -28982,12 +28999,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L23" s="11">
         <v>3</v>
       </c>
       <c r="M23" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>9.4723997009263594E-2</v>
       </c>
       <c r="N23" s="12" t="s">
@@ -29008,13 +29025,13 @@
       <c r="Z23" s="9">
         <v>2</v>
       </c>
-      <c r="AA23" s="17" cm="1">
-        <f t="array" ref="AA23">SUM(MMULT($AS$20:$AU$22,MMULT(AL20:AM22,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
-        <v>0</v>
-      </c>
-      <c r="AB23" s="14" cm="1">
-        <f t="array" ref="AB23">SUM(MMULT($AS$20:$AU$22,MMULT(AM20:AN22,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
-        <v>0</v>
+      <c r="AA23" s="92" cm="2">
+        <f t="array" ref="AA23">SUM(MMULT($AS$20:$AU$22,MMULT(AK20:AL22,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
+        <v>-1.0706937334244462E-2</v>
+      </c>
+      <c r="AB23" s="14" cm="2">
+        <f t="array" ref="AB23">SUM(MMULT($AS$20:$AU$22,MMULT(AL20:AM22,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
+        <v>0.12593630053925078</v>
       </c>
       <c r="AI23">
         <v>0</v>
@@ -29026,7 +29043,7 @@
         <v>0</v>
       </c>
       <c r="AL23" s="9">
-        <v>0</v>
+        <v>-9.7569668150918314E-3</v>
       </c>
       <c r="AM23" s="10">
         <v>0</v>
@@ -29041,7 +29058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I24" t="s">
         <v>28</v>
       </c>
@@ -29063,13 +29080,13 @@
       <c r="Z24" s="9">
         <v>3</v>
       </c>
-      <c r="AA24" s="17" cm="1">
-        <f t="array" ref="AA24">SUM(MMULT($AS$20:$AU$22,MMULT(AL21:AM23,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
-        <v>0</v>
-      </c>
-      <c r="AB24" s="14" cm="1">
-        <f t="array" ref="AB24">SUM(MMULT($AS$20:$AU$22,MMULT(AM21:AN23,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
-        <v>0</v>
+      <c r="AA24" s="92" cm="2">
+        <f t="array" ref="AA24">SUM(MMULT($AS$20:$AU$22,MMULT(AK21:AL23,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
+        <v>-1.0706937334244462E-2</v>
+      </c>
+      <c r="AB24" s="14" cm="2">
+        <f t="array" ref="AB24">SUM(MMULT($AS$20:$AU$22,MMULT(AL21:AM23,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
+        <v>-0.35073503375829551</v>
       </c>
       <c r="AI24">
         <v>0</v>
@@ -29084,7 +29101,7 @@
         <v>0.6006186867982517</v>
       </c>
       <c r="AM24" s="10">
-        <v>0</v>
+        <v>-2.9387497635154727E-3</v>
       </c>
       <c r="AN24">
         <v>0</v>
@@ -29096,7 +29113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I25">
         <v>1</v>
       </c>
@@ -29114,13 +29131,13 @@
       <c r="Z25" s="9">
         <v>4</v>
       </c>
-      <c r="AA25" s="17" cm="1">
-        <f t="array" ref="AA25">SUM(MMULT($AS$20:$AU$22,MMULT(AL22:AM24,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
-        <v>-0.44445782823070623</v>
-      </c>
-      <c r="AB25" s="14" cm="1">
-        <f t="array" ref="AB25">SUM(MMULT($AS$20:$AU$22,MMULT(AM22:AN24,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
-        <v>0</v>
+      <c r="AA25" s="92" cm="2">
+        <f t="array" ref="AA25">SUM(MMULT($AS$20:$AU$22,MMULT(AK22:AL24,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
+        <v>-0.14720933226401925</v>
+      </c>
+      <c r="AB25" s="14" cm="2">
+        <f t="array" ref="AB25">SUM(MMULT($AS$20:$AU$22,MMULT(AL22:AM24,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
+        <v>-0.66565185229321855</v>
       </c>
       <c r="AI25">
         <v>0</v>
@@ -29132,10 +29149,10 @@
         <v>0</v>
       </c>
       <c r="AL25" s="11">
-        <v>0</v>
+        <v>-9.7569668150918314E-3</v>
       </c>
       <c r="AM25" s="12">
-        <v>0</v>
+        <v>-2.9387497635154727E-3</v>
       </c>
       <c r="AN25">
         <v>0</v>
@@ -29152,7 +29169,7 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <f t="shared" ref="I26:J31" si="6">MAX(0,I17)</f>
+        <f t="shared" ref="I26:J31" si="5">MAX(0,I17)</f>
         <v>3.145200518730908</v>
       </c>
       <c r="J26">
@@ -29176,13 +29193,13 @@
       <c r="Z26" s="9">
         <v>5</v>
       </c>
-      <c r="AA26" s="17" cm="1">
-        <f t="array" ref="AA26">SUM(MMULT($AS$20:$AU$22,MMULT(AL23:AM25,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
-        <v>-0.58680445700189188</v>
-      </c>
-      <c r="AB26" s="14" cm="1">
-        <f t="array" ref="AB26">SUM(MMULT($AS$20:$AU$22,MMULT(AM23:AN25,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
-        <v>0</v>
+      <c r="AA26" s="92" cm="2">
+        <f t="array" ref="AA26">SUM(MMULT($AS$20:$AU$22,MMULT(AK23:AL25,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
+        <v>0.48064546382449713</v>
+      </c>
+      <c r="AB26" s="14" cm="2">
+        <f t="array" ref="AB26">SUM(MMULT($AS$20:$AU$22,MMULT(AL23:AM25,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
+        <v>-0.57237491515977335</v>
       </c>
       <c r="AI26">
         <v>0</v>
@@ -29209,16 +29226,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:47" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H27">
         <v>2</v>
       </c>
       <c r="I27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.2784623787054441</v>
       </c>
       <c r="J27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.34614547031331766</v>
       </c>
       <c r="L27" s="23" t="s">
@@ -29238,13 +29255,13 @@
       <c r="Z27" s="11">
         <v>6</v>
       </c>
-      <c r="AA27" s="18" cm="1">
-        <f t="array" ref="AA27">SUM(MMULT($AS$20:$AU$22,MMULT(AL24:AM26,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
-        <v>-0.5489654797336021</v>
-      </c>
-      <c r="AB27" s="15" cm="1">
-        <f t="array" ref="AB27">SUM(MMULT($AS$20:$AU$22,MMULT(AM24:AN26,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
-        <v>0</v>
+      <c r="AA27" s="18" cm="2">
+        <f t="array" ref="AA27">SUM(MMULT($AS$20:$AU$22,MMULT(AK24:AL26,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
+        <v>0.30206488410174892</v>
+      </c>
+      <c r="AB27" s="15" cm="2">
+        <f t="array" ref="AB27">SUM(MMULT($AS$20:$AU$22,MMULT(AL24:AM26,$AS$17:$AT$18))*$AA$16:$AB$18)</f>
+        <v>-0.54331501159286133</v>
       </c>
       <c r="AI27">
         <v>0</v>
@@ -29276,11 +29293,11 @@
         <v>3</v>
       </c>
       <c r="I28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.91402407230517557</v>
       </c>
       <c r="J28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.67564937474315656</v>
       </c>
       <c r="L28" s="9">
@@ -29297,7 +29314,7 @@
         <v>1</v>
       </c>
       <c r="U28" s="10">
-        <f t="shared" ref="U28:U30" si="7">P15-$M$32*$U14</f>
+        <f t="shared" ref="U28:U30" si="6">P15-$M$32*$U14</f>
         <v>-6.2712399078819221E-4</v>
       </c>
       <c r="AI28">
@@ -29330,11 +29347,11 @@
         <v>4</v>
       </c>
       <c r="I29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.1199332360563345</v>
       </c>
       <c r="J29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L29" s="9">
@@ -29351,7 +29368,7 @@
         <v>2</v>
       </c>
       <c r="U29" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3.595799725924783E-2</v>
       </c>
       <c r="AI29" t="s">
@@ -29363,11 +29380,11 @@
         <v>5</v>
       </c>
       <c r="I30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.5528430989792419</v>
       </c>
       <c r="J30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.13358922534569539</v>
       </c>
       <c r="L30" s="24" t="s">
@@ -29382,7 +29399,7 @@
         <v>3</v>
       </c>
       <c r="U30" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>4.7549850662139695E-2</v>
       </c>
     </row>
@@ -29391,11 +29408,11 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.68253504479941607</v>
       </c>
       <c r="J31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.20840954729318759</v>
       </c>
     </row>
@@ -29487,8 +29504,8 @@
       <c r="T35">
         <v>1</v>
       </c>
-      <c r="U35" s="17" cm="1">
-        <f t="array" ref="U35">SUM(MMULT(TRANSPOSE($U$14:$U$16),TRANSPOSE(P7:R7)))</f>
+      <c r="U35" s="17" cm="2">
+        <f t="array" ref="U35:U38">TRANSPOSE(MMULT(TRANSPOSE($U$14:$U$16),TRANSPOSE(P7:R10)))</f>
         <v>0.61037565361334356</v>
       </c>
       <c r="AA35">
@@ -29561,39 +29578,38 @@
       <c r="T36">
         <v>2</v>
       </c>
-      <c r="U36" s="17" cm="1">
-        <f t="array" ref="U36">SUM(MMULT(TRANSPOSE($U$14:$U$16),TRANSPOSE(P8:R8)))</f>
+      <c r="U36" s="17">
         <v>-0.46276214287105361</v>
       </c>
       <c r="Z36">
         <v>1</v>
       </c>
       <c r="AA36" s="17">
-        <f t="shared" ref="AA36:AA41" si="8">AA22</f>
-        <v>0</v>
+        <f t="shared" ref="AA36:AA41" si="7">AA22</f>
+        <v>-5.6723424576570775E-3</v>
       </c>
       <c r="AB36">
         <f>MATCH(MAX(FRONTEND!M28:Q28),FRONTEND!M28:Q28,0)</f>
         <v>4</v>
       </c>
       <c r="AC36">
-        <f t="shared" ref="AC36:AG41" si="9">IF($AB36=AC$35,$AA36,0)</f>
+        <f t="shared" ref="AC36:AG41" si="8">IF($AB36=AC$35,$AA36,0)</f>
         <v>0</v>
       </c>
       <c r="AD36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF36">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-5.6723424576570775E-3</v>
       </c>
       <c r="AG36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AI36">
@@ -29634,39 +29650,38 @@
       <c r="T37">
         <v>3</v>
       </c>
-      <c r="U37" s="20" cm="1">
-        <f t="array" ref="U37">SUM(MMULT(TRANSPOSE($U$14:$U$16),TRANSPOSE(P9:R9)))</f>
+      <c r="U37" s="20">
         <v>-5.8541800890550992E-2</v>
       </c>
       <c r="Z37">
         <v>2</v>
       </c>
       <c r="AA37" s="17">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>-1.0706937334244462E-2</v>
       </c>
       <c r="AB37">
         <f>MATCH(MAX(FRONTEND!M29:Q29),FRONTEND!M29:Q29,0)</f>
         <v>2</v>
       </c>
       <c r="AC37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD37">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-1.0706937334244462E-2</v>
       </c>
       <c r="AE37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AG37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AI37">
@@ -29708,39 +29723,38 @@
       <c r="T38">
         <v>4</v>
       </c>
-      <c r="U38" s="20" cm="1">
-        <f t="array" ref="U38">SUM(MMULT(TRANSPOSE($U$14:$U$16),TRANSPOSE(P10:R10)))</f>
+      <c r="U38" s="20">
         <v>-1.7632498581092837E-2</v>
       </c>
       <c r="Z38">
         <v>3</v>
       </c>
       <c r="AA38" s="17">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>-1.0706937334244462E-2</v>
       </c>
       <c r="AB38">
         <f>MATCH(MAX(FRONTEND!M30:Q30),FRONTEND!M30:Q30,0)</f>
         <v>3</v>
       </c>
       <c r="AC38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE38">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-1.0706937334244462E-2</v>
       </c>
       <c r="AF38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AG38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AI38">
@@ -29785,31 +29799,31 @@
         <v>4</v>
       </c>
       <c r="AA39" s="17">
-        <f t="shared" si="8"/>
-        <v>-0.44445782823070623</v>
+        <f t="shared" si="7"/>
+        <v>-0.14720933226401925</v>
       </c>
       <c r="AB39">
         <f>MATCH(MAX(FRONTEND!M31:Q31),FRONTEND!M31:Q31,0)</f>
         <v>4</v>
       </c>
       <c r="AC39">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD39">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE39">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF39">
-        <f t="shared" si="9"/>
-        <v>-0.44445782823070623</v>
+        <f t="shared" si="8"/>
+        <v>-0.14720933226401925</v>
       </c>
       <c r="AG39">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AI39">
@@ -29866,31 +29880,31 @@
         <v>5</v>
       </c>
       <c r="AA40" s="17">
-        <f t="shared" si="8"/>
-        <v>-0.58680445700189188</v>
+        <f t="shared" si="7"/>
+        <v>0.48064546382449713</v>
       </c>
       <c r="AB40">
         <f>MATCH(MAX(FRONTEND!M32:Q32),FRONTEND!M32:Q32,0)</f>
         <v>1</v>
       </c>
       <c r="AC40">
-        <f t="shared" si="9"/>
-        <v>-0.58680445700189188</v>
+        <f t="shared" si="8"/>
+        <v>0.48064546382449713</v>
       </c>
       <c r="AD40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AG40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AI40">
@@ -29950,32 +29964,32 @@
         <v>6</v>
       </c>
       <c r="AA41" s="17">
-        <f t="shared" si="8"/>
-        <v>-0.5489654797336021</v>
+        <f t="shared" si="7"/>
+        <v>0.30206488410174892</v>
       </c>
       <c r="AB41">
         <f>MATCH(MAX(FRONTEND!M33:Q33),FRONTEND!M33:Q33,0)</f>
         <v>5</v>
       </c>
       <c r="AC41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AG41">
-        <f t="shared" si="9"/>
-        <v>-0.5489654797336021</v>
+        <f t="shared" si="8"/>
+        <v>0.30206488410174892</v>
       </c>
       <c r="AI41">
         <v>0</v>
@@ -30027,7 +30041,7 @@
         <v>1</v>
       </c>
       <c r="T42">
-        <f t="shared" ref="T42:T43" si="10">U35</f>
+        <f t="shared" ref="T42:T43" si="9">U35</f>
         <v>0.61037565361334356</v>
       </c>
       <c r="U42">
@@ -30038,11 +30052,11 @@
         <v>1</v>
       </c>
       <c r="W42">
-        <f t="shared" ref="W42:W47" si="11">IF(V42=$U$42,$T$42,0)</f>
+        <f t="shared" ref="W42:W47" si="10">IF(V42=$U$42,$T$42,0)</f>
         <v>0</v>
       </c>
       <c r="X42">
-        <f t="shared" ref="X42:X47" si="12">IF(V42=$U$43,$T$43,0)</f>
+        <f t="shared" ref="X42:X47" si="11">IF(V42=$U$43,$T$43,0)</f>
         <v>0</v>
       </c>
       <c r="AI42">
@@ -30084,7 +30098,7 @@
         <v>2</v>
       </c>
       <c r="T43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>-0.46276214287105361</v>
       </c>
       <c r="U43">
@@ -30095,11 +30109,11 @@
         <v>2</v>
       </c>
       <c r="W43">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X43">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="X43">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AA43" t="s">
@@ -30147,11 +30161,11 @@
         <v>3</v>
       </c>
       <c r="W44">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X44">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="X44">
-        <f t="shared" si="12"/>
         <v>-0.46276214287105361</v>
       </c>
       <c r="AA44">
@@ -30215,34 +30229,34 @@
         <v>4</v>
       </c>
       <c r="W45">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X45">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X45">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
       <c r="Z45">
         <v>1</v>
       </c>
       <c r="AA45">
-        <f t="shared" ref="AA45:AE50" si="13">AC36*IF(AC36&gt;0,1,0)</f>
+        <f>AC36*IF(FRONTEND!M19&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AB45">
-        <f t="shared" si="13"/>
+        <f>AD36*IF(FRONTEND!N19&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AC45">
-        <f t="shared" si="13"/>
+        <f>AE36*IF(FRONTEND!O19&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AD45">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f>AF36*IF(FRONTEND!P19&gt;0,1,0)</f>
+        <v>-5.6723424576570775E-3</v>
       </c>
       <c r="AE45">
-        <f t="shared" si="13"/>
+        <f>AG36*IF(FRONTEND!Q19&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AI45">
@@ -30289,34 +30303,34 @@
         <v>5</v>
       </c>
       <c r="W46">
+        <f t="shared" si="10"/>
+        <v>0.61037565361334356</v>
+      </c>
+      <c r="X46">
         <f t="shared" si="11"/>
-        <v>0.61037565361334356</v>
-      </c>
-      <c r="X46">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Z46">
         <v>2</v>
       </c>
       <c r="AA46">
-        <f t="shared" si="13"/>
+        <f>AC37*IF(FRONTEND!M20&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AB46">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f>AD37*IF(FRONTEND!N20&gt;0,1,0)</f>
+        <v>-1.0706937334244462E-2</v>
       </c>
       <c r="AC46">
-        <f t="shared" si="13"/>
+        <f>AE37*IF(FRONTEND!O20&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AD46">
-        <f t="shared" si="13"/>
+        <f>AF37*IF(FRONTEND!P20&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AE46">
-        <f t="shared" si="13"/>
+        <f>AG37*IF(FRONTEND!Q20&gt;0,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -30333,34 +30347,34 @@
         <v>6</v>
       </c>
       <c r="W47">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X47">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="X47">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Z47">
         <v>3</v>
       </c>
       <c r="AA47">
-        <f t="shared" si="13"/>
+        <f>AC38*IF(FRONTEND!M21&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AB47">
-        <f t="shared" si="13"/>
+        <f>AD38*IF(FRONTEND!N21&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AC47">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f>AE38*IF(FRONTEND!O21&gt;0,1,0)</f>
+        <v>-1.0706937334244462E-2</v>
       </c>
       <c r="AD47">
-        <f t="shared" si="13"/>
+        <f>AF38*IF(FRONTEND!P21&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AE47">
-        <f t="shared" si="13"/>
+        <f>AG38*IF(FRONTEND!Q21&gt;0,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -30376,23 +30390,23 @@
         <v>4</v>
       </c>
       <c r="AA48">
-        <f t="shared" si="13"/>
+        <f>AC39*IF(FRONTEND!M22&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AB48">
-        <f t="shared" si="13"/>
+        <f>AD39*IF(FRONTEND!N22&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AC48">
-        <f t="shared" si="13"/>
+        <f>AE39*IF(FRONTEND!O22&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AD48">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f>AF39*IF(FRONTEND!P22&gt;0,1,0)</f>
+        <v>-0.14720933226401925</v>
       </c>
       <c r="AE48">
-        <f t="shared" si="13"/>
+        <f>AG39*IF(FRONTEND!Q22&gt;0,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -30418,23 +30432,23 @@
         <v>5</v>
       </c>
       <c r="AA49">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f>AC40*IF(FRONTEND!M23&gt;0,1,0)</f>
+        <v>0.48064546382449713</v>
       </c>
       <c r="AB49">
-        <f t="shared" si="13"/>
+        <f>AD40*IF(FRONTEND!N23&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AC49">
-        <f t="shared" si="13"/>
+        <f>AE40*IF(FRONTEND!O23&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AD49">
-        <f t="shared" si="13"/>
+        <f>AF40*IF(FRONTEND!P23&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AE49">
-        <f t="shared" si="13"/>
+        <f>AG40*IF(FRONTEND!Q23&gt;0,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -30459,24 +30473,24 @@
         <v>6</v>
       </c>
       <c r="AA50">
-        <f t="shared" si="13"/>
+        <f>AC41*IF(FRONTEND!M24&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AB50">
-        <f t="shared" si="13"/>
+        <f>AD41*IF(FRONTEND!N24&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AC50">
-        <f t="shared" si="13"/>
+        <f>AE41*IF(FRONTEND!O24&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AD50">
-        <f t="shared" si="13"/>
+        <f>AF41*IF(FRONTEND!P24&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AE50">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f>AG41*IF(FRONTEND!Q24&gt;0,1,0)</f>
+        <v>0.30206488410174892</v>
       </c>
     </row>
     <row r="51" spans="8:37" x14ac:dyDescent="0.25">
@@ -30484,11 +30498,11 @@
         <v>1</v>
       </c>
       <c r="T51">
-        <f t="shared" ref="T51:T56" si="14">$U$37/$V$50</f>
+        <f t="shared" ref="T51:T56" si="12">$U$37/$V$50</f>
         <v>-9.7569668150918314E-3</v>
       </c>
       <c r="U51">
-        <f t="shared" ref="U51:U56" si="15">$U$38/$V$50</f>
+        <f t="shared" ref="U51:U56" si="13">$U$38/$V$50</f>
         <v>-2.9387497635154727E-3</v>
       </c>
     </row>
@@ -30497,11 +30511,11 @@
         <v>2</v>
       </c>
       <c r="T52">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>-9.7569668150918314E-3</v>
       </c>
       <c r="U52">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-2.9387497635154727E-3</v>
       </c>
       <c r="Z52" s="5"/>
@@ -30525,11 +30539,11 @@
         <v>3</v>
       </c>
       <c r="T53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>-9.7569668150918314E-3</v>
       </c>
       <c r="U53">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-2.9387497635154727E-3</v>
       </c>
       <c r="Z53" s="9"/>
@@ -30552,11 +30566,11 @@
         <v>4</v>
       </c>
       <c r="T54">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>-9.7569668150918314E-3</v>
       </c>
       <c r="U54">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-2.9387497635154727E-3</v>
       </c>
       <c r="Z54" s="9">
@@ -30564,22 +30578,22 @@
       </c>
       <c r="AA54" cm="1">
         <f t="array" ref="AA54">FRONTEND!$M7-$M$32*SUM($AA$45:$AE$50*AK35:AO40)</f>
-        <v>-0.51200000000000001</v>
+        <v>-0.49670249138865791</v>
       </c>
       <c r="AB54" cm="1">
         <f t="array" ref="AB54">FRONTEND!$N7-$M$32*SUM($AA$45:$AE$50*AL35:AP40)</f>
-        <v>0.89700000000000002</v>
+        <v>0.83064812031618562</v>
       </c>
       <c r="AC54" s="10" cm="1">
         <f t="array" ref="AC54">FRONTEND!$O7-$M$32*SUM($AA$45:$AE$50*AM35:AQ40)</f>
-        <v>-0.52300000000000002</v>
+        <v>-0.59589290508104831</v>
       </c>
       <c r="AE54" s="11">
         <v>1</v>
       </c>
       <c r="AF54" s="12">
         <f>FRONTEND!$W$7-$M$32*SUM(AA22:AA27)</f>
-        <v>0.15802277649662003</v>
+        <v>-6.0841479853608084E-2</v>
       </c>
     </row>
     <row r="55" spans="8:37" x14ac:dyDescent="0.25">
@@ -30587,11 +30601,11 @@
         <v>5</v>
       </c>
       <c r="T55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>-9.7569668150918314E-3</v>
       </c>
       <c r="U55">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-2.9387497635154727E-3</v>
       </c>
       <c r="Z55" s="9">
@@ -30599,15 +30613,15 @@
       </c>
       <c r="AA55" cm="1">
         <f t="array" ref="AA55">FRONTEND!$M8-$M$32*SUM($AA$45:$AE$50*AK36:AO41)</f>
-        <v>0.122</v>
+        <v>9.4973928134451879E-2</v>
       </c>
       <c r="AB55" cm="1">
         <f t="array" ref="AB55">FRONTEND!$N8-$M$32*SUM($AA$45:$AE$50*AL36:AP41)</f>
-        <v>-0.20399999999999999</v>
+        <v>-0.17515222614268941</v>
       </c>
       <c r="AC55" s="10" cm="1">
         <f t="array" ref="AC55">FRONTEND!$O8-$M$32*SUM($AA$45:$AE$50*AM36:AQ41)</f>
-        <v>-0.74</v>
+        <v>-0.69911327024477576</v>
       </c>
     </row>
     <row r="56" spans="8:37" x14ac:dyDescent="0.25">
@@ -30615,11 +30629,11 @@
         <v>6</v>
       </c>
       <c r="T56">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>-9.7569668150918314E-3</v>
       </c>
       <c r="U56">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>-2.9387497635154727E-3</v>
       </c>
       <c r="Z56" s="9">
@@ -30627,15 +30641,15 @@
       </c>
       <c r="AA56" cm="1">
         <f t="array" ref="AA56">FRONTEND!$M9-$M$32*SUM($AA$45:$AE$50*AK37:AO42)</f>
-        <v>0.74199999999999999</v>
+        <v>0.71731237737309095</v>
       </c>
       <c r="AB56" cm="1">
         <f t="array" ref="AB56">FRONTEND!$N9-$M$32*SUM($AA$45:$AE$50*AL37:AP42)</f>
-        <v>0.80500000000000005</v>
+        <v>0.73525101812326721</v>
       </c>
       <c r="AC56" s="10" cm="1">
         <f t="array" ref="AC56">FRONTEND!$O9-$M$32*SUM($AA$45:$AE$50*AM37:AQ42)</f>
-        <v>-0.97699999999999998</v>
+        <v>-0.89052325774494723</v>
       </c>
     </row>
     <row r="57" spans="8:37" x14ac:dyDescent="0.25">
@@ -30645,15 +30659,15 @@
       </c>
       <c r="AA57" cm="1">
         <f t="array" ref="AA57">FRONTEND!$M10-$M$32*SUM($AA$45:$AE$50*AK38:AO43)</f>
-        <v>0.78200000000000003</v>
+        <v>0.77567086765024917</v>
       </c>
       <c r="AB57" cm="1">
         <f t="array" ref="AB57">FRONTEND!$N10-$M$32*SUM($AA$45:$AE$50*AL38:AP43)</f>
-        <v>0.51600000000000001</v>
+        <v>0.55354828343699902</v>
       </c>
       <c r="AC57" s="10" cm="1">
         <f t="array" ref="AC57">FRONTEND!$O10-$M$32*SUM($AA$45:$AE$50*AM38:AQ43)</f>
-        <v>-0.91400000000000003</v>
+        <v>-0.9014336887683686</v>
       </c>
     </row>
     <row r="58" spans="8:37" x14ac:dyDescent="0.25">
@@ -30670,15 +30684,15 @@
       </c>
       <c r="AA58" s="13" cm="1">
         <f t="array" ref="AA58">FRONTEND!$M11-$M$32*SUM($AA$45:$AE$50*AK39:AO44)</f>
-        <v>0.40899999999999997</v>
+        <v>0.42499272877615157</v>
       </c>
       <c r="AB58" s="13" cm="1">
         <f t="array" ref="AB58">FRONTEND!$N11-$M$32*SUM($AA$45:$AE$50*AL39:AP44)</f>
-        <v>-0.438</v>
+        <v>-0.43254176853939241</v>
       </c>
       <c r="AC58" s="12" cm="1">
         <f t="array" ref="AC58">FRONTEND!$O11-$M$32*SUM($AA$45:$AE$50*AM39:AQ44)</f>
-        <v>0.29299999999999998</v>
+        <v>0.30459114759224992</v>
       </c>
     </row>
     <row r="59" spans="8:37" x14ac:dyDescent="0.25">
@@ -30695,7 +30709,7 @@
         <v>1</v>
       </c>
       <c r="U60" s="17">
-        <f t="shared" ref="U60:V65" si="16">W42+T51</f>
+        <f t="shared" ref="U60:V65" si="14">W42+T51</f>
         <v>-9.7569668150918314E-3</v>
       </c>
       <c r="V60" s="14">
@@ -30708,11 +30722,11 @@
         <v>2</v>
       </c>
       <c r="U61" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-9.7569668150918314E-3</v>
       </c>
       <c r="V61" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-2.9387497635154727E-3</v>
       </c>
       <c r="AA61" s="4" t="s">
@@ -30724,11 +30738,11 @@
         <v>3</v>
       </c>
       <c r="U62" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-9.7569668150918314E-3</v>
       </c>
       <c r="V62" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-0.4657008926345691</v>
       </c>
       <c r="AA62" s="4" t="s">
@@ -30749,11 +30763,11 @@
         <v>4</v>
       </c>
       <c r="U63" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-9.7569668150918314E-3</v>
       </c>
       <c r="V63" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-2.9387497635154727E-3</v>
       </c>
       <c r="AA63" t="s">
@@ -30778,11 +30792,11 @@
         <v>5</v>
       </c>
       <c r="U64" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.6006186867982517</v>
       </c>
       <c r="V64" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-2.9387497635154727E-3</v>
       </c>
       <c r="AA64">
@@ -30803,19 +30817,19 @@
         <v>6</v>
       </c>
       <c r="U65" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-9.7569668150918314E-3</v>
       </c>
       <c r="V65" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>-2.9387497635154727E-3</v>
       </c>
       <c r="Z65">
         <v>1</v>
       </c>
       <c r="AA65" s="20">
-        <f t="shared" ref="AA65:AA70" si="17">AB22*IF(AB22&gt;0,1,0)</f>
-        <v>0</v>
+        <f>AB22*IF(FRONTEND!T13&gt;0,1,0)</f>
+        <v>1.5044230751469365E-2</v>
       </c>
       <c r="AI65">
         <v>0</v>
@@ -30832,7 +30846,7 @@
         <v>2</v>
       </c>
       <c r="AA66" s="20">
-        <f t="shared" si="17"/>
+        <f>AB23*IF(FRONTEND!T14&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AI66">
@@ -30850,8 +30864,8 @@
         <v>3</v>
       </c>
       <c r="AA67" s="20">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>AB24*IF(FRONTEND!T15&gt;0,1,0)</f>
+        <v>-0.35073503375829551</v>
       </c>
       <c r="AI67">
         <v>0</v>
@@ -30868,7 +30882,7 @@
         <v>4</v>
       </c>
       <c r="AA68" s="20">
-        <f t="shared" si="17"/>
+        <f>AB25*IF(FRONTEND!T16&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AI68">
@@ -30886,7 +30900,7 @@
         <v>5</v>
       </c>
       <c r="AA69" s="20">
-        <f t="shared" si="17"/>
+        <f>AB26*IF(FRONTEND!T17&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="AI69">
@@ -30904,8 +30918,8 @@
         <v>6</v>
       </c>
       <c r="AA70" s="20">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>AB27*IF(FRONTEND!T18&gt;0,1,0)</f>
+        <v>-0.54331501159286133</v>
       </c>
     </row>
     <row r="72" spans="20:37" x14ac:dyDescent="0.25">
@@ -30940,14 +30954,14 @@
       </c>
       <c r="AA74" s="10" cm="1">
         <f t="array" ref="AA74">FRONTEND!T7-$M32*SUM($AA$65:$AA$70*AJ62:AJ67)</f>
-        <v>0.122</v>
+        <v>0.12293616727776464</v>
       </c>
       <c r="AC74" s="11">
         <v>1</v>
       </c>
       <c r="AD74" s="12">
         <f>FRONTEND!$W$7-$M$32*SUM(AB22:AB27)</f>
-        <v>0</v>
+        <v>0.19910962815134287</v>
       </c>
     </row>
     <row r="75" spans="20:37" x14ac:dyDescent="0.25">
@@ -31133,11 +31147,11 @@
       </c>
       <c r="AA5" s="6"/>
       <c r="AB5" s="7"/>
-      <c r="AD5" s="5"/>
-      <c r="AE5" s="6" t="s">
+      <c r="AD5" s="90"/>
+      <c r="AE5" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="AF5" s="7" t="s">
+      <c r="AF5" s="90" t="s">
         <v>42</v>
       </c>
       <c r="AK5" s="29" t="s">
@@ -31267,11 +31281,11 @@
       <c r="AB6" s="10">
         <v>3</v>
       </c>
-      <c r="AD6" s="9"/>
-      <c r="AE6">
-        <v>1</v>
-      </c>
-      <c r="AF6" s="10"/>
+      <c r="AD6" s="90"/>
+      <c r="AE6" s="90">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="90"/>
       <c r="AJ6" t="s">
         <v>104</v>
       </c>
@@ -31446,14 +31460,14 @@
       <c r="AB7" s="36">
         <v>-0.77800000000000002</v>
       </c>
-      <c r="AD7" s="9">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="1">
+      <c r="AD7" s="90">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="91">
         <f>-1/3*((2/(1+DATA!$I$16))*X27/W21-((2*DATA!$I$16)/(1+DATA!$I$16))*(1-X27)*(1-W21))</f>
         <v>4.6452078812472958E-2</v>
       </c>
-      <c r="AF7" s="10"/>
+      <c r="AF7" s="90"/>
       <c r="AK7" s="30">
         <v>1</v>
       </c>
@@ -31625,14 +31639,14 @@
       <c r="AB8" s="36">
         <v>0.99099999999999999</v>
       </c>
-      <c r="AD8" s="9">
-        <v>2</v>
-      </c>
-      <c r="AE8" s="1">
+      <c r="AD8" s="90">
+        <v>2</v>
+      </c>
+      <c r="AE8" s="91">
         <f>-1/3*((2/(1+DATA!$I$17))*X28/W22-((2*DATA!$I$17)/(1+DATA!$I$17))*(1-X28)*(1-W22))</f>
         <v>-0.86473208596570328</v>
       </c>
-      <c r="AF8" s="10"/>
+      <c r="AF8" s="90"/>
       <c r="AJ8">
         <v>1</v>
       </c>
@@ -31817,14 +31831,14 @@
       <c r="AB9" s="36">
         <v>-0.121</v>
       </c>
-      <c r="AD9" s="11">
+      <c r="AD9" s="90">
         <v>3</v>
       </c>
-      <c r="AE9" s="21">
+      <c r="AE9" s="91">
         <f>-1/3*((2/(1+DATA!$I$18))*X29/W23-((2*DATA!$I$18)/(1+DATA!$I$18))*(1-X29)*(1-W23))</f>
         <v>-0.64121795401824033</v>
       </c>
-      <c r="AF9" s="12"/>
+      <c r="AF9" s="90"/>
       <c r="AJ9">
         <v>2</v>
       </c>
@@ -31995,6 +32009,9 @@
       <c r="AB10" s="40">
         <v>0.186</v>
       </c>
+      <c r="AD10" s="90"/>
+      <c r="AE10" s="90"/>
+      <c r="AF10" s="90"/>
       <c r="AK10" s="30"/>
       <c r="AL10" s="30"/>
       <c r="AN10" s="31"/>
@@ -32091,6 +32108,9 @@
       <c r="T11" s="7" t="s">
         <v>132</v>
       </c>
+      <c r="AD11" s="90"/>
+      <c r="AE11" s="90"/>
+      <c r="AF11" s="90"/>
       <c r="AK11" s="41" t="s">
         <v>133</v>
       </c>
@@ -32199,13 +32219,13 @@
       <c r="T12" s="10">
         <v>1</v>
       </c>
-      <c r="AD12" s="5" t="s">
+      <c r="AD12" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="AE12" s="6" t="s">
+      <c r="AE12" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="AF12" s="7"/>
+      <c r="AF12" s="90"/>
       <c r="AJ12" t="s">
         <v>104</v>
       </c>
@@ -32352,11 +32372,11 @@
       <c r="Z13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="AD13" s="9"/>
-      <c r="AE13">
-        <v>1</v>
-      </c>
-      <c r="AF13" s="10"/>
+      <c r="AD13" s="90"/>
+      <c r="AE13" s="90">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="90"/>
       <c r="AK13" s="30">
         <v>1</v>
       </c>
@@ -32522,14 +32542,14 @@
       <c r="Z14" s="10">
         <v>1</v>
       </c>
-      <c r="AD14" s="9">
-        <v>1</v>
-      </c>
-      <c r="AE14">
+      <c r="AD14" s="90">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="90">
         <f>-1/3*((2/(1+DATA!$I$16))*X27*(1-W21)-((2*DATA!$I$16)/(1+DATA!$I$16))*(1-X27)*W21)</f>
         <v>2.2513438428906352E-2</v>
       </c>
-      <c r="AF14" s="10"/>
+      <c r="AF14" s="90"/>
       <c r="AJ14">
         <v>1</v>
       </c>
@@ -32705,14 +32725,14 @@
       <c r="Z15" s="10">
         <v>0</v>
       </c>
-      <c r="AD15" s="9">
-        <v>2</v>
-      </c>
-      <c r="AE15">
+      <c r="AD15" s="90">
+        <v>2</v>
+      </c>
+      <c r="AE15" s="90">
         <f>-1/3*((2/(1+DATA!$I$17))*X28*(1-W22)-((2*DATA!$I$17)/(1+DATA!$I$17))*(1-X28)*W22)</f>
         <v>-0.21573569718452978</v>
       </c>
-      <c r="AF15" s="10"/>
+      <c r="AF15" s="90"/>
       <c r="AJ15">
         <v>2</v>
       </c>
@@ -32791,23 +32811,23 @@
         <v>1</v>
       </c>
       <c r="BL15">
-        <f t="shared" ref="BL15:BP20" si="2">BN6*IF(BN6&gt;0,1,0)</f>
+        <f>BN6*IF(FRONTEND!M19&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BM15">
-        <f t="shared" si="2"/>
+        <f>BO6*IF(FRONTEND!N19&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BN15">
-        <f t="shared" si="2"/>
+        <f>BP6*IF(FRONTEND!O19&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BO15">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>BQ6*IF(FRONTEND!P19&gt;0,1,0)</f>
+        <v>-1.8577071789366842E-3</v>
       </c>
       <c r="BP15">
-        <f t="shared" si="2"/>
+        <f>BR6*IF(FRONTEND!Q19&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BT15">
@@ -32871,14 +32891,14 @@
       <c r="Z16" s="10">
         <v>0</v>
       </c>
-      <c r="AD16" s="11">
+      <c r="AD16" s="90">
         <v>3</v>
       </c>
-      <c r="AE16" s="13">
+      <c r="AE16" s="90">
         <f>-1/3*((2/(1+DATA!$I$18))*X29*(1-W23)-((2*DATA!$I$18)/(1+DATA!$I$18))*(1-X29)*W23)</f>
         <v>-9.49928708631433E-2</v>
       </c>
-      <c r="AF16" s="12"/>
+      <c r="AF16" s="90"/>
       <c r="AK16" s="30"/>
       <c r="AL16" s="30"/>
       <c r="AN16" s="31"/>
@@ -32900,23 +32920,23 @@
         <v>2</v>
       </c>
       <c r="BL16">
-        <f t="shared" si="2"/>
+        <f>BN7*IF(FRONTEND!M20&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BM16">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>BO7*IF(FRONTEND!N20&gt;0,1,0)</f>
+        <v>-6.5509705314289266E-3</v>
       </c>
       <c r="BN16">
-        <f t="shared" si="2"/>
+        <f>BP7*IF(FRONTEND!O20&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BO16">
-        <f t="shared" si="2"/>
+        <f>BQ7*IF(FRONTEND!P20&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BP16">
-        <f t="shared" si="2"/>
+        <f>BR7*IF(FRONTEND!Q20&gt;0,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -32977,23 +32997,23 @@
         <v>3</v>
       </c>
       <c r="BL17">
-        <f t="shared" si="2"/>
+        <f>BN8*IF(FRONTEND!M21&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BM17">
-        <f t="shared" si="2"/>
+        <f>BO8*IF(FRONTEND!N21&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BN17">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>BP8*IF(FRONTEND!O21&gt;0,1,0)</f>
+        <v>-2.2195939504033459E-2</v>
       </c>
       <c r="BO17">
-        <f t="shared" si="2"/>
+        <f>BQ8*IF(FRONTEND!P21&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BP17">
-        <f t="shared" si="2"/>
+        <f>BR8*IF(FRONTEND!Q21&gt;0,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -33085,23 +33105,23 @@
         <v>4</v>
       </c>
       <c r="BL18">
-        <f t="shared" si="2"/>
+        <f>BN9*IF(FRONTEND!M22&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BM18">
-        <f t="shared" si="2"/>
+        <f>BO9*IF(FRONTEND!N22&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BN18">
-        <f t="shared" si="2"/>
+        <f>BP9*IF(FRONTEND!O22&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BO18">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>BQ9*IF(FRONTEND!P22&gt;0,1,0)</f>
+        <v>-2.6156517285840071E-2</v>
       </c>
       <c r="BP18">
-        <f t="shared" si="2"/>
+        <f>BR9*IF(FRONTEND!Q22&gt;0,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -33221,23 +33241,23 @@
         <v>5</v>
       </c>
       <c r="BL19">
-        <f t="shared" si="2"/>
+        <f>BN10*IF(FRONTEND!M23&gt;0,1,0)</f>
         <v>7.4494743577237601E-4</v>
       </c>
       <c r="BM19">
-        <f t="shared" si="2"/>
+        <f>BO10*IF(FRONTEND!N23&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BN19">
-        <f t="shared" si="2"/>
+        <f>BP10*IF(FRONTEND!O23&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BO19">
-        <f t="shared" si="2"/>
+        <f>BQ10*IF(FRONTEND!P23&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BP19">
-        <f t="shared" si="2"/>
+        <f>BR10*IF(FRONTEND!Q23&gt;0,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -33352,24 +33372,24 @@
         <v>6</v>
       </c>
       <c r="BL20">
-        <f t="shared" si="2"/>
+        <f>BN11*IF(FRONTEND!M24&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BM20">
-        <f t="shared" si="2"/>
+        <f>BO11*IF(FRONTEND!N24&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BN20">
-        <f t="shared" si="2"/>
+        <f>BP11*IF(FRONTEND!O24&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BO20">
-        <f t="shared" si="2"/>
+        <f>BQ11*IF(FRONTEND!P24&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BP20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>BR11*IF(FRONTEND!Q24&gt;0,1,0)</f>
+        <v>-4.4724543820275189E-4</v>
       </c>
     </row>
     <row r="21" spans="3:74" x14ac:dyDescent="0.25">
@@ -33391,7 +33411,7 @@
         <v>1</v>
       </c>
       <c r="W21">
-        <f t="shared" ref="W21:W23" si="3">1/(1+EXP(-W15))</f>
+        <f t="shared" ref="W21:W23" si="2">1/(1+EXP(-W15))</f>
         <v>0.32644485721914213</v>
       </c>
       <c r="X21" s="10" t="s">
@@ -33510,7 +33530,7 @@
         <v>2</v>
       </c>
       <c r="W22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.47725581066825473</v>
       </c>
       <c r="X22" s="10" t="s">
@@ -33590,7 +33610,7 @@
         <v>3</v>
       </c>
       <c r="W23" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.81914818816440027</v>
       </c>
       <c r="X23" s="12" t="s">
@@ -33746,15 +33766,15 @@
       </c>
       <c r="BL24" cm="1">
         <f t="array" ref="BL24">FRONTEND!$M7-$W$32*SUM($BL$15:$BP$20*BV5:BZ10)</f>
-        <v>-0.51200000000000001</v>
+        <v>-0.51429314843251095</v>
       </c>
       <c r="BM24" cm="1">
         <f t="array" ref="BM24">FRONTEND!$N7-$W$32*SUM($BL$15:$BP$20*BW5:CA10)</f>
-        <v>0.89690605839168669</v>
+        <v>0.9014086731473766</v>
       </c>
       <c r="BN24" s="10" cm="1">
         <f t="array" ref="BN24">FRONTEND!$O7-$W$32*SUM($BL$15:$BP$20*BX5:CB10)</f>
-        <v>-0.52307599210257671</v>
+        <v>-0.52646632591061326</v>
       </c>
       <c r="BP24" s="11">
         <v>1</v>
@@ -33849,15 +33869,15 @@
       </c>
       <c r="BL25" cm="1">
         <f t="array" ref="BL25">FRONTEND!$M8-$W$32*SUM($BL$15:$BP$20*BV6:BZ11)</f>
-        <v>0.122</v>
+        <v>0.12435160176814193</v>
       </c>
       <c r="BM25" cm="1">
         <f t="array" ref="BM25">FRONTEND!$N8-$W$32*SUM($BL$15:$BP$20*BW6:CA11)</f>
-        <v>-0.20385735576309891</v>
+        <v>-0.21069185888337275</v>
       </c>
       <c r="BN25" s="10" cm="1">
         <f t="array" ref="BN25">FRONTEND!$O8-$W$32*SUM($BL$15:$BP$20*BX6:CB11)</f>
-        <v>-0.73992810683181709</v>
+        <v>-0.7388020631004999</v>
       </c>
     </row>
     <row r="26" spans="3:74" ht="21" x14ac:dyDescent="0.35">
@@ -33980,15 +34000,15 @@
       </c>
       <c r="BL26" cm="1">
         <f t="array" ref="BL26">FRONTEND!$M9-$W$32*SUM($BL$15:$BP$20*BV7:BZ12)</f>
-        <v>0.74199999999999999</v>
+        <v>0.74282364736996709</v>
       </c>
       <c r="BM26" cm="1">
         <f t="array" ref="BM26">FRONTEND!$N9-$W$32*SUM($BL$15:$BP$20*BW7:CA12)</f>
-        <v>0.80495441981918125</v>
+        <v>0.8028549551653219</v>
       </c>
       <c r="BN26" s="10" cm="1">
         <f t="array" ref="BN26">FRONTEND!$O9-$W$32*SUM($BL$15:$BP$20*BX7:CB12)</f>
-        <v>-0.97687438275808758</v>
+        <v>-0.97979846846711627</v>
       </c>
     </row>
     <row r="27" spans="3:74" x14ac:dyDescent="0.25">
@@ -34121,15 +34141,15 @@
       </c>
       <c r="BL27" cm="1">
         <f t="array" ref="BL27">FRONTEND!$M10-$W$32*SUM($BL$15:$BP$20*BV8:BZ13)</f>
-        <v>0.78200000000000003</v>
+        <v>0.77937488702595381</v>
       </c>
       <c r="BM27" cm="1">
         <f t="array" ref="BM27">FRONTEND!$N10-$W$32*SUM($BL$15:$BP$20*BW8:CA13)</f>
-        <v>0.51603359338236943</v>
+        <v>0.51790151096112857</v>
       </c>
       <c r="BN27" s="10" cm="1">
         <f t="array" ref="BN27">FRONTEND!$O10-$W$32*SUM($BL$15:$BP$20*BX8:CB13)</f>
-        <v>-0.91400732662594641</v>
+        <v>-0.91344253028887379</v>
       </c>
     </row>
     <row r="28" spans="3:74" x14ac:dyDescent="0.25">
@@ -34183,7 +34203,7 @@
         <v>1</v>
       </c>
       <c r="AE28" s="10">
-        <f t="shared" ref="AE28:AE30" si="4">Z15-$W$32*$AE14</f>
+        <f t="shared" ref="AE28:AE30" si="3">Z15-$W$32*$AE14</f>
         <v>-2.2513438428906352E-3</v>
       </c>
       <c r="AK28" s="30"/>
@@ -34208,15 +34228,15 @@
       </c>
       <c r="BL28" s="13" cm="1">
         <f t="array" ref="BL28">FRONTEND!$M11-$W$32*SUM($BL$15:$BP$20*BV9:BZ14)</f>
-        <v>0.40899999999999997</v>
+        <v>0.40754731127105848</v>
       </c>
       <c r="BM28" s="13" cm="1">
         <f t="array" ref="BM28">FRONTEND!$N11-$W$32*SUM($BL$15:$BP$20*BW9:CA14)</f>
-        <v>-0.438</v>
+        <v>-0.43840846346399676</v>
       </c>
       <c r="BN28" s="12" cm="1">
         <f t="array" ref="BN28">FRONTEND!$O11-$W$32*SUM($BL$15:$BP$20*BX9:CB14)</f>
-        <v>0.29299999999999998</v>
+        <v>0.29675884780867645</v>
       </c>
     </row>
     <row r="29" spans="3:74" ht="21" x14ac:dyDescent="0.35">
@@ -34225,7 +34245,7 @@
         <v>-1.3324716561864931</v>
       </c>
       <c r="D29" s="27">
-        <f t="shared" ref="D29:D60" si="5">(EXP(C29)-EXP(-C29))/(EXP(C29)+EXP(-C29))</f>
+        <f t="shared" ref="D29:D60" si="4">(EXP(C29)-EXP(-C29))/(EXP(C29)+EXP(-C29))</f>
         <v>-0.8698521234405544</v>
       </c>
       <c r="E29" s="27" cm="1">
@@ -34246,7 +34266,7 @@
         <v>3.2490876142180647</v>
       </c>
       <c r="L29" s="27">
-        <f t="shared" ref="L29:L60" si="6">1/(1+EXP(-K29))</f>
+        <f t="shared" ref="L29:L60" si="5">1/(1+EXP(-K29))</f>
         <v>0.96264031351507262</v>
       </c>
       <c r="N29" cm="1">
@@ -34254,7 +34274,7 @@
         <v>-1.5211298595480627</v>
       </c>
       <c r="O29" s="27">
-        <f t="shared" ref="O29:O60" si="7">1/(1+EXP(-N29))</f>
+        <f t="shared" ref="O29:O60" si="6">1/(1+EXP(-N29))</f>
         <v>0.17929520209815511</v>
       </c>
       <c r="Q29" cm="1">
@@ -34262,7 +34282,7 @@
         <v>-0.9925746521436658</v>
       </c>
       <c r="R29" s="27">
-        <f t="shared" ref="R29:R60" si="8">(EXP(Q29)-EXP(-Q29))/(EXP(Q29)+EXP(-Q29))</f>
+        <f t="shared" ref="R29:R60" si="7">(EXP(Q29)-EXP(-Q29))/(EXP(Q29)+EXP(-Q29))</f>
         <v>-0.75845802286500963</v>
       </c>
       <c r="T29" s="42" cm="1">
@@ -34283,7 +34303,7 @@
         <v>2</v>
       </c>
       <c r="AE29" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1573569718452978E-2</v>
       </c>
       <c r="AK29" s="41" t="s">
@@ -34314,7 +34334,7 @@
         <v>1.7211878493612058</v>
       </c>
       <c r="D30" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.93800590487351898</v>
       </c>
       <c r="E30" s="28">
@@ -34333,21 +34353,21 @@
         <v>-2.7436005457934787E-2</v>
       </c>
       <c r="L30" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.49314142885365286</v>
       </c>
       <c r="N30">
         <v>-0.29554556865893822</v>
       </c>
       <c r="O30" s="28">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.42664676535736068</v>
       </c>
       <c r="Q30">
         <v>1.5295689220699173</v>
       </c>
       <c r="R30" s="28">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.910350795843623</v>
       </c>
       <c r="T30" s="43">
@@ -34365,7 +34385,7 @@
         <v>3</v>
       </c>
       <c r="AE30" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>9.499287086314331E-3</v>
       </c>
       <c r="AJ30" t="s">
@@ -34822,7 +34842,7 @@
         <v>-1.3159391393257451</v>
       </c>
       <c r="D35" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-0.86577048956970548</v>
       </c>
       <c r="E35" s="27" cm="1">
@@ -34837,7 +34857,7 @@
         <v>1.9396359621108359</v>
       </c>
       <c r="L35" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.87431214465954887</v>
       </c>
       <c r="N35" cm="1">
@@ -34845,7 +34865,7 @@
         <v>-0.35024523714605116</v>
       </c>
       <c r="O35" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.41332295297710026</v>
       </c>
       <c r="Q35" cm="1">
@@ -34853,7 +34873,7 @@
         <v>-1.3431662329090721</v>
       </c>
       <c r="R35" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-0.87243064109704138</v>
       </c>
       <c r="T35" s="42" cm="1">
@@ -34893,7 +34913,7 @@
         <v>1</v>
       </c>
       <c r="BL35" s="20">
-        <f t="shared" ref="BL35:BL40" si="9">AV56*IF(AV56&gt;0,1,0)</f>
+        <f>AV56*IF(FRONTEND!T13&gt;0,1,0)</f>
         <v>2.6933167311249648E-2</v>
       </c>
       <c r="BT35">
@@ -34911,7 +34931,7 @@
         <v>1.6384828317569704</v>
       </c>
       <c r="D36" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.92726017656815518</v>
       </c>
       <c r="E36" s="28">
@@ -34924,21 +34944,21 @@
         <v>9.9149505495609733E-2</v>
       </c>
       <c r="L36" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.52476709003407584</v>
       </c>
       <c r="N36">
         <v>-0.98488736005662325</v>
       </c>
       <c r="O36" s="28">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.2719231017214005</v>
       </c>
       <c r="Q36">
         <v>1.7232180453459758</v>
       </c>
       <c r="R36" s="28">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.93824935866036352</v>
       </c>
       <c r="T36" s="43">
@@ -35014,8 +35034,8 @@
         <v>2</v>
       </c>
       <c r="BL36" s="20">
-        <f t="shared" si="9"/>
-        <v>1.9240005657428297E-2</v>
+        <f>AV57*IF(FRONTEND!T14&gt;0,1,0)</f>
+        <v>0</v>
       </c>
       <c r="BT36">
         <v>0</v>
@@ -35110,7 +35130,7 @@
         <v>3</v>
       </c>
       <c r="BL37" s="20">
-        <f t="shared" si="9"/>
+        <f>AV58*IF(FRONTEND!T15&gt;0,1,0)</f>
         <v>3.259503431381755E-2</v>
       </c>
       <c r="BT37">
@@ -35229,8 +35249,8 @@
         <v>4</v>
       </c>
       <c r="BL38" s="20">
-        <f t="shared" si="9"/>
-        <v>3.6382396018897832E-2</v>
+        <f>AV59*IF(FRONTEND!T16&gt;0,1,0)</f>
+        <v>0</v>
       </c>
       <c r="BT38">
         <v>0</v>
@@ -35351,7 +35371,7 @@
         <v>5</v>
       </c>
       <c r="BL39" s="20">
-        <f t="shared" si="9"/>
+        <f>AV60*IF(FRONTEND!T17&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="BT39">
@@ -35408,8 +35428,8 @@
         <v>6</v>
       </c>
       <c r="BL40" s="20">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>AV61*IF(FRONTEND!T18&gt;0,1,0)</f>
+        <v>-3.8751558860882526E-3</v>
       </c>
     </row>
     <row r="41" spans="3:74" x14ac:dyDescent="0.25">
@@ -35418,7 +35438,7 @@
         <v>-0.41667405005645963</v>
       </c>
       <c r="D41" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-0.39412480444461645</v>
       </c>
       <c r="E41" s="27" cm="1">
@@ -35433,7 +35453,7 @@
         <v>1.5309229359958003</v>
       </c>
       <c r="L41" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.82214131063456064</v>
       </c>
       <c r="N41" cm="1">
@@ -35441,7 +35461,7 @@
         <v>0.42260746743272448</v>
       </c>
       <c r="O41" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.60410702525375271</v>
       </c>
       <c r="Q41" cm="1">
@@ -35449,7 +35469,7 @@
         <v>-0.45136969247195402</v>
       </c>
       <c r="R41" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-0.42302424319875959</v>
       </c>
       <c r="T41" s="42" cm="1">
@@ -35486,7 +35506,7 @@
         <v>2.9722518248582377</v>
       </c>
       <c r="D42" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.99477328991129366</v>
       </c>
       <c r="E42" s="28">
@@ -35499,21 +35519,21 @@
         <v>1.1327796228951759</v>
       </c>
       <c r="L42" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.75635150379234573</v>
       </c>
       <c r="N42">
         <v>-2.0555848856194698</v>
       </c>
       <c r="O42" s="28">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.11348927488890238</v>
       </c>
       <c r="Q42">
         <v>2.99591617756455</v>
       </c>
       <c r="R42" s="28">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.99501429837239941</v>
       </c>
       <c r="T42" s="43">
@@ -35523,7 +35543,7 @@
         <v>1</v>
       </c>
       <c r="AD42">
-        <f t="shared" ref="AD42:AD43" si="10">AE35</f>
+        <f t="shared" ref="AD42:AD43" si="8">AE35</f>
         <v>0.21564630559287151</v>
       </c>
       <c r="AE42">
@@ -35534,11 +35554,11 @@
         <v>1</v>
       </c>
       <c r="AG42">
-        <f t="shared" ref="AG42:AG47" si="11">IF(AF42=$AE$42,$AD$42,0)</f>
+        <f t="shared" ref="AG42:AG47" si="9">IF(AF42=$AE$42,$AD$42,0)</f>
         <v>0</v>
       </c>
       <c r="AH42">
-        <f t="shared" ref="AH42:AH47" si="12">IF(AF42=$AE$43,$AD$43,0)</f>
+        <f t="shared" ref="AH42:AH47" si="10">IF(AF42=$AE$43,$AD$43,0)</f>
         <v>0</v>
       </c>
       <c r="AT42" s="5"/>
@@ -35607,7 +35627,7 @@
         <v>2</v>
       </c>
       <c r="AD43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>-0.10678370645331033</v>
       </c>
       <c r="AE43">
@@ -35618,11 +35638,11 @@
         <v>2</v>
       </c>
       <c r="AG43">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH43">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT43" s="9"/>
@@ -35688,54 +35708,54 @@
         <v>3</v>
       </c>
       <c r="AG44">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH44">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT44" s="9">
         <v>1</v>
       </c>
       <c r="AU44">
-        <f t="shared" ref="AU44:AU45" si="13">L23-$W$32*SUM(AU8,AU14,AU20,AU26,AU32,AU38)</f>
+        <f t="shared" ref="AU44:AU45" si="11">L23-$W$32*SUM(AU8,AU14,AU20,AU26,AU32,AU38)</f>
         <v>-0.52634179657726887</v>
       </c>
       <c r="AV44" s="10">
-        <f t="shared" ref="AV44:AV45" si="14">M23-$W$32*SUM(AV8,AV14,AV20,AV26,AV32,AV38)</f>
+        <f t="shared" ref="AV44:AV45" si="12">M23-$W$32*SUM(AV8,AV14,AV20,AV26,AV32,AV38)</f>
         <v>0.88673409288994043</v>
       </c>
       <c r="AW44" s="9">
-        <f t="shared" ref="AW44:AW45" si="15">P23-$W$32*SUM(AW8,AW14,AW20,AW26,AW32,AW38)</f>
+        <f t="shared" ref="AW44:AW45" si="13">P23-$W$32*SUM(AW8,AW14,AW20,AW26,AW32,AW38)</f>
         <v>0.67570612729931756</v>
       </c>
       <c r="AX44" s="10">
-        <f t="shared" ref="AX44:AX45" si="16">Q23-$W$32*SUM(AX8,AX14,AX20,AX26,AX32,AX38)</f>
+        <f t="shared" ref="AX44:AX45" si="14">Q23-$W$32*SUM(AX8,AX14,AX20,AX26,AX32,AX38)</f>
         <v>0.73595212427055967</v>
       </c>
       <c r="AY44" s="27">
-        <f t="shared" ref="AY44:AY45" si="17">T23-$W$32*SUM(AY8,AY14,AY20,AY26,AY32,AY38)</f>
+        <f t="shared" ref="AY44:AY45" si="15">T23-$W$32*SUM(AY8,AY14,AY20,AY26,AY32,AY38)</f>
         <v>-1.2482584726125878E-2</v>
       </c>
       <c r="AZ44" s="9">
-        <f t="shared" ref="AZ44:AZ45" si="18">L18-$W$32*SUM(AZ8,AZ14,AZ20,AZ26,AZ32,AZ38)</f>
+        <f t="shared" ref="AZ44:AZ45" si="16">L18-$W$32*SUM(AZ8,AZ14,AZ20,AZ26,AZ32,AZ38)</f>
         <v>-0.21241076330250935</v>
       </c>
       <c r="BA44" s="10">
-        <f t="shared" ref="BA44:BA45" si="19">M18-$W$32*SUM(BA8,BA14,BA20,BA26,BA32,BA38)</f>
+        <f t="shared" ref="BA44:BA45" si="17">M18-$W$32*SUM(BA8,BA14,BA20,BA26,BA32,BA38)</f>
         <v>0.24848760935047298</v>
       </c>
       <c r="BB44" s="9">
-        <f t="shared" ref="BB44:BB45" si="20">P18-$W$32*SUM(BB8,BB14,BB20,BB26,BB32,BB38)</f>
+        <f t="shared" ref="BB44:BB45" si="18">P18-$W$32*SUM(BB8,BB14,BB20,BB26,BB32,BB38)</f>
         <v>-1.4875716792045213E-2</v>
       </c>
       <c r="BC44" s="10">
-        <f t="shared" ref="BC44:BC45" si="21">Q18-$W$32*SUM(BC8,BC14,BC20,BC26,BC32,BC38)</f>
+        <f t="shared" ref="BC44:BC45" si="19">Q18-$W$32*SUM(BC8,BC14,BC20,BC26,BC32,BC38)</f>
         <v>1.0003328611667985</v>
       </c>
       <c r="BD44" s="27">
-        <f t="shared" ref="BD44:BD45" si="22">T18-$W$32*SUM(BD8,BD14,BD20,BD26,BD32,BD38)</f>
+        <f t="shared" ref="BD44:BD45" si="20">T18-$W$32*SUM(BD8,BD14,BD20,BD26,BD32,BD38)</f>
         <v>1.7395039058108533E-3</v>
       </c>
       <c r="BE44" s="9">
@@ -35747,15 +35767,15 @@
         <v>-0.13900000000000001</v>
       </c>
       <c r="BG44" s="9">
-        <f t="shared" ref="BG44:BG45" si="23">P13-$W$32*SUM(BG8,BG14,BG20,BG26,BG32,BG38)</f>
+        <f t="shared" ref="BG44:BG45" si="21">P13-$W$32*SUM(BG8,BG14,BG20,BG26,BG32,BG38)</f>
         <v>-0.25346473374747597</v>
       </c>
       <c r="BH44" s="10">
-        <f t="shared" ref="BH44:BH45" si="24">Q13-$W$32*SUM(BH8,BH14,BH20,BH26,BH32,BH38)</f>
+        <f t="shared" ref="BH44:BH45" si="22">Q13-$W$32*SUM(BH8,BH14,BH20,BH26,BH32,BH38)</f>
         <v>-0.87140016461521719</v>
       </c>
       <c r="BI44" s="27">
-        <f t="shared" ref="BI44:BI45" si="25">T13-$W$32*SUM(BI8,BI14,BI20,BI26,BI32,BI38)</f>
+        <f t="shared" ref="BI44:BI45" si="23">T13-$W$32*SUM(BI8,BI14,BI20,BI26,BI32,BI38)</f>
         <v>6.9420802978958235E-4</v>
       </c>
       <c r="BK44" s="9">
@@ -35763,7 +35783,7 @@
       </c>
       <c r="BL44" s="10" cm="1">
         <f t="array" ref="BL44">FRONTEND!T7-$W32*SUM($BL$35:$BL$40*BU32:BU37)</f>
-        <v>0.12177429594635289</v>
+        <v>0.12286018979410132</v>
       </c>
       <c r="BN44" s="11">
         <v>1</v>
@@ -35808,74 +35828,74 @@
         <v>4</v>
       </c>
       <c r="AG45">
+        <f t="shared" si="9"/>
+        <v>0.21564630559287151</v>
+      </c>
+      <c r="AH45">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AT45" s="11">
+        <v>2</v>
+      </c>
+      <c r="AU45" s="13">
         <f t="shared" si="11"/>
-        <v>0.21564630559287151</v>
-      </c>
-      <c r="AH45">
+        <v>0.6714053620197582</v>
+      </c>
+      <c r="AV45" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AT45" s="11">
-        <v>2</v>
-      </c>
-      <c r="AU45" s="13">
+        <v>0.74095518989967868</v>
+      </c>
+      <c r="AW45" s="11">
         <f t="shared" si="13"/>
-        <v>0.6714053620197582</v>
-      </c>
-      <c r="AV45" s="12">
+        <v>-0.50727689921497154</v>
+      </c>
+      <c r="AX45" s="12">
         <f t="shared" si="14"/>
-        <v>0.74095518989967868</v>
-      </c>
-      <c r="AW45" s="11">
+        <v>0.89133538615439334</v>
+      </c>
+      <c r="AY45" s="28">
         <f t="shared" si="15"/>
-        <v>-0.50727689921497154</v>
-      </c>
-      <c r="AX45" s="12">
+        <v>-1.066405709409044E-4</v>
+      </c>
+      <c r="AZ45" s="11">
         <f t="shared" si="16"/>
-        <v>0.89133538615439334</v>
-      </c>
-      <c r="AY45" s="28">
+        <v>-0.24846042098781077</v>
+      </c>
+      <c r="BA45" s="12">
         <f t="shared" si="17"/>
-        <v>-1.066405709409044E-4</v>
-      </c>
-      <c r="AZ45" s="11">
+        <v>-0.87146489164042606</v>
+      </c>
+      <c r="BB45" s="11">
         <f t="shared" si="18"/>
-        <v>-0.24846042098781077</v>
-      </c>
-      <c r="BA45" s="12">
+        <v>0.87880135744520338</v>
+      </c>
+      <c r="BC45" s="12">
         <f t="shared" si="19"/>
-        <v>-0.87146489164042606</v>
-      </c>
-      <c r="BB45" s="11">
+        <v>-0.14017231349360459</v>
+      </c>
+      <c r="BD45" s="28">
         <f t="shared" si="20"/>
-        <v>0.87880135744520338</v>
-      </c>
-      <c r="BC45" s="12">
+        <v>1.6162325311360763E-3</v>
+      </c>
+      <c r="BE45" s="11">
+        <f t="shared" ref="BE45:BF45" si="24">L14-W40*SUM(BE9,BE15,BE21,BE27,BE33,BE39)</f>
+        <v>-1.2999999999999999E-2</v>
+      </c>
+      <c r="BF45" s="12">
+        <f t="shared" si="24"/>
+        <v>0.997</v>
+      </c>
+      <c r="BG45" s="11">
         <f t="shared" si="21"/>
-        <v>-0.14017231349360459</v>
-      </c>
-      <c r="BD45" s="28">
+        <v>-0.21092255837936302</v>
+      </c>
+      <c r="BH45" s="12">
         <f t="shared" si="22"/>
-        <v>1.6162325311360763E-3</v>
-      </c>
-      <c r="BE45" s="11">
-        <f t="shared" ref="BE45:BF45" si="26">L14-W40*SUM(BE9,BE15,BE21,BE27,BE33,BE39)</f>
-        <v>-1.2999999999999999E-2</v>
-      </c>
-      <c r="BF45" s="12">
-        <f t="shared" si="26"/>
-        <v>0.997</v>
-      </c>
-      <c r="BG45" s="11">
+        <v>0.24661859683896289</v>
+      </c>
+      <c r="BI45" s="28">
         <f t="shared" si="23"/>
-        <v>-0.21092255837936302</v>
-      </c>
-      <c r="BH45" s="12">
-        <f t="shared" si="24"/>
-        <v>0.24661859683896289</v>
-      </c>
-      <c r="BI45" s="28">
-        <f t="shared" si="25"/>
         <v>-1.0895276599877811E-3</v>
       </c>
       <c r="BK45" s="9">
@@ -35921,11 +35941,11 @@
         <v>5</v>
       </c>
       <c r="AG46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BK46" s="11">
@@ -35942,7 +35962,7 @@
         <v>-0.12061449502743135</v>
       </c>
       <c r="D47" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-0.12003298456719579</v>
       </c>
       <c r="E47" s="27" cm="1">
@@ -35957,7 +35977,7 @@
         <v>-0.24154659521655469</v>
       </c>
       <c r="L47" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.43990525192554597</v>
       </c>
       <c r="N47" cm="1">
@@ -35965,7 +35985,7 @@
         <v>0.85972600657275999</v>
       </c>
       <c r="O47" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.70260340608684868</v>
       </c>
       <c r="Q47" cm="1">
@@ -35973,7 +35993,7 @@
         <v>-1.4462983012709041E-2</v>
       </c>
       <c r="R47" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.4461974651716118E-2</v>
       </c>
       <c r="T47" s="42" cm="1">
@@ -35984,11 +36004,11 @@
         <v>6</v>
       </c>
       <c r="AG47">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH47">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>-0.10678370645331033</v>
       </c>
       <c r="AU47" t="s">
@@ -36003,7 +36023,7 @@
         <v>1.0252669646107506</v>
       </c>
       <c r="D48" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.77200311636106356</v>
       </c>
       <c r="E48" s="28">
@@ -36016,21 +36036,21 @@
         <v>0.35853244479956969</v>
       </c>
       <c r="L48" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.58868513396416156</v>
       </c>
       <c r="N48">
         <v>-0.78606191381170076</v>
       </c>
       <c r="O48" s="28">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.31301487772946457</v>
       </c>
       <c r="Q48">
         <v>0.98030515534211216</v>
       </c>
       <c r="R48" s="28">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.75319797374365927</v>
       </c>
       <c r="T48" s="43">
@@ -36160,11 +36180,11 @@
         <v>1</v>
       </c>
       <c r="AD51">
-        <f t="shared" ref="AD51:AD56" si="27">$AE$37/$AF$50</f>
+        <f t="shared" ref="AD51:AD56" si="25">$AE$37/$AF$50</f>
         <v>-1.1628955328842479E-2</v>
       </c>
       <c r="AE51">
-        <f t="shared" ref="AE51:AE56" si="28">$AE$38/$AF$50</f>
+        <f t="shared" ref="AE51:AE56" si="26">$AE$38/$AF$50</f>
         <v>3.2264210446531021E-3</v>
       </c>
       <c r="AT51">
@@ -36224,11 +36244,11 @@
         <v>2</v>
       </c>
       <c r="AD52">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>-1.1628955328842479E-2</v>
       </c>
       <c r="AE52">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>3.2264210446531021E-3</v>
       </c>
     </row>
@@ -36238,7 +36258,7 @@
         <v>-1.4869779102531528</v>
       </c>
       <c r="D53" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-0.90276714421486626</v>
       </c>
       <c r="E53" s="27" cm="1">
@@ -36253,7 +36273,7 @@
         <v>2.4834693875800906</v>
       </c>
       <c r="L53" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.92297480687918121</v>
       </c>
       <c r="N53" cm="1">
@@ -36261,7 +36281,7 @@
         <v>7.565798893655129E-2</v>
       </c>
       <c r="O53" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.51890547997358005</v>
       </c>
       <c r="Q53" cm="1">
@@ -36269,7 +36289,7 @@
         <v>-1.706339307440714</v>
       </c>
       <c r="R53" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-0.93619686455664586</v>
       </c>
       <c r="T53" s="42" cm="1">
@@ -36280,11 +36300,11 @@
         <v>3</v>
       </c>
       <c r="AD53">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>-1.1628955328842479E-2</v>
       </c>
       <c r="AE53">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>3.2264210446531021E-3</v>
       </c>
       <c r="AT53" s="5"/>
@@ -36298,7 +36318,7 @@
         <v>2.8953956996654426</v>
       </c>
       <c r="D54" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.99390748995108114</v>
       </c>
       <c r="E54" s="28">
@@ -36311,21 +36331,21 @@
         <v>0.24700694514182112</v>
       </c>
       <c r="L54" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.56143967150152563</v>
       </c>
       <c r="N54">
         <v>-1.3758213471905045</v>
       </c>
       <c r="O54" s="28">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.20168094824260754</v>
       </c>
       <c r="Q54">
         <v>2.9729485381742968</v>
       </c>
       <c r="R54" s="28">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.99478054888300471</v>
       </c>
       <c r="T54" s="43">
@@ -36335,11 +36355,11 @@
         <v>4</v>
       </c>
       <c r="AD54">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>-1.1628955328842479E-2</v>
       </c>
       <c r="AE54">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>3.2264210446531021E-3</v>
       </c>
       <c r="AT54" s="9"/>
@@ -36356,11 +36376,11 @@
         <v>5</v>
       </c>
       <c r="AD55">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>-1.1628955328842479E-2</v>
       </c>
       <c r="AE55">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>3.2264210446531021E-3</v>
       </c>
       <c r="AT55" s="9"/>
@@ -36379,11 +36399,11 @@
         <v>6</v>
       </c>
       <c r="AD56">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>-1.1628955328842479E-2</v>
       </c>
       <c r="AE56">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>3.2264210446531021E-3</v>
       </c>
       <c r="AT56" s="9">
@@ -36499,7 +36519,7 @@
         <v>-0.61517353938410202</v>
       </c>
       <c r="D59" s="27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-0.54775863079652098</v>
       </c>
       <c r="E59" s="27" cm="1">
@@ -36514,7 +36534,7 @@
         <v>1.1004800243679227</v>
       </c>
       <c r="L59" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.75035003689785562</v>
       </c>
       <c r="N59" cm="1">
@@ -36522,7 +36542,7 @@
         <v>0.59386791538926675</v>
       </c>
       <c r="O59" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.64425213213002686</v>
       </c>
       <c r="Q59" cm="1">
@@ -36530,7 +36550,7 @@
         <v>-0.68775129559914805</v>
       </c>
       <c r="R59" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-0.59653545066334235</v>
       </c>
       <c r="T59" s="42" cm="1">
@@ -36561,7 +36581,7 @@
         <v>2.3464392665184111</v>
       </c>
       <c r="D60" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.98184573812126075</v>
       </c>
       <c r="E60" s="28">
@@ -36574,21 +36594,21 @@
         <v>0.61134770108482939</v>
       </c>
       <c r="L60" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.64824816958832832</v>
       </c>
       <c r="N60">
         <v>-1.4669899062493403</v>
       </c>
       <c r="O60" s="28">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.1874005645833462</v>
       </c>
       <c r="Q60">
         <v>2.3811194633024728</v>
       </c>
       <c r="R60" s="28">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.98305193964356996</v>
       </c>
       <c r="T60" s="43">
@@ -36598,7 +36618,7 @@
         <v>1</v>
       </c>
       <c r="AE60" s="17">
-        <f t="shared" ref="AE60:AF65" si="29">AG42+AD51</f>
+        <f t="shared" ref="AE60:AF65" si="27">AG42+AD51</f>
         <v>-1.1628955328842479E-2</v>
       </c>
       <c r="AF60" s="14">
@@ -36622,11 +36642,11 @@
         <v>2</v>
       </c>
       <c r="AE61" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>-1.1628955328842479E-2</v>
       </c>
       <c r="AF61" s="14">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>3.2264210446531021E-3</v>
       </c>
       <c r="AT61" s="11">
@@ -36655,11 +36675,11 @@
         <v>3</v>
       </c>
       <c r="AE62" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>-1.1628955328842479E-2</v>
       </c>
       <c r="AF62" s="14">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>3.2264210446531021E-3</v>
       </c>
     </row>
@@ -36677,11 +36697,11 @@
         <v>4</v>
       </c>
       <c r="AE63" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>0.20401735026402903</v>
       </c>
       <c r="AF63" s="14">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>3.2264210446531021E-3</v>
       </c>
     </row>
@@ -36708,11 +36728,11 @@
         <v>5</v>
       </c>
       <c r="AE64" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>-1.1628955328842479E-2</v>
       </c>
       <c r="AF64" s="14">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>3.2264210446531021E-3</v>
       </c>
     </row>
@@ -36747,11 +36767,11 @@
         <v>6</v>
       </c>
       <c r="AE65" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>-1.1628955328842479E-2</v>
       </c>
       <c r="AF65" s="15">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>-0.10355728540865722</v>
       </c>
     </row>
@@ -37123,6 +37143,9 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <ignoredErrors>
+    <ignoredError sqref="AE35:AE38" formulaRange="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -37330,11 +37353,11 @@
       </c>
       <c r="AK5" s="6"/>
       <c r="AL5" s="7"/>
-      <c r="AN5" s="5"/>
-      <c r="AO5" s="6" t="s">
+      <c r="AN5" s="90"/>
+      <c r="AO5" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="AP5" s="7" t="s">
+      <c r="AP5" s="90" t="s">
         <v>42</v>
       </c>
       <c r="AT5" s="5"/>
@@ -37344,7 +37367,7 @@
       <c r="AV5" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="AX5" s="5" t="s">
+      <c r="AX5" s="93" t="s">
         <v>185</v>
       </c>
       <c r="AY5" s="7" t="s">
@@ -37482,11 +37505,11 @@
       <c r="AL6" s="10">
         <v>3</v>
       </c>
-      <c r="AN6" s="9"/>
-      <c r="AO6">
-        <v>1</v>
-      </c>
-      <c r="AP6" s="10"/>
+      <c r="AN6" s="90"/>
+      <c r="AO6" s="90">
+        <v>1</v>
+      </c>
+      <c r="AP6" s="90"/>
       <c r="AT6" s="9"/>
       <c r="AU6">
         <v>1</v>
@@ -37505,7 +37528,7 @@
       </c>
       <c r="CC6" s="17" cm="1">
         <f t="array" ref="CC6:CC11">CA85:CA90</f>
-        <v>2.6554831438101029E-2</v>
+        <v>-7.0377082826471871E-3</v>
       </c>
       <c r="CD6">
         <f>MATCH(MAX(FRONTEND!$M28:$Q28),FRONTEND!$M28:$Q28,0)</f>
@@ -37525,7 +37548,7 @@
       </c>
       <c r="CH6">
         <f t="shared" si="1"/>
-        <v>2.6554831438101029E-2</v>
+        <v>-7.0377082826471871E-3</v>
       </c>
       <c r="CI6">
         <f t="shared" si="1"/>
@@ -37656,14 +37679,14 @@
       <c r="AL7" s="36">
         <v>-0.77800000000000002</v>
       </c>
-      <c r="AN7" s="9">
-        <v>1</v>
-      </c>
-      <c r="AO7" s="1">
+      <c r="AN7" s="90">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="91">
         <f>-1/3*((2/(1+DATA!$I$16))*AI27/AH21-((2*DATA!$I$16)/(1+DATA!$I$16))*(1-AI27)*(1-AH21))</f>
         <v>6.8401632502594373E-2</v>
       </c>
-      <c r="AP7" s="10"/>
+      <c r="AP7" s="90"/>
       <c r="AT7" s="9">
         <v>1</v>
       </c>
@@ -37675,18 +37698,18 @@
         <v>-0.83900114593088981</v>
       </c>
       <c r="AX7" s="11">
-        <f>F47-$AH$32*SUM(AO75:AO80)</f>
-        <v>0</v>
+        <f>F47-$AH$32*SUM(AO60:AO65)</f>
+        <v>-4.0727776664446186E-2</v>
       </c>
       <c r="AY7" s="12">
-        <f>G47-$AH$32*SUM(AP75:AP80)</f>
-        <v>0</v>
+        <f>G47-$AH$32*SUM(AP60:AP65)</f>
+        <v>2.7553332053341109E-2</v>
       </c>
       <c r="CB7">
         <v>2</v>
       </c>
       <c r="CC7" s="17">
-        <v>2.7182811963848669E-2</v>
+        <v>8.1698616474118937E-3</v>
       </c>
       <c r="CD7">
         <f>MATCH(MAX(FRONTEND!$M29:$Q29),FRONTEND!$M29:$Q29,0)</f>
@@ -37698,7 +37721,7 @@
       </c>
       <c r="CF7">
         <f t="shared" si="1"/>
-        <v>2.7182811963848669E-2</v>
+        <v>8.1698616474118937E-3</v>
       </c>
       <c r="CG7">
         <f t="shared" si="1"/>
@@ -37833,14 +37856,14 @@
       <c r="AL8" s="36">
         <v>0.99099999999999999</v>
       </c>
-      <c r="AN8" s="9">
-        <v>2</v>
-      </c>
-      <c r="AO8" s="1">
+      <c r="AN8" s="90">
+        <v>2</v>
+      </c>
+      <c r="AO8" s="91">
         <f>-1/3*((2/(1+DATA!$I$17))*AI28/AH22-((2*DATA!$I$17)/(1+DATA!$I$17))*(1-AI28)*(1-AH22))</f>
         <v>-3.4742288520487117</v>
       </c>
-      <c r="AP8" s="10"/>
+      <c r="AP8" s="90"/>
       <c r="AT8" s="11">
         <v>2</v>
       </c>
@@ -37854,7 +37877,7 @@
         <v>3</v>
       </c>
       <c r="CC8" s="17">
-        <v>2.9268134939021584E-2</v>
+        <v>6.9738192301244672E-2</v>
       </c>
       <c r="CD8">
         <f>MATCH(MAX(FRONTEND!$M30:$Q30),FRONTEND!$M30:$Q30,0)</f>
@@ -37870,7 +37893,7 @@
       </c>
       <c r="CG8">
         <f t="shared" si="1"/>
-        <v>2.9268134939021584E-2</v>
+        <v>6.9738192301244672E-2</v>
       </c>
       <c r="CH8">
         <f t="shared" si="1"/>
@@ -38000,19 +38023,19 @@
       <c r="AL9" s="36">
         <v>-0.121</v>
       </c>
-      <c r="AN9" s="11">
+      <c r="AN9" s="90">
         <v>3</v>
       </c>
-      <c r="AO9" s="21">
+      <c r="AO9" s="91">
         <f>-1/3*((2/(1+DATA!$I$18))*AI29/AH23-((2*DATA!$I$18)/(1+DATA!$I$18))*(1-AI29)*(1-AH23))</f>
         <v>-1.2715447206668757</v>
       </c>
-      <c r="AP9" s="12"/>
+      <c r="AP9" s="90"/>
       <c r="CB9">
         <v>4</v>
       </c>
       <c r="CC9" s="17">
-        <v>6.3235685173184106E-2</v>
+        <v>1.960931690977482E-2</v>
       </c>
       <c r="CD9">
         <f>MATCH(MAX(FRONTEND!$M31:$Q31),FRONTEND!$M31:$Q31,0)</f>
@@ -38032,7 +38055,7 @@
       </c>
       <c r="CH9">
         <f t="shared" si="1"/>
-        <v>6.3235685173184106E-2</v>
+        <v>1.960931690977482E-2</v>
       </c>
       <c r="CI9">
         <f t="shared" si="1"/>
@@ -38152,6 +38175,9 @@
       <c r="AL10" s="40">
         <v>0.186</v>
       </c>
+      <c r="AN10" s="90"/>
+      <c r="AO10" s="90"/>
+      <c r="AP10" s="90"/>
       <c r="AU10" t="s">
         <v>188</v>
       </c>
@@ -38162,7 +38188,7 @@
         <v>5</v>
       </c>
       <c r="CC10" s="17">
-        <v>2.3176921447235384E-2</v>
+        <v>6.2852458902921595E-3</v>
       </c>
       <c r="CD10">
         <f>MATCH(MAX(FRONTEND!$M32:$Q32),FRONTEND!$M32:$Q32,0)</f>
@@ -38170,7 +38196,7 @@
       </c>
       <c r="CE10">
         <f t="shared" si="1"/>
-        <v>2.3176921447235384E-2</v>
+        <v>6.2852458902921595E-3</v>
       </c>
       <c r="CF10">
         <f t="shared" si="1"/>
@@ -38280,6 +38306,9 @@
       <c r="AD11" s="17">
         <v>-0.60898947055925845</v>
       </c>
+      <c r="AN11" s="90"/>
+      <c r="AO11" s="90"/>
+      <c r="AP11" s="90"/>
       <c r="AU11">
         <v>1</v>
       </c>
@@ -38290,7 +38319,7 @@
         <v>6</v>
       </c>
       <c r="CC11" s="17">
-        <v>0.11483137641440443</v>
+        <v>5.6593826378490045E-2</v>
       </c>
       <c r="CD11">
         <f>MATCH(MAX(FRONTEND!$M33:$Q33),FRONTEND!$M33:$Q33,0)</f>
@@ -38314,7 +38343,7 @@
       </c>
       <c r="CI11">
         <f t="shared" si="1"/>
-        <v>0.11483137641440443</v>
+        <v>5.6593826378490045E-2</v>
       </c>
       <c r="CK11">
         <v>0</v>
@@ -38419,13 +38448,13 @@
       <c r="AD12" s="17">
         <v>-0.3467356925964542</v>
       </c>
-      <c r="AN12" s="5" t="s">
+      <c r="AN12" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="AO12" s="6" t="s">
+      <c r="AO12" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="AP12" s="7"/>
+      <c r="AP12" s="90"/>
       <c r="AT12">
         <v>1</v>
       </c>
@@ -38503,11 +38532,11 @@
       <c r="AK13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="AN13" s="9"/>
-      <c r="AO13">
-        <v>1</v>
-      </c>
-      <c r="AP13" s="10"/>
+      <c r="AN13" s="90"/>
+      <c r="AO13" s="90">
+        <v>1</v>
+      </c>
+      <c r="AP13" s="90"/>
       <c r="AT13">
         <v>2</v>
       </c>
@@ -38599,14 +38628,14 @@
       <c r="AK14" s="10">
         <v>1</v>
       </c>
-      <c r="AN14" s="9">
-        <v>1</v>
-      </c>
-      <c r="AO14">
+      <c r="AN14" s="90">
+        <v>1</v>
+      </c>
+      <c r="AO14" s="90">
         <f>-1/3*((2/(1+DATA!$I$16))*AI27*(1-AH21)-((2*DATA!$I$16)/(1+DATA!$I$16))*(1-AI27)*AH21)</f>
         <v>5.6388473878492338E-4</v>
       </c>
-      <c r="AP14" s="10"/>
+      <c r="AP14" s="90"/>
       <c r="AT14">
         <v>3</v>
       </c>
@@ -38722,14 +38751,14 @@
       <c r="AK15" s="10">
         <v>0</v>
       </c>
-      <c r="AN15" s="9">
-        <v>2</v>
-      </c>
-      <c r="AO15">
+      <c r="AN15" s="90">
+        <v>2</v>
+      </c>
+      <c r="AO15" s="90">
         <f>-1/3*((2/(1+DATA!$I$17))*AI28*(1-AH22)-((2*DATA!$I$17)/(1+DATA!$I$17))*(1-AI28)*AH22)</f>
         <v>-0.36367458983097156</v>
       </c>
-      <c r="AP15" s="10"/>
+      <c r="AP15" s="90"/>
       <c r="AT15">
         <v>4</v>
       </c>
@@ -38743,23 +38772,23 @@
         <v>1</v>
       </c>
       <c r="CC15">
-        <f t="shared" ref="CC15:CG20" si="7">CE6*IF(CE6&gt;0,1,0)</f>
+        <f>CE6*IF(FRONTEND!M19&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CD15">
-        <f t="shared" si="7"/>
+        <f>CF6*IF(FRONTEND!N19&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CE15">
-        <f t="shared" si="7"/>
+        <f>CG6*IF(FRONTEND!O19&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CF15">
-        <f t="shared" si="7"/>
-        <v>2.6554831438101029E-2</v>
+        <f>CH6*IF(FRONTEND!P19&gt;0,1,0)</f>
+        <v>-7.0377082826471871E-3</v>
       </c>
       <c r="CG15">
-        <f t="shared" si="7"/>
+        <f>CI6*IF(FRONTEND!Q19&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CK15">
@@ -38876,14 +38905,14 @@
       <c r="AK16" s="10">
         <v>0</v>
       </c>
-      <c r="AN16" s="11">
+      <c r="AN16" s="90">
         <v>3</v>
       </c>
-      <c r="AO16" s="13">
+      <c r="AO16" s="90">
         <f>-1/3*((2/(1+DATA!$I$18))*AI29*(1-AH23)-((2*DATA!$I$18)/(1+DATA!$I$18))*(1-AI29)*AH23)</f>
         <v>-0.30828004225604755</v>
       </c>
-      <c r="AP16" s="12"/>
+      <c r="AP16" s="90"/>
       <c r="AT16">
         <v>5</v>
       </c>
@@ -38897,23 +38926,23 @@
         <v>2</v>
       </c>
       <c r="CC16">
-        <f t="shared" si="7"/>
+        <f>CE7*IF(FRONTEND!M20&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CD16">
-        <f t="shared" si="7"/>
-        <v>2.7182811963848669E-2</v>
+        <f>CF7*IF(FRONTEND!N20&gt;0,1,0)</f>
+        <v>8.1698616474118937E-3</v>
       </c>
       <c r="CE16">
-        <f t="shared" si="7"/>
+        <f>CG7*IF(FRONTEND!O20&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CF16">
-        <f t="shared" si="7"/>
+        <f>CH7*IF(FRONTEND!P20&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CG16">
-        <f t="shared" si="7"/>
+        <f>CI7*IF(FRONTEND!Q20&gt;0,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -39024,23 +39053,23 @@
         <v>3</v>
       </c>
       <c r="CC17">
-        <f t="shared" si="7"/>
+        <f>CE8*IF(FRONTEND!M21&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CD17">
-        <f t="shared" si="7"/>
+        <f>CF8*IF(FRONTEND!N21&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CE17">
-        <f t="shared" si="7"/>
-        <v>2.9268134939021584E-2</v>
+        <f>CG8*IF(FRONTEND!O21&gt;0,1,0)</f>
+        <v>6.9738192301244672E-2</v>
       </c>
       <c r="CF17">
-        <f t="shared" si="7"/>
+        <f>CH8*IF(FRONTEND!P21&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CG17">
-        <f t="shared" si="7"/>
+        <f>CI8*IF(FRONTEND!Q21&gt;0,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -39125,23 +39154,23 @@
         <v>4</v>
       </c>
       <c r="CC18">
-        <f t="shared" si="7"/>
+        <f>CE9*IF(FRONTEND!M22&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CD18">
-        <f t="shared" si="7"/>
+        <f>CF9*IF(FRONTEND!N22&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CE18">
-        <f t="shared" si="7"/>
+        <f>CG9*IF(FRONTEND!O22&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CF18">
-        <f t="shared" si="7"/>
-        <v>6.3235685173184106E-2</v>
+        <f>CH9*IF(FRONTEND!P22&gt;0,1,0)</f>
+        <v>1.960931690977482E-2</v>
       </c>
       <c r="CG18">
-        <f t="shared" si="7"/>
+        <f>CI9*IF(FRONTEND!Q22&gt;0,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -39248,23 +39277,23 @@
         <v>5</v>
       </c>
       <c r="CC19">
-        <f t="shared" si="7"/>
-        <v>2.3176921447235384E-2</v>
+        <f>CE10*IF(FRONTEND!M23&gt;0,1,0)</f>
+        <v>6.2852458902921595E-3</v>
       </c>
       <c r="CD19">
-        <f t="shared" si="7"/>
+        <f>CF10*IF(FRONTEND!N23&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CE19">
-        <f t="shared" si="7"/>
+        <f>CG10*IF(FRONTEND!O23&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CF19">
-        <f t="shared" si="7"/>
+        <f>CH10*IF(FRONTEND!P23&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CG19">
-        <f t="shared" si="7"/>
+        <f>CI10*IF(FRONTEND!Q23&gt;0,1,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -39351,24 +39380,24 @@
         <v>6</v>
       </c>
       <c r="CC20">
-        <f t="shared" si="7"/>
+        <f>CE11*IF(FRONTEND!M24&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CD20">
-        <f t="shared" si="7"/>
+        <f>CF11*IF(FRONTEND!N24&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CE20">
-        <f t="shared" si="7"/>
+        <f>CG11*IF(FRONTEND!O24&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CF20">
-        <f t="shared" si="7"/>
+        <f>CH11*IF(FRONTEND!P24&gt;0,1,0)</f>
         <v>0</v>
       </c>
       <c r="CG20">
-        <f t="shared" si="7"/>
-        <v>0.11483137641440443</v>
+        <f>CI11*IF(FRONTEND!Q24&gt;0,1,0)</f>
+        <v>5.6593826378490045E-2</v>
       </c>
     </row>
     <row r="21" spans="2:91" x14ac:dyDescent="0.25">
@@ -39433,7 +39462,7 @@
         <v>1</v>
       </c>
       <c r="AH21">
-        <f t="shared" ref="AH21:AH23" si="8">1/(1+EXP(-AH15))</f>
+        <f t="shared" ref="AH21:AH23" si="7">1/(1+EXP(-AH15))</f>
         <v>8.1763287123813901E-3</v>
       </c>
       <c r="AI21" s="10" t="s">
@@ -39458,12 +39487,12 @@
         <v>1</v>
       </c>
       <c r="AU21">
-        <f t="shared" ref="AU21:AV26" si="9">AU12*IF(AU12&gt;0,1,0)</f>
+        <f>AU12*IF(J38&gt;0,1,0)</f>
         <v>0.25825667182225376</v>
       </c>
       <c r="AV21">
-        <f>AV12*IF(AV12&gt;0,1,0)</f>
-        <v>0</v>
+        <f>AV12*IF(K38&gt;0,1,0)</f>
+        <v>-6.7557167413998948E-3</v>
       </c>
     </row>
     <row r="22" spans="2:91" x14ac:dyDescent="0.25">
@@ -39528,7 +39557,7 @@
         <v>2</v>
       </c>
       <c r="AH22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.11878849387110735</v>
       </c>
       <c r="AI22" s="10" t="s">
@@ -39550,11 +39579,11 @@
         <v>2</v>
       </c>
       <c r="AU22">
-        <f t="shared" si="9"/>
-        <v>6.9910769533682669E-3</v>
+        <f t="shared" ref="AU22:AV26" si="8">AU13*IF(J39&gt;0,1,0)</f>
+        <v>0</v>
       </c>
       <c r="AV22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>8.401836545354216E-3</v>
       </c>
       <c r="CB22" s="5"/>
@@ -39588,7 +39617,7 @@
         <v>3</v>
       </c>
       <c r="AH23" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.41308222724329408</v>
       </c>
       <c r="AI23" s="12" t="s">
@@ -39610,12 +39639,12 @@
         <v>3</v>
       </c>
       <c r="AU23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AV23">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>-0.30509535489336559</v>
       </c>
       <c r="CB23" s="9"/>
       <c r="CC23">
@@ -39665,11 +39694,11 @@
         <v>4</v>
       </c>
       <c r="AU24">
-        <f t="shared" si="9"/>
-        <v>6.9910769533682669E-3</v>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="AV24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>8.401836545354216E-3</v>
       </c>
       <c r="CB24" s="9">
@@ -39677,22 +39706,22 @@
       </c>
       <c r="CC24" cm="1">
         <f t="array" ref="CC24">FRONTEND!$M7-$AH$32*SUM($CC$15:$CG$20*CM5:CQ10)</f>
-        <v>-0.49076128598598973</v>
+        <v>-0.5075353218724542</v>
       </c>
       <c r="CD24" cm="1">
         <f t="array" ref="CD24">FRONTEND!$N7-$AH$32*SUM($CC$15:$CG$20*CN5:CR10)</f>
-        <v>0.87888472946934759</v>
+        <v>0.88360634069931299</v>
       </c>
       <c r="CE24" s="10" cm="1">
         <f t="array" ref="CE24">FRONTEND!$O7-$AH$32*SUM($CC$15:$CG$20*CO5:CS10)</f>
-        <v>-0.51614667646572399</v>
+        <v>-0.52332235919545689</v>
       </c>
       <c r="CG24" s="11">
         <v>1</v>
       </c>
       <c r="CH24" s="12">
         <f>FRONTEND!$W7-$AH$32*SUM(CA85:CA90)</f>
-        <v>-2.8424976137579522E-2</v>
+        <v>-1.533587348445664E-2</v>
       </c>
     </row>
     <row r="25" spans="2:91" x14ac:dyDescent="0.25">
@@ -39727,11 +39756,11 @@
         <v>5</v>
       </c>
       <c r="AU25">
-        <f t="shared" si="9"/>
-        <v>6.9910769533682669E-3</v>
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="AV25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>8.401836545354216E-3</v>
       </c>
       <c r="CB25" s="9">
@@ -39739,15 +39768,15 @@
       </c>
       <c r="CC25" cm="1">
         <f t="array" ref="CC25">FRONTEND!$M8-$AH$32*SUM($CC$15:$CG$20*CM6:CQ11)</f>
-        <v>0.10637892721113699</v>
+        <v>0.11037424731012198</v>
       </c>
       <c r="CD25" cm="1">
         <f t="array" ref="CD25">FRONTEND!$N8-$AH$32*SUM($CC$15:$CG$20*CN6:CR11)</f>
-        <v>-0.20251226774650805</v>
+        <v>-0.19728805517355932</v>
       </c>
       <c r="CE25" s="10" cm="1">
         <f t="array" ref="CE25">FRONTEND!$O8-$AH$32*SUM($CC$15:$CG$20*CO6:CS11)</f>
-        <v>-0.73980133341429699</v>
+        <v>-0.74477100152135312</v>
       </c>
     </row>
     <row r="26" spans="2:91" x14ac:dyDescent="0.25">
@@ -39793,11 +39822,11 @@
         <v>6</v>
       </c>
       <c r="AU26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.9910769533682669E-3</v>
       </c>
       <c r="AV26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>8.401836545354216E-3</v>
       </c>
       <c r="CB26" s="9">
@@ -39805,15 +39834,15 @@
       </c>
       <c r="CC26" cm="1">
         <f t="array" ref="CC26">FRONTEND!$M9-$AH$32*SUM($CC$15:$CG$20*CM7:CQ12)</f>
-        <v>0.7336269621824133</v>
+        <v>0.73377805339257285</v>
       </c>
       <c r="CD26" cm="1">
         <f t="array" ref="CD26">FRONTEND!$N9-$AH$32*SUM($CC$15:$CG$20*CN7:CR12)</f>
-        <v>0.79844006285264102</v>
+        <v>0.80076033834187366</v>
       </c>
       <c r="CE26" s="10" cm="1">
         <f t="array" ref="CE26">FRONTEND!$O9-$AH$32*SUM($CC$15:$CG$20*CO7:CS12)</f>
-        <v>-0.96687561778500264</v>
+        <v>-0.96550156550592559</v>
       </c>
     </row>
     <row r="27" spans="2:91" x14ac:dyDescent="0.25">
@@ -39854,15 +39883,15 @@
       </c>
       <c r="CC27" cm="1">
         <f t="array" ref="CC27">FRONTEND!$M10-$AH$32*SUM($CC$15:$CG$20*CM8:CQ13)</f>
-        <v>0.78789165107536008</v>
+        <v>0.78740910203121584</v>
       </c>
       <c r="CD27" cm="1">
         <f t="array" ref="CD27">FRONTEND!$N10-$AH$32*SUM($CC$15:$CG$20*CN8:CR13)</f>
-        <v>0.50784036643041774</v>
+        <v>0.51912214530736966</v>
       </c>
       <c r="CE27" s="10" cm="1">
         <f t="array" ref="CE27">FRONTEND!$O10-$AH$32*SUM($CC$15:$CG$20*CO8:CS13)</f>
-        <v>-0.91515027203019816</v>
+        <v>-0.90949606677468775</v>
       </c>
     </row>
     <row r="28" spans="2:91" x14ac:dyDescent="0.25">
@@ -39895,7 +39924,7 @@
         <v>1</v>
       </c>
       <c r="AO28" s="10">
-        <f t="shared" ref="AO28:AO30" si="10">AK15-$AH$32*$AO14</f>
+        <f t="shared" ref="AO28:AO30" si="9">AK15-$AH$32*$AO14</f>
         <v>-5.6388473878492344E-5</v>
       </c>
       <c r="AT28" s="5"/>
@@ -39916,15 +39945,15 @@
       </c>
       <c r="CC28" s="13" cm="1">
         <f t="array" ref="CC28">FRONTEND!$M11-$AH$32*SUM($CC$15:$CG$20*CM9:CQ14)</f>
-        <v>0.41010905502021844</v>
+        <v>0.41984333238898941</v>
       </c>
       <c r="CD28" s="13" cm="1">
         <f t="array" ref="CD28">FRONTEND!$N11-$AH$32*SUM($CC$15:$CG$20*CN9:CR14)</f>
-        <v>-0.43346274949059699</v>
+        <v>-0.43659544155627172</v>
       </c>
       <c r="CE28" s="12" cm="1">
         <f t="array" ref="CE28">FRONTEND!$O11-$AH$32*SUM($CC$15:$CG$20*CO9:CS14)</f>
-        <v>0.28837879954298523</v>
+        <v>0.28453706813300539</v>
       </c>
     </row>
     <row r="29" spans="2:91" x14ac:dyDescent="0.25">
@@ -39967,7 +39996,7 @@
         <v>2</v>
       </c>
       <c r="AO29" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3.6367458983097158E-2</v>
       </c>
       <c r="AT29" s="9"/>
@@ -40022,7 +40051,7 @@
         <v>3</v>
       </c>
       <c r="AO30" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3.0828004225604756E-2</v>
       </c>
       <c r="AT30" s="9">
@@ -40030,18 +40059,18 @@
       </c>
       <c r="AU30" cm="1">
         <f t="array" ref="AU30:AV31">C42:D43-$AH$32*MMULT(TRANSPOSE(_xlfn.ANCHORARRAY($M$27)),AU21:AV26)</f>
-        <v>-0.59444511713067349</v>
+        <v>-0.58717980936587555</v>
       </c>
       <c r="AV30" s="10">
-        <v>0.2402356840673763</v>
+        <v>0.38257687617002573</v>
       </c>
       <c r="AX30" s="11">
         <f>F47-AH32*SUM(AU21:AU26)</f>
-        <v>-2.8622097963572679E-2</v>
+        <v>-2.6524774877562204E-2</v>
       </c>
       <c r="AY30" s="12">
         <f>G47-AH32*SUM(AV21:AV26)</f>
-        <v>-3.3607346181416865E-3</v>
+        <v>2.7824372545334864E-2</v>
       </c>
     </row>
     <row r="31" spans="2:91" ht="26.25" x14ac:dyDescent="0.4">
@@ -40076,10 +40105,10 @@
         <v>2</v>
       </c>
       <c r="AU31" s="13">
-        <v>0.86289507896358431</v>
+        <v>0.86547207170022755</v>
       </c>
       <c r="AV31" s="12">
-        <v>0.23298900722338101</v>
+        <v>0.29430960962298591</v>
       </c>
       <c r="CC31" s="4" t="s">
         <v>68</v>
@@ -40219,17 +40248,17 @@
       </c>
       <c r="AU35" s="17" cm="1">
         <f t="array" ref="AU35:AV40">AO60:AP65+MMULT(AU21:AV26,TRANSPOSE(C42:D43))</f>
-        <v>-0.1351660283524696</v>
+        <v>-0.13686171325456098</v>
       </c>
       <c r="AV35" s="14">
-        <v>-4.4779173017418711E-2</v>
+        <v>-4.638703360187188E-2</v>
       </c>
       <c r="CB35">
         <v>1</v>
       </c>
       <c r="CC35" s="20">
-        <f t="shared" ref="CC35:CC40" si="11">CB85*IF(CB85&gt;0,1,0)</f>
-        <v>0</v>
+        <f>CB85*IF(FRONTEND!T13&gt;0,1,0)</f>
+        <v>-0.12745318879388584</v>
       </c>
       <c r="CK35">
         <v>0</v>
@@ -40274,17 +40303,17 @@
         <v>2</v>
       </c>
       <c r="AU36" s="17">
-        <v>-1.3957275411733985E-2</v>
+        <v>-1.0643504935837428E-2</v>
       </c>
       <c r="AV36" s="14">
-        <v>1.1265886289934815E-2</v>
+        <v>4.659318569001804E-3</v>
       </c>
       <c r="CB36">
         <v>2</v>
       </c>
       <c r="CC36" s="20">
-        <f t="shared" si="11"/>
-        <v>7.230541092718458E-5</v>
+        <f>CB86*IF(FRONTEND!T14&gt;0,1,0)</f>
+        <v>0</v>
       </c>
       <c r="CK36">
         <v>0</v>
@@ -40329,17 +40358,17 @@
         <v>3</v>
       </c>
       <c r="AU37" s="17">
-        <v>0.47103959618806845</v>
+        <v>0.39446066210983366</v>
       </c>
       <c r="AV37" s="14">
-        <v>2.6596814712075006E-3</v>
+        <v>-6.9953012993413513E-2</v>
       </c>
       <c r="CB37">
         <v>3</v>
       </c>
       <c r="CC37" s="20">
-        <f t="shared" si="11"/>
-        <v>0.41947790500574456</v>
+        <f>CB87*IF(FRONTEND!T15&gt;0,1,0)</f>
+        <v>0.24840555371824607</v>
       </c>
       <c r="CK37">
         <v>0</v>
@@ -40363,11 +40392,11 @@
         <v>1.8017795146138711</v>
       </c>
       <c r="M38">
-        <f t="shared" ref="M38:N43" si="12">MAX(0,J38)</f>
+        <f t="shared" ref="M38:N43" si="10">MAX(0,J38)</f>
         <v>0.80553413018563891</v>
       </c>
       <c r="N38">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1.8017795146138711</v>
       </c>
       <c r="AN38">
@@ -40381,17 +40410,17 @@
         <v>4</v>
       </c>
       <c r="AU38" s="17">
-        <v>-1.3957275411733985E-2</v>
+        <v>-1.0643504935837428E-2</v>
       </c>
       <c r="AV38" s="14">
-        <v>1.1265886289934815E-2</v>
+        <v>4.659318569001804E-3</v>
       </c>
       <c r="CB38">
         <v>4</v>
       </c>
       <c r="CC38" s="20">
-        <f t="shared" si="11"/>
-        <v>7.9996527255094298E-3</v>
+        <f>CB88*IF(FRONTEND!T16&gt;0,1,0)</f>
+        <v>0</v>
       </c>
       <c r="CK38">
         <v>0</v>
@@ -40415,28 +40444,28 @@
         <v>1.5804559738339843</v>
       </c>
       <c r="M39">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N39">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1.5804559738339843</v>
       </c>
       <c r="AT39" s="9">
         <v>5</v>
       </c>
       <c r="AU39" s="17">
-        <v>-1.3957275411733985E-2</v>
+        <v>-1.0643504935837428E-2</v>
       </c>
       <c r="AV39" s="14">
-        <v>1.1265886289934815E-2</v>
+        <v>4.659318569001804E-3</v>
       </c>
       <c r="CB39">
         <v>5</v>
       </c>
       <c r="CC39" s="20">
-        <f t="shared" si="11"/>
-        <v>7.9354770985697563E-4</v>
+        <f>CB89*IF(FRONTEND!T17&gt;0,1,0)</f>
+        <v>0</v>
       </c>
       <c r="CK39">
         <v>0</v>
@@ -40469,11 +40498,11 @@
         <v>1.6094873487311796</v>
       </c>
       <c r="M40">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N40">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1.6094873487311796</v>
       </c>
       <c r="AM40" t="s">
@@ -40498,8 +40527,8 @@
         <v>6</v>
       </c>
       <c r="CC40" s="20">
-        <f t="shared" si="11"/>
-        <v>0</v>
+        <f>CB90*IF(FRONTEND!T18&gt;0,1,0)</f>
+        <v>-2.5888064984428485E-2</v>
       </c>
     </row>
     <row r="41" spans="2:91" x14ac:dyDescent="0.25">
@@ -40527,11 +40556,11 @@
         <v>0.68113377454675761</v>
       </c>
       <c r="M41">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N41">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0.68113377454675761</v>
       </c>
       <c r="AN41">
@@ -40574,18 +40603,18 @@
         <v>1.224162928266969</v>
       </c>
       <c r="M42">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N42">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1.224162928266969</v>
       </c>
       <c r="AM42">
         <v>1</v>
       </c>
       <c r="AN42">
-        <f t="shared" ref="AN42:AN43" si="13">AO35</f>
+        <f t="shared" ref="AN42:AN43" si="11">AO35</f>
         <v>0.48379196209678976</v>
       </c>
       <c r="AO42">
@@ -40596,11 +40625,11 @@
         <v>1</v>
       </c>
       <c r="AQ42">
-        <f t="shared" ref="AQ42:AQ47" si="14">IF(AP42=$AO$42,$AN$42,0)</f>
+        <f t="shared" ref="AQ42:AQ47" si="12">IF(AP42=$AO$42,$AN$42,0)</f>
         <v>0</v>
       </c>
       <c r="AR42">
-        <f t="shared" ref="AR42:AR47" si="15">IF(AP42=$AO$43,$AN$43,0)</f>
+        <f t="shared" ref="AR42:AR47" si="13">IF(AP42=$AO$43,$AN$43,0)</f>
         <v>-0.29149140936065598</v>
       </c>
       <c r="CB42" s="5"/>
@@ -40639,18 +40668,18 @@
         <v>1.1494952943179939</v>
       </c>
       <c r="M43">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1.0058625565885284</v>
       </c>
       <c r="N43">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>1.1494952943179939</v>
       </c>
       <c r="AM43">
         <v>2</v>
       </c>
       <c r="AN43">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>-0.29149140936065598</v>
       </c>
       <c r="AO43">
@@ -40661,11 +40690,11 @@
         <v>2</v>
       </c>
       <c r="AQ43">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AR43">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AU43" s="4" t="s">
@@ -40694,11 +40723,11 @@
         <v>3</v>
       </c>
       <c r="AQ44">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>0.48379196209678976</v>
       </c>
       <c r="AR44">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AU44" s="4" t="s">
@@ -40709,14 +40738,14 @@
       </c>
       <c r="CC44" s="10" cm="1">
         <f t="array" ref="CC44">FRONTEND!T7-$AH32*SUM($CC$35:$CC$40*CL32:CL37)</f>
-        <v>0.13219626037659585</v>
+        <v>0.12849198248317065</v>
       </c>
       <c r="CE44" s="11">
         <v>1</v>
       </c>
       <c r="CF44" s="12">
         <f>FRONTEND!$W7-$AH$32*SUM(CB85:CB90)</f>
-        <v>-2.7361112369157437E-2</v>
+        <v>-7.7019357841025485E-3</v>
       </c>
     </row>
     <row r="45" spans="2:91" x14ac:dyDescent="0.25">
@@ -40755,11 +40784,11 @@
         <v>4</v>
       </c>
       <c r="AQ45">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AR45">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="CB45" s="9">
@@ -40816,11 +40845,11 @@
         <v>5</v>
       </c>
       <c r="AQ46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AR46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AT46" s="5"/>
@@ -40865,7 +40894,7 @@
         <v>-0.60067788546009937</v>
       </c>
       <c r="M47" s="9">
-        <f t="shared" ref="M47:N52" si="16">M27+J47</f>
+        <f t="shared" ref="M47:N52" si="14">M27+J47</f>
         <v>2.5629731695834477</v>
       </c>
       <c r="N47" s="10">
@@ -40899,11 +40928,11 @@
         <v>6</v>
       </c>
       <c r="AQ47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AR47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AT47" s="9"/>
@@ -40935,11 +40964,11 @@
         <v>8.2183710639367177E-2</v>
       </c>
       <c r="M48" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>3.2877566197613501</v>
       </c>
       <c r="N48" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>2.1753394208987591</v>
       </c>
       <c r="V48" s="9">
@@ -40953,10 +40982,10 @@
       </c>
       <c r="AU48" cm="1">
         <f t="array" ref="AU48:AV49">C36:D37-$AH$32*MMULT(TRANSPOSE(J27:K32),_xlfn.ANCHORARRAY(AU35))</f>
-        <v>-0.45570868013860732</v>
+        <v>-0.4597409609061156</v>
       </c>
       <c r="AV48" s="10">
-        <v>-6.7752873783791343E-2</v>
+        <v>-7.3206961697656045E-2</v>
       </c>
     </row>
     <row r="49" spans="9:77" x14ac:dyDescent="0.25">
@@ -40971,11 +41000,11 @@
         <v>8.369334213402134E-2</v>
       </c>
       <c r="M49" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>3.5269277223161581</v>
       </c>
       <c r="N49" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>2.0267546536188736</v>
       </c>
       <c r="V49" s="9">
@@ -40998,10 +41027,10 @@
         <v>2</v>
       </c>
       <c r="AU49" s="13">
-        <v>0.48358176736545966</v>
+        <v>0.49633270879771468</v>
       </c>
       <c r="AV49" s="12">
-        <v>0.78722401416705168</v>
+        <v>0.80509908101130379</v>
       </c>
     </row>
     <row r="50" spans="9:77" x14ac:dyDescent="0.25">
@@ -41016,11 +41045,11 @@
         <v>3.5418956276431393E-2</v>
       </c>
       <c r="M50" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1.5844685427129486</v>
       </c>
       <c r="N50" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.76082704099629062</v>
       </c>
       <c r="V50" s="11">
@@ -41051,22 +41080,22 @@
         <v>6.3656472269882386E-2</v>
       </c>
       <c r="M51" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>3.2612654250001047</v>
       </c>
       <c r="N51" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>0.93120964300591957</v>
       </c>
       <c r="AM51">
         <v>1</v>
       </c>
       <c r="AN51">
-        <f t="shared" ref="AN51:AN56" si="17">$AO$37/$AP$50</f>
+        <f t="shared" ref="AN51:AN56" si="15">$AO$37/$AP$50</f>
         <v>-1.2752365908721336E-2</v>
       </c>
       <c r="AO51">
-        <f t="shared" ref="AO51:AO56" si="18">$AO$38/$AP$50</f>
+        <f t="shared" ref="AO51:AO56" si="16">$AO$38/$AP$50</f>
         <v>2.6596814712075006E-3</v>
       </c>
       <c r="AU51" t="s">
@@ -41088,22 +41117,22 @@
         <v>-0.80727976847477578</v>
       </c>
       <c r="M52" s="11">
+        <f t="shared" si="14"/>
+        <v>0.94246147221659315</v>
+      </c>
+      <c r="N52" s="12">
+        <f t="shared" si="14"/>
+        <v>1.4707668740508018</v>
+      </c>
+      <c r="AM52">
+        <v>2</v>
+      </c>
+      <c r="AN52">
+        <f t="shared" si="15"/>
+        <v>-1.2752365908721336E-2</v>
+      </c>
+      <c r="AO52">
         <f t="shared" si="16"/>
-        <v>0.94246147221659315</v>
-      </c>
-      <c r="N52" s="12">
-        <f t="shared" si="16"/>
-        <v>1.4707668740508018</v>
-      </c>
-      <c r="AM52">
-        <v>2</v>
-      </c>
-      <c r="AN52">
-        <f t="shared" si="17"/>
-        <v>-1.2752365908721336E-2</v>
-      </c>
-      <c r="AO52">
-        <f t="shared" si="18"/>
         <v>2.6596814712075006E-3</v>
       </c>
       <c r="AU52">
@@ -41121,11 +41150,11 @@
         <v>3</v>
       </c>
       <c r="AN53">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>-1.2752365908721336E-2</v>
       </c>
       <c r="AO53">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>2.6596814712075006E-3</v>
       </c>
       <c r="AT53">
@@ -41133,10 +41162,10 @@
       </c>
       <c r="AU53" s="17" cm="1">
         <f t="array" ref="AU53:AV58">MMULT(_xlfn.ANCHORARRAY(AU35),TRANSPOSE(C36:D37))</f>
-        <v>6.7113681204255066E-2</v>
+        <v>6.8026770367589195E-2</v>
       </c>
       <c r="AV53" s="20">
-        <v>-0.10746464747794472</v>
+        <v>-0.10963713735621061</v>
       </c>
     </row>
     <row r="54" spans="9:77" x14ac:dyDescent="0.25">
@@ -41144,21 +41173,21 @@
         <v>4</v>
       </c>
       <c r="AN54">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>-1.2752365908721336E-2</v>
       </c>
       <c r="AO54">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>2.6596814712075006E-3</v>
       </c>
       <c r="AT54">
         <v>2</v>
       </c>
       <c r="AU54" s="17">
-        <v>5.8496682774463417E-3</v>
+        <v>4.728187676894818E-3</v>
       </c>
       <c r="AV54" s="20">
-        <v>1.4243333266026866E-3</v>
+        <v>-2.0120886033637648E-3</v>
       </c>
     </row>
     <row r="55" spans="9:77" x14ac:dyDescent="0.25">
@@ -41166,21 +41195,21 @@
         <v>5</v>
       </c>
       <c r="AN55">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>-1.2752365908721336E-2</v>
       </c>
       <c r="AO55">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>2.6596814712075006E-3</v>
       </c>
       <c r="AT55">
         <v>3</v>
       </c>
       <c r="AU55" s="17">
-        <v>-0.22345362693318654</v>
+        <v>-0.18221754895650902</v>
       </c>
       <c r="AV55" s="20">
-        <v>0.25363097336374008</v>
+        <v>0.15551901932784135</v>
       </c>
       <c r="BT55" t="s">
         <v>219</v>
@@ -41191,21 +41220,21 @@
         <v>6</v>
       </c>
       <c r="AN56">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>-1.2752365908721336E-2</v>
       </c>
       <c r="AO56">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>2.6596814712075006E-3</v>
       </c>
       <c r="AT56">
         <v>4</v>
       </c>
       <c r="AU56" s="17">
-        <v>5.8496682774463417E-3</v>
+        <v>4.728187676894818E-3</v>
       </c>
       <c r="AV56" s="20">
-        <v>1.4243333266026866E-3</v>
+        <v>-2.0120886033637648E-3</v>
       </c>
     </row>
     <row r="57" spans="9:77" x14ac:dyDescent="0.25">
@@ -41214,10 +41243,10 @@
         <v>5</v>
       </c>
       <c r="AU57" s="17">
-        <v>5.8496682774463417E-3</v>
+        <v>4.728187676894818E-3</v>
       </c>
       <c r="AV57" s="20">
-        <v>1.4243333266026866E-3</v>
+        <v>-2.0120886033637648E-3</v>
       </c>
     </row>
     <row r="58" spans="9:77" x14ac:dyDescent="0.25">
@@ -41254,7 +41283,7 @@
         <v>1</v>
       </c>
       <c r="AO60" s="17">
-        <f t="shared" ref="AO60:AP65" si="19">AQ42+AN51</f>
+        <f t="shared" ref="AO60:AP65" si="17">AQ42+AN51</f>
         <v>-1.2752365908721336E-2</v>
       </c>
       <c r="AP60" s="14">
@@ -41273,11 +41302,11 @@
         <v>2</v>
       </c>
       <c r="AO61" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>-1.2752365908721336E-2</v>
       </c>
       <c r="AP61" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>2.6596814712075006E-3</v>
       </c>
       <c r="AU61" s="17" t="s">
@@ -41312,11 +41341,11 @@
         <v>3</v>
       </c>
       <c r="AO62" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0.47103959618806845</v>
       </c>
       <c r="AP62" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>2.6596814712075006E-3</v>
       </c>
       <c r="AT62" t="s">
@@ -41383,11 +41412,11 @@
         <v>4</v>
       </c>
       <c r="AO63" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>-1.2752365908721336E-2</v>
       </c>
       <c r="AP63" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>2.6596814712075006E-3</v>
       </c>
       <c r="AU63">
@@ -41474,11 +41503,11 @@
         <v>5</v>
       </c>
       <c r="AO64" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>-1.2752365908721336E-2</v>
       </c>
       <c r="AP64" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>2.6596814712075006E-3</v>
       </c>
       <c r="AT64">
@@ -41486,98 +41515,98 @@
       </c>
       <c r="AU64" cm="1">
         <f t="array" ref="AU64:AU69">MMULT(TRANSPOSE(W7:AB12),AU53:AU58)</f>
-        <v>-4.9420995551417976E-2</v>
+        <v>-3.6265020161353752E-2</v>
       </c>
       <c r="AW64" cm="1">
         <f t="array" ref="AW64:BB69">MMULT(AU53:AU58,TRANSPOSE(_xlfn.ANCHORARRAY(N7)))</f>
-        <v>-7.2597546700115492E-2</v>
+        <v>-7.3585244468842806E-2</v>
       </c>
       <c r="AX64">
-        <v>-3.4027488596347633E-2</v>
+        <v>-3.4490436396785541E-2</v>
       </c>
       <c r="AY64">
-        <v>-2.9879099239998444E-2</v>
+        <v>-3.0285607737769504E-2</v>
       </c>
       <c r="AZ64">
-        <v>4.0784139211734058E-2</v>
+        <v>4.1339012001930284E-2</v>
       </c>
       <c r="BA64">
-        <v>1.8783896604679683E-2</v>
+        <v>1.9039453625650161E-2</v>
       </c>
       <c r="BB64">
-        <v>-2.7417544450672821E-2</v>
+        <v>-2.7790563219334163E-2</v>
       </c>
       <c r="BD64" s="1" cm="1">
         <f t="array" ref="BD64">SUM($AW64:$BB64*$W7:$AB7*(IF((ROW(AW64)-$BH$62)=(COLUMN(AW64)-$BI$62),1,0)-W7))</f>
-        <v>-2.3267705170795218E-2</v>
+        <v>-2.3584264910417423E-2</v>
       </c>
       <c r="BE64" s="1" cm="1">
         <f t="array" ref="BE64">SUM($AW64:$BB64*$W7:$AB7*(IF((ROW(AX64)-$BH$62)=(COLUMN(AX64)-$BI$62),1,0)-X7))</f>
-        <v>3.9758542296921637E-3</v>
+        <v>4.0299461726013824E-3</v>
       </c>
       <c r="BF64" s="1" cm="1">
         <f t="array" ref="BF64">SUM($AW64:$BB64*$W7:$AB7*(IF((ROW(AY64)-$BH$62)=(COLUMN(AY64)-$BI$62),1,0)-Y7))</f>
-        <v>3.0471885396308987E-3</v>
+        <v>3.0886458816250751E-3</v>
       </c>
       <c r="BG64" s="1" cm="1">
         <f t="array" ref="BG64">SUM($AW64:$BB64*$W7:$AB7*(IF((ROW(AZ64)-$BH$62)=(COLUMN(AZ64)-$BI$62),1,0)-Z7))</f>
-        <v>3.2611909739893082E-3</v>
+        <v>3.3055598431152638E-3</v>
       </c>
       <c r="BH64" s="1" cm="1">
         <f t="array" ref="BH64">SUM($AW64:$BB64*$W7:$AB7*(IF((ROW(BA64)-$BH$62)=(COLUMN(BA64)-$BI$62),1,0)-AA7))</f>
-        <v>1.408011870572755E-3</v>
+        <v>1.4271680300591209E-3</v>
       </c>
       <c r="BI64" s="1" cm="1">
         <f t="array" ref="BI64">SUM($AW64:$BB64*$W7:$AB7*(IF((ROW(BB64)-$BH$62)=(COLUMN(BB64)-$BI$62),1,0)-AB7))</f>
-        <v>1.1575459556910089E-2</v>
+        <v>1.1732944983016578E-2</v>
       </c>
       <c r="BK64" cm="1">
         <f t="array" ref="BK64:BK69">(1/SQRT($G$2))*MMULT(TRANSPOSE($BD$64:$BI$69),_xlfn.ANCHORARRAY($J$7))</f>
-        <v>0.13386534054228735</v>
+        <v>0.11543040005736412</v>
       </c>
       <c r="BL64" s="32" cm="1">
         <f t="array" ref="BL64:BL69">(1/SQRT($G$2))*MMULT($BD$64:$BI$69,_xlfn.ANCHORARRAY(L7))</f>
-        <v>7.9201151479554154E-3</v>
+        <v>8.0278692032269075E-3</v>
       </c>
       <c r="BM64" s="65" cm="1">
         <f t="array" ref="BM64:BM65">C25:C26-$AH$32*MMULT(TRANSPOSE(_xlfn.ANCHORARRAY($C$4)),_xlfn.ANCHORARRAY($BL$64))</f>
-        <v>-0.88662453010026898</v>
+        <v>-0.88261829448631857</v>
       </c>
       <c r="BN64" s="66" cm="1">
         <f t="array" ref="BN64:BN65">E25:E26-$AH$32*MMULT(TRANSPOSE(_xlfn.ANCHORARRAY($C$4)),_xlfn.ANCHORARRAY($BK$64))</f>
-        <v>0.40639223029945731</v>
+        <v>0.40622925073145733</v>
       </c>
       <c r="BO64" cm="1">
         <f t="array" ref="BO64:BO65">G25:G26-$AH$32*MMULT(TRANSPOSE(_xlfn.ANCHORARRAY($C$4)),_xlfn.ANCHORARRAY($AU$64))</f>
-        <v>-2.0330706705037775E-2</v>
+        <v>-2.9435692144075255E-2</v>
       </c>
       <c r="BQ64" cm="1">
         <f t="array" ref="BQ64:BR69">MMULT(_xlfn.ANCHORARRAY(BL64),TRANSPOSE(C25:C26))</f>
-        <v>-6.827139257537568E-3</v>
+        <v>-6.9200232531815946E-3</v>
       </c>
       <c r="BR64">
-        <v>6.9697013302007652E-3</v>
+        <v>7.0645248988396789E-3</v>
       </c>
       <c r="BS64" s="34" cm="1">
         <f t="array" ref="BS64:BT69">MMULT(_xlfn.ANCHORARRAY(BK64),TRANSPOSE(E25:E26))</f>
-        <v>5.4750924281795524E-2</v>
+        <v>4.721103362346192E-2</v>
       </c>
       <c r="BT64">
-        <v>-9.7453967914785194E-2</v>
+        <v>-8.4033331241761072E-2</v>
       </c>
       <c r="BU64" s="34" cm="1">
         <f t="array" ref="BU64:BV69">MMULT(_xlfn.ANCHORARRAY(AU64),TRANSPOSE(G25:G26))</f>
-        <v>2.5698917686737348E-3</v>
+        <v>1.885781048390395E-3</v>
       </c>
       <c r="BV64">
-        <v>3.2024805117318852E-2</v>
+        <v>2.3499733064557233E-2</v>
       </c>
       <c r="BX64" cm="1">
         <f t="array" ref="BX64:BY69">_xlfn.ANCHORARRAY(BQ64)+_xlfn.ANCHORARRAY(BS64)+_xlfn.ANCHORARRAY(BU64)</f>
-        <v>5.0493676792931687E-2</v>
+        <v>4.2176791418670714E-2</v>
       </c>
       <c r="BY64">
-        <v>-5.8459461467265578E-2</v>
+        <v>-5.3469073278364157E-2</v>
       </c>
     </row>
     <row r="65" spans="40:77" x14ac:dyDescent="0.25">
@@ -41585,99 +41614,99 @@
         <v>6</v>
       </c>
       <c r="AO65" s="18">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>-1.2752365908721336E-2</v>
       </c>
       <c r="AP65" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>2.6596814712075006E-3</v>
       </c>
       <c r="AT65">
         <v>2</v>
       </c>
       <c r="AU65">
-        <v>-5.1138415448969349E-3</v>
+        <v>-2.3955305147244483E-3</v>
       </c>
       <c r="AW65">
-        <v>-6.3276452480626319E-3</v>
+        <v>-5.1145283572750803E-3</v>
       </c>
       <c r="AX65">
-        <v>-2.9658560971708701E-3</v>
+        <v>-2.3972511918587676E-3</v>
       </c>
       <c r="AY65">
-        <v>-2.6042800193145808E-3</v>
+        <v>-2.1049953793075664E-3</v>
       </c>
       <c r="AZ65">
-        <v>3.5547697740458675E-3</v>
+        <v>2.8732601307743166E-3</v>
       </c>
       <c r="BA65">
-        <v>1.6372155739873249E-3</v>
+        <v>1.3233335864861191E-3</v>
       </c>
       <c r="BB65">
-        <v>-2.3897294432481124E-3</v>
+        <v>-1.9315777867682832E-3</v>
       </c>
       <c r="BD65" s="1" cm="1">
         <f t="array" ref="BD65">SUM($AW65:$BB65*$W8:$AB8*(IF((ROW(AW65)-$BH$62)=(COLUMN(AW65)-$BI$62),1,0)-W8))</f>
-        <v>1.0918541667667837E-3</v>
+        <v>8.8252720862432195E-4</v>
       </c>
       <c r="BE65" s="1" cm="1">
         <f t="array" ref="BE65">SUM($AW65:$BB65*$W8:$AB8*(IF((ROW(AX65)-$BH$62)=(COLUMN(AX65)-$BI$62),1,0)-X8))</f>
-        <v>-3.032423385238786E-3</v>
+        <v>-2.4510564020346218E-3</v>
       </c>
       <c r="BF65" s="1" cm="1">
         <f t="array" ref="BF65">SUM($AW65:$BB65*$W8:$AB8*(IF((ROW(AY65)-$BH$62)=(COLUMN(AY65)-$BI$62),1,0)-Y8))</f>
-        <v>1.8473364685021951E-4</v>
+        <v>1.4931707425405526E-4</v>
       </c>
       <c r="BG65" s="1" cm="1">
         <f t="array" ref="BG65">SUM($AW65:$BB65*$W8:$AB8*(IF((ROW(AZ65)-$BH$62)=(COLUMN(AZ65)-$BI$62),1,0)-Z8))</f>
-        <v>2.054613475461813E-4</v>
+        <v>1.6607092325073621E-4</v>
       </c>
       <c r="BH65" s="1" cm="1">
         <f t="array" ref="BH65">SUM($AW65:$BB65*$W8:$AB8*(IF((ROW(BA65)-$BH$62)=(COLUMN(BA65)-$BI$62),1,0)-AA8))</f>
-        <v>5.5107686553899899E-5</v>
+        <v>4.4542608590461536E-5</v>
       </c>
       <c r="BI65" s="1" cm="1">
         <f t="array" ref="BI65">SUM($AW65:$BB65*$W8:$AB8*(IF((ROW(BB65)-$BH$62)=(COLUMN(BB65)-$BI$62),1,0)-AB8))</f>
-        <v>1.4952665375217019E-3</v>
+        <v>1.2085985873150468E-3</v>
       </c>
       <c r="BK65">
-        <v>2.2561952965966296E-2</v>
+        <v>1.7263353395707937E-2</v>
       </c>
       <c r="BL65" s="32">
-        <v>-1.7681455960956707E-3</v>
+        <v>-1.4291621031996332E-3</v>
       </c>
       <c r="BM65" s="65">
-        <v>0.87109753457267114</v>
+        <v>0.87266763411009285</v>
       </c>
       <c r="BN65" s="66">
-        <v>-0.71070774816698201</v>
+        <v>-0.71402065944868864</v>
       </c>
       <c r="BO65">
-        <v>-0.64379272205181581</v>
+        <v>-0.64498408192627465</v>
       </c>
       <c r="BQ65">
-        <v>1.5241415038344682E-3</v>
+        <v>1.2319377329580838E-3</v>
       </c>
       <c r="BR65">
-        <v>-1.5559681245641901E-3</v>
+        <v>-1.2576626508156773E-3</v>
       </c>
       <c r="BS65" s="34">
-        <v>9.227838763080214E-3</v>
+        <v>7.0607115388445461E-3</v>
       </c>
       <c r="BT65">
-        <v>-1.6425101759223463E-2</v>
+        <v>-1.2567721272075378E-2</v>
       </c>
       <c r="BU65" s="34">
-        <v>2.6591976033464061E-4</v>
+        <v>1.245675867656713E-4</v>
       </c>
       <c r="BV65">
-        <v>3.3137693210932139E-3</v>
+        <v>1.5523037735414426E-3</v>
       </c>
       <c r="BX65">
-        <v>1.1017900027249323E-2</v>
+        <v>8.4172168585683015E-3</v>
       </c>
       <c r="BY65">
-        <v>-1.4667300562694439E-2</v>
+        <v>-1.2273080149349613E-2</v>
       </c>
     </row>
     <row r="66" spans="40:77" x14ac:dyDescent="0.25">
@@ -41685,81 +41714,81 @@
         <v>3</v>
       </c>
       <c r="AU66">
-        <v>-1.5665498201556862E-3</v>
+        <v>1.0841606025645484E-4</v>
       </c>
       <c r="AW66">
-        <v>0.24171204477997987</v>
+        <v>0.19710656281378353</v>
       </c>
       <c r="AX66">
-        <v>0.11329382632343897</v>
+        <v>9.2386611163550902E-2</v>
       </c>
       <c r="AY66">
-        <v>9.9481848929648162E-2</v>
+        <v>8.1123492719329809E-2</v>
       </c>
       <c r="AZ66">
-        <v>-0.13578995615624451</v>
+        <v>-0.11073131066743007</v>
       </c>
       <c r="BA66">
-        <v>-6.254059900960296E-2</v>
+        <v>-5.0999372076467445E-2</v>
       </c>
       <c r="BB66">
-        <v>9.1286152676665788E-2</v>
+        <v>7.4440228259912353E-2</v>
       </c>
       <c r="BD66" s="1" cm="1">
         <f t="array" ref="BD66">SUM($AW66:$BB66*$W9:$AB9*(IF((ROW(AW66)-$BH$62)=(COLUMN(AW66)-$BI$62),1,0)-W9))</f>
-        <v>-4.4550489873477615E-2</v>
+        <v>-3.6329153305639308E-2</v>
       </c>
       <c r="BE66" s="1" cm="1">
         <f t="array" ref="BE66">SUM($AW66:$BB66*$W9:$AB9*(IF((ROW(AX66)-$BH$62)=(COLUMN(AX66)-$BI$62),1,0)-X9))</f>
-        <v>-9.2192514374096913E-3</v>
+        <v>-7.5179330190100948E-3</v>
       </c>
       <c r="BF66" s="1" cm="1">
         <f t="array" ref="BF66">SUM($AW66:$BB66*$W9:$AB9*(IF((ROW(AY66)-$BH$62)=(COLUMN(AY66)-$BI$62),1,0)-Y9))</f>
-        <v>0.12573159445743323</v>
+        <v>0.10252911659060966</v>
       </c>
       <c r="BG66" s="1" cm="1">
         <f t="array" ref="BG66">SUM($AW66:$BB66*$W9:$AB9*(IF((ROW(AZ66)-$BH$62)=(COLUMN(AZ66)-$BI$62),1,0)-Z9))</f>
-        <v>-6.4344288054314063E-3</v>
+        <v>-5.2470208783473495E-3</v>
       </c>
       <c r="BH66" s="1" cm="1">
         <f t="array" ref="BH66">SUM($AW66:$BB66*$W9:$AB9*(IF((ROW(BA66)-$BH$62)=(COLUMN(BA66)-$BI$62),1,0)-AA9))</f>
-        <v>-1.4010843090642437E-3</v>
+        <v>-1.142528551373421E-3</v>
       </c>
       <c r="BI66" s="1" cm="1">
         <f t="array" ref="BI66">SUM($AW66:$BB66*$W9:$AB9*(IF((ROW(BB66)-$BH$62)=(COLUMN(BB66)-$BI$62),1,0)-AB9))</f>
-        <v>-6.4126340032050255E-2</v>
+        <v>-5.2292480836239469E-2</v>
       </c>
       <c r="BK66">
-        <v>-0.31489887428458468</v>
+        <v>-0.25762402758616465</v>
       </c>
       <c r="BL66" s="32">
-        <v>0.10166702975054996</v>
+        <v>8.2905420802916283E-2</v>
       </c>
       <c r="BM66" s="65"/>
       <c r="BN66" s="66"/>
       <c r="BQ66">
-        <v>-8.7636979644974064E-2</v>
+        <v>-7.1464472732113829E-2</v>
       </c>
       <c r="BR66">
-        <v>8.9466986180483973E-2</v>
+        <v>7.2956770306566332E-2</v>
       </c>
       <c r="BS66" s="34">
-        <v>-0.12879363958239512</v>
+        <v>-0.10536822728274134</v>
       </c>
       <c r="BT66">
-        <v>0.22924638047917764</v>
+        <v>0.18755029208272786</v>
       </c>
       <c r="BU66" s="34">
-        <v>8.1460590648095682E-5</v>
+        <v>-5.6376351333356515E-6</v>
       </c>
       <c r="BV66">
-        <v>1.0151242834608846E-3</v>
+        <v>-7.0253607046182737E-5</v>
       </c>
       <c r="BX66">
-        <v>-0.21634915863672108</v>
+        <v>-0.17683833764998852</v>
       </c>
       <c r="BY66">
-        <v>0.3197284909431225</v>
+        <v>0.26043680878224806</v>
       </c>
     </row>
     <row r="67" spans="40:77" x14ac:dyDescent="0.25">
@@ -41767,81 +41796,81 @@
         <v>4</v>
       </c>
       <c r="AU67">
-        <v>-2.2735483143796471E-3</v>
+        <v>-3.7825042605404687E-4</v>
       </c>
       <c r="AW67">
-        <v>-6.3276452480626319E-3</v>
+        <v>-5.1145283572750803E-3</v>
       </c>
       <c r="AX67">
-        <v>-2.9658560971708701E-3</v>
+        <v>-2.3972511918587676E-3</v>
       </c>
       <c r="AY67">
-        <v>-2.6042800193145808E-3</v>
+        <v>-2.1049953793075664E-3</v>
       </c>
       <c r="AZ67">
-        <v>3.5547697740458675E-3</v>
+        <v>2.8732601307743166E-3</v>
       </c>
       <c r="BA67">
-        <v>1.6372155739873249E-3</v>
+        <v>1.3233335864861191E-3</v>
       </c>
       <c r="BB67">
-        <v>-2.3897294432481124E-3</v>
+        <v>-1.9315777867682832E-3</v>
       </c>
       <c r="BD67" s="1" cm="1">
         <f t="array" ref="BD67">SUM($AW67:$BB67*$W10:$AB10*(IF((ROW(AW67)-$BH$62)=(COLUMN(AW67)-$BI$62),1,0)-W10))</f>
-        <v>8.5668608249727914E-4</v>
+        <v>6.9244483381187551E-4</v>
       </c>
       <c r="BE67" s="1" cm="1">
         <f t="array" ref="BE67">SUM($AW67:$BB67*$W10:$AB10*(IF((ROW(AX67)-$BH$62)=(COLUMN(AX67)-$BI$62),1,0)-X10))</f>
-        <v>3.4269757442756496E-4</v>
+        <v>2.7699663834912568E-4</v>
       </c>
       <c r="BF67" s="1" cm="1">
         <f t="array" ref="BF67">SUM($AW67:$BB67*$W10:$AB10*(IF((ROW(AY67)-$BH$62)=(COLUMN(AY67)-$BI$62),1,0)-Y10))</f>
-        <v>2.5879537186051182E-4</v>
+        <v>2.0917991072862303E-4</v>
       </c>
       <c r="BG67" s="1" cm="1">
         <f t="array" ref="BG67">SUM($AW67:$BB67*$W10:$AB10*(IF((ROW(AZ67)-$BH$62)=(COLUMN(AZ67)-$BI$62),1,0)-Z10))</f>
-        <v>-2.6315573457362817E-3</v>
+        <v>-2.1270431797175454E-3</v>
       </c>
       <c r="BH67" s="1" cm="1">
         <f t="array" ref="BH67">SUM($AW67:$BB67*$W10:$AB10*(IF((ROW(BA67)-$BH$62)=(COLUMN(BA67)-$BI$62),1,0)-AA10))</f>
-        <v>1.1455698841532792E-4</v>
+        <v>9.2594471214013936E-5</v>
       </c>
       <c r="BI67" s="1" cm="1">
         <f t="array" ref="BI67">SUM($AW67:$BB67*$W10:$AB10*(IF((ROW(BB67)-$BH$62)=(COLUMN(BB67)-$BI$62),1,0)-AB10))</f>
-        <v>1.058821328535598E-3</v>
+        <v>8.5582732561390712E-4</v>
       </c>
       <c r="BK67">
-        <v>1.4254289525436564E-2</v>
+        <v>1.0700138019456846E-2</v>
       </c>
       <c r="BL67" s="32">
-        <v>-1.6282368577459933E-3</v>
+        <v>-1.316076242398715E-3</v>
       </c>
       <c r="BM67" s="65"/>
       <c r="BN67" s="66"/>
       <c r="BQ67">
-        <v>1.4035401713770462E-3</v>
+        <v>1.1344577209476923E-3</v>
       </c>
       <c r="BR67">
-        <v>-1.4328484348164741E-3</v>
+        <v>-1.1581470933108692E-3</v>
       </c>
       <c r="BS67" s="34">
-        <v>5.8300044159035544E-3</v>
+        <v>4.3763564499578493E-3</v>
       </c>
       <c r="BT67">
-        <v>-1.0377122774517819E-2</v>
+        <v>-7.7897004781645835E-3</v>
       </c>
       <c r="BU67" s="34">
-        <v>1.1822451234774165E-4</v>
+        <v>1.9669022154810437E-5</v>
       </c>
       <c r="BV67">
-        <v>1.4732593077180114E-3</v>
+        <v>2.4510627608302236E-4</v>
       </c>
       <c r="BX67">
-        <v>7.3517690996283422E-3</v>
+        <v>5.5304831930603517E-3</v>
       </c>
       <c r="BY67">
-        <v>-1.033671190161628E-2</v>
+        <v>-8.7027412953924292E-3</v>
       </c>
     </row>
     <row r="68" spans="40:77" x14ac:dyDescent="0.25">
@@ -41849,81 +41878,81 @@
         <v>5</v>
       </c>
       <c r="AU68">
-        <v>1.5092455554243836E-3</v>
+        <v>1.9192532403149666E-3</v>
       </c>
       <c r="AW68">
-        <v>-6.3276452480626319E-3</v>
+        <v>-5.1145283572750803E-3</v>
       </c>
       <c r="AX68">
-        <v>-2.9658560971708701E-3</v>
+        <v>-2.3972511918587676E-3</v>
       </c>
       <c r="AY68">
-        <v>-2.6042800193145808E-3</v>
+        <v>-2.1049953793075664E-3</v>
       </c>
       <c r="AZ68">
-        <v>3.5547697740458675E-3</v>
+        <v>2.8732601307743166E-3</v>
       </c>
       <c r="BA68">
-        <v>1.6372155739873249E-3</v>
+        <v>1.3233335864861191E-3</v>
       </c>
       <c r="BB68">
-        <v>-2.3897294432481124E-3</v>
+        <v>-1.9315777867682832E-3</v>
       </c>
       <c r="BD68" s="1" cm="1">
         <f t="array" ref="BD68">SUM($AW68:$BB68*$W11:$AB11*(IF((ROW(AW68)-$BH$62)=(COLUMN(AW68)-$BI$62),1,0)-W11))</f>
-        <v>1.2294574365284568E-3</v>
+        <v>9.9374959825896964E-4</v>
       </c>
       <c r="BE68" s="1" cm="1">
         <f t="array" ref="BE68">SUM($AW68:$BB68*$W11:$AB11*(IF((ROW(AX68)-$BH$62)=(COLUMN(AX68)-$BI$62),1,0)-X11))</f>
-        <v>1.8536699993838913E-4</v>
+        <v>1.4982900281556923E-4</v>
       </c>
       <c r="BF68" s="1" cm="1">
         <f t="array" ref="BF68">SUM($AW68:$BB68*$W11:$AB11*(IF((ROW(AY68)-$BH$62)=(COLUMN(AY68)-$BI$62),1,0)-Y11))</f>
-        <v>1.0380008270756347E-4</v>
+        <v>8.3899846733328978E-5</v>
       </c>
       <c r="BG68" s="1" cm="1">
         <f t="array" ref="BG68">SUM($AW68:$BB68*$W11:$AB11*(IF((ROW(AZ68)-$BH$62)=(COLUMN(AZ68)-$BI$62),1,0)-Z11))</f>
-        <v>1.2035148423482171E-4</v>
+        <v>9.7278063928695087E-5</v>
       </c>
       <c r="BH68" s="1" cm="1">
         <f t="array" ref="BH68">SUM($AW68:$BB68*$W11:$AB11*(IF((ROW(BA68)-$BH$62)=(COLUMN(BA68)-$BI$62),1,0)-AA11))</f>
-        <v>-3.5430966603222621E-3</v>
+        <v>-2.8638249508904012E-3</v>
       </c>
       <c r="BI68" s="1" cm="1">
         <f t="array" ref="BI68">SUM($AW68:$BB68*$W11:$AB11*(IF((ROW(BB68)-$BH$62)=(COLUMN(BB68)-$BI$62),1,0)-AB11))</f>
-        <v>1.9041206569130314E-3</v>
+        <v>1.5390684391538381E-3</v>
       </c>
       <c r="BK68">
-        <v>1.1630724139600026E-2</v>
+        <v>9.0134785069505233E-3</v>
       </c>
       <c r="BL68" s="32">
-        <v>-4.9600403296797642E-3</v>
+        <v>-4.0091164919750103E-3</v>
       </c>
       <c r="BM68" s="65"/>
       <c r="BN68" s="66"/>
       <c r="BQ68">
-        <v>4.2755547641839566E-3</v>
+        <v>3.4558584160824589E-3</v>
       </c>
       <c r="BR68">
-        <v>-4.3648354901181926E-3</v>
+        <v>-3.5280225129380089E-3</v>
       </c>
       <c r="BS68" s="34">
-        <v>4.7569661730964101E-3</v>
+        <v>3.6865127093427636E-3</v>
       </c>
       <c r="BT68">
-        <v>-8.4671671736288191E-3</v>
+        <v>-6.5618123530599808E-3</v>
       </c>
       <c r="BU68" s="34">
-        <v>-7.8480768882067939E-5</v>
+        <v>-9.9801168496378256E-5</v>
       </c>
       <c r="BV68">
-        <v>-9.7799111991500056E-4</v>
+        <v>-1.2436760997240983E-3</v>
       </c>
       <c r="BX68">
-        <v>8.9540401683982987E-3</v>
+        <v>7.0425699569288437E-3</v>
       </c>
       <c r="BY68">
-        <v>-1.3809993783662012E-2</v>
+        <v>-1.1333510965722087E-2</v>
       </c>
     </row>
     <row r="69" spans="40:77" x14ac:dyDescent="0.25">
@@ -41931,7 +41960,7 @@
         <v>6</v>
       </c>
       <c r="AU69">
-        <v>-7.6075582943720257E-2</v>
+        <v>-5.7145415479228204E-2</v>
       </c>
       <c r="AW69">
         <v>-6.3276452480626319E-3</v>
@@ -41976,7 +42005,7 @@
         <v>-1.566153918871768E-3</v>
       </c>
       <c r="BK69">
-        <v>0.13258656711129438</v>
+        <v>0.10521665760668522</v>
       </c>
       <c r="BL69" s="32">
         <v>1.2300873336375218E-3</v>
@@ -41990,22 +42019,22 @@
         <v>1.0824768536010193E-3</v>
       </c>
       <c r="BS69" s="34">
-        <v>5.4227905948519395E-2</v>
+        <v>4.3033612961134254E-2</v>
       </c>
       <c r="BT69">
-        <v>-9.6523020857022301E-2</v>
+        <v>-7.6597726737666835E-2</v>
       </c>
       <c r="BU69" s="34">
-        <v>3.9559303130734533E-3</v>
+        <v>2.9715616049198665E-3</v>
       </c>
       <c r="BV69">
-        <v>4.9296977747530731E-2</v>
+        <v>3.7030229230539877E-2</v>
       </c>
       <c r="BX69">
-        <v>5.7123500979997306E-2</v>
+        <v>4.4944839284458582E-2</v>
       </c>
       <c r="BY69">
-        <v>-4.6143566255890549E-2</v>
+        <v>-3.8485020653525936E-2</v>
       </c>
     </row>
     <row r="70" spans="40:77" x14ac:dyDescent="0.25">
@@ -42202,98 +42231,98 @@
       </c>
       <c r="AU75" cm="1">
         <f t="array" ref="AU75:AU80">MMULT(TRANSPOSE(W17:AB22),AV53:AV58)</f>
-        <v>2.0165383605654473E-2</v>
+        <v>4.7864083402975556E-3</v>
       </c>
       <c r="AW75" cm="1">
         <f t="array" ref="AW75:BB80">MMULT(AV53:AV58,TRANSPOSE(_xlfn.ANCHORARRAY(N17)))</f>
-        <v>-0.37434515731521262</v>
+        <v>-0.38191286524829882</v>
       </c>
       <c r="AX75">
-        <v>-0.33167127860338813</v>
+        <v>-0.33837629753368564</v>
       </c>
       <c r="AY75">
-        <v>-0.35371464965222255</v>
+        <v>-0.36086529420555369</v>
       </c>
       <c r="AZ75">
-        <v>-1.9785008349599693E-2</v>
+        <v>-2.018497923667428E-2</v>
       </c>
       <c r="BA75">
-        <v>-0.25004441466286259</v>
+        <v>-0.25509927663580556</v>
       </c>
       <c r="BB75">
-        <v>-0.13657953598310546</v>
+        <v>-0.13934060826561998</v>
       </c>
       <c r="BD75" s="1" cm="1">
         <f t="array" ref="BD75">SUM($AW75:$BB75*$W17:$AB17*(IF((ROW(AW75)-$BH$73)=(COLUMN(AW75)-$BI$73),1,0)-W17))</f>
-        <v>-0.18141773394785637</v>
+        <v>-0.18508524880031557</v>
       </c>
       <c r="BE75" s="1" cm="1">
         <f t="array" ref="BE75">SUM($AW75:$BB75*$W17:$AB17*(IF((ROW(AX75)-$BH$73)=(COLUMN(AX75)-$BI$73),1,0)-X17))</f>
-        <v>2.8747647108416218E-2</v>
+        <v>2.9328805413335161E-2</v>
       </c>
       <c r="BF75" s="1" cm="1">
         <f t="array" ref="BF75">SUM($AW75:$BB75*$W17:$AB17*(IF((ROW(AY75)-$BH$73)=(COLUMN(AY75)-$BI$73),1,0)-Y17))</f>
-        <v>2.6321277756146046E-2</v>
+        <v>2.6853384926738947E-2</v>
       </c>
       <c r="BG75" s="1" cm="1">
         <f t="array" ref="BG75">SUM($AW75:$BB75*$W17:$AB17*(IF((ROW(AZ75)-$BH$73)=(COLUMN(AZ75)-$BI$73),1,0)-Z17))</f>
-        <v>4.8952411605231429E-2</v>
+        <v>4.9942026527207486E-2</v>
       </c>
       <c r="BH75" s="1" cm="1">
         <f t="array" ref="BH75">SUM($AW75:$BB75*$W17:$AB17*(IF((ROW(BA75)-$BH$73)=(COLUMN(BA75)-$BI$73),1,0)-AA17))</f>
-        <v>2.7655196643718072E-2</v>
+        <v>2.8214270126951348E-2</v>
       </c>
       <c r="BI75" s="1" cm="1">
         <f t="array" ref="BI75">SUM($AW75:$BB75*$W17:$AB17*(IF((ROW(BB75)-$BH$73)=(COLUMN(BB75)-$BI$73),1,0)-AB17))</f>
-        <v>4.974120083434462E-2</v>
+        <v>5.0746761806082626E-2</v>
       </c>
       <c r="BK75" cm="1">
         <f t="array" ref="BK75:BK80">(1/SQRT($G$2))*MMULT(TRANSPOSE($BD$75:$BI$80),_xlfn.ANCHORARRAY(J17))</f>
-        <v>0.30639857133503351</v>
+        <v>0.26912594218631281</v>
       </c>
       <c r="BL75" s="32" cm="1">
         <f t="array" ref="BL75:BL80">(1/SQRT($G$2))*MMULT($BD$75:$BI$80,_xlfn.ANCHORARRAY(L17))</f>
-        <v>-3.1344669579470345E-2</v>
+        <v>-3.1978328917653773E-2</v>
       </c>
       <c r="BM75" s="65" cm="1">
         <f t="array" ref="BM75:BM76">C31:C32-$AH$32*MMULT(TRANSPOSE(_xlfn.ANCHORARRAY($C$4)),_xlfn.ANCHORARRAY(BL75))</f>
-        <v>-0.51350648232209584</v>
+        <v>-0.49860433345276023</v>
       </c>
       <c r="BN75" s="66" cm="1">
         <f t="array" ref="BN75:BN76">E31:E32-$AH$32*MMULT(TRANSPOSE(_xlfn.ANCHORARRAY($C$4)),_xlfn.ANCHORARRAY(BK75))</f>
-        <v>0.25392389188182823</v>
+        <v>0.24279971513095466</v>
       </c>
       <c r="BO75" cm="1">
         <f t="array" ref="BO75:BO76">G31:G32-$AH$32*MMULT(TRANSPOSE(_xlfn.ANCHORARRAY($C$4)),_xlfn.ANCHORARRAY(AU75))</f>
-        <v>0.91487763144325351</v>
+        <v>0.93735181542325319</v>
       </c>
       <c r="BQ75" cm="1">
         <f t="array" ref="BQ75:BR80">MMULT(_xlfn.ANCHORARRAY(BL75),TRANSPOSE(C31:C32))</f>
-        <v>1.5264854085202059E-2</v>
+        <v>1.5573446182897388E-2</v>
       </c>
       <c r="BR75">
-        <v>-7.4600313599139422E-3</v>
+        <v>-7.6108422824015974E-3</v>
       </c>
       <c r="BS75" s="34" cm="1">
         <f t="array" ref="BS75:BT80">MMULT(_xlfn.ANCHORARRAY(BK75),TRANSPOSE(E31:E32))</f>
-        <v>7.6906041405093412E-2</v>
+        <v>6.7550611488764511E-2</v>
       </c>
       <c r="BT75">
-        <v>-2.5124682849472748E-2</v>
+        <v>-2.206832725927765E-2</v>
       </c>
       <c r="BU75" s="34" cm="1">
         <f t="array" ref="BU75:BV80">MMULT(_xlfn.ANCHORARRAY(AU75),TRANSPOSE(G31:G32))</f>
-        <v>1.9056287507343474E-2</v>
+        <v>4.5231558815811901E-3</v>
       </c>
       <c r="BV75">
-        <v>8.7719418684596949E-3</v>
+        <v>2.0820876280294369E-3</v>
       </c>
       <c r="BX75" cm="1">
         <f t="array" ref="BX75:BY80">_xlfn.ANCHORARRAY(BQ75)+_xlfn.ANCHORARRAY(BS75)+_xlfn.ANCHORARRAY(BU75)</f>
-        <v>0.11122718299763895</v>
+        <v>8.7647213553243078E-2</v>
       </c>
       <c r="BY75">
-        <v>-2.3812772340926994E-2</v>
+        <v>-2.7597081913649811E-2</v>
       </c>
     </row>
     <row r="76" spans="40:77" x14ac:dyDescent="0.25">
@@ -42301,88 +42330,88 @@
         <v>2</v>
       </c>
       <c r="AU76">
-        <v>1.7835795688977338E-2</v>
+        <v>3.9349063935451021E-3</v>
       </c>
       <c r="AW76">
-        <v>4.9615598778734319E-3</v>
+        <v>-7.0089619464200033E-3</v>
       </c>
       <c r="AX76">
-        <v>4.3959615248231705E-3</v>
+        <v>-6.2099677931566092E-3</v>
       </c>
       <c r="AY76">
-        <v>4.6881237265553009E-3</v>
+        <v>-6.6226915744929896E-3</v>
       </c>
       <c r="AZ76">
-        <v>2.6222992789541149E-4</v>
+        <v>-3.7043986791895098E-4</v>
       </c>
       <c r="BA76">
-        <v>3.3140814332291895E-3</v>
+        <v>-4.6816467450950718E-3</v>
       </c>
       <c r="BB76">
-        <v>1.8102212159826127E-3</v>
+        <v>-2.5572142490926401E-3</v>
       </c>
       <c r="BD76" s="1" cm="1">
         <f t="array" ref="BD76">SUM($AW76:$BB76*$W18:$AB18*(IF((ROW(AW76)-$BH$73)=(COLUMN(AW76)-$BI$73),1,0)-W18))</f>
-        <v>-3.882728659443336E-4</v>
+        <v>5.4849478978729585E-4</v>
       </c>
       <c r="BE76" s="1" cm="1">
         <f t="array" ref="BE76">SUM($AW76:$BB76*$W18:$AB18*(IF((ROW(AX76)-$BH$73)=(COLUMN(AX76)-$BI$73),1,0)-X18))</f>
-        <v>2.3835088633585139E-3</v>
+        <v>-3.3670707062785511E-3</v>
       </c>
       <c r="BF76" s="1" cm="1">
         <f t="array" ref="BF76">SUM($AW76:$BB76*$W18:$AB18*(IF((ROW(AY76)-$BH$73)=(COLUMN(AY76)-$BI$73),1,0)-Y18))</f>
-        <v>-3.1875256045856817E-4</v>
+        <v>4.502867286841273E-4</v>
       </c>
       <c r="BG76" s="1" cm="1">
         <f t="array" ref="BG76">SUM($AW76:$BB76*$W18:$AB18*(IF((ROW(AZ76)-$BH$73)=(COLUMN(AZ76)-$BI$73),1,0)-Z18))</f>
-        <v>-6.6297611049320933E-4</v>
+        <v>9.3655512464037728E-4</v>
       </c>
       <c r="BH76" s="1" cm="1">
         <f t="array" ref="BH76">SUM($AW76:$BB76*$W18:$AB18*(IF((ROW(BA76)-$BH$73)=(COLUMN(BA76)-$BI$73),1,0)-AA18))</f>
-        <v>-3.379043956034102E-4</v>
+        <v>4.7734162412798535E-4</v>
       </c>
       <c r="BI76" s="1" cm="1">
         <f t="array" ref="BI76">SUM($AW76:$BB76*$W18:$AB18*(IF((ROW(BB76)-$BH$73)=(COLUMN(BB76)-$BI$73),1,0)-AB18))</f>
-        <v>-6.7560293085899251E-4</v>
+        <v>9.5439243903876539E-4</v>
       </c>
       <c r="BK76">
-        <v>5.4075395310013652E-2</v>
+        <v>2.4884492406375167E-2</v>
       </c>
       <c r="BL76" s="32">
-        <v>6.2744106891926619E-4</v>
+        <v>-8.863564451349772E-4</v>
       </c>
       <c r="BM76" s="65">
-        <v>0.22671230148628035</v>
+        <v>0.23163203418359843</v>
       </c>
       <c r="BN76" s="66">
-        <v>-4.2632794616754489E-2</v>
+        <v>-5.9394018002787041E-2</v>
       </c>
       <c r="BO76">
-        <v>0.43176834168700268</v>
+        <v>0.43419421642110601</v>
       </c>
       <c r="BQ76">
-        <v>-3.0556380056368264E-4</v>
+        <v>4.3165558878073388E-4</v>
       </c>
       <c r="BR76">
-        <v>1.4933097440278536E-4</v>
+        <v>-2.1095283394212457E-4</v>
       </c>
       <c r="BS76" s="34">
-        <v>1.3572924222813428E-2</v>
+        <v>6.2460075940001672E-3</v>
       </c>
       <c r="BT76">
-        <v>-4.4341824154211194E-3</v>
+        <v>-2.040528377322764E-3</v>
       </c>
       <c r="BU76" s="34">
-        <v>1.6854826926083585E-2</v>
+        <v>3.7184865419001211E-3</v>
       </c>
       <c r="BV76">
-        <v>7.7585711247051426E-3</v>
+        <v>1.7116842811921193E-3</v>
       </c>
       <c r="BX76">
-        <v>3.0122187348333329E-2</v>
+        <v>1.0396149724681022E-2</v>
       </c>
       <c r="BY76">
-        <v>3.4737196836868087E-3</v>
+        <v>-5.3979693007276917E-4</v>
       </c>
     </row>
     <row r="77" spans="40:77" x14ac:dyDescent="0.25">
@@ -42390,81 +42419,81 @@
         <v>3</v>
       </c>
       <c r="AU77">
-        <v>1.5537603125764144E-2</v>
+        <v>3.1172312189197051E-3</v>
       </c>
       <c r="AW77">
-        <v>0.88350475111683335</v>
+        <v>0.54173901019622817</v>
       </c>
       <c r="AX77">
-        <v>0.78278867705063826</v>
+        <v>0.47998288923989008</v>
       </c>
       <c r="AY77">
-        <v>0.83481398757409553</v>
+        <v>0.51188327256267563</v>
       </c>
       <c r="AZ77">
-        <v>4.669527182647272E-2</v>
+        <v>2.8632161070033635E-2</v>
       </c>
       <c r="BA77">
-        <v>0.59013833631310375</v>
+        <v>0.36185539216283497</v>
       </c>
       <c r="BB77">
-        <v>0.32234601299997218</v>
+        <v>0.19765305144376408</v>
       </c>
       <c r="BD77" s="1" cm="1">
         <f t="array" ref="BD77">SUM($AW77:$BB77*$W19:$AB19*(IF((ROW(AW77)-$BH$73)=(COLUMN(AW77)-$BI$73),1,0)-W19))</f>
-        <v>-6.5813942003029896E-2</v>
+        <v>-4.0355164760306483E-2</v>
       </c>
       <c r="BE77" s="1" cm="1">
         <f t="array" ref="BE77">SUM($AW77:$BB77*$W19:$AB19*(IF((ROW(AX77)-$BH$73)=(COLUMN(AX77)-$BI$73),1,0)-X19))</f>
-        <v>-5.9293495654091928E-2</v>
+        <v>-3.6357019706025784E-2</v>
       </c>
       <c r="BF77" s="1" cm="1">
         <f t="array" ref="BF77">SUM($AW77:$BB77*$W19:$AB19*(IF((ROW(AY77)-$BH$73)=(COLUMN(AY77)-$BI$73),1,0)-Y19))</f>
-        <v>0.42355631381024128</v>
+        <v>0.25971221763761637</v>
       </c>
       <c r="BG77" s="1" cm="1">
         <f t="array" ref="BG77">SUM($AW77:$BB77*$W19:$AB19*(IF((ROW(AZ77)-$BH$73)=(COLUMN(AZ77)-$BI$73),1,0)-Z19))</f>
-        <v>-0.11977871581947544</v>
+        <v>-7.3444769672819932E-2</v>
       </c>
       <c r="BH77" s="1" cm="1">
         <f t="array" ref="BH77">SUM($AW77:$BB77*$W19:$AB19*(IF((ROW(BA77)-$BH$73)=(COLUMN(BA77)-$BI$73),1,0)-AA19))</f>
-        <v>-5.6335335632873046E-2</v>
+        <v>-3.4543163379988612E-2</v>
       </c>
       <c r="BI77" s="1" cm="1">
         <f t="array" ref="BI77">SUM($AW77:$BB77*$W19:$AB19*(IF((ROW(BB77)-$BH$73)=(COLUMN(BB77)-$BI$73),1,0)-AB19))</f>
-        <v>-0.12233482470077094</v>
+        <v>-7.5012100118475561E-2</v>
       </c>
       <c r="BK77">
-        <v>-0.66420592319267679</v>
+        <v>-0.42163167355800807</v>
       </c>
       <c r="BL77" s="32">
-        <v>0.15069743499961202</v>
+        <v>9.2403214779095688E-2</v>
       </c>
       <c r="BM77" s="65"/>
       <c r="BN77" s="66"/>
       <c r="BQ77">
-        <v>-7.3389650844811055E-2</v>
+        <v>-4.50003655974196E-2</v>
       </c>
       <c r="BR77">
-        <v>3.586598952990766E-2</v>
+        <v>2.1991965117424774E-2</v>
       </c>
       <c r="BS77" s="34">
-        <v>-0.16671568672136189</v>
+        <v>-0.10582955006306002</v>
       </c>
       <c r="BT77">
-        <v>5.4464885701799498E-2</v>
+        <v>3.4573797231756666E-2</v>
       </c>
       <c r="BU77" s="34">
-        <v>1.4683034953847115E-2</v>
+        <v>2.9457835018791212E-3</v>
       </c>
       <c r="BV77">
-        <v>6.7588573597074028E-3</v>
+        <v>1.3559955802300717E-3</v>
       </c>
       <c r="BX77">
-        <v>-0.22542230261232582</v>
+        <v>-0.1478841321586005</v>
       </c>
       <c r="BY77">
-        <v>9.7089732591414568E-2</v>
+        <v>5.792175792941151E-2</v>
       </c>
     </row>
     <row r="78" spans="40:77" x14ac:dyDescent="0.25">
@@ -42472,81 +42501,81 @@
         <v>4</v>
       </c>
       <c r="AU78">
-        <v>4.0277917080391086E-2</v>
+        <v>1.2732986698198619E-2</v>
       </c>
       <c r="AW78">
-        <v>4.9615598778734319E-3</v>
+        <v>-7.0089619464200033E-3</v>
       </c>
       <c r="AX78">
-        <v>4.3959615248231705E-3</v>
+        <v>-6.2099677931566092E-3</v>
       </c>
       <c r="AY78">
-        <v>4.6881237265553009E-3</v>
+        <v>-6.6226915744929896E-3</v>
       </c>
       <c r="AZ78">
-        <v>2.6222992789541149E-4</v>
+        <v>-3.7043986791895098E-4</v>
       </c>
       <c r="BA78">
-        <v>3.3140814332291895E-3</v>
+        <v>-4.6816467450950718E-3</v>
       </c>
       <c r="BB78">
-        <v>1.8102212159826127E-3</v>
+        <v>-2.5572142490926401E-3</v>
       </c>
       <c r="BD78" s="1" cm="1">
         <f t="array" ref="BD78">SUM($AW78:$BB78*$W20:$AB20*(IF((ROW(AW78)-$BH$73)=(COLUMN(AW78)-$BI$73),1,0)-W20))</f>
-        <v>-4.8005381723977979E-4</v>
+        <v>6.7814941673331373E-4</v>
       </c>
       <c r="BE78" s="1" cm="1">
         <f t="array" ref="BE78">SUM($AW78:$BB78*$W20:$AB20*(IF((ROW(AX78)-$BH$73)=(COLUMN(AX78)-$BI$73),1,0)-X20))</f>
-        <v>-4.6196582925162857E-4</v>
+        <v>6.5259736805974369E-4</v>
       </c>
       <c r="BF78" s="1" cm="1">
         <f t="array" ref="BF78">SUM($AW78:$BB78*$W20:$AB20*(IF((ROW(AY78)-$BH$73)=(COLUMN(AY78)-$BI$73),1,0)-Y20))</f>
-        <v>-4.4257553043083089E-4</v>
+        <v>6.2520560621267456E-4</v>
       </c>
       <c r="BG78" s="1" cm="1">
         <f t="array" ref="BG78">SUM($AW78:$BB78*$W20:$AB20*(IF((ROW(AZ78)-$BH$73)=(COLUMN(AZ78)-$BI$73),1,0)-Z20))</f>
-        <v>2.4410555406159783E-3</v>
+        <v>-3.4483641867501316E-3</v>
       </c>
       <c r="BH78" s="1" cm="1">
         <f t="array" ref="BH78">SUM($AW78:$BB78*$W20:$AB20*(IF((ROW(BA78)-$BH$73)=(COLUMN(BA78)-$BI$73),1,0)-AA20))</f>
-        <v>-4.533439615709201E-4</v>
+        <v>6.4041766168339851E-4</v>
       </c>
       <c r="BI78" s="1" cm="1">
         <f t="array" ref="BI78">SUM($AW78:$BB78*$W20:$AB20*(IF((ROW(BB78)-$BH$73)=(COLUMN(BB78)-$BI$73),1,0)-AB20))</f>
-        <v>-6.031164021228191E-4</v>
+        <v>8.5199413406100157E-4</v>
       </c>
       <c r="BK78">
-        <v>0.12492147289763267</v>
+        <v>5.293864551040614E-2</v>
       </c>
       <c r="BL78" s="32">
-        <v>-8.691378788796112E-4</v>
+        <v>1.227790144471737E-3</v>
       </c>
       <c r="BM78" s="65"/>
       <c r="BN78" s="66"/>
       <c r="BQ78">
-        <v>4.2327014701437063E-4</v>
+        <v>-5.9793380035773585E-4</v>
       </c>
       <c r="BR78">
-        <v>-2.0685481517334747E-4</v>
+        <v>2.922140543842734E-4</v>
       </c>
       <c r="BS78" s="34">
-        <v>3.1355289697305798E-2</v>
+        <v>1.3287600023111941E-2</v>
       </c>
       <c r="BT78">
-        <v>-1.024356077760588E-2</v>
+        <v>-4.3409689318533035E-3</v>
       </c>
       <c r="BU78" s="34">
-        <v>3.8062631640969576E-2</v>
+        <v>1.2032672429797693E-2</v>
       </c>
       <c r="BV78">
-        <v>1.7520893929970121E-2</v>
+        <v>5.5388492137163989E-3</v>
       </c>
       <c r="BX78">
-        <v>6.984119148528975E-2</v>
+        <v>2.4722338652551898E-2</v>
       </c>
       <c r="BY78">
-        <v>7.0704783371908948E-3</v>
+        <v>1.4900943362473693E-3</v>
       </c>
     </row>
     <row r="79" spans="40:77" x14ac:dyDescent="0.25">
@@ -42554,81 +42583,81 @@
         <v>5</v>
       </c>
       <c r="AU79">
-        <v>1.6788907398584945E-2</v>
+        <v>3.5594331777896115E-3</v>
       </c>
       <c r="AW79">
-        <v>4.9615598778734319E-3</v>
+        <v>-7.0089619464200033E-3</v>
       </c>
       <c r="AX79">
-        <v>4.3959615248231705E-3</v>
+        <v>-6.2099677931566092E-3</v>
       </c>
       <c r="AY79">
-        <v>4.6881237265553009E-3</v>
+        <v>-6.6226915744929896E-3</v>
       </c>
       <c r="AZ79">
-        <v>2.6222992789541149E-4</v>
+        <v>-3.7043986791895098E-4</v>
       </c>
       <c r="BA79">
-        <v>3.3140814332291895E-3</v>
+        <v>-4.6816467450950718E-3</v>
       </c>
       <c r="BB79">
-        <v>1.8102212159826127E-3</v>
+        <v>-2.5572142490926401E-3</v>
       </c>
       <c r="BD79" s="1" cm="1">
         <f t="array" ref="BD79">SUM($AW79:$BB79*$W21:$AB21*(IF((ROW(AW79)-$BH$73)=(COLUMN(AW79)-$BI$73),1,0)-W21))</f>
-        <v>-3.6953460610197224E-4</v>
+        <v>5.2202413269355694E-4</v>
       </c>
       <c r="BE79" s="1" cm="1">
         <f t="array" ref="BE79">SUM($AW79:$BB79*$W21:$AB21*(IF((ROW(AX79)-$BH$73)=(COLUMN(AX79)-$BI$73),1,0)-X21))</f>
-        <v>-3.3291114579230371E-4</v>
+        <v>4.7028789530550574E-4</v>
       </c>
       <c r="BF79" s="1" cm="1">
         <f t="array" ref="BF79">SUM($AW79:$BB79*$W21:$AB21*(IF((ROW(AY79)-$BH$73)=(COLUMN(AY79)-$BI$73),1,0)-Y21))</f>
-        <v>-2.9629429744028546E-4</v>
+        <v>4.1856099831859907E-4</v>
       </c>
       <c r="BG79" s="1" cm="1">
         <f t="array" ref="BG79">SUM($AW79:$BB79*$W21:$AB21*(IF((ROW(AZ79)-$BH$73)=(COLUMN(AZ79)-$BI$73),1,0)-Z21))</f>
-        <v>-6.7267966316503583E-4</v>
+        <v>9.502628764555312E-4</v>
       </c>
       <c r="BH79" s="1" cm="1">
         <f t="array" ref="BH79">SUM($AW79:$BB79*$W21:$AB21*(IF((ROW(BA79)-$BH$73)=(COLUMN(BA79)-$BI$73),1,0)-AA21))</f>
-        <v>2.3584596348306401E-3</v>
+        <v>-3.3316848409739694E-3</v>
       </c>
       <c r="BI79" s="1" cm="1">
         <f t="array" ref="BI79">SUM($AW79:$BB79*$W21:$AB21*(IF((ROW(BB79)-$BH$73)=(COLUMN(BB79)-$BI$73),1,0)-AB21))</f>
-        <v>-6.8703992233104267E-4</v>
+        <v>9.705489382007763E-4</v>
       </c>
       <c r="BK79">
-        <v>5.0478495537893353E-2</v>
+        <v>2.3985539533138929E-2</v>
       </c>
       <c r="BL79" s="32">
-        <v>7.2990386263435865E-4</v>
+        <v>-1.031100807744741E-3</v>
       </c>
       <c r="BM79" s="65"/>
       <c r="BN79" s="66"/>
       <c r="BQ79">
-        <v>-3.5546318110293265E-4</v>
+        <v>5.0214609337168883E-4</v>
       </c>
       <c r="BR79">
-        <v>1.7371711930697735E-4</v>
+        <v>-2.4540199224324836E-4</v>
       </c>
       <c r="BS79" s="34">
-        <v>1.2670102380011232E-2</v>
+        <v>6.0203704228178716E-3</v>
       </c>
       <c r="BT79">
-        <v>-4.1392366341072555E-3</v>
+        <v>-1.9668142417173921E-3</v>
       </c>
       <c r="BU79" s="34">
-        <v>1.5865517491662772E-2</v>
+        <v>3.3636643530111825E-3</v>
       </c>
       <c r="BV79">
-        <v>7.3031747183844508E-3</v>
+        <v>1.5483534323384809E-3</v>
       </c>
       <c r="BX79">
-        <v>2.818015669057107E-2</v>
+        <v>9.886180869200744E-3</v>
       </c>
       <c r="BY79">
-        <v>3.3376552035841722E-3</v>
+        <v>-6.6386280162215937E-4</v>
       </c>
     </row>
     <row r="80" spans="40:77" x14ac:dyDescent="0.25">
@@ -42636,7 +42665,7 @@
         <v>6</v>
       </c>
       <c r="AU80">
-        <v>4.1258052292834108E-2</v>
+        <v>1.3138983659391531E-2</v>
       </c>
       <c r="AW80">
         <v>4.9615598778734319E-3</v>
@@ -42681,7 +42710,7 @@
         <v>2.5074137826775669E-3</v>
       </c>
       <c r="BK80">
-        <v>0.12833198811210347</v>
+        <v>5.0697053921775044E-2</v>
       </c>
       <c r="BL80" s="32">
         <v>-9.5474828187867627E-4</v>
@@ -42695,22 +42724,22 @@
         <v>-2.2723009108712494E-4</v>
       </c>
       <c r="BS80" s="34">
-        <v>3.221132901613797E-2</v>
+        <v>1.2724960534365537E-2</v>
       </c>
       <c r="BT80">
-        <v>-1.0523223025192485E-2</v>
+        <v>-4.157158421585554E-3</v>
       </c>
       <c r="BU80" s="34">
-        <v>3.8988859416728229E-2</v>
+        <v>1.2416339558124996E-2</v>
       </c>
       <c r="BV80">
-        <v>1.7947252747382837E-2</v>
+        <v>5.7154578918353158E-3</v>
       </c>
       <c r="BX80">
-        <v>7.1665150846141112E-2</v>
+        <v>2.5606262505765448E-2</v>
       </c>
       <c r="BY80">
-        <v>7.1967996311032272E-3</v>
+        <v>1.3310693791626369E-3</v>
       </c>
     </row>
     <row r="82" spans="74:81" x14ac:dyDescent="0.25">
@@ -42757,17 +42786,17 @@
       </c>
       <c r="BX85" cm="1">
         <f t="array" ref="BX85:BY90">_xlfn.ANCHORARRAY(BX64)+_xlfn.ANCHORARRAY(BX75)</f>
-        <v>0.16172085979057063</v>
+        <v>0.12982400497191379</v>
       </c>
       <c r="BY85">
-        <v>-8.2272233808192569E-2</v>
+        <v>-8.1066155192013961E-2</v>
       </c>
       <c r="CA85" s="63" cm="1">
         <f t="array" ref="CA85:CB90">_xlfn.ANCHORARRAY(AU35)+_xlfn.ANCHORARRAY(BX85)</f>
-        <v>2.6554831438101029E-2</v>
+        <v>-7.0377082826471871E-3</v>
       </c>
       <c r="CB85" s="14">
-        <v>-0.12705140682561128</v>
+        <v>-0.12745318879388584</v>
       </c>
     </row>
     <row r="86" spans="74:81" x14ac:dyDescent="0.25">
@@ -42775,16 +42804,16 @@
         <v>2</v>
       </c>
       <c r="BX86">
-        <v>4.1140087375582654E-2</v>
+        <v>1.8813366583249322E-2</v>
       </c>
       <c r="BY86">
-        <v>-1.119358087900763E-2</v>
+        <v>-1.2812877079422382E-2</v>
       </c>
       <c r="CA86" s="63">
-        <v>2.7182811963848669E-2</v>
+        <v>8.1698616474118937E-3</v>
       </c>
       <c r="CB86" s="14">
-        <v>7.230541092718458E-5</v>
+        <v>-8.1535585104205791E-3</v>
       </c>
     </row>
     <row r="87" spans="74:81" x14ac:dyDescent="0.25">
@@ -42792,16 +42821,16 @@
         <v>3</v>
       </c>
       <c r="BX87">
-        <v>-0.44177146124904687</v>
+        <v>-0.32472246980858899</v>
       </c>
       <c r="BY87">
-        <v>0.41681822353453707</v>
+        <v>0.31835856671165957</v>
       </c>
       <c r="CA87" s="63">
-        <v>2.9268134939021584E-2</v>
+        <v>6.9738192301244672E-2</v>
       </c>
       <c r="CB87" s="14">
-        <v>0.41947790500574456</v>
+        <v>0.24840555371824607</v>
       </c>
     </row>
     <row r="88" spans="74:81" x14ac:dyDescent="0.25">
@@ -42809,16 +42838,16 @@
         <v>4</v>
       </c>
       <c r="BX88">
-        <v>7.7192960584918091E-2</v>
+        <v>3.025282184561225E-2</v>
       </c>
       <c r="BY88">
-        <v>-3.2662335644253852E-3</v>
+        <v>-7.2126469591450599E-3</v>
       </c>
       <c r="CA88" s="63">
-        <v>6.3235685173184106E-2</v>
+        <v>1.960931690977482E-2</v>
       </c>
       <c r="CB88" s="14">
-        <v>7.9996527255094298E-3</v>
+        <v>-2.5533283901432559E-3</v>
       </c>
     </row>
     <row r="89" spans="74:81" x14ac:dyDescent="0.25">
@@ -42826,16 +42855,16 @@
         <v>5</v>
       </c>
       <c r="BX89">
-        <v>3.7134196858969369E-2</v>
+        <v>1.6928750826129588E-2</v>
       </c>
       <c r="BY89">
-        <v>-1.0472338580077839E-2</v>
+        <v>-1.1997373767344246E-2</v>
       </c>
       <c r="CA89" s="63">
-        <v>2.3176921447235384E-2</v>
+        <v>6.2852458902921595E-3</v>
       </c>
       <c r="CB89" s="14">
-        <v>7.9354770985697563E-4</v>
+        <v>-7.3380551983424419E-3</v>
       </c>
     </row>
     <row r="90" spans="74:81" x14ac:dyDescent="0.25">
@@ -42843,16 +42872,16 @@
         <v>6</v>
       </c>
       <c r="BX90">
-        <v>0.12878865182613841</v>
+        <v>7.055110179022403E-2</v>
       </c>
       <c r="BY90">
-        <v>-3.894676662478732E-2</v>
+        <v>-3.71539512743633E-2</v>
       </c>
       <c r="CA90" s="64">
-        <v>0.11483137641440443</v>
+        <v>5.6593826378490045E-2</v>
       </c>
       <c r="CB90" s="15">
-        <v>-2.7680880334852505E-2</v>
+        <v>-2.5888064984428485E-2</v>
       </c>
     </row>
     <row r="91" spans="74:81" x14ac:dyDescent="0.25">
@@ -42862,11 +42891,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="AO35:AO38" formulaRange="1"/>
   </ignoredErrors>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
